--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -586,76 +586,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.700829254523912</v>
+        <v>2.700829254523909</v>
       </c>
       <c r="C2" t="n">
         <v>2.709151361034767</v>
       </c>
       <c r="D2" t="n">
-        <v>2.691182090786414</v>
+        <v>2.691182090786411</v>
       </c>
       <c r="E2" t="n">
-        <v>2.682221380567878</v>
+        <v>2.682221380567877</v>
       </c>
       <c r="F2" t="n">
-        <v>2.688291422511203</v>
+        <v>2.6882914225112</v>
       </c>
       <c r="G2" t="n">
-        <v>2.722153043145396</v>
+        <v>2.722153043145394</v>
       </c>
       <c r="H2" t="n">
-        <v>2.702277479889485</v>
+        <v>2.702277479889482</v>
       </c>
       <c r="I2" t="n">
-        <v>2.690353565252786</v>
+        <v>2.690353565252785</v>
       </c>
       <c r="J2" t="n">
         <v>2.706008009890701</v>
       </c>
       <c r="K2" t="n">
-        <v>2.70100667829389</v>
+        <v>2.701006678293889</v>
       </c>
       <c r="L2" t="n">
         <v>2.71137629517779</v>
       </c>
       <c r="M2" t="n">
-        <v>2.725840173883356</v>
+        <v>2.725840173883355</v>
       </c>
       <c r="N2" t="n">
-        <v>2.703865336505708</v>
+        <v>2.703865336505706</v>
       </c>
       <c r="O2" t="n">
-        <v>2.990735126962555</v>
+        <v>2.990735126962554</v>
       </c>
       <c r="P2" t="n">
-        <v>2.700856787934724</v>
+        <v>2.700856787934722</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.694266389866276</v>
+        <v>2.694266389866274</v>
       </c>
       <c r="R2" t="n">
-        <v>2.690560197395098</v>
+        <v>2.690560197395095</v>
       </c>
       <c r="S2" t="n">
-        <v>2.708568600099952</v>
+        <v>2.708568600099951</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6983503059305</v>
+        <v>2.698350305930498</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1187141848039</v>
+        <v>3.118714184803899</v>
       </c>
       <c r="V2" t="n">
-        <v>2.686029498342862</v>
+        <v>2.686029498342861</v>
       </c>
       <c r="W2" t="n">
-        <v>3.092980539543939</v>
+        <v>3.092980539543937</v>
       </c>
       <c r="X2" t="n">
-        <v>2.697438572578758</v>
+        <v>2.697438572578757</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.697217664238571</v>
+        <v>2.697217664238568</v>
       </c>
       <c r="Z2" t="n">
         <v>2.863014672403931</v>
@@ -664,7 +664,7 @@
         <v>2.705455575541662</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.717002086029949</v>
+        <v>2.717002086029948</v>
       </c>
     </row>
     <row r="3">
@@ -677,22 +677,22 @@
         <v>1.952027721696517</v>
       </c>
       <c r="C3" t="n">
-        <v>1.851801951143109</v>
+        <v>1.851801951143108</v>
       </c>
       <c r="D3" t="n">
         <v>1.884479187836992</v>
       </c>
       <c r="E3" t="n">
-        <v>1.820065494608603</v>
+        <v>1.820065494608602</v>
       </c>
       <c r="F3" t="n">
-        <v>1.863966612535173</v>
+        <v>1.863966612535174</v>
       </c>
       <c r="G3" t="n">
-        <v>2.104146489486692</v>
+        <v>2.10414648948669</v>
       </c>
       <c r="H3" t="n">
-        <v>1.964475978447745</v>
+        <v>1.964475978447747</v>
       </c>
       <c r="I3" t="n">
         <v>1.878646821425674</v>
@@ -701,19 +701,19 @@
         <v>1.989565906451694</v>
       </c>
       <c r="K3" t="n">
-        <v>1.954704709630933</v>
+        <v>1.954704709630932</v>
       </c>
       <c r="L3" t="n">
-        <v>2.028096199136588</v>
+        <v>2.028096199136587</v>
       </c>
       <c r="M3" t="n">
-        <v>2.133797075615289</v>
+        <v>2.133797075615288</v>
       </c>
       <c r="N3" t="n">
-        <v>1.974861969057574</v>
+        <v>1.974861969057572</v>
       </c>
       <c r="O3" t="n">
-        <v>2.417564732042379</v>
+        <v>2.417564732042376</v>
       </c>
       <c r="P3" t="n">
         <v>1.952404244944486</v>
@@ -725,34 +725,34 @@
         <v>1.880240728090334</v>
       </c>
       <c r="S3" t="n">
-        <v>2.007482227110233</v>
+        <v>2.007482227110232</v>
       </c>
       <c r="T3" t="n">
         <v>1.935841031008604</v>
       </c>
       <c r="U3" t="n">
-        <v>2.710747732376086</v>
+        <v>2.710747732376084</v>
       </c>
       <c r="V3" t="n">
-        <v>1.846880726655469</v>
+        <v>1.846880726655471</v>
       </c>
       <c r="W3" t="n">
-        <v>2.634280759856614</v>
+        <v>2.634280759856611</v>
       </c>
       <c r="X3" t="n">
-        <v>1.929116549786936</v>
+        <v>1.929116549786935</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.927163275321828</v>
+        <v>1.927163275321829</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.196063133432587</v>
+        <v>2.196063133432586</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.986060262560264</v>
+        <v>1.986060262560263</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.069112131029691</v>
+        <v>2.069112131029689</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5950009853708405</v>
+        <v>0.5950009853708388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.357906685618637</v>
+        <v>0.357906685618635</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4860318330412147</v>
+        <v>0.4860318330412133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3848164889925035</v>
+        <v>0.3848164889925023</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4533804050995973</v>
+        <v>0.4533804050995962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8358629872778884</v>
+        <v>0.835862987277888</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6113593570915775</v>
+        <v>0.6113593570915762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4766732559983363</v>
+        <v>0.476673255998336</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6530628899319217</v>
+        <v>0.6530628899319197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5970050684716994</v>
+        <v>0.5970050684716978</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7141346614348135</v>
+        <v>0.7141346614348113</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8792105907306813</v>
+        <v>0.8792105907306791</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6292949280219479</v>
+        <v>0.6292949280219461</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5685663010850555</v>
+        <v>0.568566301085054</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5953119879119674</v>
+        <v>0.5953119879119655</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5208704099959356</v>
+        <v>0.5208704099959355</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4790072611012129</v>
+        <v>0.4790072611012115</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6824204539270871</v>
+        <v>0.6824204539270863</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5670001206355489</v>
+        <v>0.5670001206355476</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7318045657168123</v>
+        <v>0.7318045657168092</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4249182526281212</v>
+        <v>0.4249182526281201</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6650318910139156</v>
+        <v>0.6650318910139136</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5567016730095901</v>
+        <v>0.5567016730095881</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5501070297192036</v>
+        <v>0.5501070297192013</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5454446827645658</v>
+        <v>0.5454446827645638</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6472574094791683</v>
+        <v>0.6472574094791667</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7757338702692378</v>
+        <v>0.7757338702692357</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.675652756215343</v>
+        <v>6.675652756215342</v>
       </c>
       <c r="C5" t="n">
-        <v>2.498663741011248</v>
+        <v>2.498663741011247</v>
       </c>
       <c r="D5" t="n">
-        <v>5.25613462200127</v>
+        <v>5.256134622001271</v>
       </c>
       <c r="E5" t="n">
-        <v>2.944083537750227</v>
+        <v>2.944083537750222</v>
       </c>
       <c r="F5" t="n">
-        <v>4.668897814975928</v>
+        <v>4.668897814975911</v>
       </c>
       <c r="G5" t="n">
-        <v>11.48438711941113</v>
+        <v>11.48438711941112</v>
       </c>
       <c r="H5" t="n">
-        <v>8.260460704861252</v>
+        <v>8.26046070486125</v>
       </c>
       <c r="I5" t="n">
-        <v>5.115733093989326</v>
+        <v>5.115733093989323</v>
       </c>
       <c r="J5" t="n">
-        <v>8.196239053733454</v>
+        <v>8.196239053733448</v>
       </c>
       <c r="K5" t="n">
-        <v>7.55446316861344</v>
+        <v>7.554463168613452</v>
       </c>
       <c r="L5" t="n">
         <v>9.546497480710297</v>
       </c>
       <c r="M5" t="n">
-        <v>13.7907871645786</v>
+        <v>13.79078716457861</v>
       </c>
       <c r="N5" t="n">
-        <v>9.685152453804388</v>
+        <v>9.685152453804369</v>
       </c>
       <c r="O5" t="n">
-        <v>6.044652872045116</v>
+        <v>6.044652872045119</v>
       </c>
       <c r="P5" t="n">
-        <v>6.788908089656362</v>
+        <v>6.788908089656357</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.87044643712364</v>
+        <v>5.870446437123629</v>
       </c>
       <c r="R5" t="n">
-        <v>5.233559290606109</v>
+        <v>5.233559290606105</v>
       </c>
       <c r="S5" t="n">
-        <v>8.565904866569621</v>
+        <v>8.565904866569607</v>
       </c>
       <c r="T5" t="n">
-        <v>7.006681391071794</v>
+        <v>7.006681391071782</v>
       </c>
       <c r="U5" t="n">
-        <v>9.791761473464343</v>
+        <v>9.791761473464319</v>
       </c>
       <c r="V5" t="n">
-        <v>3.591346436745748</v>
+        <v>3.591346436745744</v>
       </c>
       <c r="W5" t="n">
-        <v>8.63304532783966</v>
+        <v>8.633045327839648</v>
       </c>
       <c r="X5" t="n">
-        <v>6.670084248111261</v>
+        <v>6.670084248111253</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.395978804029631</v>
+        <v>6.395978804029611</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.908834742608376</v>
+        <v>5.908834742608359</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.330808166921996</v>
+        <v>8.33080816692199</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.9293465364164</v>
+        <v>11.92934653641637</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6192048585356138</v>
+        <v>0.7188983849197264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4818040851675243</v>
+        <v>0.4818040851675226</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5102357062059844</v>
+        <v>0.5102357062059765</v>
       </c>
       <c r="E6" t="n">
-        <v>0.508713888541391</v>
+        <v>0.4090203621572655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4775842782643673</v>
+        <v>0.5772778046484837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8600668604426587</v>
+        <v>0.9597603868267743</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7352567566404641</v>
+        <v>0.7352567566404633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6005706555472251</v>
+        <v>0.5008771291630995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6772667630966833</v>
+        <v>0.7769602894808074</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6212089416364661</v>
+        <v>0.6212089416364613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8380320609837014</v>
+        <v>0.7383385345995749</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9034144638954513</v>
+        <v>0.903414463895443</v>
       </c>
       <c r="N6" t="n">
-        <v>0.654487225977056</v>
+        <v>0.6544872259770604</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6977786915322449</v>
+        <v>0.6977786915322446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7245252821207563</v>
+        <v>0.7245252821207545</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5450742831607089</v>
+        <v>0.5450742831606993</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6029046606501002</v>
+        <v>0.5032111342659743</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8063178534759753</v>
+        <v>0.8063178534759737</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5912039938003197</v>
+        <v>0.5912039938003109</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7601078208466706</v>
+        <v>0.760107820846661</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5488156521770091</v>
+        <v>0.5488156521770075</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6943537729571088</v>
+        <v>0.7942448449478156</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6805990725584763</v>
+        <v>0.6805990725584757</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5814773617990371</v>
+        <v>0.5814773617990412</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5696485559293357</v>
+        <v>0.5696485559293268</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.771154809028056</v>
+        <v>0.6714612826439308</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8024280884437313</v>
+        <v>0.80242808844373</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7093579447502794</v>
+        <v>0.7093579447502772</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4722636449980747</v>
+        <v>0.4722636449980737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6003887924206522</v>
+        <v>0.6003887924206512</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4991734483719412</v>
+        <v>0.4991734483719405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5677373644790352</v>
+        <v>0.5677373644790344</v>
       </c>
       <c r="G7" t="n">
         <v>0.9502199466573256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7257163164710149</v>
+        <v>0.7257163164710144</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5910302153777756</v>
+        <v>0.5910302153777748</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7674198493113598</v>
+        <v>0.7674198493113585</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7113620278511379</v>
+        <v>0.711362027851137</v>
       </c>
       <c r="L7" t="n">
-        <v>0.828491620814253</v>
+        <v>0.8284916208142517</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9935675501101189</v>
+        <v>0.9935675501101177</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7436518874013851</v>
+        <v>0.7436518874013842</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6825397634430007</v>
+        <v>0.6825397634429995</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7092854502699102</v>
+        <v>0.7092854502699097</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6352273693753752</v>
+        <v>0.6352273693753745</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5933642204806507</v>
+        <v>0.5933642204806499</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7967774133065256</v>
+        <v>0.7967774133065242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6813570800149874</v>
+        <v>0.6813570800149863</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8500183029476573</v>
+        <v>0.8500183029476571</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5392752120075598</v>
+        <v>0.539275212007559</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7793888503933548</v>
+        <v>0.7793888503933534</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6710586323890281</v>
+        <v>0.6710586323890273</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6685633710637274</v>
+        <v>0.6685633710637262</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6598016421440037</v>
+        <v>0.6598016421440027</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7616143688586069</v>
+        <v>0.761614368858606</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8900908296486759</v>
+        <v>0.8900908296486738</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7630066911335642</v>
+        <v>0.7630066911335628</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6601942891967018</v>
+        <v>0.6601942891966991</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7883194366192789</v>
+        <v>0.7883194366192764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6871040925705674</v>
+        <v>0.6156029430728303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6423056611440232</v>
+        <v>0.6423056611440214</v>
       </c>
       <c r="G8" t="n">
-        <v>1.138150590855952</v>
+        <v>1.165994817125807</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9136469606696418</v>
+        <v>0.9136469606696402</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7789608595764026</v>
+        <v>0.7789608595764005</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9553504935099851</v>
+        <v>0.9553504935099834</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8992926720497655</v>
+        <v>0.8992926720497626</v>
       </c>
       <c r="L8" t="n">
-        <v>1.016422265012879</v>
+        <v>1.016422265012876</v>
       </c>
       <c r="M8" t="n">
-        <v>1.181498194308745</v>
+        <v>1.181498194308755</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8274915958944522</v>
+        <v>0.827491595894451</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7953680618425919</v>
+        <v>0.7953680618425897</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8151019492131099</v>
+        <v>0.8151019492131083</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6624866580307188</v>
+        <v>0.6624866580307173</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7812948646792767</v>
+        <v>0.7812948646792753</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9847080575051508</v>
+        <v>0.9847080575051496</v>
       </c>
       <c r="T8" t="n">
-        <v>0.869287724213613</v>
+        <v>0.8692877242136114</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9556639895671486</v>
+        <v>0.9727595376599745</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7272058562061857</v>
+        <v>0.6906250205160968</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9673458847293295</v>
+        <v>0.9673458847293269</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7106251237381174</v>
+        <v>0.7106251237381153</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9901942396107148</v>
+        <v>0.9901942396107121</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8477322863426294</v>
+        <v>0.7109560333435593</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.949545013057234</v>
+        <v>0.949545013057231</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.218290144489362</v>
+        <v>1.218290144489358</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.06736055511404</v>
+        <v>1.067360555114039</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9728835121550103</v>
+        <v>0.9728835121550089</v>
       </c>
       <c r="D9" t="n">
         <v>1.101008659577588</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9997933155288773</v>
+        <v>0.966877852156478</v>
       </c>
       <c r="F9" t="n">
-        <v>1.068357231635971</v>
+        <v>0.7395855006307722</v>
       </c>
       <c r="G9" t="n">
-        <v>1.450839813814262</v>
+        <v>1.450839836916411</v>
       </c>
       <c r="H9" t="n">
-        <v>1.226336183627951</v>
+        <v>1.22633618362795</v>
       </c>
       <c r="I9" t="n">
-        <v>1.091650082534711</v>
+        <v>1.09165008253471</v>
       </c>
       <c r="J9" t="n">
-        <v>1.268039716468294</v>
+        <v>1.268039716468293</v>
       </c>
       <c r="K9" t="n">
-        <v>1.211981895008073</v>
+        <v>1.211981895008071</v>
       </c>
       <c r="L9" t="n">
-        <v>1.329111487971187</v>
+        <v>1.329111487971185</v>
       </c>
       <c r="M9" t="n">
-        <v>1.494187417267053</v>
+        <v>1.494187417267051</v>
       </c>
       <c r="N9" t="n">
         <v>1.244271754558322</v>
       </c>
       <c r="O9" t="n">
-        <v>1.230806330539505</v>
+        <v>1.230806330539503</v>
       </c>
       <c r="P9" t="n">
-        <v>1.267830948076776</v>
+        <v>1.267830948076775</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.135847259634461</v>
+        <v>1.13584725963446</v>
       </c>
       <c r="R9" t="n">
-        <v>1.093984087637587</v>
+        <v>1.093984087637586</v>
       </c>
       <c r="S9" t="n">
-        <v>1.297397280463461</v>
+        <v>1.29739728046346</v>
       </c>
       <c r="T9" t="n">
-        <v>1.181976947171923</v>
+        <v>1.181976947171921</v>
       </c>
       <c r="U9" t="n">
-        <v>1.350880774218273</v>
+        <v>1.350880774218271</v>
       </c>
       <c r="V9" t="n">
-        <v>1.039895079164496</v>
+        <v>1.204472166268913</v>
       </c>
       <c r="W9" t="n">
-        <v>1.280008717550289</v>
+        <v>1.280008717550288</v>
       </c>
       <c r="X9" t="n">
-        <v>1.171678499545963</v>
+        <v>1.171678499545962</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.169183238220664</v>
+        <v>1.169183238220662</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.160421509300938</v>
+        <v>1.074435994649556</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.262234236015541</v>
+        <v>1.26223423601554</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.390710696805611</v>
+        <v>1.390710696805609</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.592776438996193</v>
+        <v>2.592776438996192</v>
       </c>
       <c r="C2" t="n">
-        <v>2.618326353294565</v>
+        <v>2.618326353294564</v>
       </c>
       <c r="D2" t="n">
         <v>2.596380969337611</v>
       </c>
       <c r="E2" t="n">
-        <v>2.594205708705822</v>
+        <v>2.594205708705821</v>
       </c>
       <c r="F2" t="n">
-        <v>2.582874274589681</v>
+        <v>2.58287427458968</v>
       </c>
       <c r="G2" t="n">
-        <v>2.600703931073221</v>
+        <v>2.60070393107322</v>
       </c>
       <c r="H2" t="n">
-        <v>2.599420385284968</v>
+        <v>2.599420385284967</v>
       </c>
       <c r="I2" t="n">
-        <v>2.593904305864694</v>
+        <v>2.593904305864693</v>
       </c>
       <c r="J2" t="n">
-        <v>2.597217932218061</v>
+        <v>2.597217932218059</v>
       </c>
       <c r="K2" t="n">
         <v>2.593478481730207</v>
       </c>
       <c r="L2" t="n">
-        <v>2.571816771458864</v>
+        <v>2.571816771458863</v>
       </c>
       <c r="M2" t="n">
-        <v>2.592593314844926</v>
+        <v>2.592593314844924</v>
       </c>
       <c r="N2" t="n">
-        <v>2.593886522652693</v>
+        <v>2.593886522652692</v>
       </c>
       <c r="O2" t="n">
-        <v>2.819780429975738</v>
+        <v>2.819780429975737</v>
       </c>
       <c r="P2" t="n">
         <v>2.592917596149041</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.595858343351156</v>
+        <v>2.595858343351155</v>
       </c>
       <c r="R2" t="n">
-        <v>2.561366616628566</v>
+        <v>2.561366616628565</v>
       </c>
       <c r="S2" t="n">
         <v>2.584899972379037</v>
       </c>
       <c r="T2" t="n">
-        <v>2.587592824457485</v>
+        <v>2.587592824457484</v>
       </c>
       <c r="U2" t="n">
         <v>2.988983253560101</v>
       </c>
       <c r="V2" t="n">
-        <v>2.603455731809532</v>
+        <v>2.603455731809531</v>
       </c>
       <c r="W2" t="n">
-        <v>2.992017640788151</v>
+        <v>2.992017640788148</v>
       </c>
       <c r="X2" t="n">
-        <v>2.635667756264205</v>
+        <v>2.635667756264204</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.61848872306966</v>
+        <v>2.618488723069659</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.74900092550923</v>
+        <v>2.749000925509229</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.627186286261677</v>
+        <v>2.627186286261675</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.596561760827924</v>
+        <v>2.596561760827923</v>
       </c>
     </row>
     <row r="3">
@@ -1543,10 +1543,10 @@
         <v>1.685399824347609</v>
       </c>
       <c r="E3" t="n">
-        <v>1.669915579031044</v>
+        <v>1.669915579031043</v>
       </c>
       <c r="F3" t="n">
-        <v>1.588909428308933</v>
+        <v>1.588909428308932</v>
       </c>
       <c r="G3" t="n">
         <v>1.716003083669358</v>
@@ -1558,13 +1558,13 @@
         <v>1.667704095344132</v>
       </c>
       <c r="J3" t="n">
-        <v>1.691273365073799</v>
+        <v>1.691273365073798</v>
       </c>
       <c r="K3" t="n">
         <v>1.664770058650007</v>
       </c>
       <c r="L3" t="n">
-        <v>1.510969442173786</v>
+        <v>1.510969442173785</v>
       </c>
       <c r="M3" t="n">
         <v>1.660644854372804</v>
@@ -1576,7 +1576,7 @@
         <v>2.001639933986068</v>
       </c>
       <c r="P3" t="n">
-        <v>1.660777879464314</v>
+        <v>1.660777879464313</v>
       </c>
       <c r="Q3" t="n">
         <v>1.681658920917767</v>
@@ -1585,10 +1585,10 @@
         <v>1.434625757654409</v>
       </c>
       <c r="S3" t="n">
-        <v>1.603882387332525</v>
+        <v>1.603882387332526</v>
       </c>
       <c r="T3" t="n">
-        <v>1.622537889129414</v>
+        <v>1.622537889129413</v>
       </c>
       <c r="U3" t="n">
         <v>2.35260780966597</v>
@@ -1603,10 +1603,10 @@
         <v>1.965389614909276</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.84332260695286</v>
+        <v>1.843322606952859</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.965023293964453</v>
+        <v>1.965023293964454</v>
       </c>
       <c r="AA3" t="n">
         <v>1.905393055417317</v>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1122554338214305</v>
+        <v>0.112255433821431</v>
       </c>
       <c r="C4" t="n">
-        <v>0.104852380561468</v>
+        <v>0.1048523805614677</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1529702621936212</v>
+        <v>0.1529702621936217</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1283996926882376</v>
+        <v>0.1283996926882386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004059316291765425</v>
+        <v>0.0004059316291766951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2018001036579716</v>
+        <v>0.2018001036579727</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1873018635194237</v>
+        <v>0.1873018635194242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1249952089455333</v>
+        <v>0.1249952089455342</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1621845455837043</v>
+        <v>0.1621845455837044</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1201853294577268</v>
+        <v>0.1201853294577275</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1244936529361201</v>
+        <v>-0.1244936529361196</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1143709228432114</v>
+        <v>0.1143709228432122</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04402037169280616</v>
+        <v>0.04402037169280688</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1138498687983757</v>
+        <v>0.1138498687983759</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1470669612567767</v>
+        <v>0.1470669612567763</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2425329590530907</v>
+        <v>-0.2425329590530897</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02328712002699616</v>
+        <v>0.02328712002699653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05370412302622656</v>
+        <v>0.05370412302622667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1875890353287826</v>
+        <v>0.1875890353287827</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2312888039122884</v>
+        <v>0.2312888039122889</v>
       </c>
       <c r="W4" t="n">
         <v>0.4649899706878985</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5967325933443866</v>
+        <v>0.5967325933443878</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3975259307507339</v>
+        <v>0.3975259307507338</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2107079708219345</v>
+        <v>0.2107079708219351</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5009304879968688</v>
+        <v>0.5009304879968698</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1549777416069579</v>
+        <v>0.1549777416069588</v>
       </c>
     </row>
     <row r="5">
@@ -1713,82 +1713,82 @@
         <v>-0.3026700565533276</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4538494086142039</v>
+        <v>-0.4538494086142058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3747760674314231</v>
+        <v>0.3747760674314238</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03870415960380488</v>
+        <v>-0.03870415960380492</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3714817443512</v>
+        <v>-2.371481744351195</v>
       </c>
       <c r="G5" t="n">
-        <v>1.108890374296981</v>
+        <v>1.108890374296982</v>
       </c>
       <c r="H5" t="n">
-        <v>1.043527424454797</v>
+        <v>1.043527424454798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.130196343871286</v>
+        <v>-0.1301963438712856</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4899706756505277</v>
+        <v>0.4899706756505258</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.160806052020944</v>
+        <v>-0.1608060520209423</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.073731428017171</v>
+        <v>-4.073731428017169</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3055956462961403</v>
+        <v>-0.3055956462961398</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.346486178054942</v>
+        <v>-1.346486178054938</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2672160923782109</v>
+        <v>-0.2672160923782076</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2647200230389031</v>
+        <v>0.2647200230389038</v>
       </c>
       <c r="R5" t="n">
-        <v>-7.073738482932776</v>
+        <v>-7.073738482932781</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.699669749242172</v>
+        <v>-1.699669749242168</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.453723653786874</v>
+        <v>-1.453723653786877</v>
       </c>
       <c r="U5" t="n">
-        <v>0.977912474207604</v>
+        <v>0.9779124742076039</v>
       </c>
       <c r="V5" t="n">
-        <v>1.607271359595708</v>
+        <v>1.607271359595711</v>
       </c>
       <c r="W5" t="n">
-        <v>5.871139189375591</v>
+        <v>5.871139189375592</v>
       </c>
       <c r="X5" t="n">
-        <v>8.01513632575883</v>
+        <v>8.015136325758819</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.863285432862453</v>
+        <v>4.863285432862449</v>
       </c>
       <c r="Z5" t="n">
         <v>1.215754976263294</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.598545892029872</v>
+        <v>6.598545892029881</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4285140667632257</v>
+        <v>0.4285140667632275</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1649643620968649</v>
+        <v>0.1229391848368451</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1575613088369009</v>
+        <v>0.1155361315768818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2056791904690548</v>
+        <v>0.2056791904690564</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1811086209636719</v>
+        <v>0.1390834437036527</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05311485990461029</v>
+        <v>0.01108968264459113</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2124838546733858</v>
+        <v>0.254509031933406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.197985614534838</v>
+        <v>0.240010791794858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1356789599609476</v>
+        <v>0.1777041372209683</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1728682965991176</v>
+        <v>0.2148934738591385</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1728942577331613</v>
+        <v>0.1308690804731417</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1138099019207054</v>
+        <v>-0.07178472466068563</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1250546738586259</v>
+        <v>0.1670798511186468</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1027472971922665</v>
+        <v>0.1027472971922669</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1226383661955254</v>
+        <v>0.1725032508838436</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1997758895322105</v>
+        <v>0.1997758895322112</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2318492080376761</v>
+        <v>-0.1898240307776564</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0339708710424098</v>
+        <v>0.07599604830243062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1064130513016601</v>
+        <v>0.06438787404164023</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2034343662597665</v>
+        <v>0.2454595435197866</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2419725549277027</v>
+        <v>0.2839977321877228</v>
       </c>
       <c r="W6" t="n">
         <v>0.4793446224013699</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6074163443598011</v>
+        <v>0.6074163443598019</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4154346940881996</v>
+        <v>0.4154346940881932</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2634168990973683</v>
+        <v>0.221391721837349</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5116142390122833</v>
+        <v>0.5116142390122834</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1658489072816945</v>
+        <v>0.1658489072816947</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1761335538238736</v>
+        <v>0.1761335538238742</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1687305005639109</v>
+        <v>0.1687305005639106</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2168483821960641</v>
+        <v>0.2168483821960646</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1922778126906812</v>
+        <v>0.1922778126906816</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06428405163161935</v>
+        <v>0.06428405163161982</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2656782236604144</v>
+        <v>0.2656782236604155</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2511799835218671</v>
+        <v>0.2511799835218676</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1888733289479763</v>
+        <v>0.1888733289479766</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2260626655861475</v>
+        <v>0.2260626655861476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1840634494601704</v>
+        <v>0.1840634494601709</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06061553293367745</v>
+        <v>-0.06061553293367691</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1782490428456547</v>
+        <v>0.1782490428456552</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1075657160152841</v>
+        <v>0.1075657160152844</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1773952131208527</v>
+        <v>0.1773952131208537</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2109450812592196</v>
+        <v>0.2109450812592197</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.178654839050648</v>
+        <v>-0.1786548390506474</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08716524002943875</v>
+        <v>0.08716524002943898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1175822430286693</v>
+        <v>0.1175822430286695</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2549039906763162</v>
+        <v>0.2549039906763169</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2951669239147321</v>
+        <v>0.2951669239147322</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5288680906903416</v>
+        <v>0.5288680906903418</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6606107133468297</v>
+        <v>0.6606107133468302</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4665656306687465</v>
+        <v>0.4665656306687463</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2745860908243774</v>
+        <v>0.2745860908243779</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5648086079993122</v>
+        <v>0.5648086079993131</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.218855861609401</v>
+        <v>0.2188558616094021</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1938125236216406</v>
+        <v>0.1938125236216415</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2540381394643477</v>
+        <v>0.2540381394643479</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3021560210965003</v>
+        <v>0.3021560210965018</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2775854515911174</v>
+        <v>0.2415751802277421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09249877767502561</v>
+        <v>0.09249877767502615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3509858625608507</v>
+        <v>0.3650091076533256</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3364876224223028</v>
+        <v>0.3364876224223042</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2741809678484124</v>
+        <v>0.2741809678484139</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3113703044865835</v>
+        <v>0.3113703044865839</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2693710883606064</v>
+        <v>0.2693710883606073</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02469210596675804</v>
+        <v>0.02469210596675975</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2635566817460909</v>
+        <v>0.2635566817459829</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1551890399050566</v>
+        <v>0.1551890399050576</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2214871699932058</v>
+        <v>0.221487169993207</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2153334740469822</v>
+        <v>0.2153334740469827</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0933472001502112</v>
+        <v>-0.09334720015021009</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1724728789298752</v>
+        <v>0.1724728789298762</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2028898819291062</v>
+        <v>0.202889881929107</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2993082896202963</v>
+        <v>0.3078489816292271</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3804745628151677</v>
+        <v>0.3608008072472406</v>
       </c>
       <c r="W8" t="n">
-        <v>0.614189020496289</v>
+        <v>0.6141890204962901</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6711974079978102</v>
+        <v>0.6711974079978117</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6172695026847304</v>
+        <v>0.6172695026847307</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.359893729724814</v>
+        <v>0.2910088233786403</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.650116246899749</v>
+        <v>0.6501162468997499</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3748073003434992</v>
+        <v>0.3748073003435002</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.239467174720415</v>
+        <v>0.2394671747204142</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2741257341033794</v>
+        <v>0.2741257341033799</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3222436157355334</v>
+        <v>0.3222436157355336</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2976730462301517</v>
+        <v>0.2879654219732959</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1696792851710907</v>
+        <v>0.07271574696372878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.371073457199885</v>
+        <v>0.3710734888884076</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3565752170613364</v>
+        <v>0.3565752170613359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2942685624874479</v>
+        <v>0.2942685624874458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.331457899125619</v>
+        <v>0.3314578991256165</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2894586829996403</v>
+        <v>0.2894586829996393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0447797006057931</v>
+        <v>0.04477970060579173</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2836442763851266</v>
+        <v>0.2836442763851239</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1382034926832213</v>
+        <v>-0.1382034926832262</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2272329307796687</v>
+        <v>0.2272329307796688</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3000939590430591</v>
+        <v>0.3000939590430585</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3163403464872127</v>
+        <v>0.3163403464872129</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.07325960551117697</v>
+        <v>-0.07325960551117836</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1925604735689095</v>
+        <v>0.1925604735689085</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2229774765681386</v>
+        <v>0.2229774765681385</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3620239687862638</v>
+        <v>0.3620239687862643</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4005621574542005</v>
+        <v>0.4491003985231324</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6342633242298112</v>
+        <v>0.6342633242298111</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7660059468863003</v>
+        <v>0.7660059468862985</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5719608642082147</v>
+        <v>0.5719608642082149</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3799813243638458</v>
+        <v>0.3546219247878535</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.670203841538783</v>
+        <v>0.6702038415387823</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3242510951488728</v>
+        <v>0.3242510951488706</v>
       </c>
     </row>
   </sheetData>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.687367213287888</v>
+        <v>2.68736721328789</v>
       </c>
       <c r="C2" t="n">
-        <v>2.698976773865168</v>
+        <v>2.698976773865169</v>
       </c>
       <c r="D2" t="n">
-        <v>2.683846159488495</v>
+        <v>2.683846159488496</v>
       </c>
       <c r="E2" t="n">
         <v>2.674075478295038</v>
@@ -2324,16 +2324,16 @@
         <v>2.713148672937383</v>
       </c>
       <c r="H2" t="n">
-        <v>2.687147365672162</v>
+        <v>2.687147365672163</v>
       </c>
       <c r="I2" t="n">
         <v>2.676940663749473</v>
       </c>
       <c r="J2" t="n">
-        <v>2.697361362355053</v>
+        <v>2.697361362355055</v>
       </c>
       <c r="K2" t="n">
-        <v>2.689154028961304</v>
+        <v>2.689154028961303</v>
       </c>
       <c r="L2" t="n">
         <v>2.699446272550293</v>
@@ -2342,13 +2342,13 @@
         <v>2.714506102975359</v>
       </c>
       <c r="N2" t="n">
-        <v>2.690450096778339</v>
+        <v>2.690450096778341</v>
       </c>
       <c r="O2" t="n">
         <v>2.971435511523081</v>
       </c>
       <c r="P2" t="n">
-        <v>2.697154646451392</v>
+        <v>2.697154646451393</v>
       </c>
       <c r="Q2" t="n">
         <v>2.682095304390471</v>
@@ -2366,22 +2366,22 @@
         <v>3.100221634088915</v>
       </c>
       <c r="V2" t="n">
-        <v>2.673090874821282</v>
+        <v>2.673090874821283</v>
       </c>
       <c r="W2" t="n">
-        <v>3.082255749687389</v>
+        <v>3.082255749687387</v>
       </c>
       <c r="X2" t="n">
-        <v>2.691414547255611</v>
+        <v>2.691414547255612</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.687994503042241</v>
+        <v>2.687994503042243</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.846422530187715</v>
+        <v>2.846422530187716</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.690265466449596</v>
+        <v>2.690265466449597</v>
       </c>
       <c r="AB2" t="n">
         <v>2.708205300213541</v>
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.906458216289374</v>
+        <v>1.906458216289376</v>
       </c>
       <c r="C3" t="n">
         <v>1.830600819483669</v>
       </c>
       <c r="D3" t="n">
-        <v>1.882543866590908</v>
+        <v>1.88254386659091</v>
       </c>
       <c r="E3" t="n">
         <v>1.812324539440175</v>
@@ -2409,61 +2409,61 @@
         <v>1.829749047080206</v>
       </c>
       <c r="G3" t="n">
-        <v>2.090133029148203</v>
+        <v>2.090133029148204</v>
       </c>
       <c r="H3" t="n">
-        <v>1.906574433850678</v>
+        <v>1.906574433850679</v>
       </c>
       <c r="I3" t="n">
-        <v>1.833181522699609</v>
+        <v>1.833181522699611</v>
       </c>
       <c r="J3" t="n">
-        <v>1.978211186898917</v>
+        <v>1.978211186898918</v>
       </c>
       <c r="K3" t="n">
-        <v>1.919757120385382</v>
+        <v>1.919757120385384</v>
       </c>
       <c r="L3" t="n">
-        <v>1.993365366644681</v>
+        <v>1.993365366644682</v>
       </c>
       <c r="M3" t="n">
         <v>2.102989945946971</v>
       </c>
       <c r="N3" t="n">
-        <v>1.929471493618115</v>
+        <v>1.929471493618117</v>
       </c>
       <c r="O3" t="n">
         <v>2.368176745373066</v>
       </c>
       <c r="P3" t="n">
-        <v>1.976264150337879</v>
+        <v>1.976264150337881</v>
       </c>
       <c r="Q3" t="n">
         <v>1.869792851884713</v>
       </c>
       <c r="R3" t="n">
-        <v>1.856526312452582</v>
+        <v>1.856526312452583</v>
       </c>
       <c r="S3" t="n">
-        <v>1.991054404851306</v>
+        <v>1.991054404851307</v>
       </c>
       <c r="T3" t="n">
-        <v>1.882879144399226</v>
+        <v>1.882879144399227</v>
       </c>
       <c r="U3" t="n">
         <v>2.652651172518</v>
       </c>
       <c r="V3" t="n">
-        <v>1.804953947897245</v>
+        <v>1.804953947897246</v>
       </c>
       <c r="W3" t="n">
-        <v>2.633273512971494</v>
+        <v>2.633273512971493</v>
       </c>
       <c r="X3" t="n">
-        <v>1.936504458397015</v>
+        <v>1.936504458397016</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.911639277449449</v>
+        <v>1.91163927744945</v>
       </c>
       <c r="Z3" t="n">
         <v>2.151566945260357</v>
@@ -2472,7 +2472,7 @@
         <v>1.92793421957974</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.056434338284621</v>
+        <v>2.05643433828462</v>
       </c>
     </row>
     <row r="4">
@@ -2485,82 +2485,82 @@
         <v>0.521211386484435</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3235502826063865</v>
+        <v>0.3235502826063857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4814394640554994</v>
+        <v>0.4814394640554995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3710751252399951</v>
+        <v>0.3710751252399948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3981019160920984</v>
+        <v>0.3981019160920976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8124248332828563</v>
+        <v>0.8124248332828549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.518728106529908</v>
+        <v>0.5187281065299084</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4034387129982589</v>
+        <v>0.4034387129982575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6336465315401699</v>
+        <v>0.6336465315401695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5413942914914772</v>
+        <v>0.5413942914914761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.657649917495071</v>
+        <v>0.6576499174950695</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8292394313660035</v>
+        <v>0.829239431366002</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5560339737055198</v>
+        <v>0.5560339737055178</v>
       </c>
       <c r="O4" t="n">
         <v>0.506771602028647</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6317649465079211</v>
+        <v>0.6317649465079196</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4616627502901847</v>
+        <v>0.4616627502901832</v>
       </c>
       <c r="R4" t="n">
-        <v>0.440090854643156</v>
+        <v>0.4400908546431569</v>
       </c>
       <c r="S4" t="n">
         <v>0.6550805857001429</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4819847727331477</v>
+        <v>0.4819847727331465</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6493404974023415</v>
+        <v>0.6493404974023428</v>
       </c>
       <c r="V4" t="n">
-        <v>0.356912627392688</v>
+        <v>0.356912627392687</v>
       </c>
       <c r="W4" t="n">
-        <v>0.673884787439226</v>
+        <v>0.6738847874392244</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669278855154528</v>
+        <v>0.5669278855154521</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5240634179753371</v>
+        <v>0.5240634179753378</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4846700782932446</v>
+        <v>0.4846700782932439</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5539484892082417</v>
+        <v>0.5539484892082411</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7541215091660279</v>
+        <v>0.754121509166026</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.148565897617671</v>
+        <v>5.148565897617669</v>
       </c>
       <c r="C5" t="n">
-        <v>1.864153612118166</v>
+        <v>1.864153612118163</v>
       </c>
       <c r="D5" t="n">
-        <v>5.072613521927622</v>
+        <v>5.07261352192762</v>
       </c>
       <c r="E5" t="n">
         <v>2.715849683856319</v>
       </c>
       <c r="F5" t="n">
-        <v>3.420186902544531</v>
+        <v>3.420186902544532</v>
       </c>
       <c r="G5" t="n">
-        <v>10.47196693481291</v>
+        <v>10.4719669348129</v>
       </c>
       <c r="H5" t="n">
-        <v>6.038885075169139</v>
+        <v>6.038885075169154</v>
       </c>
       <c r="I5" t="n">
-        <v>3.554694012057016</v>
+        <v>3.554694012057013</v>
       </c>
       <c r="J5" t="n">
-        <v>7.518534463942027</v>
+        <v>7.518534463942037</v>
       </c>
       <c r="K5" t="n">
-        <v>5.834014741650752</v>
+        <v>5.834014741650749</v>
       </c>
       <c r="L5" t="n">
-        <v>8.116694973326721</v>
+        <v>8.116694973326728</v>
       </c>
       <c r="M5" t="n">
-        <v>12.10451652273616</v>
+        <v>12.10451652273618</v>
       </c>
       <c r="N5" t="n">
-        <v>7.77259941627968</v>
+        <v>7.772599416279673</v>
       </c>
       <c r="O5" t="n">
         <v>4.778440472800913</v>
       </c>
       <c r="P5" t="n">
-        <v>7.212504641552486</v>
+        <v>7.212504641552488</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.55681700007622</v>
+        <v>4.556817000076221</v>
       </c>
       <c r="R5" t="n">
-        <v>4.351203831735579</v>
+        <v>4.351203831735591</v>
       </c>
       <c r="S5" t="n">
-        <v>7.685744914001528</v>
+        <v>7.68574491400156</v>
       </c>
       <c r="T5" t="n">
-        <v>5.077765226672965</v>
+        <v>5.077765226672963</v>
       </c>
       <c r="U5" t="n">
-        <v>7.870139434828581</v>
+        <v>7.870139434828558</v>
       </c>
       <c r="V5" t="n">
-        <v>2.311525586917378</v>
+        <v>2.311525586917372</v>
       </c>
       <c r="W5" t="n">
-        <v>8.493467472225454</v>
+        <v>8.493467472225456</v>
       </c>
       <c r="X5" t="n">
-        <v>6.658226844675158</v>
+        <v>6.658226844675179</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.674104526802181</v>
+        <v>5.674104526802206</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.628633754539451</v>
+        <v>4.628633754539442</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.207486796244665</v>
+        <v>6.207486796244673</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.99467602656505</v>
+        <v>10.99467602656504</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6311097483558158</v>
+        <v>0.5414112035994296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4334486444777682</v>
+        <v>0.4334486444777689</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5016392811704943</v>
+        <v>0.5913378259268813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3912749423549898</v>
+        <v>0.3912749423549894</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5080002779634797</v>
+        <v>0.4183017332070925</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9223231951542374</v>
+        <v>0.8326246503978512</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5389279236449032</v>
+        <v>0.6286264684012904</v>
       </c>
       <c r="I6" t="n">
-        <v>0.423638530113254</v>
+        <v>0.4236385301132538</v>
       </c>
       <c r="J6" t="n">
         <v>0.7435448934115512</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5615941086064725</v>
+        <v>0.6512926533628594</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6778497346100651</v>
+        <v>0.6778497346100657</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8494392484809969</v>
+        <v>0.8494392484809959</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5768331920650358</v>
+        <v>0.5768331920650565</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6213689499988733</v>
+        <v>0.6213689499988738</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7463532894273228</v>
+        <v>0.746353289427325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.481862567405179</v>
+        <v>0.5715611121615659</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4602906717581514</v>
+        <v>0.5499892165145379</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6752804028151381</v>
+        <v>0.7649789475715254</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5918831346045289</v>
+        <v>0.5021845898481421</v>
       </c>
       <c r="U6" t="n">
-        <v>0.763472354125783</v>
+        <v>0.6737738093693949</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4668109892640689</v>
+        <v>0.4668109892640693</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7884855483023723</v>
+        <v>0.7884855483023726</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5871277026304478</v>
+        <v>0.6768262473868339</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5507749039324432</v>
+        <v>0.5507749039324661</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5048698954082396</v>
+        <v>0.5945684401646261</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6638468510796225</v>
+        <v>0.5741483063232365</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7766047440045114</v>
+        <v>0.7766047440045107</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6230561293061752</v>
+        <v>0.6230561293061739</v>
       </c>
       <c r="C7" t="n">
         <v>0.4253950254281271</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5832842068772394</v>
+        <v>0.5832842068772398</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4729198680617354</v>
+        <v>0.4729198680617351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4999466589138384</v>
+        <v>0.4999466589138382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9142695761045957</v>
+        <v>0.9142695761045941</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6205728493516484</v>
+        <v>0.6205728493516495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5052834558199993</v>
+        <v>0.5052834558199991</v>
       </c>
       <c r="J7" t="n">
-        <v>0.73549127436191</v>
+        <v>0.7354912743619093</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6432390343132175</v>
+        <v>0.6432390343132173</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7594946603168109</v>
+        <v>0.7594946603168102</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9310841741877431</v>
+        <v>0.9310841741877426</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6578787165272589</v>
+        <v>0.6578787165272597</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6082576832719672</v>
+        <v>0.6082576832719673</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7332510277512392</v>
+        <v>0.7332510277512398</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5635074931119249</v>
+        <v>0.5635074931119244</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5419355974648975</v>
+        <v>0.5419355974648974</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7569253285218834</v>
+        <v>0.7569253285218832</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5838295155548863</v>
+        <v>0.5838295155548866</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7551426731577322</v>
+        <v>0.7551426731577323</v>
       </c>
       <c r="V7" t="n">
-        <v>0.458757370214428</v>
+        <v>0.4587573702144275</v>
       </c>
       <c r="W7" t="n">
-        <v>0.775729530260966</v>
+        <v>0.7757295302609657</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6687726283371933</v>
+        <v>0.668772628337193</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6301416556491372</v>
+        <v>0.6301416556491385</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5865148211149848</v>
+        <v>0.5865148211149844</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6557932320299821</v>
+        <v>0.6557932320299815</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8559662519877681</v>
+        <v>0.8559662519877673</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6704105677141756</v>
+        <v>0.6704105677141738</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5923180570601232</v>
+        <v>0.5923180570601219</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7502072385092363</v>
+        <v>0.7502072385092369</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6398428996937312</v>
+        <v>0.5761761508738965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5659284867072176</v>
+        <v>0.5659284867072167</v>
       </c>
       <c r="G8" t="n">
-        <v>1.081192607736593</v>
+        <v>1.105985934451057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7874958809836449</v>
+        <v>0.7874958809836446</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6722064874519951</v>
+        <v>0.6722064874519953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.902414305993905</v>
+        <v>0.9024143059939039</v>
       </c>
       <c r="K8" t="n">
-        <v>0.810162065945214</v>
+        <v>0.8101620659452126</v>
       </c>
       <c r="L8" t="n">
-        <v>0.926417691948807</v>
+        <v>0.9264176919488063</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09800720581974</v>
+        <v>1.098007205819731</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7321160849960135</v>
+        <v>0.7321160849960119</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7083245382832455</v>
+        <v>0.7083245382832437</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8270743681076111</v>
+        <v>0.8270743681076103</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5873639739570833</v>
+        <v>0.587363973957082</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7088586290968932</v>
+        <v>0.7088586290968931</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9238483601538805</v>
+        <v>0.9238483601538818</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7507525471868839</v>
+        <v>0.7507525471868814</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8488255871156063</v>
+        <v>0.8640459448714027</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6256804018464248</v>
+        <v>0.5930711065303397</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9426760604519756</v>
+        <v>0.9426760604519746</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7035878082790932</v>
+        <v>0.7035878082790934</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9160585250609583</v>
+        <v>0.9160585250609621</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7534378527469813</v>
+        <v>0.6316482115253362</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8227162636619777</v>
+        <v>0.822716263661976</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.147788677316506</v>
+        <v>1.147788677316504</v>
       </c>
     </row>
     <row r="9">
@@ -2922,28 +2922,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9041335211901083</v>
+        <v>0.9041335211901086</v>
       </c>
       <c r="C9" t="n">
-        <v>0.823152325286294</v>
+        <v>0.8231523252862936</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9810415067354072</v>
+        <v>0.9810415067354084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8706771679199019</v>
+        <v>0.8437479340766249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.897703958772005</v>
+        <v>0.6287249038828342</v>
       </c>
       <c r="G9" t="n">
-        <v>1.312026875962762</v>
+        <v>1.312026892848394</v>
       </c>
       <c r="H9" t="n">
         <v>1.018330149209816</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9030407556781648</v>
+        <v>0.9030407556781652</v>
       </c>
       <c r="J9" t="n">
         <v>1.133248574220077</v>
@@ -2952,10 +2952,10 @@
         <v>1.040996334171385</v>
       </c>
       <c r="L9" t="n">
-        <v>1.157251960174977</v>
+        <v>1.157251960174978</v>
       </c>
       <c r="M9" t="n">
-        <v>1.328841474045911</v>
+        <v>1.32884147404591</v>
       </c>
       <c r="N9" t="n">
         <v>1.055636016385426</v>
@@ -2964,25 +2964,25 @@
         <v>1.04504123591343</v>
       </c>
       <c r="P9" t="n">
-        <v>1.17844411438329</v>
+        <v>1.178444114383291</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.961264809855724</v>
+        <v>0.9612648098557227</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9396928973230646</v>
+        <v>0.9396928973230643</v>
       </c>
       <c r="S9" t="n">
-        <v>1.15468262838005</v>
+        <v>1.154682628380051</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9815868154130547</v>
+        <v>0.981586815413054</v>
       </c>
       <c r="U9" t="n">
         <v>1.153176034934308</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8565146700725953</v>
+        <v>0.9911606218223704</v>
       </c>
       <c r="W9" t="n">
         <v>1.173486830119134</v>
@@ -2994,13 +2994,13 @@
         <v>1.027898955507305</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9842721209731529</v>
+        <v>0.9139245187520333</v>
       </c>
       <c r="AA9" t="n">
         <v>1.053550531888149</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.253723551845935</v>
+        <v>1.253723551845936</v>
       </c>
     </row>
   </sheetData>
@@ -3169,10 +3169,10 @@
         <v>2.678674090579006</v>
       </c>
       <c r="C2" t="n">
-        <v>2.697219322226922</v>
+        <v>2.697219322226923</v>
       </c>
       <c r="D2" t="n">
-        <v>2.683321921368579</v>
+        <v>2.68332192136858</v>
       </c>
       <c r="E2" t="n">
         <v>2.670801853188791</v>
@@ -3187,28 +3187,28 @@
         <v>2.679952969298208</v>
       </c>
       <c r="I2" t="n">
-        <v>2.673117623952275</v>
+        <v>2.673117623952276</v>
       </c>
       <c r="J2" t="n">
-        <v>2.692078225118515</v>
+        <v>2.692078225118516</v>
       </c>
       <c r="K2" t="n">
         <v>2.680869710361792</v>
       </c>
       <c r="L2" t="n">
-        <v>2.691007828313256</v>
+        <v>2.691007828313257</v>
       </c>
       <c r="M2" t="n">
-        <v>2.705044677341144</v>
+        <v>2.705044677341145</v>
       </c>
       <c r="N2" t="n">
-        <v>2.680599361720735</v>
+        <v>2.680599361720736</v>
       </c>
       <c r="O2" t="n">
-        <v>2.955079370310245</v>
+        <v>2.955079370310246</v>
       </c>
       <c r="P2" t="n">
-        <v>2.693426376636928</v>
+        <v>2.69342637663693</v>
       </c>
       <c r="Q2" t="n">
         <v>2.668975193142845</v>
@@ -3217,22 +3217,22 @@
         <v>2.673863784145331</v>
       </c>
       <c r="S2" t="n">
-        <v>2.692992528330863</v>
+        <v>2.692992528330864</v>
       </c>
       <c r="T2" t="n">
-        <v>2.678087751180784</v>
+        <v>2.678087751180785</v>
       </c>
       <c r="U2" t="n">
-        <v>3.08574700796228</v>
+        <v>3.085747007962281</v>
       </c>
       <c r="V2" t="n">
         <v>2.673491320999168</v>
       </c>
       <c r="W2" t="n">
-        <v>3.070821100507929</v>
+        <v>3.070821100507931</v>
       </c>
       <c r="X2" t="n">
-        <v>2.694847651188418</v>
+        <v>2.694847651188419</v>
       </c>
       <c r="Y2" t="n">
         <v>2.694068646525744</v>
@@ -3241,10 +3241,10 @@
         <v>2.841579208094478</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.685554567743872</v>
+        <v>2.685554567743873</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.702127338221933</v>
+        <v>2.702127338221934</v>
       </c>
     </row>
     <row r="3">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.868411097153414</v>
+        <v>1.868411097153413</v>
       </c>
       <c r="C3" t="n">
         <v>1.842575484323703</v>
@@ -3263,28 +3263,28 @@
         <v>1.902502898618257</v>
       </c>
       <c r="E3" t="n">
-        <v>1.812700261787574</v>
+        <v>1.812700261787573</v>
       </c>
       <c r="F3" t="n">
         <v>1.804122312026425</v>
       </c>
       <c r="G3" t="n">
-        <v>2.070883420297322</v>
+        <v>2.070883420297323</v>
       </c>
       <c r="H3" t="n">
-        <v>1.878879252261233</v>
+        <v>1.878879252261235</v>
       </c>
       <c r="I3" t="n">
         <v>1.829595292865489</v>
       </c>
       <c r="J3" t="n">
-        <v>1.96413308753661</v>
+        <v>1.964133087536611</v>
       </c>
       <c r="K3" t="n">
-        <v>1.884038499308598</v>
+        <v>1.884038499308597</v>
       </c>
       <c r="L3" t="n">
-        <v>1.956810698805063</v>
+        <v>1.956810698805064</v>
       </c>
       <c r="M3" t="n">
         <v>2.059402067851794</v>
@@ -3293,10 +3293,10 @@
         <v>1.882851283217087</v>
       </c>
       <c r="O3" t="n">
-        <v>2.320558101892854</v>
+        <v>2.320558101892857</v>
       </c>
       <c r="P3" t="n">
-        <v>1.973230790548872</v>
+        <v>1.973230790548873</v>
       </c>
       <c r="Q3" t="n">
         <v>1.799703839923157</v>
@@ -3305,19 +3305,19 @@
         <v>1.835047918098096</v>
       </c>
       <c r="S3" t="n">
-        <v>1.970286455316364</v>
+        <v>1.970286455316366</v>
       </c>
       <c r="T3" t="n">
         <v>1.865134289745377</v>
       </c>
       <c r="U3" t="n">
-        <v>2.593138484052093</v>
+        <v>2.593138484052095</v>
       </c>
       <c r="V3" t="n">
         <v>1.831308509403693</v>
       </c>
       <c r="W3" t="n">
-        <v>2.59852982020687</v>
+        <v>2.598529820206869</v>
       </c>
       <c r="X3" t="n">
         <v>1.98476094415236</v>
@@ -3326,10 +3326,10 @@
         <v>1.978729074141184</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.149545634358895</v>
+        <v>2.149545634358896</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.918064145676755</v>
+        <v>1.918064145676754</v>
       </c>
       <c r="AB3" t="n">
         <v>2.036880275822603</v>
@@ -3345,82 +3345,82 @@
         <v>0.4545527023778617</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3370868922565328</v>
+        <v>0.3370868922565325</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5070520892538672</v>
+        <v>0.507052089253867</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3656321596472439</v>
+        <v>0.3656321596472443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3517380112295714</v>
+        <v>0.3517380112295718</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7763111388877365</v>
+        <v>0.7763111388877363</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4689982258245227</v>
+        <v>0.4689982258245231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3917898557279906</v>
+        <v>0.3917898557279913</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6055409424349322</v>
+        <v>0.6055409424349318</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4793532378594069</v>
+        <v>0.4793532378594075</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5938679438858696</v>
+        <v>0.5938679438858699</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7544925217283307</v>
+        <v>0.7544925217283309</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4762995255921658</v>
+        <v>0.4762995255921656</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4467633746820114</v>
+        <v>0.4467633746820134</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6211865597889544</v>
+        <v>0.6211865597889565</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3449991941231482</v>
+        <v>0.3449991941231483</v>
       </c>
       <c r="R4" t="n">
-        <v>0.400218078359198</v>
+        <v>0.4002180783591979</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6162860435918838</v>
+        <v>0.616286043591884</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4479297291454657</v>
+        <v>0.4479297291454666</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5598039784598761</v>
+        <v>0.5598039784598777</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3932123145147072</v>
+        <v>0.3932123145147067</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6239045556423687</v>
+        <v>0.623904555642368</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6372405096666207</v>
+        <v>0.6372405096666224</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.625201083875824</v>
+        <v>0.6252010838758252</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4806510579185312</v>
+        <v>0.480651057918531</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5322708571308679</v>
+        <v>0.5322708571308681</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7172404910520862</v>
+        <v>0.7172404910520866</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95805547617909</v>
+        <v>3.958055476179096</v>
       </c>
       <c r="C5" t="n">
         <v>2.11571954365816</v>
       </c>
       <c r="D5" t="n">
-        <v>5.363361201520199</v>
+        <v>5.363361201520212</v>
       </c>
       <c r="E5" t="n">
-        <v>2.630839924161279</v>
+        <v>2.630839924161283</v>
       </c>
       <c r="F5" t="n">
-        <v>2.489305903689301</v>
+        <v>2.4893059036893</v>
       </c>
       <c r="G5" t="n">
-        <v>9.218173476927133</v>
+        <v>9.218173476927124</v>
       </c>
       <c r="H5" t="n">
-        <v>4.908349806584056</v>
+        <v>4.908349806584053</v>
       </c>
       <c r="I5" t="n">
-        <v>3.28380497919188</v>
+        <v>3.283804979191891</v>
       </c>
       <c r="J5" t="n">
-        <v>6.664528239504012</v>
+        <v>6.664528239504015</v>
       </c>
       <c r="K5" t="n">
-        <v>4.374490176141153</v>
+        <v>4.374490176141156</v>
       </c>
       <c r="L5" t="n">
-        <v>6.615425339196344</v>
+        <v>6.61542533919635</v>
       </c>
       <c r="M5" t="n">
-        <v>10.12171948613882</v>
+        <v>10.12171948613883</v>
       </c>
       <c r="N5" t="n">
-        <v>5.824242682867667</v>
+        <v>5.824242682867696</v>
       </c>
       <c r="O5" t="n">
-        <v>3.650765202289627</v>
+        <v>3.650765202289632</v>
       </c>
       <c r="P5" t="n">
-        <v>6.662665286208421</v>
+        <v>6.662665286208461</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.286921718727473</v>
+        <v>2.286921718727479</v>
       </c>
       <c r="R5" t="n">
-        <v>3.498812330607801</v>
+        <v>3.498812330607802</v>
       </c>
       <c r="S5" t="n">
-        <v>6.654793725326599</v>
+        <v>6.654793725326618</v>
       </c>
       <c r="T5" t="n">
-        <v>4.311426980293397</v>
+        <v>4.311426980293407</v>
       </c>
       <c r="U5" t="n">
-        <v>5.910987345501433</v>
+        <v>5.910987345501463</v>
       </c>
       <c r="V5" t="n">
-        <v>2.861340048766615</v>
+        <v>2.861340048766598</v>
       </c>
       <c r="W5" t="n">
-        <v>7.239212027820789</v>
+        <v>7.239212027820781</v>
       </c>
       <c r="X5" t="n">
-        <v>7.665096555827006</v>
+        <v>7.665096555827024</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.264827038208009</v>
+        <v>7.264827038208028</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.188246371154393</v>
+        <v>4.188246371154398</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.615963444585396</v>
+        <v>5.615963444585392</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.792095436789179</v>
+        <v>9.79209543678917</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5558832499031242</v>
+        <v>0.4751269518135873</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3576611416922565</v>
+        <v>0.3576611416922572</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6083826367791285</v>
+        <v>0.6083826367791302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.386206409082968</v>
+        <v>0.386206409082969</v>
       </c>
       <c r="F6" t="n">
-        <v>0.372312260665296</v>
+        <v>0.4530685587548343</v>
       </c>
       <c r="G6" t="n">
-        <v>0.877641686413</v>
+        <v>0.7968853883234615</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4895724752602472</v>
+        <v>0.4895724752602473</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4931204032532539</v>
+        <v>0.4123641051637156</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7068714899601938</v>
+        <v>0.7068714899601951</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4999274872951305</v>
+        <v>0.5806837853846701</v>
       </c>
       <c r="L6" t="n">
-        <v>0.695198491411132</v>
+        <v>0.6144421933215933</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8558230692535932</v>
+        <v>0.855823069253593</v>
       </c>
       <c r="N6" t="n">
         <v>0.4974084702634688</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5523129958492277</v>
+        <v>0.4678723193533158</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7267173183120419</v>
+        <v>0.7267173183120438</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4463297416484096</v>
+        <v>0.4463297416484109</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5015486258844601</v>
+        <v>0.5015486258844607</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6368602930276057</v>
+        <v>0.6368602930276077</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4685039785811904</v>
+        <v>0.4685039785811914</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6643747357511943</v>
+        <v>0.5836184376616597</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4945428620399701</v>
+        <v>0.4945428620399699</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7294573123479288</v>
+        <v>0.6486212556320207</v>
       </c>
       <c r="X6" t="n">
-        <v>0.657814759102346</v>
+        <v>0.657814759102348</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6512560220058002</v>
+        <v>0.6512560220058007</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5819816054437933</v>
+        <v>0.501225307354255</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5528451065665918</v>
+        <v>0.6336014046561294</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7397703213979724</v>
+        <v>0.7397703213979731</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5443327824142756</v>
+        <v>0.5443327824142759</v>
       </c>
       <c r="C7" t="n">
         <v>0.4268669722929465</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5968321692902804</v>
+        <v>0.5968321692902809</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4554122396836578</v>
+        <v>0.4554122396836581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4415180912659856</v>
+        <v>0.4415180912659858</v>
       </c>
       <c r="G7" t="n">
-        <v>0.866091218924149</v>
+        <v>0.8660912189241498</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5587783058609351</v>
+        <v>0.5587783058609355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4815699357644034</v>
+        <v>0.4815699357644052</v>
       </c>
       <c r="J7" t="n">
-        <v>0.695321022471345</v>
+        <v>0.6953210224713459</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5691333178958197</v>
+        <v>0.5691333178958208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6836480239222824</v>
+        <v>0.6836480239222831</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8442726017647434</v>
+        <v>0.8442726017647435</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5660796056285791</v>
+        <v>0.5660796056285797</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5362095118002203</v>
+        <v>0.5362095118002214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7106326969071607</v>
+        <v>0.710632696907164</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4347792741595612</v>
+        <v>0.4347792741595619</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4899981583956114</v>
+        <v>0.4899981583956116</v>
       </c>
       <c r="S7" t="n">
-        <v>0.706066123628296</v>
+        <v>0.7060661236282973</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5377098091818795</v>
+        <v>0.5377098091818805</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6522253153843103</v>
+        <v>0.6522253153843124</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4829923945511199</v>
+        <v>0.4829923945511205</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7136846356787817</v>
+        <v>0.7136846356787818</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7270205897030338</v>
+        <v>0.7270205897030348</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7182213736782962</v>
+        <v>0.7182213736782972</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5704311379549442</v>
+        <v>0.5704311379549449</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6220509371672812</v>
+        <v>0.6220509371672815</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8070205710885</v>
+        <v>0.8070205710884998</v>
       </c>
     </row>
     <row r="8">
@@ -3694,82 +3694,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5852466540506212</v>
+        <v>0.5852466540506208</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5726671566651049</v>
+        <v>0.5726671566651056</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7426323536624394</v>
+        <v>0.7426323536624402</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6012124240558169</v>
+        <v>0.5453635564943947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4987720245842265</v>
+        <v>0.4987720245842271</v>
       </c>
       <c r="G8" t="n">
-        <v>1.011891403296309</v>
+        <v>1.033640263505903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7045784902330952</v>
+        <v>0.7045784902330958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6273701201365642</v>
+        <v>0.6273701201365646</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8411212068435041</v>
+        <v>0.8411212068435057</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7149335022679788</v>
+        <v>0.7149335022679801</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8294482082944409</v>
+        <v>0.8294482082944422</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9900727861369019</v>
+        <v>0.9900727861368901</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6305753505100169</v>
+        <v>0.6305753505100177</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6233823654810425</v>
+        <v>0.6233823654810435</v>
       </c>
       <c r="P8" t="n">
-        <v>0.792328700748636</v>
+        <v>0.7923287007486384</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4550805914539837</v>
+        <v>0.4550805914539843</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6357983427677701</v>
+        <v>0.6357983427677715</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8518663080004537</v>
+        <v>0.8518663080004565</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6835099935540379</v>
+        <v>0.6835099935540396</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7338900316877726</v>
+        <v>0.7472254670242877</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6287925789232804</v>
+        <v>0.5998990441537918</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8595054331287211</v>
+        <v>0.8595054331287217</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7569349459179211</v>
+        <v>0.7569349459179227</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9679562924645893</v>
+        <v>0.9679562924645911</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7162313223271032</v>
+        <v>0.6093966924913059</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7678511215394406</v>
+        <v>0.7678511215394414</v>
       </c>
       <c r="AB8" t="n">
         <v>1.062383279481617</v>
@@ -3782,28 +3782,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.779312008303535</v>
+        <v>0.7793120083035351</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7611680770506819</v>
+        <v>0.7611680770506818</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9311332740480153</v>
+        <v>0.9311332740480163</v>
       </c>
       <c r="E9" t="n">
-        <v>0.789713344441393</v>
+        <v>0.7667902759128805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7758191960237206</v>
+        <v>0.5468551305894349</v>
       </c>
       <c r="G9" t="n">
-        <v>1.200392323681887</v>
+        <v>1.200392344466699</v>
       </c>
       <c r="H9" t="n">
         <v>0.8930794106186719</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8158710405221385</v>
+        <v>0.8158710405221394</v>
       </c>
       <c r="J9" t="n">
         <v>1.029622127229082</v>
@@ -3815,49 +3815,49 @@
         <v>1.017949128680018</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17857370652248</v>
+        <v>1.178573706522479</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9003807103863163</v>
+        <v>0.9003807103863162</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9037597277551561</v>
+        <v>0.9037597277551562</v>
       </c>
       <c r="P9" t="n">
-        <v>1.085341392713253</v>
+        <v>1.085341392713254</v>
       </c>
       <c r="Q9" t="n">
         <v>0.7690803997021096</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8242992631533475</v>
+        <v>0.8242992631533472</v>
       </c>
       <c r="S9" t="n">
         <v>1.040367228386032</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8720109139396157</v>
+        <v>0.8720109139396162</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9871253730200823</v>
+        <v>0.9871253730200845</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8172934993088569</v>
+        <v>0.9319086964788732</v>
       </c>
       <c r="W9" t="n">
         <v>1.047985740436518</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06132169446077</v>
+        <v>1.061321694460771</v>
       </c>
       <c r="Y9" t="n">
         <v>1.052522478436032</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9047322427126804</v>
+        <v>0.8448499900544817</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9563520419250169</v>
+        <v>0.956352041925017</v>
       </c>
       <c r="AB9" t="n">
         <v>1.141321675846237</v>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672297873117212</v>
+        <v>2.672297873117211</v>
       </c>
       <c r="C2" t="n">
-        <v>2.694340263196876</v>
+        <v>2.694340263196875</v>
       </c>
       <c r="D2" t="n">
         <v>2.671470166762514</v>
@@ -4038,10 +4038,10 @@
         <v>2.663049028935491</v>
       </c>
       <c r="F2" t="n">
-        <v>2.667198115458163</v>
+        <v>2.667198115458162</v>
       </c>
       <c r="G2" t="n">
-        <v>2.696085847332211</v>
+        <v>2.696085847332212</v>
       </c>
       <c r="H2" t="n">
         <v>2.673545629615623</v>
@@ -4053,7 +4053,7 @@
         <v>2.684534543569245</v>
       </c>
       <c r="K2" t="n">
-        <v>2.680412437418543</v>
+        <v>2.680412437418542</v>
       </c>
       <c r="L2" t="n">
         <v>2.682156415112697</v>
@@ -4062,22 +4062,22 @@
         <v>2.694010652391706</v>
       </c>
       <c r="N2" t="n">
-        <v>2.673397517006392</v>
+        <v>2.673397517006393</v>
       </c>
       <c r="O2" t="n">
-        <v>2.940829659073771</v>
+        <v>2.940829659073769</v>
       </c>
       <c r="P2" t="n">
-        <v>2.686991249945159</v>
+        <v>2.686991249945158</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.667819029499452</v>
+        <v>2.667819029499453</v>
       </c>
       <c r="R2" t="n">
-        <v>2.668295549367388</v>
+        <v>2.668295549367389</v>
       </c>
       <c r="S2" t="n">
-        <v>2.685396823094014</v>
+        <v>2.685396823094013</v>
       </c>
       <c r="T2" t="n">
         <v>2.671892707996023</v>
@@ -4098,10 +4098,10 @@
         <v>2.70585595890969</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.832185749129601</v>
+        <v>2.8321857491296</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.683044007508071</v>
+        <v>2.683044007508072</v>
       </c>
       <c r="AB2" t="n">
         <v>2.69387511295085</v>
@@ -4114,19 +4114,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.851280033674471</v>
+        <v>1.851280033674472</v>
       </c>
       <c r="C3" t="n">
         <v>1.852034476028299</v>
       </c>
       <c r="D3" t="n">
-        <v>1.846037253843525</v>
+        <v>1.846037253843526</v>
       </c>
       <c r="E3" t="n">
         <v>1.785721673290676</v>
       </c>
       <c r="F3" t="n">
-        <v>1.815684577966184</v>
+        <v>1.815684577966185</v>
       </c>
       <c r="G3" t="n">
         <v>2.02006167407383</v>
@@ -4135,7 +4135,7 @@
         <v>1.861602746654363</v>
       </c>
       <c r="I3" t="n">
-        <v>1.833943739155944</v>
+        <v>1.833943739155945</v>
       </c>
       <c r="J3" t="n">
         <v>1.93860809915929</v>
@@ -4147,10 +4147,10 @@
         <v>1.921775530512291</v>
       </c>
       <c r="M3" t="n">
-        <v>2.008514499124111</v>
+        <v>2.00851449912411</v>
       </c>
       <c r="N3" t="n">
-        <v>1.859959327212069</v>
+        <v>1.859959327212068</v>
       </c>
       <c r="O3" t="n">
         <v>2.282409301616573</v>
@@ -4159,7 +4159,7 @@
         <v>1.955491116396283</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.819850492542677</v>
+        <v>1.819850492542678</v>
       </c>
       <c r="R3" t="n">
         <v>1.823779611239247</v>
@@ -4186,7 +4186,7 @@
         <v>2.091742755156202</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.125946839081295</v>
+        <v>2.125946839081294</v>
       </c>
       <c r="AA3" t="n">
         <v>1.928727663540073</v>
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4215468614935493</v>
+        <v>0.4215468614935488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3468210583082325</v>
+        <v>0.3468210583082326</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4121975374535025</v>
+        <v>0.4121975374535026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.317076911782506</v>
+        <v>0.3170769117825061</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3639427527301687</v>
+        <v>0.3639427527301686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6902429732607622</v>
+        <v>0.6902429732607621</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4356408451394706</v>
+        <v>0.4356408451394702</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3926892365736466</v>
+        <v>0.392689236573647</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5594316426588711</v>
+        <v>0.5594316426588709</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5132045981610932</v>
+        <v>0.5132045981610939</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5329036284859249</v>
+        <v>0.5329036284859252</v>
       </c>
       <c r="M4" t="n">
-        <v>0.66921560742677</v>
+        <v>0.6692156074267697</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4339678450830557</v>
+        <v>0.4339678450830554</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3966030533448863</v>
+        <v>0.396603053344886</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5875153120524859</v>
+        <v>0.5875153120524856</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3709562624611216</v>
+        <v>0.3709562624611219</v>
       </c>
       <c r="R4" t="n">
         <v>0.3763387735794055</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5695055272962319</v>
+        <v>0.5695055272962318</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4169703350645764</v>
+        <v>0.4169703350645758</v>
       </c>
       <c r="U4" t="n">
         <v>0.5739230430905452</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4762334668935016</v>
+        <v>0.4762334668935017</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6129756902457003</v>
+        <v>0.6129756902457</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6452684475056835</v>
+        <v>0.6452684475056831</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7988288485719298</v>
+        <v>0.7988288485719306</v>
       </c>
       <c r="Z4" t="n">
         <v>0.4448030966710731</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.542929392904395</v>
+        <v>0.5429293929043957</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6631023709364139</v>
+        <v>0.663102370936414</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.446082675318205</v>
+        <v>3.446082675318209</v>
       </c>
       <c r="C5" t="n">
-        <v>2.409325436767249</v>
+        <v>2.409325436767251</v>
       </c>
       <c r="D5" t="n">
-        <v>3.625137446373852</v>
+        <v>3.625137446373858</v>
       </c>
       <c r="E5" t="n">
-        <v>1.832131214295198</v>
+        <v>1.832131214295202</v>
       </c>
       <c r="F5" t="n">
-        <v>2.842755406793397</v>
+        <v>2.842755406793398</v>
       </c>
       <c r="G5" t="n">
-        <v>7.68313695524896</v>
+        <v>7.683136955248974</v>
       </c>
       <c r="H5" t="n">
-        <v>4.42989624578492</v>
+        <v>4.429896245784929</v>
       </c>
       <c r="I5" t="n">
-        <v>3.400758392005066</v>
+        <v>3.400758392005069</v>
       </c>
       <c r="J5" t="n">
         <v>5.887442622390813</v>
       </c>
       <c r="K5" t="n">
-        <v>5.068921930654537</v>
+        <v>5.06892193065454</v>
       </c>
       <c r="L5" t="n">
-        <v>5.48535930733543</v>
+        <v>5.485359307335433</v>
       </c>
       <c r="M5" t="n">
-        <v>8.323123643854622</v>
+        <v>8.323123643854624</v>
       </c>
       <c r="N5" t="n">
-        <v>5.915171196201479</v>
+        <v>5.915171196201491</v>
       </c>
       <c r="O5" t="n">
-        <v>2.996598013177525</v>
+        <v>2.996598013177524</v>
       </c>
       <c r="P5" t="n">
-        <v>6.041408001527361</v>
+        <v>6.04140800152737</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.829170846647972</v>
+        <v>2.829170846647984</v>
       </c>
       <c r="R5" t="n">
-        <v>3.198081535771077</v>
+        <v>3.198081535771089</v>
       </c>
       <c r="S5" t="n">
-        <v>5.935794145139909</v>
+        <v>5.935794145139915</v>
       </c>
       <c r="T5" t="n">
         <v>3.889787991148791</v>
       </c>
       <c r="U5" t="n">
-        <v>6.056898423638827</v>
+        <v>6.056898423638801</v>
       </c>
       <c r="V5" t="n">
-        <v>4.24055147267469</v>
+        <v>4.240551472674692</v>
       </c>
       <c r="W5" t="n">
-        <v>7.201496047013983</v>
+        <v>7.201496047013981</v>
       </c>
       <c r="X5" t="n">
-        <v>7.725721382848129</v>
+        <v>7.725721382848134</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.64621440714911</v>
+        <v>10.64621440714913</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.570678373289061</v>
+        <v>3.570678373289059</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.982603278217635</v>
+        <v>5.982603278217648</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.768634539978999</v>
+        <v>8.768634539979004</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4454530132785005</v>
+        <v>0.521175711276646</v>
       </c>
       <c r="C6" t="n">
         <v>0.3707272100931839</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4361036892384536</v>
+        <v>0.4361036892384537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.340983063567457</v>
+        <v>0.4167057615656031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3878489045151199</v>
+        <v>0.3878489045151198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7141491250457135</v>
+        <v>0.7898718230438604</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5352696949225672</v>
+        <v>0.4595469969244212</v>
       </c>
       <c r="I6" t="n">
         <v>0.4165953883585983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5833377944438227</v>
+        <v>0.6590604924419682</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6128334479441895</v>
+        <v>0.6128334479441897</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5568097802708767</v>
+        <v>0.6325324782690223</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6931217592117215</v>
+        <v>0.6931217592117205</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4588864631736617</v>
+        <v>0.4588864631736567</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4215216714354783</v>
+        <v>0.5006354895099269</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6915242083076067</v>
+        <v>0.6092086598189634</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4705851122442182</v>
+        <v>0.4705851122442187</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4759676233625033</v>
+        <v>0.4759676233625031</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6691343770793287</v>
+        <v>0.6691343770793283</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4408764868495275</v>
+        <v>0.5165991848476732</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6753239223034807</v>
+        <v>0.5996012243053344</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5758623166765984</v>
+        <v>0.5001396186784528</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7170116741800925</v>
+        <v>0.7170116741800926</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6691745992906331</v>
+        <v>0.6691745992906345</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8276742425200823</v>
+        <v>0.8276742425200782</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5444319464541697</v>
+        <v>0.5444319464541699</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6425582426874925</v>
+        <v>0.6425582426874928</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6889307704625399</v>
+        <v>0.6889307704625397</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5082469041755692</v>
+        <v>0.5082469041755691</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4335211009902531</v>
+        <v>0.4335211009902533</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4988975801355232</v>
+        <v>0.4988975801355231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4037769544645265</v>
+        <v>0.4037769544645262</v>
       </c>
       <c r="F7" t="n">
         <v>0.4506427954121892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.776943015942782</v>
+        <v>0.7769430159427821</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5223408878214908</v>
+        <v>0.5223408878214905</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4793892792556676</v>
+        <v>0.4793892792556677</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6461316853408914</v>
+        <v>0.6461316853408913</v>
       </c>
       <c r="K7" t="n">
-        <v>0.599904640843113</v>
+        <v>0.5999046408431136</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6196036711679462</v>
+        <v>0.6196036711679466</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7559156501087897</v>
+        <v>0.7559156501087896</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5206678877650761</v>
+        <v>0.5206678877650758</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4829694253219426</v>
+        <v>0.482969425321942</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6738816840295428</v>
+        <v>0.6738816840295432</v>
       </c>
       <c r="Q7" t="n">
         <v>0.457656305143142</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4630388162614268</v>
+        <v>0.4630388162614265</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6562055699782525</v>
+        <v>0.6562055699782527</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5036703777465962</v>
+        <v>0.5036703777465958</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6612410176103982</v>
+        <v>0.6612410176103987</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5629335095755221</v>
+        <v>0.5629335095755215</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6996757329277202</v>
+        <v>0.6996757329277198</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7319684901877039</v>
+        <v>0.7319684901877033</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8873009206837884</v>
+        <v>0.8873009206837897</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5315031393530938</v>
+        <v>0.5315031393530931</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6296294355864157</v>
+        <v>0.6296294355864163</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.749802413618436</v>
+        <v>0.7498024136184355</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5461200324013044</v>
+        <v>0.5461200324013041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5714331035922</v>
+        <v>0.5714331035921998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6368095827374698</v>
+        <v>0.6368095827374699</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5416889570664738</v>
+        <v>0.4884212074405453</v>
       </c>
       <c r="F8" t="n">
-        <v>0.504100811076883</v>
+        <v>0.5041008110768829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9148550185447309</v>
+        <v>0.9355987308324881</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6602528904234387</v>
+        <v>0.6602528904234379</v>
       </c>
       <c r="I8" t="n">
         <v>0.617301281857615</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7840436879428395</v>
+        <v>0.7840436879428393</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7378166434450607</v>
+        <v>0.7378166434450613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7575156737698938</v>
+        <v>0.7575156737698933</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8938276527107378</v>
+        <v>0.8938276527107084</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5810330265644675</v>
+        <v>0.5810330265644672</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5649787862831751</v>
+        <v>0.5649787862831745</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7506673138980804</v>
+        <v>0.7506673138980801</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.475869511301222</v>
+        <v>0.4758695113012227</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6009508188633733</v>
+        <v>0.6009508188633732</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7941175725802002</v>
+        <v>0.7941175725802003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6415823803485441</v>
+        <v>0.6415823803485436</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7381513862888731</v>
+        <v>0.7508436676768563</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7008455121774704</v>
+        <v>0.6728020987648046</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8376073959494781</v>
+        <v>0.837607395949478</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7593504579101955</v>
+        <v>0.7593504579101962</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.123591611905383</v>
+        <v>1.123591611905384</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6694151419550411</v>
+        <v>0.567517994134791</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7675414381883636</v>
+        <v>0.7675414381883632</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9922133855409884</v>
+        <v>0.9922133855409879</v>
       </c>
     </row>
     <row r="9">
@@ -4642,82 +4642,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7156418598327793</v>
+        <v>0.7156418598327792</v>
       </c>
       <c r="C9" t="n">
         <v>0.7313404439789092</v>
       </c>
       <c r="D9" t="n">
-        <v>0.796716923124179</v>
+        <v>0.7967169231241787</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7015962974531824</v>
+        <v>0.6807267258367895</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7484621384008451</v>
+        <v>0.5400092326231548</v>
       </c>
       <c r="G9" t="n">
-        <v>1.074762358931438</v>
+        <v>1.074762369520754</v>
       </c>
       <c r="H9" t="n">
-        <v>0.820160230810147</v>
+        <v>0.8201602308101461</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7772086222443225</v>
+        <v>0.7772086222443222</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9439510283295476</v>
+        <v>0.9439510283295469</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8977239838317698</v>
+        <v>0.8977239838317701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9174230141566019</v>
+        <v>0.9174230141566013</v>
       </c>
       <c r="M9" t="n">
-        <v>1.053734993097446</v>
+        <v>1.053734993097445</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8184872307537312</v>
+        <v>0.8184872307537303</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8110889766751819</v>
+        <v>0.8110889766751808</v>
       </c>
       <c r="P9" t="n">
         <v>1.008518440881551</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7554756587211132</v>
+        <v>0.7554756587211129</v>
       </c>
       <c r="R9" t="n">
-        <v>0.760858159250082</v>
+        <v>0.7608581592500815</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9540249129669093</v>
+        <v>0.9540249129669094</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8014897207352506</v>
+        <v>0.8014897207352514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9602144581910593</v>
+        <v>0.9602144581910598</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8607528525641776</v>
+        <v>0.9651005569392865</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9974950759163753</v>
+        <v>0.9974950759163751</v>
       </c>
       <c r="X9" t="n">
-        <v>1.029787833176358</v>
+        <v>1.029787833176359</v>
       </c>
       <c r="Y9" t="n">
         <v>1.185120263672445</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8293224823417489</v>
+        <v>0.7748046218360418</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.927448778575071</v>
+        <v>0.9274487785750716</v>
       </c>
       <c r="AB9" t="n">
         <v>1.047621756607089</v>
@@ -4886,82 +4886,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.614141996236271</v>
+        <v>2.614141996236274</v>
       </c>
       <c r="C2" t="n">
         <v>2.641547679288493</v>
       </c>
       <c r="D2" t="n">
-        <v>2.619422810771436</v>
+        <v>2.619422810771437</v>
       </c>
       <c r="E2" t="n">
-        <v>2.610678444628742</v>
+        <v>2.610678444628744</v>
       </c>
       <c r="F2" t="n">
         <v>2.61045925868026</v>
       </c>
       <c r="G2" t="n">
-        <v>2.625144227042194</v>
+        <v>2.625144227042195</v>
       </c>
       <c r="H2" t="n">
-        <v>2.615029284580119</v>
+        <v>2.615029284580122</v>
       </c>
       <c r="I2" t="n">
-        <v>2.614150261051236</v>
+        <v>2.614150261051238</v>
       </c>
       <c r="J2" t="n">
-        <v>2.620133653935315</v>
+        <v>2.620133653935317</v>
       </c>
       <c r="K2" t="n">
-        <v>2.619917048399953</v>
+        <v>2.619917048399954</v>
       </c>
       <c r="L2" t="n">
-        <v>2.611596486330554</v>
+        <v>2.611596486330555</v>
       </c>
       <c r="M2" t="n">
-        <v>2.625618822176029</v>
+        <v>2.625618822176028</v>
       </c>
       <c r="N2" t="n">
-        <v>2.616626539880056</v>
+        <v>2.616626539880058</v>
       </c>
       <c r="O2" t="n">
-        <v>2.862345376507481</v>
+        <v>2.862345376507484</v>
       </c>
       <c r="P2" t="n">
-        <v>2.61506832325549</v>
+        <v>2.615068323255491</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.613962248813448</v>
+        <v>2.613962248813449</v>
       </c>
       <c r="R2" t="n">
-        <v>2.598755426724658</v>
+        <v>2.598755426724663</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61744312080342</v>
+        <v>2.617443120803427</v>
       </c>
       <c r="T2" t="n">
-        <v>2.612948531288767</v>
+        <v>2.612948531288769</v>
       </c>
       <c r="U2" t="n">
-        <v>3.015650894302446</v>
+        <v>3.015650894302451</v>
       </c>
       <c r="V2" t="n">
-        <v>2.614052441801086</v>
+        <v>2.614052441801087</v>
       </c>
       <c r="W2" t="n">
-        <v>3.009270593916459</v>
+        <v>3.009270593916464</v>
       </c>
       <c r="X2" t="n">
-        <v>2.625928805735797</v>
+        <v>2.625928805735802</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.61760723027963</v>
+        <v>2.617607230279631</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.763336026098984</v>
+        <v>2.763336026098985</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.626677273039888</v>
+        <v>2.62667727303989</v>
       </c>
       <c r="AB2" t="n">
         <v>2.622744322974275</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.715474676283844</v>
+        <v>1.715474676283848</v>
       </c>
       <c r="C3" t="n">
-        <v>1.753026576183321</v>
+        <v>1.75302657618332</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75341438470159</v>
+        <v>1.753414384701595</v>
       </c>
       <c r="E3" t="n">
-        <v>1.690878387956408</v>
+        <v>1.690878387956411</v>
       </c>
       <c r="F3" t="n">
-        <v>1.689317450894289</v>
+        <v>1.689317450894293</v>
       </c>
       <c r="G3" t="n">
-        <v>1.793335333706889</v>
+        <v>1.793335333706892</v>
       </c>
       <c r="H3" t="n">
-        <v>1.722086057530558</v>
+        <v>1.72208605753056</v>
       </c>
       <c r="I3" t="n">
-        <v>1.715726797186498</v>
+        <v>1.7157267971865</v>
       </c>
       <c r="J3" t="n">
-        <v>1.758039546909672</v>
+        <v>1.758039546909673</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75663820458942</v>
+        <v>1.756638204589426</v>
       </c>
       <c r="L3" t="n">
-        <v>1.697425156660048</v>
+        <v>1.697425156660053</v>
       </c>
       <c r="M3" t="n">
         <v>1.798607038908415</v>
       </c>
       <c r="N3" t="n">
-        <v>1.733305038494126</v>
+        <v>1.73330503849413</v>
       </c>
       <c r="O3" t="n">
-        <v>2.118377552760454</v>
+        <v>2.118377552760455</v>
       </c>
       <c r="P3" t="n">
-        <v>1.722077754650193</v>
+        <v>1.722077754650197</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71428840425024</v>
+        <v>1.714288404250245</v>
       </c>
       <c r="R3" t="n">
-        <v>1.605392039405517</v>
+        <v>1.605392039405519</v>
       </c>
       <c r="S3" t="n">
-        <v>1.738723298999486</v>
+        <v>1.738723298999488</v>
       </c>
       <c r="T3" t="n">
-        <v>1.707094661101373</v>
+        <v>1.707094661101378</v>
       </c>
       <c r="U3" t="n">
-        <v>2.452807654929507</v>
+        <v>2.45280765492951</v>
       </c>
       <c r="V3" t="n">
-        <v>1.714836660759394</v>
+        <v>1.714836660759401</v>
       </c>
       <c r="W3" t="n">
-        <v>2.525068414885088</v>
+        <v>2.525068414885093</v>
       </c>
       <c r="X3" t="n">
-        <v>1.799861189876389</v>
+        <v>1.799861189876391</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.740302449011237</v>
+        <v>1.740302449011241</v>
       </c>
       <c r="Z3" t="n">
         <v>1.964392036866587</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.805063995953042</v>
+        <v>1.805063995953046</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.776626062159155</v>
+        <v>1.776626062159154</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1987024274226911</v>
+        <v>0.1987024274226913</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1825805812074304</v>
+        <v>0.1825805812074307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2583516568920916</v>
+        <v>0.2583516568920914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1595800187031951</v>
+        <v>0.1595800187031949</v>
       </c>
       <c r="F4" t="n">
         <v>0.1571042125845731</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3229776856518255</v>
+        <v>0.3229776856518256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2087247574392683</v>
+        <v>0.2087247574392674</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1987957823097208</v>
+        <v>0.1987957823097199</v>
       </c>
       <c r="J4" t="n">
         <v>0.2660674405240631</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2639342982667233</v>
+        <v>0.2639342982667222</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1699497220452103</v>
+        <v>0.1699497220452098</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3307574306157224</v>
+        <v>0.330757430615723</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2267664908257823</v>
+        <v>0.2267664908257822</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1846296859950956</v>
+        <v>0.1846296859950953</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2091657172362653</v>
+        <v>0.209165717236265</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1966720975940096</v>
+        <v>0.1966720975940089</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02490404661739701</v>
+        <v>0.02490404661739624</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2359901480010478</v>
+        <v>0.2359901480010483</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1852216918196356</v>
+        <v>0.1852216918196346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3507012799240734</v>
+        <v>0.3507012799240739</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1955975180045396</v>
+        <v>0.1955975180045394</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5223445850790592</v>
+        <v>0.522344585079059</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3318398629201407</v>
+        <v>0.3318398629201405</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2358850217747161</v>
+        <v>0.2358850217747154</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2042417519021042</v>
+        <v>0.2042417519021026</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.340294145431772</v>
+        <v>0.3402941454317724</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.294671074098022</v>
+        <v>0.2946710740980215</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8629444486424538</v>
+        <v>0.8629444486424546</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6330965517521744</v>
+        <v>0.6330965517521747</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129975620348223</v>
+        <v>2.129975620348225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1917686470000856</v>
+        <v>0.1917686470000852</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1468494719436498</v>
+        <v>0.1468494719436568</v>
       </c>
       <c r="G5" t="n">
-        <v>2.844104598636482</v>
+        <v>2.844104598636489</v>
       </c>
       <c r="H5" t="n">
-        <v>1.207478766861081</v>
+        <v>1.207478766861082</v>
       </c>
       <c r="I5" t="n">
-        <v>0.972121784471786</v>
+        <v>0.9721217844717837</v>
       </c>
       <c r="J5" t="n">
-        <v>2.032233663466547</v>
+        <v>2.032233663466548</v>
       </c>
       <c r="K5" t="n">
-        <v>2.066695689638279</v>
+        <v>2.066695689638272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3848677716941151</v>
+        <v>0.3848677716941136</v>
       </c>
       <c r="M5" t="n">
-        <v>3.308331676946064</v>
+        <v>3.30833167694606</v>
       </c>
       <c r="N5" t="n">
         <v>3.521218544577847</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6152619755961252</v>
+        <v>0.6152619755961135</v>
       </c>
       <c r="P5" t="n">
-        <v>1.056243045852522</v>
+        <v>1.056243045852529</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.878276294594285</v>
+        <v>0.8782762945942821</v>
       </c>
       <c r="R5" t="n">
         <v>-2.572224843049404</v>
       </c>
       <c r="S5" t="n">
-        <v>1.394642311071663</v>
+        <v>1.394642311071659</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6846917943322705</v>
+        <v>0.6846917943322717</v>
       </c>
       <c r="U5" t="n">
-        <v>3.647112151930289</v>
+        <v>3.647112151930283</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8423580711840916</v>
+        <v>0.8423580711840848</v>
       </c>
       <c r="W5" t="n">
         <v>7.07355877326451</v>
       </c>
       <c r="X5" t="n">
-        <v>3.52682190754529</v>
+        <v>3.526821907545286</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6565420746762</v>
+        <v>1.656542074676208</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9425278524834874</v>
+        <v>0.9425278524834859</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.609345938340228</v>
+        <v>3.609345938340229</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.904070016094549</v>
+        <v>2.904070016094544</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2112021048660758</v>
+        <v>0.2112021048660693</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2504708348031887</v>
+        <v>0.2504708348031888</v>
       </c>
       <c r="D6" t="n">
-        <v>0.32624191048785</v>
+        <v>0.2708513343354695</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2274702722989528</v>
+        <v>0.1720796961465729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.22499446618033</v>
+        <v>0.2249944661803312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3354773630952091</v>
+        <v>0.3908679392475828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.221224434882649</v>
+        <v>0.2212244348826452</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2666860359054778</v>
+        <v>0.2112954597530977</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2785671179674448</v>
+        <v>0.2785671179674408</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3318245518624809</v>
+        <v>0.2764339757101004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2378399756409682</v>
+        <v>0.1824493994885873</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3432571080591041</v>
+        <v>0.3986476842114807</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2396707152781695</v>
+        <v>0.2396707152781656</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2577968790824813</v>
+        <v>0.2577968790824821</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2823146321390212</v>
+        <v>0.2196292584167587</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2645623511897672</v>
+        <v>0.2645623511897665</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09279430021315405</v>
+        <v>0.03740372406077441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.303880401596806</v>
+        <v>0.2484898254444264</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1977213692630161</v>
+        <v>0.2531119454153923</v>
       </c>
       <c r="U6" t="n">
-        <v>0.420550351773975</v>
+        <v>0.3651597756215965</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2080971954479253</v>
+        <v>0.2634877716002975</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5391152033869933</v>
+        <v>0.5391152033869951</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3443395403635282</v>
+        <v>0.3443395403635185</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2523559053279198</v>
+        <v>0.2523559053279154</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2167414293454824</v>
+        <v>0.2721320054978596</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3527938228751569</v>
+        <v>0.4081843990275303</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3079767053814841</v>
+        <v>0.3079767053814838</v>
       </c>
     </row>
     <row r="7">
@@ -5329,82 +5329,82 @@
         <v>0.2743720182544646</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2582501720392039</v>
+        <v>0.258250172039204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3340212477238644</v>
+        <v>0.3340212477238647</v>
       </c>
       <c r="E7" t="n">
-        <v>0.235249609534968</v>
+        <v>0.2352496095349678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2327738034163462</v>
+        <v>0.2327738034163459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3986472764835984</v>
+        <v>0.3986472764835982</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2843943482710403</v>
+        <v>0.2843943482710404</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2744653731414933</v>
+        <v>0.274465373141493</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3417370313558366</v>
+        <v>0.3417370313558362</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3396038890984955</v>
+        <v>0.3396038890984953</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2456193128769827</v>
+        <v>0.2456193128769826</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4064270214474953</v>
+        <v>0.4064270214474954</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3024360816575548</v>
+        <v>0.3024360816575549</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2599418799399627</v>
+        <v>0.2599418799399617</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2844779111811311</v>
+        <v>0.2844779111811321</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2723416884257824</v>
+        <v>0.2723416884257823</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1005736374491702</v>
+        <v>0.1005736374491694</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3116597388328214</v>
+        <v>0.3116597388328215</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2608912826514073</v>
+        <v>0.2608912826514072</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4270502632990505</v>
+        <v>0.4270502632990507</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2712671088363123</v>
+        <v>0.2712671088363125</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5980141759108309</v>
+        <v>0.5980141759108318</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4075094537519143</v>
+        <v>0.4075094537519139</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3135134308606328</v>
+        <v>0.3135134308606334</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2799113427338747</v>
+        <v>0.2799113427338755</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4159637362635458</v>
+        <v>0.4159637362635457</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3703406649297942</v>
+        <v>0.370340664929794</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3004470179690127</v>
+        <v>0.3004470179690129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3681350878246937</v>
+        <v>0.368135087824694</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4439061635093564</v>
+        <v>0.4439061635093549</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3451345253204576</v>
+        <v>0.3005082172659757</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2719054085377451</v>
+        <v>0.2719054085377459</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5085321922690889</v>
+        <v>0.5259107243299658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3942792640565299</v>
+        <v>0.3942792640565304</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3843502889269842</v>
+        <v>0.3843502889269832</v>
       </c>
       <c r="J8" t="n">
         <v>0.4516219471413262</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4494888048839867</v>
+        <v>0.4494888048839853</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3555042286624731</v>
+        <v>0.3555042286624732</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5163119372329855</v>
+        <v>0.5163119372328588</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3473542913727469</v>
+        <v>0.3473542913727463</v>
       </c>
       <c r="O8" t="n">
-        <v>0.323070901424768</v>
+        <v>0.3230709014247683</v>
       </c>
       <c r="P8" t="n">
-        <v>0.343230629283662</v>
+        <v>0.3432306292836615</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2819461267858538</v>
+        <v>0.2819461267858536</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2104585532346585</v>
+        <v>0.2104585532346594</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4215446546183126</v>
+        <v>0.4215446546183119</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3707761984368985</v>
+        <v>0.3707761984368976</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4859713944266748</v>
+        <v>0.4965935536064311</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3811520246218046</v>
+        <v>0.3574573833985913</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7079155626643963</v>
+        <v>0.7079155626643955</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4247952374026245</v>
+        <v>0.4247952374026246</v>
       </c>
       <c r="Y8" t="n">
         <v>0.50550625188734</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3897962585193673</v>
+        <v>0.3044295302359144</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5258486520490365</v>
+        <v>0.5258486520490355</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5677720460469539</v>
+        <v>0.5677720460469533</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4441226609695468</v>
+        <v>0.4441226609695469</v>
       </c>
       <c r="C9" t="n">
-        <v>0.504213607549396</v>
+        <v>0.5042136075493966</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5799846832340573</v>
+        <v>0.5799846832340575</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4812130450451593</v>
+        <v>0.4636234431612072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4787372389265387</v>
+        <v>0.3030459513830403</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6446107119937902</v>
+        <v>0.6446107117686759</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5303577837812329</v>
+        <v>0.5303577837812331</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5204288086516848</v>
+        <v>0.5204288086516851</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5877004668660283</v>
+        <v>0.5877004668660277</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5855673246086878</v>
+        <v>0.5855673246086875</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4915827483871745</v>
+        <v>0.4915827483871755</v>
       </c>
       <c r="M9" t="n">
-        <v>0.652390456957687</v>
+        <v>0.6523904569576874</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5483995171677458</v>
+        <v>0.5483995171677467</v>
       </c>
       <c r="O9" t="n">
-        <v>0.531519531777505</v>
+        <v>0.5315195317775053</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5615484879618863</v>
+        <v>0.5615484879618856</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5183051237108605</v>
+        <v>0.5183051237108601</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3465370729593624</v>
+        <v>0.3465370729593622</v>
       </c>
       <c r="S9" t="n">
-        <v>0.557623174343015</v>
+        <v>0.557623174343014</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5068547181615999</v>
+        <v>0.5068547181615995</v>
       </c>
       <c r="U9" t="n">
         <v>0.6742931245201842</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5172305443465052</v>
+        <v>0.6051784130581871</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8439776114210233</v>
+        <v>0.8439776114210239</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6534728892621068</v>
+        <v>0.6534728892621066</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5594768663708256</v>
+        <v>0.5594768663708255</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5258747782440678</v>
+        <v>0.4799252412051838</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6619271717737376</v>
+        <v>0.6619271717737382</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.616304100439986</v>
+        <v>0.6163041004399868</v>
       </c>
     </row>
   </sheetData>
@@ -5746,25 +5746,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.585986685034264</v>
+        <v>2.585986685034265</v>
       </c>
       <c r="C2" t="n">
-        <v>2.622947155455639</v>
+        <v>2.62294715545564</v>
       </c>
       <c r="D2" t="n">
-        <v>2.597743323193722</v>
+        <v>2.597743323193721</v>
       </c>
       <c r="E2" t="n">
-        <v>2.57904944886457</v>
+        <v>2.579049448864571</v>
       </c>
       <c r="F2" t="n">
         <v>2.581660610243694</v>
       </c>
       <c r="G2" t="n">
-        <v>2.60388911242635</v>
+        <v>2.603889112426349</v>
       </c>
       <c r="H2" t="n">
-        <v>2.595600853448176</v>
+        <v>2.595600853448177</v>
       </c>
       <c r="I2" t="n">
         <v>2.592084471869994</v>
@@ -5776,10 +5776,10 @@
         <v>2.592568568434787</v>
       </c>
       <c r="L2" t="n">
-        <v>2.578178095384616</v>
+        <v>2.578178095384615</v>
       </c>
       <c r="M2" t="n">
-        <v>2.593766425735275</v>
+        <v>2.593766425735276</v>
       </c>
       <c r="N2" t="n">
         <v>2.600996827198443</v>
@@ -5788,7 +5788,7 @@
         <v>2.831613109433075</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58593947012609</v>
+        <v>2.585939470126089</v>
       </c>
       <c r="Q2" t="n">
         <v>2.595601890850383</v>
@@ -5797,7 +5797,7 @@
         <v>2.562988558611878</v>
       </c>
       <c r="S2" t="n">
-        <v>2.591046420410601</v>
+        <v>2.591046420410602</v>
       </c>
       <c r="T2" t="n">
         <v>2.589319986879846</v>
@@ -5809,22 +5809,22 @@
         <v>2.598109113882605</v>
       </c>
       <c r="W2" t="n">
-        <v>2.967294508555577</v>
+        <v>2.967294508555575</v>
       </c>
       <c r="X2" t="n">
-        <v>2.630547523110113</v>
+        <v>2.630547523110114</v>
       </c>
       <c r="Y2" t="n">
         <v>2.606173869049691</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.738406615462419</v>
+        <v>2.738406615462418</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.621074657912431</v>
+        <v>2.62107465791243</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.594815921131369</v>
+        <v>2.59481592113137</v>
       </c>
     </row>
     <row r="3">
@@ -5843,7 +5843,7 @@
         <v>1.699221837906704</v>
       </c>
       <c r="E3" t="n">
-        <v>1.565901089325629</v>
+        <v>1.565901089325628</v>
       </c>
       <c r="F3" t="n">
         <v>1.5844340270498</v>
@@ -5852,7 +5852,7 @@
         <v>1.742520016278084</v>
       </c>
       <c r="H3" t="n">
-        <v>1.683974426584242</v>
+        <v>1.683974426584241</v>
       </c>
       <c r="I3" t="n">
         <v>1.658832342830574</v>
@@ -5861,10 +5861,10 @@
         <v>1.697489544291927</v>
       </c>
       <c r="K3" t="n">
-        <v>1.662409473315778</v>
+        <v>1.662409473315777</v>
       </c>
       <c r="L3" t="n">
-        <v>1.561009042069595</v>
+        <v>1.561009042069594</v>
       </c>
       <c r="M3" t="n">
         <v>1.672775056938129</v>
@@ -5873,37 +5873,37 @@
         <v>1.72238406540933</v>
       </c>
       <c r="O3" t="n">
-        <v>2.067496384552573</v>
+        <v>2.067496384552572</v>
       </c>
       <c r="P3" t="n">
-        <v>1.615279715604162</v>
+        <v>1.615279715604163</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.683934795652452</v>
+        <v>1.683934795652451</v>
       </c>
       <c r="R3" t="n">
-        <v>1.450609369958318</v>
+        <v>1.450609369958317</v>
       </c>
       <c r="S3" t="n">
-        <v>1.651700697292291</v>
+        <v>1.65170069729229</v>
       </c>
       <c r="T3" t="n">
         <v>1.639202914451991</v>
       </c>
       <c r="U3" t="n">
-        <v>2.316297383635216</v>
+        <v>2.316297383635215</v>
       </c>
       <c r="V3" t="n">
-        <v>1.701698180259373</v>
+        <v>1.701698180259372</v>
       </c>
       <c r="W3" t="n">
-        <v>2.384339204545054</v>
+        <v>2.384339204545052</v>
       </c>
       <c r="X3" t="n">
         <v>1.93287324831922</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.759413294044331</v>
+        <v>1.75941329404433</v>
       </c>
       <c r="Z3" t="n">
         <v>1.920930273692842</v>
@@ -5912,7 +5912,7 @@
         <v>1.86575666120683</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.678143870901126</v>
+        <v>1.678143870901127</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03348025628444039</v>
+        <v>0.0334802562844414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1334361462866597</v>
+        <v>0.1334361462866611</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1662768926162709</v>
+        <v>0.1662768926162706</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04487901753855024</v>
+        <v>-0.04487901753854846</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01538474856779432</v>
+        <v>-0.01538474856779595</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2356964092015329</v>
+        <v>0.2356964092015349</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1420767112555373</v>
+        <v>0.1420767112555365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1023575637145597</v>
+        <v>0.1023575637145599</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1634664327222929</v>
+        <v>0.1634664327222927</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1078256571093003</v>
+        <v>0.1078256571093015</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05472135593703456</v>
+        <v>-0.05472135593703657</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1247396873481708</v>
+        <v>0.1247396873481736</v>
       </c>
       <c r="N4" t="n">
         <v>0.2030267170353766</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1296107415245825</v>
+        <v>0.1296107415245821</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03294694217666345</v>
+        <v>0.03294694217666175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1420884291907079</v>
+        <v>0.1420884291907094</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2262941613172772</v>
+        <v>-0.226294161317276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09063229495344662</v>
+        <v>0.09063229495344928</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07113143402492453</v>
+        <v>0.07113143402492852</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1525353900753485</v>
+        <v>0.152535390075348</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1685541057280161</v>
+        <v>0.1685541057280164</v>
       </c>
       <c r="W4" t="n">
-        <v>0.321621650460227</v>
+        <v>0.3216216504602268</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5368154213494408</v>
+        <v>0.5368154213494424</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2603492726693412</v>
+        <v>0.2603492726693409</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1447604992477523</v>
+        <v>0.1447604992477549</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4298150512083229</v>
+        <v>0.4298150512083269</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1328167360687734</v>
+        <v>0.1328167360687767</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.471832465873531</v>
+        <v>-1.471832465873534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1739374400041592</v>
+        <v>0.1739374400041541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7397067988059195</v>
+        <v>0.7397067988059198</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.943959030870325</v>
+        <v>-2.943959030870335</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.475707894900349</v>
+        <v>-2.475707894900345</v>
       </c>
       <c r="G5" t="n">
-        <v>1.674902497488921</v>
+        <v>1.67490249748892</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3342304978824814</v>
+        <v>0.3342304978824878</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3918438316835241</v>
+        <v>-0.3918438316835179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6261912206904965</v>
+        <v>0.6261912206904952</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2318515920889106</v>
+        <v>-0.2318515920888979</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.430432701632699</v>
+        <v>-2.430432701632698</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05589722513609857</v>
+        <v>0.05589722513610221</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5326594207851781</v>
+        <v>0.5326594207851775</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1113772443533308</v>
+        <v>0.1113772443533343</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.461656484849132</v>
+        <v>-1.461656484849128</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3100630910448435</v>
+        <v>0.3100630910448484</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.496865163834959</v>
+        <v>-6.496865163834977</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4556869580532832</v>
+        <v>-0.4556869580532852</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8918723020434058</v>
+        <v>-0.8918723020434006</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4833226074579541</v>
+        <v>0.4833226074579579</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7413194533317606</v>
+        <v>0.7413194533317666</v>
       </c>
       <c r="W5" t="n">
-        <v>3.307051927592045</v>
+        <v>3.307051927592048</v>
       </c>
       <c r="X5" t="n">
-        <v>7.047757396519945</v>
+        <v>7.047757396519956</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.435471728761174</v>
+        <v>2.435471728761177</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3429548096015235</v>
+        <v>0.3429548096015247</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.410102820488407</v>
+        <v>5.410102820488392</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1629418082447419</v>
+        <v>0.1629418082447426</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04016403430892068</v>
+        <v>0.04016403430892251</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1841981897804441</v>
+        <v>0.1401199243111412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.172960670640752</v>
+        <v>0.1729606706407509</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005883025955233857</v>
+        <v>0.005883025955235294</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03537729492599039</v>
+        <v>0.03537729492599283</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2864584526953169</v>
+        <v>0.2423801872260141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.192838754749321</v>
+        <v>0.1487604892800198</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1090413417390406</v>
+        <v>0.1090413417390447</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2142284762160774</v>
+        <v>0.1701502107467738</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1145094351337801</v>
+        <v>0.1145094351337822</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.003959312443250193</v>
+        <v>-0.003959312443249235</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1314234653726508</v>
+        <v>0.1755017308419561</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2107322438611907</v>
+        <v>0.2107322438612071</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1373162683503971</v>
+        <v>0.1373162683503988</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08817576478445327</v>
+        <v>0.03885880261955348</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1928504726844928</v>
+        <v>0.1487722072151909</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1755321178234926</v>
+        <v>-0.1755321178234914</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1413943384472309</v>
+        <v>0.09731607297793068</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1218934775187089</v>
+        <v>0.1218934775187095</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1603736817326356</v>
+        <v>0.1603736817326354</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1752378837524975</v>
+        <v>0.2193161492218009</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3318816062591964</v>
+        <v>0.3318816062591937</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5434991993739219</v>
+        <v>0.5434991993739231</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2704894324669807</v>
+        <v>0.2704894324669773</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1955225427415363</v>
+        <v>0.1955225427415387</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4364988292328033</v>
+        <v>0.480577094702107</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1404771969788436</v>
+        <v>0.1404771969788438</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09521427838683932</v>
+        <v>0.09521427838684035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195170168389058</v>
+        <v>0.1951701683890551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2280109147186692</v>
+        <v>0.2280109147186738</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0168550045638482</v>
+        <v>0.01685500456384914</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04634927353460438</v>
+        <v>0.04634927353460731</v>
       </c>
       <c r="G7" t="n">
-        <v>0.297430431303931</v>
+        <v>0.2974304313039329</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2038107333579351</v>
+        <v>0.2038107333579354</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1640915858169579</v>
+        <v>0.1640915858169599</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2252004548246915</v>
+        <v>0.2252004548246927</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1695596792116983</v>
+        <v>0.169559679211699</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007012666165364639</v>
+        <v>0.007012666165362516</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1864737094505687</v>
+        <v>0.1864737094505694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2647607391377759</v>
+        <v>0.2647607391377738</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1910120602153694</v>
+        <v>0.1910120602153721</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09434826086744888</v>
+        <v>0.09434826086744834</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2038224512931069</v>
+        <v>0.2038224512931077</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1645601392148792</v>
+        <v>-0.1645601392148785</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1523663170558446</v>
+        <v>0.1523663170558462</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1328654561273227</v>
+        <v>0.132865456127322</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2135339347660389</v>
+        <v>0.2135339347660396</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2302881278304152</v>
+        <v>0.2302881278304149</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3833556725626263</v>
+        <v>0.3833556725626247</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5985494434518399</v>
+        <v>0.5985494434518411</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3232378084045452</v>
+        <v>0.3232378084045432</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2064945213501503</v>
+        <v>0.2064945213501502</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4915490733107206</v>
+        <v>0.4915490733107211</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1945507581711727</v>
+        <v>0.1945507581711753</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1107821511053511</v>
+        <v>0.1107821511053552</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2749132138086726</v>
+        <v>0.2749132138086718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3077539601382849</v>
+        <v>0.3077539601382865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09659804998346364</v>
+        <v>0.06242666357886864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07191488812278848</v>
+        <v>0.07191488812278761</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3771734767235465</v>
+        <v>0.3904806168406297</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2835537787775502</v>
+        <v>0.2835537787775515</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2438346312365729</v>
+        <v>0.2438346312365753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3049435002443067</v>
+        <v>0.3049435002443068</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2493027246313143</v>
+        <v>0.2493027246313145</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08675571158497877</v>
+        <v>0.0867557115849813</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2662167548701838</v>
+        <v>0.2662167548698696</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2947572894280261</v>
+        <v>0.294757289428024</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2350120826943169</v>
+        <v>0.2350120826943205</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1349972475898222</v>
+        <v>0.134997247589821</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2067784378623608</v>
+        <v>0.2067784378623628</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.08481709379526371</v>
+        <v>-0.08481709379526121</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2321093624754597</v>
+        <v>0.2321093624754611</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2126085015469381</v>
+        <v>0.2126085015469386</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2545436876623249</v>
+        <v>0.2626370662542959</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3100311732500301</v>
+        <v>0.2911599999616068</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4631113301916772</v>
+        <v>0.4631113301916776</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6073872120860192</v>
+        <v>0.6073872120860224</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4647241815126326</v>
+        <v>0.4647241815126316</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.286237566769765</v>
+        <v>0.2208703072921543</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5712921187303357</v>
+        <v>0.5712921187303368</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3413301376709104</v>
+        <v>0.3413301376709135</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22116066704698</v>
+        <v>0.2211606670469803</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3795747564326499</v>
+        <v>0.3795747564326498</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4124155027622613</v>
+        <v>0.412415502762261</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2012595926074404</v>
+        <v>0.18776768768466</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2307538615781966</v>
+        <v>0.09599174188887979</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4818350193475237</v>
+        <v>0.4818350311106882</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3882153214015277</v>
+        <v>0.3882153214015314</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3484961738605504</v>
+        <v>0.3484961738605543</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4096050428682844</v>
+        <v>0.4096050428682836</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3539642672552908</v>
+        <v>0.3539642672552917</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1914172542089568</v>
+        <v>0.1914172542089548</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3708782974941606</v>
+        <v>0.3708782974941649</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4491653271813675</v>
+        <v>0.4491653271813712</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3951223380632284</v>
+        <v>0.39512233806323</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3026718283129529</v>
+        <v>0.302671828312954</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3882270510998617</v>
+        <v>0.3882270510998623</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01984444882871308</v>
+        <v>0.01984444882871694</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3367709050994364</v>
+        <v>0.3367709050994387</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3172700441709147</v>
+        <v>0.3172700441709184</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3998285138541452</v>
+        <v>0.3998285138541501</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4146927158740073</v>
+        <v>0.4821522360742729</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5677602606062172</v>
+        <v>0.5677602606062154</v>
       </c>
       <c r="X9" t="n">
-        <v>0.782954031495433</v>
+        <v>0.7829540314954357</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5076423964481377</v>
+        <v>0.5076423964481367</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3908991093937418</v>
+        <v>0.3556540181424536</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6759536613543127</v>
+        <v>0.6759536613543173</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3789553462147652</v>
+        <v>0.378955346214766</v>
       </c>
     </row>
   </sheetData>
@@ -6609,13 +6609,13 @@
         <v>2.570525186073963</v>
       </c>
       <c r="C2" t="n">
-        <v>2.608080148830592</v>
+        <v>2.608080148830591</v>
       </c>
       <c r="D2" t="n">
         <v>2.584687119927795</v>
       </c>
       <c r="E2" t="n">
-        <v>2.568847299024839</v>
+        <v>2.56884729902484</v>
       </c>
       <c r="F2" t="n">
         <v>2.575898954167184</v>
@@ -6633,7 +6633,7 @@
         <v>2.587984265709649</v>
       </c>
       <c r="K2" t="n">
-        <v>2.585988444838983</v>
+        <v>2.585988444838984</v>
       </c>
       <c r="L2" t="n">
         <v>2.566575440529754</v>
@@ -6651,19 +6651,19 @@
         <v>2.575527743446744</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.588147949230974</v>
+        <v>2.588147949230975</v>
       </c>
       <c r="R2" t="n">
-        <v>2.556204761767544</v>
+        <v>2.556204761767543</v>
       </c>
       <c r="S2" t="n">
         <v>2.57934304441559</v>
       </c>
       <c r="T2" t="n">
-        <v>2.583423379344824</v>
+        <v>2.583423379344823</v>
       </c>
       <c r="U2" t="n">
-        <v>2.959586250575723</v>
+        <v>2.959586250575721</v>
       </c>
       <c r="V2" t="n">
         <v>2.591616045965091</v>
@@ -6672,13 +6672,13 @@
         <v>2.948304615956509</v>
       </c>
       <c r="X2" t="n">
-        <v>2.633876757721439</v>
+        <v>2.63387675772144</v>
       </c>
       <c r="Y2" t="n">
         <v>2.595031773897859</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.717535869177692</v>
+        <v>2.717535869177693</v>
       </c>
       <c r="AA2" t="n">
         <v>2.617333395931918</v>
@@ -6697,7 +6697,7 @@
         <v>1.555766020266634</v>
       </c>
       <c r="C3" t="n">
-        <v>1.67809918702598</v>
+        <v>1.678099187025979</v>
       </c>
       <c r="D3" t="n">
         <v>1.656318190605468</v>
@@ -6706,7 +6706,7 @@
         <v>1.543792191673909</v>
       </c>
       <c r="F3" t="n">
-        <v>1.593445128643631</v>
+        <v>1.59344512864363</v>
       </c>
       <c r="G3" t="n">
         <v>1.721927146578597</v>
@@ -6730,7 +6730,7 @@
         <v>1.678505015422191</v>
       </c>
       <c r="N3" t="n">
-        <v>1.725679056940064</v>
+        <v>1.725679056940065</v>
       </c>
       <c r="O3" t="n">
         <v>1.999406473068628</v>
@@ -6742,13 +6742,13 @@
         <v>1.680986147402294</v>
       </c>
       <c r="R3" t="n">
-        <v>1.452299238598176</v>
+        <v>1.452299238598175</v>
       </c>
       <c r="S3" t="n">
-        <v>1.618495831594272</v>
+        <v>1.618495831594271</v>
       </c>
       <c r="T3" t="n">
-        <v>1.647277531378012</v>
+        <v>1.647277531378011</v>
       </c>
       <c r="U3" t="n">
         <v>2.298364434517924</v>
@@ -6772,7 +6772,7 @@
         <v>1.889354547651245</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.680408186933574</v>
+        <v>1.680408186933573</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06237793403485256</v>
+        <v>-0.06237793403485289</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06294073326863495</v>
+        <v>0.06294073326863554</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09758762365562382</v>
+        <v>0.09758762365562318</v>
       </c>
       <c r="E4" t="n">
         <v>-0.08133044012085636</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.001678751366477993</v>
+        <v>-0.001678751366477368</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2019613803541692</v>
+        <v>0.2019613803541699</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1504652907005211</v>
+        <v>0.1504652907005213</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1257462963005492</v>
+        <v>0.1257462963005491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1345772693028363</v>
+        <v>0.1345772693028355</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1122866871665267</v>
+        <v>0.1122866871665264</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.106992126929404</v>
+        <v>-0.1069921269294046</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1330365265725814</v>
+        <v>0.1330365265725812</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2074208916527008</v>
+        <v>0.2074208916527009</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04848129660506383</v>
+        <v>0.04848129660506421</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005871747219226097</v>
+        <v>-0.005871747219226016</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1366792826951507</v>
+        <v>0.1366792826951509</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2241337142965215</v>
+        <v>-0.2241337142965212</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03722383234906359</v>
+        <v>0.03722383234906356</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08331309242156443</v>
+        <v>0.08331309242156462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1446634117872869</v>
+        <v>0.1446634117872867</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1741659172170799</v>
+        <v>0.1741659172170797</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2879593593302565</v>
+        <v>0.2879593593302569</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6532072108861828</v>
+        <v>0.6532072108861831</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2135870882866674</v>
+        <v>0.2135870882866687</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06991769811235435</v>
+        <v>0.06991769811235519</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4663423291511152</v>
+        <v>0.4663423291511155</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1354946815007037</v>
+        <v>0.1354946815007038</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.860131329686383</v>
+        <v>-2.860131329686386</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8990765961952483</v>
+        <v>-0.8990765961952492</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3015232420185103</v>
+        <v>-0.3015232420185102</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.194645883985957</v>
+        <v>-3.194645883985961</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.135716059383649</v>
+        <v>-2.13571605938365</v>
       </c>
       <c r="G5" t="n">
-        <v>1.368444294418043</v>
+        <v>1.368444294418042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6616670032867512</v>
+        <v>0.66166700328675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1918925751872741</v>
+        <v>0.191892575187271</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3395110527389544</v>
+        <v>0.3395110527389546</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03175617690378307</v>
+        <v>-0.03175617690378413</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.296507845174467</v>
+        <v>-3.296507845174462</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3260150104960284</v>
+        <v>0.326015010496028</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5619336037453344</v>
+        <v>0.5619336037453327</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.015026240207874</v>
+        <v>-1.015026240207875</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.882477110691442</v>
+        <v>-1.882477110691439</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3732140150640774</v>
+        <v>0.3732140150640771</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.374633922487022</v>
+        <v>-6.374633922487035</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.204063418803358</v>
+        <v>-1.204063418803354</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5650195405942551</v>
+        <v>-0.5650195405942569</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5000242846166741</v>
+        <v>0.5000242846166736</v>
       </c>
       <c r="V5" t="n">
-        <v>0.97895859023108</v>
+        <v>0.9789585902310796</v>
       </c>
       <c r="W5" t="n">
-        <v>2.947353652692534</v>
+        <v>2.947353652692523</v>
       </c>
       <c r="X5" t="n">
-        <v>9.049064582461551</v>
+        <v>9.049064582461554</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.779970204523149</v>
+        <v>1.779970204523151</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.656110481064436</v>
+        <v>-0.6561104810644376</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.24033831459505</v>
+        <v>6.240338314595039</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3774189206143224</v>
+        <v>0.3774189206143226</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01816603417322085</v>
+        <v>-0.01816603417322077</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1071526331302665</v>
+        <v>0.1071526331302664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.141799523517256</v>
+        <v>0.1417995235172558</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0371185402592245</v>
+        <v>-0.03711854025922482</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003252152136462627</v>
+        <v>0.04253314849515394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2068922838571103</v>
+        <v>0.2461732802158018</v>
       </c>
       <c r="H6" t="n">
-        <v>0.155396194203462</v>
+        <v>0.1553961942034618</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1699581961621811</v>
+        <v>0.1306771998034899</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1787891691644684</v>
+        <v>0.139508172805777</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1172175906694678</v>
+        <v>0.1564985870281586</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06278022706777239</v>
+        <v>-0.06278022706777314</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1772484264342132</v>
+        <v>0.1772484264342138</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2135013502726447</v>
+        <v>0.2135013502726453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05456175522501076</v>
+        <v>0.09700404134668</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04264121131093498</v>
+        <v>0.04264121131093485</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1808911825567825</v>
+        <v>0.1808911825567829</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1799218144348896</v>
+        <v>-0.2192028107935813</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0421547358520043</v>
+        <v>0.04215473585200391</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1275249922831963</v>
+        <v>0.1275249922831964</v>
       </c>
       <c r="U6" t="n">
-        <v>0.189723472385673</v>
+        <v>0.1897234723856727</v>
       </c>
       <c r="V6" t="n">
         <v>0.1790968207200208</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3365050883789777</v>
+        <v>0.3365050883789771</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6974191107478152</v>
+        <v>0.6581381143891235</v>
       </c>
       <c r="Y6" t="n">
         <v>0.2217123869439771</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1141295979739863</v>
+        <v>0.07484860161529489</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5105542290127468</v>
+        <v>0.4712732326540556</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1416167699939161</v>
+        <v>0.1416167699939163</v>
       </c>
     </row>
     <row r="7">
@@ -7046,58 +7046,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.003862220282145862</v>
+        <v>-0.003862220282146001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1214564470213418</v>
+        <v>0.1214564470213416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1561033374083303</v>
+        <v>0.15610333740833</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02281472636814968</v>
+        <v>-0.02281472636814997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05683696238622825</v>
+        <v>0.05683696238622793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2604770941068759</v>
+        <v>0.2604770941068764</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2089810044532278</v>
+        <v>0.2089810044532275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.184262010053256</v>
+        <v>0.1842620100532556</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1930929830555432</v>
+        <v>0.193092983055543</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1708024009192335</v>
+        <v>0.1708024009192334</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04847641317669762</v>
+        <v>-0.04847641317669782</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1915522403252881</v>
+        <v>0.1915522403252879</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2659366054054079</v>
+        <v>0.2659366054054073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1066645118171911</v>
+        <v>0.106664511817191</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05231146799290158</v>
+        <v>0.05231146799290166</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1951949964478576</v>
+        <v>0.1951949964478574</v>
       </c>
       <c r="R7" t="n">
         <v>-0.1656180005438148</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09573954610177002</v>
+        <v>0.09573954610176993</v>
       </c>
       <c r="T7" t="n">
         <v>0.1418288061742708</v>
@@ -7106,25 +7106,25 @@
         <v>0.2017576112835549</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2326816309697864</v>
+        <v>0.2326816309697867</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3464750730829638</v>
+        <v>0.3464750730829634</v>
       </c>
       <c r="X7" t="n">
         <v>0.7117229246388894</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2729509627761281</v>
+        <v>0.2729509627761283</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1284334118650614</v>
+        <v>0.1284334118650611</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.524858042903822</v>
+        <v>0.5248580429038212</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1940103952534102</v>
+        <v>0.19401039525341</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008293034529091636</v>
+        <v>0.008293034529091858</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1917376256384759</v>
+        <v>0.1917376256384751</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2263845160254644</v>
+        <v>0.2263845160254638</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04746645224898328</v>
+        <v>0.01651611243227343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07804755679203626</v>
+        <v>0.07804755679203543</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3307582727240099</v>
+        <v>0.3428110616782297</v>
       </c>
       <c r="H8" t="n">
         <v>0.2792621830703622</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2545431886703903</v>
+        <v>0.2545431886703893</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2633741616726774</v>
+        <v>0.2633741616726762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2410835795363676</v>
+        <v>0.2410835795363677</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02180476544043583</v>
+        <v>0.02180476544043639</v>
       </c>
       <c r="M8" t="n">
-        <v>0.261833418942422</v>
+        <v>0.2618334189419945</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2911604688129106</v>
+        <v>0.2911604688129105</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1446030152028002</v>
+        <v>0.1446030152027997</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08721480931854365</v>
+        <v>0.08721480931854286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1959271805754083</v>
+        <v>0.1959271805754084</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.09533682192668133</v>
+        <v>-0.09533682192668128</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1660207247189041</v>
+        <v>0.1660207247189038</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2121099847914048</v>
+        <v>0.2121099847914053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2371311325664541</v>
+        <v>0.244436713076171</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3029628095869207</v>
+        <v>0.2854202676952761</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4167676750932303</v>
+        <v>0.4167676750932293</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7177824651712474</v>
+        <v>0.7177824651712468</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3984571981451143</v>
+        <v>0.3984571981451142</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1987145904821948</v>
+        <v>0.1395089478003858</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5951392215209564</v>
+        <v>0.5951392215209549</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3250089616826453</v>
+        <v>0.3250089616826451</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1051992444234145</v>
+        <v>0.1051992444234144</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2826173476659739</v>
+        <v>0.2826173476659736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3172642380529628</v>
+        <v>0.3172642380529624</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1383461742764819</v>
+        <v>0.1263218242628249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2179978630308601</v>
+        <v>0.0978944654716469</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4216379947515078</v>
+        <v>0.4216379782296976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3701419050978605</v>
+        <v>0.3701419050978604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3454229106978886</v>
+        <v>0.3454229106978887</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3542538837001756</v>
+        <v>0.354253883700175</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3319633015638658</v>
+        <v>0.3319633015638664</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1126844874679351</v>
+        <v>0.1126844874679346</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3527131409699206</v>
+        <v>0.3527131409699209</v>
       </c>
       <c r="N9" t="n">
-        <v>0.42709750605004</v>
+        <v>0.4270975060500397</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2854235738571008</v>
+        <v>0.2854235738571006</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2348255190680307</v>
+        <v>0.2348255190680304</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3563558805706795</v>
+        <v>0.3563558805706799</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.004457099899182665</v>
+        <v>-0.004457099899183442</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2569004467464024</v>
+        <v>0.2569004467464021</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3029897068189041</v>
+        <v>0.3029897068189035</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3651881869213806</v>
+        <v>0.3651881869213803</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3938425316144188</v>
+        <v>0.4539641470349633</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5076359737275966</v>
+        <v>0.5076359737275958</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8728838252835223</v>
+        <v>0.8728838252835224</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.434111863420761</v>
+        <v>0.4341118634207612</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2895943125096932</v>
+        <v>0.2581829789404072</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6860189435484539</v>
+        <v>0.6860189435484534</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3551712958980425</v>
+        <v>0.3551712958980424</v>
       </c>
     </row>
   </sheetData>
@@ -7469,19 +7469,19 @@
         <v>2.663956568447261</v>
       </c>
       <c r="C2" t="n">
-        <v>2.681823080872271</v>
+        <v>2.681823080872272</v>
       </c>
       <c r="D2" t="n">
-        <v>2.665371637540476</v>
+        <v>2.665371637540475</v>
       </c>
       <c r="E2" t="n">
         <v>2.655046903066025</v>
       </c>
       <c r="F2" t="n">
-        <v>2.654117472032273</v>
+        <v>2.654117472032272</v>
       </c>
       <c r="G2" t="n">
-        <v>2.697039747373097</v>
+        <v>2.697039747373096</v>
       </c>
       <c r="H2" t="n">
         <v>2.669780653794422</v>
@@ -7490,7 +7490,7 @@
         <v>2.65559739983621</v>
       </c>
       <c r="J2" t="n">
-        <v>2.677924632695115</v>
+        <v>2.677924632695114</v>
       </c>
       <c r="K2" t="n">
         <v>2.663661044184626</v>
@@ -7499,13 +7499,13 @@
         <v>2.678088052499235</v>
       </c>
       <c r="M2" t="n">
-        <v>2.697181116308182</v>
+        <v>2.697181116308181</v>
       </c>
       <c r="N2" t="n">
-        <v>2.668793288751869</v>
+        <v>2.668793288751868</v>
       </c>
       <c r="O2" t="n">
-        <v>2.936110343848216</v>
+        <v>2.936110343848215</v>
       </c>
       <c r="P2" t="n">
         <v>2.671398660085467</v>
@@ -7517,7 +7517,7 @@
         <v>2.649854331991783</v>
       </c>
       <c r="S2" t="n">
-        <v>2.670505434534135</v>
+        <v>2.670505434534134</v>
       </c>
       <c r="T2" t="n">
         <v>2.658150428523766</v>
@@ -7554,13 +7554,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.824416726313598</v>
+        <v>1.824416726313597</v>
       </c>
       <c r="C3" t="n">
         <v>1.793777653122086</v>
       </c>
       <c r="D3" t="n">
-        <v>1.835338012851765</v>
+        <v>1.835338012851764</v>
       </c>
       <c r="E3" t="n">
         <v>1.761293219131518</v>
@@ -7569,28 +7569,28 @@
         <v>1.754770406503222</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05922770475926</v>
+        <v>2.059227704759261</v>
       </c>
       <c r="H3" t="n">
         <v>1.867219821710195</v>
       </c>
       <c r="I3" t="n">
-        <v>1.765375778980639</v>
+        <v>1.765375778980638</v>
       </c>
       <c r="J3" t="n">
-        <v>1.923870069285613</v>
+        <v>1.923870069285612</v>
       </c>
       <c r="K3" t="n">
         <v>1.82250794968482</v>
       </c>
       <c r="L3" t="n">
-        <v>1.925316563760455</v>
+        <v>1.925316563760456</v>
       </c>
       <c r="M3" t="n">
         <v>2.062005491788692</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85958153068151</v>
+        <v>1.859581530681509</v>
       </c>
       <c r="O3" t="n">
         <v>2.270898364720112</v>
@@ -7605,7 +7605,7 @@
         <v>1.724262976083226</v>
       </c>
       <c r="S3" t="n">
-        <v>1.870726308972845</v>
+        <v>1.870726308972846</v>
       </c>
       <c r="T3" t="n">
         <v>1.783638673875839</v>
@@ -7620,7 +7620,7 @@
         <v>2.572216141679005</v>
       </c>
       <c r="X3" t="n">
-        <v>1.904127824337324</v>
+        <v>1.904127824337325</v>
       </c>
       <c r="Y3" t="n">
         <v>1.893113776046961</v>
@@ -7632,7 +7632,7 @@
         <v>1.898069417664461</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.005059574832379</v>
+        <v>2.00505957483238</v>
       </c>
     </row>
     <row r="4">
@@ -7645,79 +7645,79 @@
         <v>0.384939537474885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2598331824432769</v>
+        <v>0.259833182443277</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4009233938466664</v>
+        <v>0.4009233938466661</v>
       </c>
       <c r="E4" t="n">
-        <v>0.284300768345243</v>
+        <v>0.2843007683452431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2738024172595966</v>
+        <v>0.273802417259597</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7586292624563749</v>
+        <v>0.7586292624563756</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4507252606826946</v>
+        <v>0.4507252606826952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2905188826054824</v>
+        <v>0.2905188826054829</v>
       </c>
       <c r="J4" t="n">
         <v>0.5422855520531387</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3816014549805196</v>
+        <v>0.3816014549805197</v>
       </c>
       <c r="L4" t="n">
         <v>0.5445611506457594</v>
       </c>
       <c r="M4" t="n">
-        <v>0.760868888601884</v>
+        <v>0.7608688886018851</v>
       </c>
       <c r="N4" t="n">
         <v>0.4395725183166986</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3794876922798551</v>
+        <v>0.3794876922798552</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4690013860596977</v>
+        <v>0.4690013860596976</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3328167991693394</v>
+        <v>0.3328167991693398</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2256482893609754</v>
+        <v>0.2256482893609758</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4589119925533362</v>
+        <v>0.4589119925533383</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3193565160826631</v>
+        <v>0.3193565160826634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5447997091232213</v>
+        <v>0.5447997091232214</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3189906561792668</v>
+        <v>0.318990656179267</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5881342251099181</v>
+        <v>0.5881342251099188</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5097876641359664</v>
+        <v>0.5097876641359671</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4891144296553788</v>
+        <v>0.4891144296553779</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3747849067592385</v>
+        <v>0.3747849067592391</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.500724910250896</v>
+        <v>0.500724910250897</v>
       </c>
       <c r="AB4" t="n">
         <v>0.6672362193772964</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.110519633461475</v>
+        <v>3.110519633461474</v>
       </c>
       <c r="C5" t="n">
         <v>1.029671890462193</v>
       </c>
       <c r="D5" t="n">
-        <v>3.869824533274184</v>
+        <v>3.869824533274174</v>
       </c>
       <c r="E5" t="n">
-        <v>1.466383884758474</v>
+        <v>1.466383884758476</v>
       </c>
       <c r="F5" t="n">
         <v>1.329383045830831</v>
       </c>
       <c r="G5" t="n">
-        <v>9.450253273523206</v>
+        <v>9.450253273523204</v>
       </c>
       <c r="H5" t="n">
-        <v>5.041965246000513</v>
+        <v>5.041965246000505</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66940093498988</v>
+        <v>1.669400934989886</v>
       </c>
       <c r="J5" t="n">
-        <v>5.961251958248529</v>
+        <v>5.961251958248535</v>
       </c>
       <c r="K5" t="n">
-        <v>3.158853488851415</v>
+        <v>3.15885348885141</v>
       </c>
       <c r="L5" t="n">
-        <v>6.152394953331772</v>
+        <v>6.152394953331774</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28210492442114</v>
+        <v>10.28210492442113</v>
       </c>
       <c r="N5" t="n">
-        <v>6.160798365535202</v>
+        <v>6.16079836553521</v>
       </c>
       <c r="O5" t="n">
-        <v>2.946286747408001</v>
+        <v>2.946286747407991</v>
       </c>
       <c r="P5" t="n">
-        <v>4.67259536363959</v>
+        <v>4.672595363639574</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.397783503876789</v>
+        <v>2.397783503876795</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3737368245954646</v>
+        <v>0.3737368245954676</v>
       </c>
       <c r="S5" t="n">
-        <v>4.270037683223855</v>
+        <v>4.270037683223853</v>
       </c>
       <c r="T5" t="n">
-        <v>2.237908363906599</v>
+        <v>2.2379083639066</v>
       </c>
       <c r="U5" t="n">
-        <v>6.269947333144355</v>
+        <v>6.269947333144362</v>
       </c>
       <c r="V5" t="n">
-        <v>1.997511251366768</v>
+        <v>1.997511251366765</v>
       </c>
       <c r="W5" t="n">
         <v>7.246161791912737</v>
       </c>
       <c r="X5" t="n">
-        <v>5.930329136025104</v>
+        <v>5.93032913602512</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.374660138184057</v>
+        <v>5.37466013818405</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.959082309669635</v>
+        <v>2.959082309669633</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.574276152407159</v>
+        <v>5.574276152407164</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.567901602760104</v>
+        <v>9.567901602760097</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4858458113817986</v>
+        <v>0.4858458113817983</v>
       </c>
       <c r="C6" t="n">
-        <v>0.276856027978657</v>
+        <v>0.2768560279786572</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5018296677535798</v>
+        <v>0.5018296677535797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3852070422521566</v>
+        <v>0.3852070422521569</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3747086911665096</v>
+        <v>0.3747086911665102</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7756521079917551</v>
+        <v>0.7756521079917549</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5516315345896086</v>
+        <v>0.5516315345896088</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3075417281408629</v>
+        <v>0.3075417281408632</v>
       </c>
       <c r="J6" t="n">
-        <v>0.643191825960052</v>
+        <v>0.5593083975885187</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3986243005158994</v>
+        <v>0.3986243005159001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5615839961811393</v>
+        <v>0.6454674245526727</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8617751625087966</v>
+        <v>0.8617751625087972</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4572777072534432</v>
+        <v>0.457277707253442</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3971928812165842</v>
+        <v>0.3971928812165987</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5747084068669046</v>
+        <v>0.5747084068669049</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3498396447047203</v>
+        <v>0.4337230730762536</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3265545632678892</v>
+        <v>0.3265545632678896</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5598182664602503</v>
+        <v>0.5598182664602518</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4202627899895766</v>
+        <v>0.3363793616180434</v>
       </c>
       <c r="U6" t="n">
-        <v>0.649627759832756</v>
+        <v>0.6496277598327559</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3360135017146473</v>
+        <v>0.4198969300861806</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6096185518578372</v>
+        <v>0.6096185518578324</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6106939380428801</v>
+        <v>0.5268105096713473</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5122931192213588</v>
+        <v>0.5122931192213571</v>
       </c>
       <c r="Z6" t="n">
         <v>0.3918077522946196</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6016311841578096</v>
+        <v>0.6016311841578101</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6865396801404317</v>
+        <v>0.6865396801404323</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4784847660866973</v>
+        <v>0.4784847660866977</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3533784110550897</v>
+        <v>0.35337841105509</v>
       </c>
       <c r="D7" t="n">
-        <v>0.49446862245848</v>
+        <v>0.4944686224584796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.377845996957056</v>
+        <v>0.3778459969570561</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3673476458714099</v>
+        <v>0.3673476458714101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8521744910681888</v>
+        <v>0.8521744910681892</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5442704892945089</v>
+        <v>0.5442704892945084</v>
       </c>
       <c r="I7" t="n">
         <v>0.3840641112172962</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6358307806649512</v>
+        <v>0.6358307806649515</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4751466835923323</v>
+        <v>0.475146683592333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6381063792575723</v>
+        <v>0.6381063792575727</v>
       </c>
       <c r="M7" t="n">
-        <v>0.854414117213697</v>
+        <v>0.8544141172136975</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5331177469285114</v>
+        <v>0.5331177469285121</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4726745332013786</v>
+        <v>0.472674533201379</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5621882269812207</v>
+        <v>0.5621882269812201</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4263620277811533</v>
+        <v>0.4263620277811527</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3191935179727885</v>
+        <v>0.3191935179727887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5524572211651505</v>
+        <v>0.5524572211651513</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129017446944761</v>
+        <v>0.4129017446944765</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6417718470059232</v>
+        <v>0.6417718470059235</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4125358847910807</v>
+        <v>0.4125358847910808</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6816794537217306</v>
+        <v>0.681679453721731</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6033328927477796</v>
+        <v>0.6033328927477808</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5865814350698129</v>
+        <v>0.5865814350698135</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4683301353710519</v>
+        <v>0.4683301353710521</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5942701388627097</v>
+        <v>0.5942701388627101</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7607814479891095</v>
+        <v>0.7607814479891096</v>
       </c>
     </row>
     <row r="8">
@@ -7994,82 +7994,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5190936696604836</v>
+        <v>0.5190936696604831</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5024732640640587</v>
+        <v>0.5024732640640591</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6435634754674491</v>
+        <v>0.643563475467449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5269408499660249</v>
+        <v>0.4691752820452097</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4248573924540865</v>
+        <v>0.4248573924540861</v>
       </c>
       <c r="G8" t="n">
-        <v>1.001269344077157</v>
+        <v>1.023764612404888</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6933653423034773</v>
+        <v>0.6933653423034771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5331589642262643</v>
+        <v>0.533158964226265</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7849256336739197</v>
+        <v>0.7849256336739204</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6242415366013012</v>
+        <v>0.6242415366013013</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7872012322665415</v>
+        <v>0.7872012322665423</v>
       </c>
       <c r="M8" t="n">
-        <v>1.003508970222666</v>
+        <v>1.003508970222598</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5981178397969928</v>
+        <v>0.5981178397969934</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5611429839811223</v>
+        <v>0.5611429839811226</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6449918656496487</v>
+        <v>0.6449918656496494</v>
       </c>
       <c r="Q8" t="n">
         <v>0.4456509662449719</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4682883709817579</v>
+        <v>0.4682883709817572</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7015520741741187</v>
+        <v>0.7015520741741199</v>
       </c>
       <c r="T8" t="n">
         <v>0.5619965977034449</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7245056477728233</v>
+        <v>0.7383052549905078</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5616307378000484</v>
+        <v>0.5318632324046062</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8307956272347576</v>
+        <v>0.8307956272347583</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6325647839848044</v>
+        <v>0.6325647839848059</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8433604591003558</v>
+        <v>0.8433604591003567</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6174249883800195</v>
+        <v>0.5069238567451567</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7433649918716787</v>
+        <v>0.7433649918716786</v>
       </c>
       <c r="AB8" t="n">
         <v>1.023198946543858</v>
@@ -8082,82 +8082,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.740293908676296</v>
+        <v>0.7402939086762961</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7235805103807949</v>
+        <v>0.7235805103807951</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8646707217841855</v>
+        <v>0.864670721784185</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7480480962827606</v>
+        <v>0.7230314345587753</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7375497451971145</v>
+        <v>0.4876744126880316</v>
       </c>
       <c r="G9" t="n">
-        <v>1.222376590393893</v>
+        <v>1.222376578126526</v>
       </c>
       <c r="H9" t="n">
-        <v>0.914472588620213</v>
+        <v>0.9144725886202126</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7542662105430004</v>
+        <v>0.7542662105430005</v>
       </c>
       <c r="J9" t="n">
-        <v>1.006032879990656</v>
+        <v>1.006032879990657</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8453487829180368</v>
+        <v>0.8453487829180376</v>
       </c>
       <c r="L9" t="n">
-        <v>1.008308478583277</v>
+        <v>1.008308478583278</v>
       </c>
       <c r="M9" t="n">
-        <v>1.224616216539401</v>
+        <v>1.224616216539402</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9033198462542161</v>
+        <v>0.9033198462542164</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8791562878184971</v>
+        <v>0.8791562878184981</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9764822436643644</v>
+        <v>0.9764822436643643</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7965641148394862</v>
+        <v>0.7965641148394869</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6893956172984933</v>
+        <v>0.6893956172984937</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9226593204908551</v>
+        <v>0.9226593204908563</v>
       </c>
       <c r="T9" t="n">
-        <v>0.783103844020181</v>
+        <v>0.7831038440201809</v>
       </c>
       <c r="U9" t="n">
         <v>1.01246881386336</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7827379841167852</v>
+        <v>0.9078209596263366</v>
       </c>
       <c r="W9" t="n">
-        <v>1.051881553047435</v>
+        <v>1.051881553047436</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9735349920734842</v>
+        <v>0.9735349920734857</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.956783534395518</v>
+        <v>0.9567835343955188</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8385322346967566</v>
+        <v>0.7731809155914362</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9644722381884141</v>
+        <v>0.9644722381884134</v>
       </c>
       <c r="AB9" t="n">
         <v>1.130983547314815</v>
@@ -8326,73 +8326,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.621562328267533</v>
+        <v>2.621562328267535</v>
       </c>
       <c r="C2" t="n">
         <v>2.650796890948696</v>
       </c>
       <c r="D2" t="n">
-        <v>2.626950789725747</v>
+        <v>2.626950789725748</v>
       </c>
       <c r="E2" t="n">
-        <v>2.621201914971927</v>
+        <v>2.621201914971929</v>
       </c>
       <c r="F2" t="n">
         <v>2.610801391120185</v>
       </c>
       <c r="G2" t="n">
-        <v>2.663692314914925</v>
+        <v>2.663692314914926</v>
       </c>
       <c r="H2" t="n">
-        <v>2.63739360408543</v>
+        <v>2.637393604085431</v>
       </c>
       <c r="I2" t="n">
-        <v>2.620399913509422</v>
+        <v>2.620399913509421</v>
       </c>
       <c r="J2" t="n">
         <v>2.636845786131814</v>
       </c>
       <c r="K2" t="n">
-        <v>2.623107354665409</v>
+        <v>2.623107354665411</v>
       </c>
       <c r="L2" t="n">
         <v>2.605041455460612</v>
       </c>
       <c r="M2" t="n">
-        <v>2.623953191970918</v>
+        <v>2.623953191970919</v>
       </c>
       <c r="N2" t="n">
-        <v>2.625457264137343</v>
+        <v>2.625457264137345</v>
       </c>
       <c r="O2" t="n">
-        <v>2.866399006291328</v>
+        <v>2.866399006291327</v>
       </c>
       <c r="P2" t="n">
-        <v>2.632438549472847</v>
+        <v>2.632438549472848</v>
       </c>
       <c r="Q2" t="n">
         <v>2.623898633346739</v>
       </c>
       <c r="R2" t="n">
-        <v>2.596262684908833</v>
+        <v>2.596262684908834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61373278227831</v>
+        <v>2.613732782278311</v>
       </c>
       <c r="T2" t="n">
-        <v>2.614656197802632</v>
+        <v>2.614656197802633</v>
       </c>
       <c r="U2" t="n">
         <v>3.017188685539977</v>
       </c>
       <c r="V2" t="n">
-        <v>2.630044849677585</v>
+        <v>2.630044849677586</v>
       </c>
       <c r="W2" t="n">
-        <v>3.012273943640395</v>
+        <v>3.012273943640396</v>
       </c>
       <c r="X2" t="n">
-        <v>2.655420996036137</v>
+        <v>2.655420996036138</v>
       </c>
       <c r="Y2" t="n">
         <v>2.666188948249979</v>
@@ -8401,10 +8401,10 @@
         <v>2.777753934415557</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.636322134102907</v>
+        <v>2.636322134102908</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.64847336643524</v>
+        <v>2.648473366435241</v>
       </c>
     </row>
     <row r="3">
@@ -8429,7 +8429,7 @@
         <v>1.606090683937542</v>
       </c>
       <c r="G3" t="n">
-        <v>1.981597083038531</v>
+        <v>1.98159708303853</v>
       </c>
       <c r="H3" t="n">
         <v>1.796494613200936</v>
@@ -8447,16 +8447,16 @@
         <v>1.565823637965684</v>
       </c>
       <c r="M3" t="n">
-        <v>1.702668649898859</v>
+        <v>1.702668649898858</v>
       </c>
       <c r="N3" t="n">
         <v>1.710774683217471</v>
       </c>
       <c r="O3" t="n">
-        <v>2.075670659789148</v>
+        <v>2.075670659789149</v>
       </c>
       <c r="P3" t="n">
-        <v>1.760313130451902</v>
+        <v>1.760313130451901</v>
       </c>
       <c r="Q3" t="n">
         <v>1.699667073568405</v>
@@ -8477,13 +8477,13 @@
         <v>1.743256593578475</v>
       </c>
       <c r="W3" t="n">
-        <v>2.460636995892237</v>
+        <v>2.460636995892238</v>
       </c>
       <c r="X3" t="n">
         <v>1.92463404315926</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.001355507363005</v>
+        <v>2.001355507363004</v>
       </c>
       <c r="Z3" t="n">
         <v>1.980578862873694</v>
@@ -8492,7 +8492,7 @@
         <v>1.78832786016949</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.874344781432971</v>
+        <v>1.87434478143297</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1439193550509111</v>
+        <v>0.1439193550509115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1470449125615455</v>
+        <v>0.1470449125615446</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2047845060361715</v>
+        <v>0.204784506036171</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1398483210787158</v>
+        <v>0.1398483210787149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02236961969595395</v>
+        <v>0.02236961969595283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6197969349845897</v>
+        <v>0.6197969349845877</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3227408981607379</v>
+        <v>0.3227408981607376</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1307893456208175</v>
+        <v>0.1307893456208181</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3161671753813716</v>
+        <v>0.3161671753813717</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1613711389621508</v>
+        <v>0.1613711389621495</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.04269150328023366</v>
+        <v>-0.04269150328023544</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1756918440721398</v>
+        <v>0.1756918440721388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1879144474594614</v>
+        <v>0.1879144474594618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.119865375558706</v>
+        <v>0.1198653755587041</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2667712768738791</v>
+        <v>0.266771276873881</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1703089956739435</v>
+        <v>0.170308995673943</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1418517550965276</v>
+        <v>-0.1418517550965277</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05548103133353015</v>
+        <v>0.05548103133353037</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0659114344728727</v>
+        <v>0.06591143447287269</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2287901655103394</v>
+        <v>0.2287901655103393</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2371466621111374</v>
+        <v>0.2371466621111371</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4171109111716285</v>
+        <v>0.4171109111716289</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5263685832539862</v>
+        <v>0.5263685832539847</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6453199224299576</v>
+        <v>0.6453199224299579</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2262795694046418</v>
+        <v>0.2262795694046409</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3106381518076063</v>
+        <v>0.3106381518076066</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4453292430273847</v>
+        <v>0.4453292430273854</v>
       </c>
     </row>
     <row r="5">
@@ -8590,61 +8590,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2513398566001751</v>
+        <v>-0.2513398566001752</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2049464329184973</v>
+        <v>-0.2049464329184983</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8060305467542016</v>
+        <v>0.8060305467542006</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3532894011481017</v>
+        <v>-0.3532894011481039</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.476515569202962</v>
+        <v>-2.476515569202967</v>
       </c>
       <c r="G5" t="n">
-        <v>7.0645296885988</v>
+        <v>7.064529688598775</v>
       </c>
       <c r="H5" t="n">
-        <v>3.154225552065777</v>
+        <v>3.154225552065774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.560652296330634</v>
+        <v>-0.5606522963306317</v>
       </c>
       <c r="J5" t="n">
-        <v>2.457966361513283</v>
+        <v>2.457966361513275</v>
       </c>
       <c r="K5" t="n">
         <v>0.06663419065737175</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.190934508780628</v>
+        <v>-3.190934508780633</v>
       </c>
       <c r="M5" t="n">
         <v>0.2990485278724834</v>
       </c>
       <c r="N5" t="n">
-        <v>1.136057148287496</v>
+        <v>1.136057148287487</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5892983563938406</v>
+        <v>-0.5892983563938201</v>
       </c>
       <c r="P5" t="n">
-        <v>1.740915200897731</v>
+        <v>1.74091520089774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1922314528492384</v>
+        <v>0.1922314528492362</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.771172772676953</v>
+        <v>-5.771172772676951</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.588915673034621</v>
+        <v>-1.588915673034625</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.737044568693668</v>
+        <v>-1.737044568693672</v>
       </c>
       <c r="U5" t="n">
         <v>1.179610500920488</v>
@@ -8653,22 +8653,22 @@
         <v>1.274326565465001</v>
       </c>
       <c r="W5" t="n">
-        <v>4.562588549716121</v>
+        <v>4.562588549716123</v>
       </c>
       <c r="X5" t="n">
-        <v>6.484703757491184</v>
+        <v>6.484703757491179</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.568570834886946</v>
+        <v>8.56857083488697</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.057654205412536</v>
+        <v>1.057654205412535</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.670889458954699</v>
+        <v>2.670889458954706</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.408272955389437</v>
+        <v>5.40827295538943</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.220373937194377</v>
+        <v>0.1543176475552025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.22349949470501</v>
+        <v>0.2234994947050095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2151827985404637</v>
+        <v>0.2151827985404617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1502466135830073</v>
+        <v>0.2163029032221798</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03276791220024265</v>
+        <v>0.09882420183941751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6962515171280531</v>
+        <v>0.6301952274888782</v>
       </c>
       <c r="H6" t="n">
-        <v>0.333139190665029</v>
+        <v>0.399195480304203</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1411876381251093</v>
+        <v>0.2072439277642836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3926217575248376</v>
+        <v>0.3265654678856627</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1717694314664389</v>
+        <v>0.2378257211056143</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03376307886323129</v>
+        <v>-0.03229321077594473</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1860901365764314</v>
+        <v>0.2521464262156034</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1989347491060923</v>
+        <v>0.1989347491060503</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2009931530594212</v>
+        <v>0.1308856772053154</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2755025726413324</v>
+        <v>0.2755025726413317</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.180707288178236</v>
+        <v>0.2467635778174076</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.06539717295306149</v>
+        <v>-0.06539717295306316</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06587932383782236</v>
+        <v>0.06587932383782115</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07630972697716544</v>
+        <v>0.07630972697716396</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3079223822359221</v>
+        <v>0.2418660925967478</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3136012442546027</v>
+        <v>0.3136012442546019</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4310353461170445</v>
+        <v>0.4310353461170455</v>
       </c>
       <c r="X6" t="n">
-        <v>0.602823165397452</v>
+        <v>0.5367668757582746</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.660213344655799</v>
+        <v>0.6602133446558026</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2366778619089336</v>
+        <v>0.2366778619089318</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.387092733951072</v>
+        <v>0.3870927339510715</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4574198118322325</v>
+        <v>0.4574198118322347</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2167559556015597</v>
+        <v>0.2167559556015595</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2198815131121927</v>
+        <v>0.2198815131121926</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2776211065868191</v>
+        <v>0.2776211065868188</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2126849216293629</v>
+        <v>0.2126849216293626</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09520622024660197</v>
+        <v>0.09520622024660076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.692633535535238</v>
+        <v>0.6926335355352349</v>
       </c>
       <c r="H7" t="n">
-        <v>0.395577498711385</v>
+        <v>0.3955774987113852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2036259461714653</v>
+        <v>0.2036259461714657</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3890037759320203</v>
+        <v>0.3890037759320191</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2342077395127981</v>
+        <v>0.2342077395127978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03014509727041258</v>
+        <v>0.03014509727041198</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2485284446227869</v>
+        <v>0.2485284446227864</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2607510480101104</v>
+        <v>0.2607510480101096</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1923685179526195</v>
+        <v>0.1923685179526193</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3392744192677959</v>
+        <v>0.3392744192677958</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2431455962245928</v>
+        <v>0.2431455962245908</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.06901515454588036</v>
+        <v>-0.06901515454588039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.128317631884178</v>
+        <v>0.1283176318841784</v>
       </c>
       <c r="T7" t="n">
-        <v>0.13874803502352</v>
+        <v>0.1387480350235206</v>
       </c>
       <c r="U7" t="n">
-        <v>0.303188341906937</v>
+        <v>0.3031883419069371</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3099832626617847</v>
+        <v>0.3099832626617848</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4899475117222785</v>
+        <v>0.4899475117222779</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5992051838046358</v>
+        <v>0.5992051838046329</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.720834157562723</v>
+        <v>0.7208341575627223</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2991161699552888</v>
+        <v>0.2991161699552886</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3834747523582525</v>
+        <v>0.3834747523582542</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5181658435780341</v>
+        <v>0.5181658435780334</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2427118036121969</v>
+        <v>0.2427118036121972</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3273138433297305</v>
+        <v>0.3273138433297293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3850534368043568</v>
+        <v>0.3850534368043554</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3201172518469017</v>
+        <v>0.2767334284933928</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1338551519401001</v>
+        <v>0.1338551519400991</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8000658657527725</v>
+        <v>0.8169605451014785</v>
       </c>
       <c r="H8" t="n">
-        <v>0.503009828928922</v>
+        <v>0.5030098289289217</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3110582763890042</v>
+        <v>0.3110582763890025</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4964361061495565</v>
+        <v>0.4964361061495562</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3416400697303337</v>
+        <v>0.3416400697303345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1375774274879496</v>
+        <v>0.1375774274879486</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3559607748403251</v>
+        <v>0.3559607748402229</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3050254737780048</v>
+        <v>0.3050254737780042</v>
       </c>
       <c r="O8" t="n">
         <v>0.2543327423694881</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3969841852462798</v>
+        <v>0.3969841852462761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2530894558932696</v>
+        <v>0.2530894558932691</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03841717567165832</v>
+        <v>0.03841717567165677</v>
       </c>
       <c r="S8" t="n">
-        <v>0.235749962101716</v>
+        <v>0.2357499621017152</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2461803652410587</v>
+        <v>0.2461803652410575</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3610308548338877</v>
+        <v>0.3713626510645478</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4174155928793219</v>
+        <v>0.3944778941278667</v>
       </c>
       <c r="W8" t="n">
         <v>0.5973958543228991</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6166165249146291</v>
+        <v>0.616616524914628</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9082391608866696</v>
+        <v>0.9082391608866685</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4065485001728276</v>
+        <v>0.3235585504858776</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4909070825757913</v>
+        <v>0.4909070825757911</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7107071723382777</v>
+        <v>0.7107071723382766</v>
       </c>
     </row>
     <row r="9">
@@ -8945,82 +8945,82 @@
         <v>0.4067260982560931</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4906735093506832</v>
+        <v>0.4906735093506815</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5484131028253096</v>
+        <v>0.5484131028253079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4834769178678531</v>
+        <v>0.4648236106188264</v>
       </c>
       <c r="F9" t="n">
-        <v>0.36599821648509</v>
+        <v>0.1796817060260631</v>
       </c>
       <c r="G9" t="n">
-        <v>0.963425531773726</v>
+        <v>0.9634255927352012</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6663694949498751</v>
+        <v>0.6663694949498743</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4744179424099563</v>
+        <v>0.4744179424099544</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6597957721705101</v>
+        <v>0.6597957721705089</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5049997357512868</v>
+        <v>0.5049997357512864</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3009370935089027</v>
+        <v>0.3009370935089014</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5193204408612773</v>
+        <v>0.5193204408612755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5315430442486007</v>
+        <v>0.5315430442485984</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4902783099624073</v>
+        <v>0.4902783099624076</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6430093319088358</v>
+        <v>0.643009331908834</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.513937653424558</v>
+        <v>0.5139376534245572</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2017768416926118</v>
+        <v>0.2017768416926091</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3991096281226695</v>
+        <v>0.3991096281226675</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4095400312620113</v>
+        <v>0.4095400312620103</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5750963968815954</v>
+        <v>0.5750963968815936</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5807752589002747</v>
+        <v>0.6740420065735876</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7607395079607671</v>
+        <v>0.7607395079607664</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8699971800431218</v>
+        <v>0.8699971800431208</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9916261538012112</v>
+        <v>0.9916261538012108</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.569908166193779</v>
+        <v>0.521179799649415</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6542667485967452</v>
+        <v>0.6542667485967434</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.788957839816525</v>
+        <v>0.7889578398165223</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.700829254523909</v>
+        <v>2.697725228200455</v>
       </c>
       <c r="C2" t="n">
-        <v>2.709151361034767</v>
+        <v>2.702639480244241</v>
       </c>
       <c r="D2" t="n">
-        <v>2.691182090786411</v>
+        <v>2.687978871921092</v>
       </c>
       <c r="E2" t="n">
-        <v>2.682221380567877</v>
+        <v>2.675176840259549</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6882914225112</v>
+        <v>2.682975220234052</v>
       </c>
       <c r="G2" t="n">
-        <v>2.722153043145394</v>
+        <v>2.708597689297739</v>
       </c>
       <c r="H2" t="n">
-        <v>2.702277479889482</v>
+        <v>2.695839288957797</v>
       </c>
       <c r="I2" t="n">
-        <v>2.690353565252785</v>
+        <v>2.683997951876753</v>
       </c>
       <c r="J2" t="n">
-        <v>2.706008009890701</v>
+        <v>2.697755753143283</v>
       </c>
       <c r="K2" t="n">
-        <v>2.701006678293889</v>
+        <v>2.695246811788161</v>
       </c>
       <c r="L2" t="n">
-        <v>2.71137629517779</v>
+        <v>2.710475776153448</v>
       </c>
       <c r="M2" t="n">
-        <v>2.725840173883355</v>
+        <v>2.716403956687403</v>
       </c>
       <c r="N2" t="n">
-        <v>2.703865336505706</v>
+        <v>2.698037918703968</v>
       </c>
       <c r="O2" t="n">
-        <v>2.990735126962554</v>
+        <v>2.984229030873059</v>
       </c>
       <c r="P2" t="n">
-        <v>2.700856787934722</v>
+        <v>2.692554456655992</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.694266389866274</v>
+        <v>2.688454158220473</v>
       </c>
       <c r="R2" t="n">
-        <v>2.690560197395095</v>
+        <v>2.684468101162446</v>
       </c>
       <c r="S2" t="n">
-        <v>2.708568600099951</v>
+        <v>2.701393751943495</v>
       </c>
       <c r="T2" t="n">
-        <v>2.698350305930498</v>
+        <v>2.692101922761875</v>
       </c>
       <c r="U2" t="n">
-        <v>3.118714184803899</v>
+        <v>3.113550618573962</v>
       </c>
       <c r="V2" t="n">
-        <v>2.686029498342861</v>
+        <v>2.680943831842452</v>
       </c>
       <c r="W2" t="n">
-        <v>3.092980539543937</v>
+        <v>3.087568757853364</v>
       </c>
       <c r="X2" t="n">
-        <v>2.697438572578757</v>
+        <v>2.692266878223649</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.697217664238568</v>
+        <v>2.689664707120905</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.863014672403931</v>
+        <v>2.856443716554025</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.705455575541662</v>
+        <v>2.699495518543625</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.717002086029948</v>
+        <v>2.715143280633163</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.952027721696517</v>
+        <v>1.967620034927502</v>
       </c>
       <c r="C3" t="n">
-        <v>1.851801951143108</v>
+        <v>1.844926382224464</v>
       </c>
       <c r="D3" t="n">
-        <v>1.884479187836992</v>
+        <v>1.899503326408757</v>
       </c>
       <c r="E3" t="n">
-        <v>1.820065494608602</v>
+        <v>1.807617162333339</v>
       </c>
       <c r="F3" t="n">
-        <v>1.863966612535174</v>
+        <v>1.863870131064064</v>
       </c>
       <c r="G3" t="n">
-        <v>2.10414648948669</v>
+        <v>2.04536490241931</v>
       </c>
       <c r="H3" t="n">
-        <v>1.964475978447747</v>
+        <v>1.956332484509553</v>
       </c>
       <c r="I3" t="n">
-        <v>1.878646821425674</v>
+        <v>1.871101795707869</v>
       </c>
       <c r="J3" t="n">
-        <v>1.989565906451694</v>
+        <v>1.968528699246639</v>
       </c>
       <c r="K3" t="n">
-        <v>1.954704709630932</v>
+        <v>1.951426126246798</v>
       </c>
       <c r="L3" t="n">
-        <v>2.028096199136587</v>
+        <v>2.059489417485527</v>
       </c>
       <c r="M3" t="n">
-        <v>2.133797075615288</v>
+        <v>2.10430613853266</v>
       </c>
       <c r="N3" t="n">
-        <v>1.974861969057572</v>
+        <v>1.971099217576704</v>
       </c>
       <c r="O3" t="n">
-        <v>2.417564732042376</v>
+        <v>2.418695397229901</v>
       </c>
       <c r="P3" t="n">
-        <v>1.952404244944486</v>
+        <v>1.931029811373022</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.906345164524769</v>
+        <v>1.902691209217461</v>
       </c>
       <c r="R3" t="n">
-        <v>1.880240728090334</v>
+        <v>1.874582402609689</v>
       </c>
       <c r="S3" t="n">
-        <v>2.007482227110232</v>
+        <v>1.994122991075683</v>
       </c>
       <c r="T3" t="n">
-        <v>1.935841031008604</v>
+        <v>1.929065258455182</v>
       </c>
       <c r="U3" t="n">
-        <v>2.710747732376084</v>
+        <v>2.710856412520415</v>
       </c>
       <c r="V3" t="n">
-        <v>1.846880726655471</v>
+        <v>1.848388560281658</v>
       </c>
       <c r="W3" t="n">
-        <v>2.634280759856611</v>
+        <v>2.630616642330299</v>
       </c>
       <c r="X3" t="n">
-        <v>1.929116549786935</v>
+        <v>1.930044572168908</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.927163275321829</v>
+        <v>1.911081179989437</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.196063133432586</v>
+        <v>2.188178851819827</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.986060262560263</v>
+        <v>1.981349966031068</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.069112131029689</v>
+        <v>2.093317437807349</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5950009853708388</v>
+        <v>0.5610842872544276</v>
       </c>
       <c r="C4" t="n">
-        <v>0.357906685618635</v>
+        <v>0.2891746208302046</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4860318330412133</v>
+        <v>0.4509947095336142</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3848164889925023</v>
+        <v>0.3063898726909896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4533804050995962</v>
+        <v>0.3944761619350109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.835862987277888</v>
+        <v>0.683893736927475</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6113593570915762</v>
+        <v>0.5397817359336881</v>
       </c>
       <c r="I4" t="n">
-        <v>0.476673255998336</v>
+        <v>0.4060283863191232</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6530628899319197</v>
+        <v>0.561027735556524</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5970050684716978</v>
+        <v>0.5330894337496758</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7141346614348113</v>
+        <v>0.7051075919253491</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8792105907306791</v>
+        <v>0.7739936206792769</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6292949280219461</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O4" t="n">
-        <v>0.568566301085054</v>
+        <v>0.5163657387351357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5953119879119655</v>
+        <v>0.5026780439872969</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5208704099959355</v>
+        <v>0.4563632869276353</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4790072611012115</v>
+        <v>0.4113389387803787</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6824204539270863</v>
+        <v>0.6025219505363851</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5670001206355476</v>
+        <v>0.4975664654773624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7318045657168092</v>
+        <v>0.6740036125027696</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4249182526281201</v>
+        <v>0.3688428982336557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6650318910139136</v>
+        <v>0.5991453816453975</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5567016730095881</v>
+        <v>0.499429713301363</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5501070297192013</v>
+        <v>0.4670874097179747</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5454446827645638</v>
+        <v>0.4747928093599099</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6472574094791667</v>
+        <v>0.5810805310543155</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7757338702692357</v>
+        <v>0.7549387817299072</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.675652756215342</v>
+        <v>7.201509147590627</v>
       </c>
       <c r="C5" t="n">
-        <v>2.498663741011247</v>
+        <v>2.369017369667043</v>
       </c>
       <c r="D5" t="n">
-        <v>5.256134622001271</v>
+        <v>5.842498803471555</v>
       </c>
       <c r="E5" t="n">
-        <v>2.944083537750222</v>
+        <v>2.622936493270815</v>
       </c>
       <c r="F5" t="n">
-        <v>4.668897814975911</v>
+        <v>4.750765156733681</v>
       </c>
       <c r="G5" t="n">
-        <v>11.48438711941112</v>
+        <v>9.762335866454455</v>
       </c>
       <c r="H5" t="n">
-        <v>8.26046070486125</v>
+        <v>8.063741559069625</v>
       </c>
       <c r="I5" t="n">
-        <v>5.115733093989323</v>
+        <v>4.943210946745638</v>
       </c>
       <c r="J5" t="n">
-        <v>8.196239053733448</v>
+        <v>7.618631709688998</v>
       </c>
       <c r="K5" t="n">
-        <v>7.554463168613452</v>
+        <v>7.526111362832647</v>
       </c>
       <c r="L5" t="n">
-        <v>9.546497480710297</v>
+        <v>10.6177754845596</v>
       </c>
       <c r="M5" t="n">
-        <v>13.79078716457861</v>
+        <v>12.87356285801898</v>
       </c>
       <c r="N5" t="n">
-        <v>9.685152453804369</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O5" t="n">
-        <v>6.044652872045119</v>
+        <v>6.223010248131131</v>
       </c>
       <c r="P5" t="n">
-        <v>6.788908089656357</v>
+        <v>6.21185824115284</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.870446437123629</v>
+        <v>5.829209006093925</v>
       </c>
       <c r="R5" t="n">
-        <v>5.233559290606105</v>
+        <v>5.124523848171404</v>
       </c>
       <c r="S5" t="n">
-        <v>8.565904866569607</v>
+        <v>8.226475115219207</v>
       </c>
       <c r="T5" t="n">
-        <v>7.006681391071782</v>
+        <v>6.860895701021572</v>
       </c>
       <c r="U5" t="n">
-        <v>9.791761473464319</v>
+        <v>9.858296563125711</v>
       </c>
       <c r="V5" t="n">
-        <v>3.591346436745744</v>
+        <v>3.701491464772033</v>
       </c>
       <c r="W5" t="n">
-        <v>8.633045327839648</v>
+        <v>8.563322456505045</v>
       </c>
       <c r="X5" t="n">
-        <v>6.670084248111253</v>
+        <v>6.78074717401152</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.395978804029611</v>
+        <v>5.956113113626497</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.908834742608359</v>
+        <v>5.747825618427287</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.33080816692199</v>
+        <v>8.255170236172955</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.92934653641637</v>
+        <v>12.8612195711343</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7188983849197264</v>
+        <v>0.5864340599113597</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4818040851675226</v>
+        <v>0.4088406309789194</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5102357062059765</v>
+        <v>0.5706607196823278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4090203621572655</v>
+        <v>0.4260558828397044</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5772778046484837</v>
+        <v>0.4198259345919432</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9597603868267743</v>
+        <v>0.8035597470761898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7352567566404633</v>
+        <v>0.6594477460824023</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5008771291630995</v>
+        <v>0.4313781589760562</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7769602894808074</v>
+        <v>0.5863775082134576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6212089416364613</v>
+        <v>0.6527554438983895</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7383385345995749</v>
+        <v>0.8247736020740658</v>
       </c>
       <c r="M6" t="n">
-        <v>0.903414463895443</v>
+        <v>0.893659630827992</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6544872259770604</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6977786915322446</v>
+        <v>0.5428381257310242</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7245252821207545</v>
+        <v>0.6274030016379069</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5450742831606993</v>
+        <v>0.5760292970763492</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5032111342659743</v>
+        <v>0.531004948929093</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8063178534759737</v>
+        <v>0.6278717231933193</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5912039938003109</v>
+        <v>0.5229162381342957</v>
       </c>
       <c r="U6" t="n">
-        <v>0.760107820846661</v>
+        <v>0.7023029690797462</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5488156521770075</v>
+        <v>0.48850890838237</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7942448449478156</v>
+        <v>0.7238700327420485</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6805990725584757</v>
+        <v>0.6190957234500768</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5814773617990412</v>
+        <v>0.4987283558070083</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5696485559293268</v>
+        <v>0.5001425820168433</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6714612826439308</v>
+        <v>0.7007465412030298</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.80242808844373</v>
+        <v>0.7831516781996374</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7093579447502772</v>
+        <v>0.6715773757207947</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4722636449980737</v>
+        <v>0.3996677092965722</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6003887924206512</v>
+        <v>0.5614877979999815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4991734483719405</v>
+        <v>0.4168829611573563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5677373644790344</v>
+        <v>0.5049692504013784</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9502199466573256</v>
+        <v>0.7943868253938429</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7257163164710144</v>
+        <v>0.6502748244000558</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5910302153777748</v>
+        <v>0.51652147478549</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7674198493113585</v>
+        <v>0.6715208240228917</v>
       </c>
       <c r="K7" t="n">
-        <v>0.711362027851137</v>
+        <v>0.6435825222160411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8284916208142517</v>
+        <v>0.8156006803917201</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9935675501101177</v>
+        <v>0.8844867091456438</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7436518874013842</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6825397634429995</v>
+        <v>0.6264753753805611</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7092854502699097</v>
+        <v>0.6127876806327243</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6352273693753745</v>
+        <v>0.5668563753940028</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5933642204806499</v>
+        <v>0.5218320272467465</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7967774133065242</v>
+        <v>0.7130150390027546</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6813570800149863</v>
+        <v>0.6080595539437308</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8500183029476571</v>
+        <v>0.7872696361533517</v>
       </c>
       <c r="V7" t="n">
-        <v>0.539275212007559</v>
+        <v>0.4793359867000229</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7793888503933534</v>
+        <v>0.709638470111766</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6710586323890273</v>
+        <v>0.6099228017677304</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6685633710637262</v>
+        <v>0.5805300821043875</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6598016421440027</v>
+        <v>0.5852858978262775</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.761614368858606</v>
+        <v>0.6915736195206839</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8900908296486738</v>
+        <v>0.8654318701962763</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7630066911335628</v>
+        <v>0.7240679744388097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6601942891966991</v>
+        <v>0.5819025323860085</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7883194366192764</v>
+        <v>0.7437226210894178</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6156029430728303</v>
+        <v>0.5300328120039962</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6423056611440214</v>
+        <v>0.5776724829119256</v>
       </c>
       <c r="G8" t="n">
-        <v>1.165994817125807</v>
+        <v>1.003524958604737</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9136469606696402</v>
+        <v>0.8325096474894929</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7789608595764005</v>
+        <v>0.6987562978749279</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9553504935099834</v>
+        <v>0.8537556471123281</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8992926720497626</v>
+        <v>0.8258173453054793</v>
       </c>
       <c r="L8" t="n">
-        <v>1.016422265012876</v>
+        <v>0.9978355034811557</v>
       </c>
       <c r="M8" t="n">
-        <v>1.181498194308755</v>
+        <v>1.06672153223512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.827491595894451</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7953680618425897</v>
+        <v>0.7361586360633455</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8151019492131083</v>
+        <v>0.7156960856071507</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6624866580307173</v>
+        <v>0.5938492727818167</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7812948646792753</v>
+        <v>0.7040668503361827</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9847080575051496</v>
+        <v>0.8952498620921898</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8692877242136114</v>
+        <v>0.7902943770331657</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9727595376599745</v>
+        <v>0.9065149509951014</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6906250205160968</v>
+        <v>0.6262865270619264</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9673458847293269</v>
+        <v>0.8918987915602953</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7106251237381153</v>
+        <v>0.6488070150644972</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9901942396107121</v>
+        <v>0.8920408050357774</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7109560333435593</v>
+        <v>0.6353664309739633</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.949545013057231</v>
+        <v>0.87380844261012</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.218290144489358</v>
+        <v>1.183195384585969</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.067360555114039</v>
+        <v>1.010950742521336</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9728835121550089</v>
+        <v>0.8748515780449311</v>
       </c>
       <c r="D9" t="n">
-        <v>1.101008659577588</v>
+        <v>1.03667166674834</v>
       </c>
       <c r="E9" t="n">
-        <v>0.966877852156478</v>
+        <v>0.8607223347653183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7395855006307722</v>
+        <v>0.6670728209309114</v>
       </c>
       <c r="G9" t="n">
-        <v>1.450839836916411</v>
+        <v>1.269570713315539</v>
       </c>
       <c r="H9" t="n">
-        <v>1.22633618362795</v>
+        <v>1.125458693148414</v>
       </c>
       <c r="I9" t="n">
-        <v>1.09165008253471</v>
+        <v>0.991705343533849</v>
       </c>
       <c r="J9" t="n">
-        <v>1.268039716468293</v>
+        <v>1.146704692771251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.211981895008071</v>
+        <v>1.118766390964401</v>
       </c>
       <c r="L9" t="n">
-        <v>1.329111487971185</v>
+        <v>1.29078454914008</v>
       </c>
       <c r="M9" t="n">
-        <v>1.494187417267051</v>
+        <v>1.359670577894003</v>
       </c>
       <c r="N9" t="n">
-        <v>1.244271754558322</v>
+        <v>8.01408394358586</v>
       </c>
       <c r="O9" t="n">
-        <v>1.230806330539503</v>
+        <v>1.147050143994055</v>
       </c>
       <c r="P9" t="n">
-        <v>1.267830948076775</v>
+        <v>1.143150792828193</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.13584725963446</v>
+        <v>1.042040263315698</v>
       </c>
       <c r="R9" t="n">
-        <v>1.093984087637586</v>
+        <v>0.9970158959951051</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29739728046346</v>
+        <v>1.188198907751113</v>
       </c>
       <c r="T9" t="n">
-        <v>1.181976947171921</v>
+        <v>1.083243422692089</v>
       </c>
       <c r="U9" t="n">
-        <v>1.350880774218271</v>
+        <v>1.262630153637542</v>
       </c>
       <c r="V9" t="n">
-        <v>1.204472166268913</v>
+        <v>1.111242098661583</v>
       </c>
       <c r="W9" t="n">
-        <v>1.280008717550288</v>
+        <v>1.184822338860123</v>
       </c>
       <c r="X9" t="n">
-        <v>1.171678499545962</v>
+        <v>1.085106670516088</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.169183238220662</v>
+        <v>1.055713950852746</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.074435994649556</v>
+        <v>0.9785881182546585</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.26223423601554</v>
+        <v>1.166757488269044</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.390710696805609</v>
+        <v>1.340615738944635</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.592776438996192</v>
+        <v>2.591161317580908</v>
       </c>
       <c r="C2" t="n">
-        <v>2.618326353294564</v>
+        <v>2.615593628781776</v>
       </c>
       <c r="D2" t="n">
-        <v>2.596380969337611</v>
+        <v>2.594727952435032</v>
       </c>
       <c r="E2" t="n">
-        <v>2.594205708705821</v>
+        <v>2.592523871270374</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58287427458968</v>
+        <v>2.58118310228682</v>
       </c>
       <c r="G2" t="n">
-        <v>2.60070393107322</v>
+        <v>2.598723641209711</v>
       </c>
       <c r="H2" t="n">
-        <v>2.599420385284967</v>
+        <v>2.597785132037784</v>
       </c>
       <c r="I2" t="n">
-        <v>2.593904305864693</v>
+        <v>2.59286011954347</v>
       </c>
       <c r="J2" t="n">
-        <v>2.597217932218059</v>
+        <v>2.595516863958469</v>
       </c>
       <c r="K2" t="n">
-        <v>2.593478481730207</v>
+        <v>2.592584851912546</v>
       </c>
       <c r="L2" t="n">
-        <v>2.571816771458863</v>
+        <v>2.570182032313517</v>
       </c>
       <c r="M2" t="n">
-        <v>2.592593314844924</v>
+        <v>2.591016167949279</v>
       </c>
       <c r="N2" t="n">
-        <v>2.593886522652692</v>
+        <v>2.592286474770312</v>
       </c>
       <c r="O2" t="n">
-        <v>2.819780429975737</v>
+        <v>2.813460402251725</v>
       </c>
       <c r="P2" t="n">
-        <v>2.592917596149041</v>
+        <v>2.591223101927591</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.595858343351155</v>
+        <v>2.594228978259872</v>
       </c>
       <c r="R2" t="n">
-        <v>2.561366616628565</v>
+        <v>2.559838440562478</v>
       </c>
       <c r="S2" t="n">
-        <v>2.584899972379037</v>
+        <v>2.582913350421483</v>
       </c>
       <c r="T2" t="n">
-        <v>2.587592824457484</v>
+        <v>2.586722848151323</v>
       </c>
       <c r="U2" t="n">
-        <v>2.988983253560101</v>
+        <v>2.979999816597866</v>
       </c>
       <c r="V2" t="n">
-        <v>2.603455731809531</v>
+        <v>2.601771717679689</v>
       </c>
       <c r="W2" t="n">
-        <v>2.992017640788148</v>
+        <v>2.981880794231905</v>
       </c>
       <c r="X2" t="n">
-        <v>2.635667756264204</v>
+        <v>2.633860364769502</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.618488723069659</v>
+        <v>2.616760860298328</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.749000925509229</v>
+        <v>2.745407690195294</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.627186286261675</v>
+        <v>2.625615103947895</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.596561760827923</v>
+        <v>2.59516365714338</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.659756436519166</v>
+        <v>1.65879372086243</v>
       </c>
       <c r="C3" t="n">
-        <v>1.698319091071346</v>
+        <v>1.69521398675042</v>
       </c>
       <c r="D3" t="n">
-        <v>1.685399824347609</v>
+        <v>1.684169045075399</v>
       </c>
       <c r="E3" t="n">
-        <v>1.669915579031043</v>
+        <v>1.668492358684402</v>
       </c>
       <c r="F3" t="n">
-        <v>1.588909428308932</v>
+        <v>1.587404411787472</v>
       </c>
       <c r="G3" t="n">
-        <v>1.716003083669358</v>
+        <v>1.712454509032789</v>
       </c>
       <c r="H3" t="n">
-        <v>1.707211039714351</v>
+        <v>1.706104655481177</v>
       </c>
       <c r="I3" t="n">
-        <v>1.667704095344132</v>
+        <v>1.670823814086225</v>
       </c>
       <c r="J3" t="n">
-        <v>1.691273365073798</v>
+        <v>1.68970516356903</v>
       </c>
       <c r="K3" t="n">
-        <v>1.664770058650007</v>
+        <v>1.66893775161601</v>
       </c>
       <c r="L3" t="n">
-        <v>1.510969442173785</v>
+        <v>1.509870891607075</v>
       </c>
       <c r="M3" t="n">
-        <v>1.660644854372804</v>
+        <v>1.659908411532485</v>
       </c>
       <c r="N3" t="n">
-        <v>1.667568580098379</v>
+        <v>1.666711604439586</v>
       </c>
       <c r="O3" t="n">
-        <v>2.001639933986068</v>
+        <v>1.992539869541578</v>
       </c>
       <c r="P3" t="n">
-        <v>1.660777879464313</v>
+        <v>1.659252585560336</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.681658920917767</v>
+        <v>1.680595812283264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.434625757654409</v>
+        <v>1.434285234424961</v>
       </c>
       <c r="S3" t="n">
-        <v>1.603882387332526</v>
+        <v>1.600284738059492</v>
       </c>
       <c r="T3" t="n">
-        <v>1.622537889129413</v>
+        <v>1.626905344436027</v>
       </c>
       <c r="U3" t="n">
-        <v>2.35260780966597</v>
+        <v>2.339857717897884</v>
       </c>
       <c r="V3" t="n">
-        <v>1.735546770847178</v>
+        <v>1.734098272590474</v>
       </c>
       <c r="W3" t="n">
-        <v>2.489980145301833</v>
+        <v>2.474125884561633</v>
       </c>
       <c r="X3" t="n">
-        <v>1.965389614909276</v>
+        <v>1.963057986679946</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.843322606952859</v>
+        <v>1.841552368341715</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.965023293964454</v>
+        <v>1.960820664607206</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.905393055417317</v>
+        <v>1.904741954534674</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.686706502092848</v>
+        <v>1.687247534551345</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.112255433821431</v>
+        <v>0.09568441449888429</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1048523805614677</v>
+        <v>0.08766156807486819</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1529702621936217</v>
+        <v>0.1359711959093221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1283996926882386</v>
+        <v>0.1110750852270499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004059316291766951</v>
+        <v>-0.01702411745365875</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2018001036579727</v>
+        <v>0.1811043387269766</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1873018635194242</v>
+        <v>0.1705034458945006</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1249952089455342</v>
+        <v>0.1148731641535481</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1621845455837044</v>
+        <v>0.1446438105686483</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1201853294577275</v>
+        <v>0.1117638896328759</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1244936529361196</v>
+        <v>-0.1412862635443227</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1143709228432122</v>
+        <v>0.09814087600801574</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04402037169280688</v>
+        <v>0.02667362989259436</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1138498687983759</v>
+        <v>0.09638229711686205</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1470669612567763</v>
+        <v>0.1303350530614293</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2425329590530897</v>
+        <v>-0.2581218906596082</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02328712002699653</v>
+        <v>0.002519831180818853</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05370412302622667</v>
+        <v>0.04554986049489845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1875890353287827</v>
+        <v>0.1741876946773098</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2312888039122889</v>
+        <v>0.2139436211004776</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4649899706878985</v>
+        <v>0.4467236884271242</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5967325933443878</v>
+        <v>0.5779897950262122</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3975259307507338</v>
+        <v>0.3820814253336881</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2107079708219351</v>
+        <v>0.1941846074640941</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5009304879968698</v>
+        <v>0.4848557810387746</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1549777416069588</v>
+        <v>0.1407630311804538</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3026700565533276</v>
+        <v>-0.3097373850807678</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4538494086142058</v>
+        <v>-0.4701036641305643</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3747760674314238</v>
+        <v>0.361380914756843</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03870415960380492</v>
+        <v>-0.05098926981614345</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.371481744351195</v>
+        <v>-2.393494662688556</v>
       </c>
       <c r="G5" t="n">
-        <v>1.108890374296982</v>
+        <v>1.039424504857788</v>
       </c>
       <c r="H5" t="n">
-        <v>1.043527424454798</v>
+        <v>1.032445080019691</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1301963438712856</v>
+        <v>-0.01924255494901472</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4899706756505258</v>
+        <v>0.469838969943762</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1608060520209423</v>
+        <v>-0.03353573899332363</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.073731428017169</v>
+        <v>-4.082552921159547</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3055956462961398</v>
+        <v>-0.3050563357538487</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.346486178054938</v>
+        <v>-1.364298868113133</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2672160923782076</v>
+        <v>-0.2881144671126994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2647200230389038</v>
+        <v>0.2554625847034607</v>
       </c>
       <c r="R5" t="n">
-        <v>-7.073738482932781</v>
+        <v>-7.062576164584051</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.699669749242168</v>
+        <v>-1.772412471149399</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.453723653786877</v>
+        <v>-1.305690862716662</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9779124742076039</v>
+        <v>0.9852245974293862</v>
       </c>
       <c r="V5" t="n">
-        <v>1.607271359595711</v>
+        <v>1.589506478177887</v>
       </c>
       <c r="W5" t="n">
-        <v>5.871139189375592</v>
+        <v>5.833329571398569</v>
       </c>
       <c r="X5" t="n">
-        <v>8.015136325758819</v>
+        <v>7.971382448702352</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.863285432862449</v>
+        <v>4.832201099424162</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.215754976263294</v>
+        <v>1.21065933860975</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.598545892029881</v>
+        <v>6.599230175613488</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4285140667632275</v>
+        <v>0.4664906834129982</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1229391848368451</v>
+        <v>0.1046568585524205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1155361315768818</v>
+        <v>0.1361225978324827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2056791904690564</v>
+        <v>0.144943639962861</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1390834437036527</v>
+        <v>0.1595361149846649</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01108968264459113</v>
+        <v>0.03143691230395497</v>
       </c>
       <c r="G6" t="n">
-        <v>0.254509031933406</v>
+        <v>0.1900767827805146</v>
       </c>
       <c r="H6" t="n">
-        <v>0.240010791794858</v>
+        <v>0.179475889948039</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1777041372209683</v>
+        <v>0.123845608207086</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2148934738591385</v>
+        <v>0.1931048403262624</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1308690804731417</v>
+        <v>0.1207363336864137</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07178472466068563</v>
+        <v>-0.09282523378670786</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1670798511186468</v>
+        <v>0.1071133200615522</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1027472971922669</v>
+        <v>0.07983576469089036</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1725032508838436</v>
+        <v>0.1039183358113461</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1997758895322112</v>
+        <v>0.139307497114965</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1898240307776564</v>
+        <v>-0.2491494466060693</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07599604830243062</v>
+        <v>0.05098086093843187</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06438787404164023</v>
+        <v>0.05452230454843605</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2454595435197866</v>
+        <v>0.225410324964852</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2839977321877228</v>
+        <v>0.222916065154015</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4793446224013699</v>
+        <v>0.4592452265264918</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6074163443598019</v>
+        <v>0.6264508247838257</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4154346940881932</v>
+        <v>0.3958344431438929</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.221391721837349</v>
+        <v>0.2031570515176305</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5116142390122834</v>
+        <v>0.5333168107963878</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1658489072816947</v>
+        <v>0.1501060680556903</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1761335538238742</v>
+        <v>0.1590455249377193</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1687305005639106</v>
+        <v>0.151022678513704</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2168483821960646</v>
+        <v>0.1993323063481582</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1922778126906816</v>
+        <v>0.1744361956658859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06428405163161982</v>
+        <v>0.04633699298517709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2656782236604155</v>
+        <v>0.2444654491658124</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2511799835218676</v>
+        <v>0.2338645563333389</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1888733289479766</v>
+        <v>0.1782342745923856</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2260626655861476</v>
+        <v>0.2080049210074844</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1840634494601709</v>
+        <v>0.1751250000717134</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06061553293367691</v>
+        <v>-0.07792515310548485</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1782490428456552</v>
+        <v>0.1615019864468522</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1075657160152844</v>
+        <v>0.08970157674739732</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1773952131208537</v>
+        <v>0.1594102439716644</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2109450812592197</v>
+        <v>0.1936961635002646</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1786548390506474</v>
+        <v>-0.1947607802207693</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08716524002943898</v>
+        <v>0.06588094161965542</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1175822430286695</v>
+        <v>0.1089109709337341</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2549039906763169</v>
+        <v>0.2392782157526664</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2951669239147322</v>
+        <v>0.2773047315393139</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5288680906903418</v>
+        <v>0.5100847988659585</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6606107133468302</v>
+        <v>0.6413509054650478</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4665656306687463</v>
+        <v>0.4482041363024508</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2745860908243779</v>
+        <v>0.257545717902931</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5648086079993131</v>
+        <v>0.5482168914776104</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2188558616094021</v>
+        <v>0.2041241416192897</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1938125236216415</v>
+        <v>0.1739736180607274</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2540381394643479</v>
+        <v>0.2289158088775472</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3021560210965018</v>
+        <v>0.2772254367120028</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2415751802277421</v>
+        <v>0.2188023010504301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09249877767502615</v>
+        <v>0.07107430302178812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3650091076533256</v>
+        <v>0.3354147901803332</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3364876224223042</v>
+        <v>0.3117576866971807</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2741809678484139</v>
+        <v>0.2561274049562277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3113703044865839</v>
+        <v>0.2858980513713267</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2693710883606073</v>
+        <v>0.2530181304355564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02469210596675975</v>
+        <v>-3.202274164215702e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2635566817459829</v>
+        <v>0.2393951168108953</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1551890399050576</v>
+        <v>0.1325324154843324</v>
       </c>
       <c r="P8" t="n">
-        <v>0.221487169993207</v>
+        <v>0.1989532366011831</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2153334740469827</v>
+        <v>0.1962501896973009</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.09334720015021009</v>
+        <v>-0.1168676498569274</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1724728789298762</v>
+        <v>0.1437740719834991</v>
       </c>
       <c r="T8" t="n">
-        <v>0.202889881929107</v>
+        <v>0.1868041012975784</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3078489816292271</v>
+        <v>0.2869294134879729</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3608008072472406</v>
+        <v>0.3373910574440824</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6141890204962901</v>
+        <v>0.5879903036643117</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6711974079978117</v>
+        <v>0.649675802439287</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6172695026847307</v>
+        <v>0.5877752306323791</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2910088233786403</v>
+        <v>0.2713042031319067</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6501162468997499</v>
+        <v>0.6261100218414531</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3748073003435002</v>
+        <v>0.3477895184345978</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2394671747204142</v>
+        <v>0.2746299530984407</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2741257341033799</v>
+        <v>0.3218498566745983</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3222436157355336</v>
+        <v>0.3701594845090534</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2879654219732959</v>
+        <v>0.3325135931512143</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07271574696372878</v>
+        <v>0.08981452010382455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3710734888884076</v>
+        <v>0.415292654229065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3565752170613359</v>
+        <v>0.4046917344942314</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2942685624874458</v>
+        <v>0.3490614527532783</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3314578991256165</v>
+        <v>0.3788320991683782</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2894586829996393</v>
+        <v>0.3459521782326062</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04477970060579173</v>
+        <v>0.09290202505540668</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2836442763851239</v>
+        <v>0.3323291646077458</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1382034926832262</v>
+        <v>-0.1432132706433129</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2272329307796688</v>
+        <v>0.2791693293259368</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3000939590430585</v>
+        <v>0.35285953845344</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3163403464872129</v>
+        <v>0.3645233685635146</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.07325960551117836</v>
+        <v>-0.02393360205987696</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1925604735689085</v>
+        <v>0.2367081197805496</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2229774765681385</v>
+        <v>0.2797381490946285</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3620239687862643</v>
+        <v>0.4111375838069673</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4491003985231324</v>
+        <v>0.5118808974615955</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6342633242298111</v>
+        <v>0.6809119770268508</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7660059468862985</v>
+        <v>0.8121780836259412</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5719608642082149</v>
+        <v>0.6190313144633457</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3546219247878535</v>
+        <v>0.3950664408733435</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6702038415387823</v>
+        <v>0.7190440696385048</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3242510951488706</v>
+        <v>0.3749513197801826</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.68736721328789</v>
+        <v>2.682229752605384</v>
       </c>
       <c r="C2" t="n">
-        <v>2.698976773865169</v>
+        <v>2.691300341479791</v>
       </c>
       <c r="D2" t="n">
-        <v>2.683846159488496</v>
+        <v>2.681665665225075</v>
       </c>
       <c r="E2" t="n">
-        <v>2.674075478295038</v>
+        <v>2.665825827116727</v>
       </c>
       <c r="F2" t="n">
-        <v>2.676468191013043</v>
+        <v>2.670107189662628</v>
       </c>
       <c r="G2" t="n">
-        <v>2.713148672937383</v>
+        <v>2.697963103764204</v>
       </c>
       <c r="H2" t="n">
-        <v>2.687147365672163</v>
+        <v>2.67987846673792</v>
       </c>
       <c r="I2" t="n">
-        <v>2.676940663749473</v>
+        <v>2.67072324234416</v>
       </c>
       <c r="J2" t="n">
-        <v>2.697361362355055</v>
+        <v>2.687292138134788</v>
       </c>
       <c r="K2" t="n">
-        <v>2.689154028961303</v>
+        <v>2.682226114281997</v>
       </c>
       <c r="L2" t="n">
-        <v>2.699446272550293</v>
+        <v>2.696846221106005</v>
       </c>
       <c r="M2" t="n">
-        <v>2.714506102975359</v>
+        <v>2.703461048296316</v>
       </c>
       <c r="N2" t="n">
-        <v>2.690450096778341</v>
+        <v>2.683647587341869</v>
       </c>
       <c r="O2" t="n">
-        <v>2.971435511523081</v>
+        <v>2.96250916258444</v>
       </c>
       <c r="P2" t="n">
-        <v>2.697154646451393</v>
+        <v>2.686504644108034</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.682095304390471</v>
+        <v>2.674911672284111</v>
       </c>
       <c r="R2" t="n">
-        <v>2.680185519786423</v>
+        <v>2.675570682552229</v>
       </c>
       <c r="S2" t="n">
-        <v>2.699218806666677</v>
+        <v>2.690320466637252</v>
       </c>
       <c r="T2" t="n">
-        <v>2.683894436289667</v>
+        <v>2.676861538395904</v>
       </c>
       <c r="U2" t="n">
-        <v>3.100221634088915</v>
+        <v>3.09388242342168</v>
       </c>
       <c r="V2" t="n">
-        <v>2.673090874821283</v>
+        <v>2.666291948787912</v>
       </c>
       <c r="W2" t="n">
-        <v>3.082255749687387</v>
+        <v>3.075843740811688</v>
       </c>
       <c r="X2" t="n">
-        <v>2.691414547255612</v>
+        <v>2.68474516032428</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.687994503042243</v>
+        <v>2.679056607388794</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.846422530187716</v>
+        <v>2.838272881279905</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.690265466449597</v>
+        <v>2.683317754036061</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.708205300213541</v>
+        <v>2.70443599432994</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.906458216289376</v>
+        <v>1.915552174805995</v>
       </c>
       <c r="C3" t="n">
-        <v>1.830600819483669</v>
+        <v>1.823558637970916</v>
       </c>
       <c r="D3" t="n">
-        <v>1.88254386659091</v>
+        <v>1.912915147802132</v>
       </c>
       <c r="E3" t="n">
-        <v>1.812324539440175</v>
+        <v>1.799273709662555</v>
       </c>
       <c r="F3" t="n">
-        <v>1.829749047080206</v>
+        <v>1.830193134623629</v>
       </c>
       <c r="G3" t="n">
-        <v>2.090133029148204</v>
+        <v>2.027749341082766</v>
       </c>
       <c r="H3" t="n">
-        <v>1.906574433850679</v>
+        <v>1.900518103163961</v>
       </c>
       <c r="I3" t="n">
-        <v>1.833181522699611</v>
+        <v>1.834658569534769</v>
       </c>
       <c r="J3" t="n">
-        <v>1.978211186898918</v>
+        <v>1.952221978677433</v>
       </c>
       <c r="K3" t="n">
-        <v>1.919757120385384</v>
+        <v>1.916132784209859</v>
       </c>
       <c r="L3" t="n">
-        <v>1.993365366644682</v>
+        <v>2.020627366809694</v>
       </c>
       <c r="M3" t="n">
-        <v>2.102989945946971</v>
+        <v>2.070039020280494</v>
       </c>
       <c r="N3" t="n">
-        <v>1.929471493618117</v>
+        <v>1.926750245066961</v>
       </c>
       <c r="O3" t="n">
-        <v>2.368176745373066</v>
+        <v>2.364811437131583</v>
       </c>
       <c r="P3" t="n">
-        <v>1.976264150337881</v>
+        <v>1.946158873447457</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.869792851884713</v>
+        <v>1.864347914245794</v>
       </c>
       <c r="R3" t="n">
-        <v>1.856526312452583</v>
+        <v>1.869498046765696</v>
       </c>
       <c r="S3" t="n">
-        <v>1.991054404851307</v>
+        <v>1.973405874893537</v>
       </c>
       <c r="T3" t="n">
-        <v>1.882879144399227</v>
+        <v>1.878513367563541</v>
       </c>
       <c r="U3" t="n">
-        <v>2.652651172518</v>
+        <v>2.651614053287445</v>
       </c>
       <c r="V3" t="n">
-        <v>1.804953947897246</v>
+        <v>1.802236504361019</v>
       </c>
       <c r="W3" t="n">
-        <v>2.633273512971493</v>
+        <v>2.628967396936902</v>
       </c>
       <c r="X3" t="n">
-        <v>1.936504458397016</v>
+        <v>1.934736828609618</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.91163927744945</v>
+        <v>1.893677970463222</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.151566945260357</v>
+        <v>2.141611137536231</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.92793421957974</v>
+        <v>1.924173161462677</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05643433828462</v>
+        <v>2.07503213526142</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.521211386484435</v>
+        <v>0.4769565124976554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3235502826063857</v>
+        <v>0.254591945510537</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4814394640554995</v>
+        <v>0.4705848860440265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3710751252399948</v>
+        <v>0.2916666279247302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3981019160920976</v>
+        <v>0.3400265874047386</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8124248332828549</v>
+        <v>0.6546719515356285</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5187281065299084</v>
+        <v>0.4503976569797223</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4034387129982575</v>
+        <v>0.3469851858408852</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6336465315401695</v>
+        <v>0.5337165795548497</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5413942914914761</v>
+        <v>0.4769154159612727</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6576499174950695</v>
+        <v>0.6420562481198525</v>
       </c>
       <c r="M4" t="n">
-        <v>0.829239431366002</v>
+        <v>0.718524822685474</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5560339737055178</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O4" t="n">
-        <v>0.506771602028647</v>
+        <v>0.4496899016262545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6317649465079196</v>
+        <v>0.5252433785673264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4616627502901832</v>
+        <v>0.394295428785587</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4400908546431569</v>
+        <v>0.4017392529236823</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6550805857001429</v>
+        <v>0.5683448493999173</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4819847727331465</v>
+        <v>0.4163200635010239</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6493404974023428</v>
+        <v>0.5893030778733959</v>
       </c>
       <c r="V4" t="n">
-        <v>0.356912627392687</v>
+        <v>0.2941034100232776</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6738847874392244</v>
+        <v>0.606239846265216</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669278855154521</v>
+        <v>0.5053691998273</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5240634179753378</v>
+        <v>0.4379929924281923</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4846700782932439</v>
+        <v>0.411277077190263</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5539484892082411</v>
+        <v>0.4892459891625247</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.754121509166026</v>
+        <v>0.7244742109301491</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.148565897617669</v>
+        <v>5.487509371340874</v>
       </c>
       <c r="C5" t="n">
-        <v>1.864153612118163</v>
+        <v>1.771208169308962</v>
       </c>
       <c r="D5" t="n">
-        <v>5.07261352192762</v>
+        <v>6.139471097371673</v>
       </c>
       <c r="E5" t="n">
-        <v>2.715849683856319</v>
+        <v>2.427413171459129</v>
       </c>
       <c r="F5" t="n">
-        <v>3.420186902544532</v>
+        <v>3.543752586402506</v>
       </c>
       <c r="G5" t="n">
-        <v>10.4719669348129</v>
+        <v>8.796266655041482</v>
       </c>
       <c r="H5" t="n">
-        <v>6.038885075169154</v>
+        <v>5.957031160095716</v>
       </c>
       <c r="I5" t="n">
-        <v>3.554694012057013</v>
+        <v>3.713497284775157</v>
       </c>
       <c r="J5" t="n">
-        <v>7.518534463942037</v>
+        <v>6.868214991183042</v>
       </c>
       <c r="K5" t="n">
-        <v>5.834014741650749</v>
+        <v>5.824081096676911</v>
       </c>
       <c r="L5" t="n">
-        <v>8.116694973326728</v>
+        <v>9.030055196030055</v>
       </c>
       <c r="M5" t="n">
-        <v>12.10451652273618</v>
+        <v>11.17105978826167</v>
       </c>
       <c r="N5" t="n">
-        <v>7.772599416279673</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O5" t="n">
-        <v>4.778440472800913</v>
+        <v>4.88884850719993</v>
       </c>
       <c r="P5" t="n">
-        <v>7.212504641552488</v>
+        <v>6.45422871983245</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.556817000076221</v>
+        <v>4.494752982680543</v>
       </c>
       <c r="R5" t="n">
-        <v>4.351203831735591</v>
+        <v>4.883957437296933</v>
       </c>
       <c r="S5" t="n">
-        <v>7.68574491400156</v>
+        <v>7.276576158064042</v>
       </c>
       <c r="T5" t="n">
-        <v>5.077765226672963</v>
+        <v>5.04976449830643</v>
       </c>
       <c r="U5" t="n">
-        <v>7.870139434828558</v>
+        <v>7.92226581792233</v>
       </c>
       <c r="V5" t="n">
-        <v>2.311525586917372</v>
+        <v>2.321730680112148</v>
       </c>
       <c r="W5" t="n">
-        <v>8.493467472225456</v>
+        <v>8.426132031688537</v>
       </c>
       <c r="X5" t="n">
-        <v>6.658226844675179</v>
+        <v>6.709948648856289</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.674104526802206</v>
+        <v>5.239543688284163</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.628633754539442</v>
+        <v>4.45846324461235</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.207486796244673</v>
+        <v>6.195869540788676</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.99467602656504</v>
+        <v>11.7205452477763</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5414112035994296</v>
+        <v>0.4977235637159484</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4334486444777689</v>
+        <v>0.3593241635016765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5913378259268813</v>
+        <v>0.4913519372623216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3912749423549894</v>
+        <v>0.396398845915869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4183017332070925</v>
+        <v>0.3607936386230331</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8326246503978512</v>
+        <v>0.7594041695267665</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6286264684012904</v>
+        <v>0.5551298749708626</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4236385301132538</v>
+        <v>0.451717403832024</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7435448934115512</v>
+        <v>0.6384487975459899</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6512926533628594</v>
+        <v>0.4976824671795678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6778497346100657</v>
+        <v>0.7467884661109901</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8494392484809959</v>
+        <v>0.8232570406766121</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5768331920650565</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6213689499988738</v>
+        <v>0.4711736832018384</v>
       </c>
       <c r="P6" t="n">
-        <v>0.746353289427325</v>
+        <v>0.6343421531281067</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5715611121615659</v>
+        <v>0.4150624800038812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5499892165145379</v>
+        <v>0.50647147091482</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7649789475715254</v>
+        <v>0.5891119006182116</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5021845898481421</v>
+        <v>0.437087114719318</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6737738093693949</v>
+        <v>0.6131915142208245</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4668109892640693</v>
+        <v>0.314870461241572</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7884855483023726</v>
+        <v>0.6317407306773281</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6768262473868339</v>
+        <v>0.6101014178184399</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5507749039324661</v>
+        <v>0.4643863330422696</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5945684401646261</v>
+        <v>0.4320441284085592</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5741483063232365</v>
+        <v>0.5939782071536643</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7766047440045107</v>
+        <v>0.7478512800224888</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6230561293061739</v>
+        <v>0.5752071261544035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4253950254281271</v>
+        <v>0.3528425591672852</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5832842068772398</v>
+        <v>0.5688354997007751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4729198680617351</v>
+        <v>0.3899172415814782</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4999466589138382</v>
+        <v>0.4382772010614868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9142695761045941</v>
+        <v>0.7529225651923763</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6205728493516495</v>
+        <v>0.5486482706364704</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5052834558199991</v>
+        <v>0.445235799497633</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7354912743619093</v>
+        <v>0.6319671932115987</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6432390343132173</v>
+        <v>0.5751660296180211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7594946603168102</v>
+        <v>0.7403068617766042</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9310841741877426</v>
+        <v>0.8167754363422209</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6578787165272597</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6082576832719673</v>
+        <v>0.5475818600851873</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7332510277512398</v>
+        <v>0.6231353370262592</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5635074931119244</v>
+        <v>0.4925460424423352</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5419355974648974</v>
+        <v>0.49998986658043</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7569253285218832</v>
+        <v>0.6665954630566642</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5838295155548866</v>
+        <v>0.5145706771577717</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7551426731577323</v>
+        <v>0.6905461035182064</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4587573702144275</v>
+        <v>0.3923540236800203</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7757295302609657</v>
+        <v>0.7044904599219636</v>
       </c>
       <c r="X7" t="n">
-        <v>0.668772628337193</v>
+        <v>0.6036198134840493</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6301416556491385</v>
+        <v>0.5393649912140749</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5865148211149844</v>
+        <v>0.5095276908470114</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6557932320299815</v>
+        <v>0.5874966028192732</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8559662519877673</v>
+        <v>0.8227248245868999</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6704105677141738</v>
+        <v>0.6210438303216466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5923180570601219</v>
+        <v>0.5134648043323032</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7502072385092369</v>
+        <v>0.7294577448657936</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5761761508738965</v>
+        <v>0.4894195721429417</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5659284867072167</v>
+        <v>0.5019961509794172</v>
       </c>
       <c r="G8" t="n">
-        <v>1.105985934451057</v>
+        <v>0.9373463400352708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7874958809836446</v>
+        <v>0.7092705158014886</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6722064874519953</v>
+        <v>0.6058580446626514</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9024143059939039</v>
+        <v>0.7925894383766168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8101620659452126</v>
+        <v>0.7357882747830394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9264176919488063</v>
+        <v>0.900929106941617</v>
       </c>
       <c r="M8" t="n">
-        <v>1.098007205819731</v>
+        <v>0.9773976815073417</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7321160849960119</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7083245382832437</v>
+        <v>0.6440366892038275</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8270743681076103</v>
+        <v>0.7135964081833135</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.587363973957082</v>
+        <v>0.5158247679730448</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7088586290968931</v>
+        <v>0.6606121117454475</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9238483601538818</v>
+        <v>0.8272177082216837</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7507525471868814</v>
+        <v>0.6751929223227899</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8640459448714027</v>
+        <v>0.7954500291955037</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5930711065303397</v>
+        <v>0.5217999762215138</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9426760604519746</v>
+        <v>0.8651352636529316</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7035878082790934</v>
+        <v>0.6374188618793728</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9160585250609621</v>
+        <v>0.8144203897978313</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6316482115253362</v>
+        <v>0.5532321946659265</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.822716263661976</v>
+        <v>0.7481188479842904</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.147788677316504</v>
+        <v>1.103250165459462</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9041335211901086</v>
+        <v>0.8383755497573858</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8231523252862936</v>
+        <v>0.7260759733783726</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9810415067354084</v>
+        <v>0.9420689139118613</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8437479340766249</v>
+        <v>0.7377481162680217</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6287249038828342</v>
+        <v>0.5577807530564887</v>
       </c>
       <c r="G9" t="n">
-        <v>1.312026892848394</v>
+        <v>1.126155994173126</v>
       </c>
       <c r="H9" t="n">
-        <v>1.018330149209816</v>
+        <v>0.9218816848475603</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9030407556781652</v>
+        <v>0.8184692137087211</v>
       </c>
       <c r="J9" t="n">
-        <v>1.133248574220077</v>
+        <v>1.005200607422688</v>
       </c>
       <c r="K9" t="n">
-        <v>1.040996334171385</v>
+        <v>0.9483994438291097</v>
       </c>
       <c r="L9" t="n">
-        <v>1.157251960174978</v>
+        <v>1.11354027598769</v>
       </c>
       <c r="M9" t="n">
-        <v>1.32884147404591</v>
+        <v>1.19000885055331</v>
       </c>
       <c r="N9" t="n">
-        <v>1.055636016385426</v>
+        <v>6.390361199836811</v>
       </c>
       <c r="O9" t="n">
-        <v>1.04504123591343</v>
+        <v>0.9576493429281246</v>
       </c>
       <c r="P9" t="n">
-        <v>1.178444114383291</v>
+        <v>1.041135593266249</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9612648098557227</v>
+        <v>0.8657794714230851</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9396928973230643</v>
+        <v>0.8732232807915183</v>
       </c>
       <c r="S9" t="n">
-        <v>1.154682628380051</v>
+        <v>1.039828877267752</v>
       </c>
       <c r="T9" t="n">
-        <v>0.981586815413054</v>
+        <v>0.8878040913688577</v>
       </c>
       <c r="U9" t="n">
-        <v>1.153176034934308</v>
+        <v>1.063908490870367</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9911606218223704</v>
+        <v>0.8925999234451064</v>
       </c>
       <c r="W9" t="n">
-        <v>1.173486830119134</v>
+        <v>1.077723874133052</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06652992819536</v>
+        <v>0.9768532276951376</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.027898955507305</v>
+        <v>0.9125984054251631</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9139245187520333</v>
+        <v>0.8164017089471266</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.053550531888149</v>
+        <v>0.960730017030361</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.253723551845936</v>
+        <v>1.195958238797988</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.678674090579006</v>
+        <v>2.672047349274314</v>
       </c>
       <c r="C2" t="n">
-        <v>2.697219322226923</v>
+        <v>2.68787739970846</v>
       </c>
       <c r="D2" t="n">
-        <v>2.68332192136858</v>
+        <v>2.680392009183838</v>
       </c>
       <c r="E2" t="n">
-        <v>2.670801853188791</v>
+        <v>2.661787447051865</v>
       </c>
       <c r="F2" t="n">
-        <v>2.669571788331786</v>
+        <v>2.66203271895922</v>
       </c>
       <c r="G2" t="n">
-        <v>2.707159733117023</v>
+        <v>2.691095152016629</v>
       </c>
       <c r="H2" t="n">
-        <v>2.679952969298208</v>
+        <v>2.671928997654845</v>
       </c>
       <c r="I2" t="n">
-        <v>2.673117623952276</v>
+        <v>2.665675243809016</v>
       </c>
       <c r="J2" t="n">
-        <v>2.692078225118516</v>
+        <v>2.68108482772379</v>
       </c>
       <c r="K2" t="n">
-        <v>2.680869710361792</v>
+        <v>2.672134965941316</v>
       </c>
       <c r="L2" t="n">
-        <v>2.691007828313257</v>
+        <v>2.686569635473952</v>
       </c>
       <c r="M2" t="n">
-        <v>2.705044677341145</v>
+        <v>2.693237291451481</v>
       </c>
       <c r="N2" t="n">
-        <v>2.680599361720736</v>
+        <v>2.672293837671493</v>
       </c>
       <c r="O2" t="n">
-        <v>2.955079370310246</v>
+        <v>2.943620693105744</v>
       </c>
       <c r="P2" t="n">
-        <v>2.69342637663693</v>
+        <v>2.681543926796318</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.668975193142845</v>
+        <v>2.660809367733972</v>
       </c>
       <c r="R2" t="n">
-        <v>2.673863784145331</v>
+        <v>2.668337351351107</v>
       </c>
       <c r="S2" t="n">
-        <v>2.692992528330864</v>
+        <v>2.683025969363164</v>
       </c>
       <c r="T2" t="n">
-        <v>2.678087751180785</v>
+        <v>2.669793248149384</v>
       </c>
       <c r="U2" t="n">
-        <v>3.085747007962281</v>
+        <v>3.07757320181054</v>
       </c>
       <c r="V2" t="n">
-        <v>2.673491320999168</v>
+        <v>2.665956801124032</v>
       </c>
       <c r="W2" t="n">
-        <v>3.070821100507931</v>
+        <v>3.062320160911439</v>
       </c>
       <c r="X2" t="n">
-        <v>2.694847651188419</v>
+        <v>2.68700525043864</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.694068646525744</v>
+        <v>2.682830579193503</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.841579208094478</v>
+        <v>2.832022085052255</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.685554567743873</v>
+        <v>2.677650603776432</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.702127338221934</v>
+        <v>2.696698545906433</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.868411097153413</v>
+        <v>1.872470112073578</v>
       </c>
       <c r="C3" t="n">
-        <v>1.842575484323703</v>
+        <v>1.83281536844156</v>
       </c>
       <c r="D3" t="n">
-        <v>1.902502898618257</v>
+        <v>1.933073090733255</v>
       </c>
       <c r="E3" t="n">
-        <v>1.812700261787573</v>
+        <v>1.79975540079381</v>
       </c>
       <c r="F3" t="n">
-        <v>1.804122312026425</v>
+        <v>1.801714624197169</v>
       </c>
       <c r="G3" t="n">
-        <v>2.070883420297323</v>
+        <v>2.007839976402368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.878879252261235</v>
+        <v>1.87300524920383</v>
       </c>
       <c r="I3" t="n">
-        <v>1.829595292865489</v>
+        <v>1.827885461459543</v>
       </c>
       <c r="J3" t="n">
-        <v>1.964133087536611</v>
+        <v>1.937127987001215</v>
       </c>
       <c r="K3" t="n">
-        <v>1.884038499308597</v>
+        <v>1.873105050005258</v>
       </c>
       <c r="L3" t="n">
-        <v>1.956810698805064</v>
+        <v>1.976513359021031</v>
       </c>
       <c r="M3" t="n">
-        <v>2.059402067851794</v>
+        <v>2.026547626609576</v>
       </c>
       <c r="N3" t="n">
-        <v>1.882851283217087</v>
+        <v>1.874962983847797</v>
       </c>
       <c r="O3" t="n">
-        <v>2.320558101892857</v>
+        <v>2.311646382191754</v>
       </c>
       <c r="P3" t="n">
-        <v>1.973230790548873</v>
+        <v>1.93992048230803</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.799703839923157</v>
+        <v>1.792814288266062</v>
       </c>
       <c r="R3" t="n">
-        <v>1.835047918098096</v>
+        <v>1.847078699616997</v>
       </c>
       <c r="S3" t="n">
-        <v>1.970286455316366</v>
+        <v>1.950589636272262</v>
       </c>
       <c r="T3" t="n">
-        <v>1.865134289745377</v>
+        <v>1.85732232034075</v>
       </c>
       <c r="U3" t="n">
-        <v>2.593138484052095</v>
+        <v>2.591639231851396</v>
       </c>
       <c r="V3" t="n">
-        <v>1.831308509403693</v>
+        <v>1.828899061331237</v>
       </c>
       <c r="W3" t="n">
-        <v>2.598529820206869</v>
+        <v>2.593792221912525</v>
       </c>
       <c r="X3" t="n">
-        <v>1.98476094415236</v>
+        <v>1.980182896128464</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.978729074141184</v>
+        <v>1.949917290759077</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.149545634358896</v>
+        <v>2.137333682493193</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.918064145676754</v>
+        <v>1.913044305391522</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.036880275822603</v>
+        <v>2.04922381919951</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4545527023778617</v>
+        <v>0.407581424772971</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3370868922565325</v>
+        <v>0.2708350355816703</v>
       </c>
       <c r="D4" t="n">
-        <v>0.507052089253867</v>
+        <v>0.501838197184277</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3656321596472443</v>
+        <v>0.2916911093822357</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3517380112295718</v>
+        <v>0.2944615684064227</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7763111388877363</v>
+        <v>0.6227351191696222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4689982258245231</v>
+        <v>0.4062445887866503</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3917898557279913</v>
+        <v>0.3356055622291251</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6055409424349318</v>
+        <v>0.5092791173289669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4793532378594075</v>
+        <v>0.4085710953324505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5938679438858699</v>
+        <v>0.5716173279795991</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7544925217283309</v>
+        <v>0.6492193878670401</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4762995255921656</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4467633746820134</v>
+        <v>0.3894871591257478</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6211865597889565</v>
+        <v>0.5148496365254933</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3449991941231483</v>
+        <v>0.280643253547893</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4002180783591979</v>
+        <v>0.3656752915470081</v>
       </c>
       <c r="S4" t="n">
-        <v>0.616286043591884</v>
+        <v>0.5315899890912766</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4479297291454666</v>
+        <v>0.3821203156291479</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5598039784598777</v>
+        <v>0.5066425410507474</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3932123145147067</v>
+        <v>0.3362089086008507</v>
       </c>
       <c r="W4" t="n">
-        <v>0.623904555642368</v>
+        <v>0.5651153745046185</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6372405096666224</v>
+        <v>0.5765377993985449</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6252010838758252</v>
+        <v>0.5261848300091474</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.480651057918531</v>
+        <v>0.4100096706653265</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5322708571308681</v>
+        <v>0.4708727619988337</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7172404910520866</v>
+        <v>0.6830462560138304</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.958055476179096</v>
+        <v>4.170838344833232</v>
       </c>
       <c r="C5" t="n">
-        <v>2.11571954365816</v>
+        <v>2.006870883029005</v>
       </c>
       <c r="D5" t="n">
-        <v>5.363361201520212</v>
+        <v>6.380363568734685</v>
       </c>
       <c r="E5" t="n">
-        <v>2.630839924161283</v>
+        <v>2.385795812483976</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4893059036893</v>
+        <v>2.542952330450365</v>
       </c>
       <c r="G5" t="n">
-        <v>9.218173476927124</v>
+        <v>7.678075947073498</v>
       </c>
       <c r="H5" t="n">
-        <v>4.908349806584053</v>
+        <v>4.862250212122918</v>
       </c>
       <c r="I5" t="n">
-        <v>3.283804979191891</v>
+        <v>3.360799954183372</v>
       </c>
       <c r="J5" t="n">
-        <v>6.664528239504015</v>
+        <v>6.057281150282477</v>
       </c>
       <c r="K5" t="n">
-        <v>4.374490176141156</v>
+        <v>4.193324208790639</v>
       </c>
       <c r="L5" t="n">
-        <v>6.61542533919635</v>
+        <v>7.27780174617819</v>
       </c>
       <c r="M5" t="n">
-        <v>10.12171948613883</v>
+        <v>9.274190589615381</v>
       </c>
       <c r="N5" t="n">
-        <v>5.824242682867696</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O5" t="n">
-        <v>3.650765202289632</v>
+        <v>3.686737984293954</v>
       </c>
       <c r="P5" t="n">
-        <v>6.662665286208461</v>
+        <v>5.898502499935379</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.286921718727479</v>
+        <v>2.210860075239822</v>
       </c>
       <c r="R5" t="n">
-        <v>3.498812330607802</v>
+        <v>3.992983793333264</v>
       </c>
       <c r="S5" t="n">
-        <v>6.654793725326618</v>
+        <v>6.242126373335311</v>
       </c>
       <c r="T5" t="n">
-        <v>4.311426980293407</v>
+        <v>4.207565087017858</v>
       </c>
       <c r="U5" t="n">
-        <v>5.910987345501463</v>
+        <v>6.025228910518868</v>
       </c>
       <c r="V5" t="n">
-        <v>2.861340048766598</v>
+        <v>2.898378065444698</v>
       </c>
       <c r="W5" t="n">
-        <v>7.239212027820781</v>
+        <v>7.262263708540135</v>
       </c>
       <c r="X5" t="n">
-        <v>7.665096555827024</v>
+        <v>7.655309600745091</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.264827038208028</v>
+        <v>6.577334688066912</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.188246371154398</v>
+        <v>4.01507191164377</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.615963444585392</v>
+        <v>5.592627239607832</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.79209543678917</v>
+        <v>10.30577393607277</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4751269518135873</v>
+        <v>0.5024395574342215</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3576611416922572</v>
+        <v>0.2911834661992054</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6083826367791302</v>
+        <v>0.5966963298455273</v>
       </c>
       <c r="E6" t="n">
-        <v>0.386206409082969</v>
+        <v>0.3865492420434862</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4530685587548343</v>
+        <v>0.3148099990239573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7968853883234615</v>
+        <v>0.6430835497871561</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4895724752602473</v>
+        <v>0.4265930194041854</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4123641051637156</v>
+        <v>0.3559539928466599</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7068714899601951</v>
+        <v>0.6041372499902189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5806837853846701</v>
+        <v>0.5034292279937013</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6144421933215933</v>
+        <v>0.6664754606408494</v>
       </c>
       <c r="M6" t="n">
-        <v>0.855823069253593</v>
+        <v>0.6695678184845748</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4974084702634688</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4678723193533158</v>
+        <v>0.4883504966487201</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7267173183120438</v>
+        <v>0.6136724186072775</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4463297416484109</v>
+        <v>0.3755013862091434</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5015486258844607</v>
+        <v>0.3860237221645427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6368602930276077</v>
+        <v>0.6264481217525268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4685039785811914</v>
+        <v>0.4024687462466826</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5836184376616597</v>
+        <v>0.5301891089001847</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4945428620399699</v>
+        <v>0.4310670412621008</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6486212556320207</v>
+        <v>0.6639933428894682</v>
       </c>
       <c r="X6" t="n">
-        <v>0.657814759102348</v>
+        <v>0.5968862300160804</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6512560220058007</v>
+        <v>0.5521731392681352</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.501225307354255</v>
+        <v>0.504867803326577</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6336014046561294</v>
+        <v>0.5657308946600854</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7397703213979731</v>
+        <v>0.7056420265565466</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5443327824142759</v>
+        <v>0.4948793727496889</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4268669722929465</v>
+        <v>0.3581329835583893</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5968321692902809</v>
+        <v>0.5891361451609953</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4554122396836581</v>
+        <v>0.3789890573589539</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4415180912659858</v>
+        <v>0.3817595163831406</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8660912189241498</v>
+        <v>0.7100330671463398</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5587783058609355</v>
+        <v>0.493542536763369</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4815699357644052</v>
+        <v>0.4229035102058445</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6953210224713459</v>
+        <v>0.5965770653056841</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5691333178958208</v>
+        <v>0.4958690433091686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6836480239222831</v>
+        <v>0.6589152759563179</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8442726017647435</v>
+        <v>0.7365173358437573</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5660796056285797</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5362095118002214</v>
+        <v>0.4764512029414833</v>
       </c>
       <c r="P7" t="n">
-        <v>0.710632696907164</v>
+        <v>0.6018136803412295</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4347792741595619</v>
+        <v>0.3679412015246117</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4899981583956116</v>
+        <v>0.4529732395237261</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7060661236282973</v>
+        <v>0.6188879370679953</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5377098091818805</v>
+        <v>0.4694182636058651</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6522253153843124</v>
+        <v>0.596725250130305</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4829923945511205</v>
+        <v>0.4235068565775688</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7136846356787818</v>
+        <v>0.6524133224813364</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7270205897030348</v>
+        <v>0.6638357473752647</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7182213736782972</v>
+        <v>0.6166809152177679</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5704311379549449</v>
+        <v>0.4973076186420445</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6220509371672815</v>
+        <v>0.558170709975553</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8070205710884998</v>
+        <v>0.7703442039905498</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5852466540506208</v>
+        <v>0.5338350084806455</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5726671566651056</v>
+        <v>0.4973954961140183</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7426323536624402</v>
+        <v>0.7283986577166252</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5453635564943947</v>
+        <v>0.4648411168847659</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4987720245842271</v>
+        <v>0.436341791205109</v>
       </c>
       <c r="G8" t="n">
-        <v>1.033640263505903</v>
+        <v>0.8700948640456723</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7045784902330958</v>
+        <v>0.6328050493190001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6273701201365646</v>
+        <v>0.5621660227614739</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8411212068435057</v>
+        <v>0.7358395778613147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7149335022679801</v>
+        <v>0.635131555864799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8294482082944422</v>
+        <v>0.7981777885119485</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9900727861368901</v>
+        <v>0.8757798483995787</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6305753505100177</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6233823654810435</v>
+        <v>0.5596606512038519</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7923287007486384</v>
+        <v>0.6797854032194498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4550805914539843</v>
+        <v>0.387184246582239</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6357983427677715</v>
+        <v>0.5922357520793574</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8518663080004565</v>
+        <v>0.7581504496236258</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6835099935540396</v>
+        <v>0.6086807761614951</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7472254670242877</v>
+        <v>0.6873811021582643</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5998990441537918</v>
+        <v>0.5352860565468317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8595054331287217</v>
+        <v>0.7916955481536033</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7569349459179227</v>
+        <v>0.6922721169707042</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9679562924645911</v>
+        <v>0.8555709116930321</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6093966924913059</v>
+        <v>0.5344000026431801</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7678511215394414</v>
+        <v>0.6974332225311843</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.062383279481617</v>
+        <v>1.014385636860154</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7793120083035351</v>
+        <v>0.7133704816224133</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7611680770506818</v>
+        <v>0.6699344458864066</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9311332740480163</v>
+        <v>0.9009376074890127</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7667902759128805</v>
+        <v>0.6692548845958877</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5468551305894349</v>
+        <v>0.4784551236312272</v>
       </c>
       <c r="G9" t="n">
-        <v>1.200392344466699</v>
+        <v>1.021834547519499</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8930794106186719</v>
+        <v>0.8053439990913884</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8158710405221394</v>
+        <v>0.734704972533863</v>
       </c>
       <c r="J9" t="n">
-        <v>1.029622127229082</v>
+        <v>0.9083785276337034</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9034344226535568</v>
+        <v>0.8076705056371852</v>
       </c>
       <c r="L9" t="n">
-        <v>1.017949128680018</v>
+        <v>0.9707167382843362</v>
       </c>
       <c r="M9" t="n">
-        <v>1.178573706522479</v>
+        <v>1.048318798171778</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9003807103863162</v>
+        <v>4.600288343215076</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9037597277551562</v>
+        <v>0.8195095224113714</v>
       </c>
       <c r="P9" t="n">
-        <v>1.085341392713254</v>
+        <v>0.9515972076114253</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7690803997021096</v>
+        <v>0.6797426818977697</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8242992631533472</v>
+        <v>0.7647747018517435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.040367228386032</v>
+        <v>0.9306893993960135</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8720109139396162</v>
+        <v>0.7812197259338844</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9871253730200845</v>
+        <v>0.9089400885873852</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9319086964788732</v>
+        <v>0.842986350914811</v>
       </c>
       <c r="W9" t="n">
-        <v>1.047985740436518</v>
+        <v>0.964214784809354</v>
       </c>
       <c r="X9" t="n">
-        <v>1.061321694460771</v>
+        <v>0.975637209703283</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.052522478436032</v>
+        <v>0.9284823775457859</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8448499900544817</v>
+        <v>0.7528512424824225</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.956352041925017</v>
+        <v>0.8699721723035719</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.141321675846237</v>
+        <v>1.082145666318569</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672297873117211</v>
+        <v>2.66615080872666</v>
       </c>
       <c r="C2" t="n">
-        <v>2.694340263196875</v>
+        <v>2.685329377744259</v>
       </c>
       <c r="D2" t="n">
-        <v>2.671470166762514</v>
+        <v>2.668210226361532</v>
       </c>
       <c r="E2" t="n">
-        <v>2.663049028935491</v>
+        <v>2.655090726236734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.667198115458162</v>
+        <v>2.660552652029079</v>
       </c>
       <c r="G2" t="n">
-        <v>2.696085847332212</v>
+        <v>2.681939410045278</v>
       </c>
       <c r="H2" t="n">
-        <v>2.673545629615623</v>
+        <v>2.666221043927937</v>
       </c>
       <c r="I2" t="n">
-        <v>2.669743074564355</v>
+        <v>2.662573863465164</v>
       </c>
       <c r="J2" t="n">
-        <v>2.684534543569245</v>
+        <v>2.674903125675851</v>
       </c>
       <c r="K2" t="n">
-        <v>2.680412437418542</v>
+        <v>2.672360625848101</v>
       </c>
       <c r="L2" t="n">
-        <v>2.682156415112697</v>
+        <v>2.677698942461813</v>
       </c>
       <c r="M2" t="n">
-        <v>2.694010652391706</v>
+        <v>2.683597918349943</v>
       </c>
       <c r="N2" t="n">
-        <v>2.673397517006393</v>
+        <v>2.666039130558016</v>
       </c>
       <c r="O2" t="n">
-        <v>2.940829659073769</v>
+        <v>2.929576512604188</v>
       </c>
       <c r="P2" t="n">
-        <v>2.686991249945158</v>
+        <v>2.67625016575017</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.667819029499453</v>
+        <v>2.660454218461141</v>
       </c>
       <c r="R2" t="n">
-        <v>2.668295549367389</v>
+        <v>2.66305184793832</v>
       </c>
       <c r="S2" t="n">
-        <v>2.685396823094013</v>
+        <v>2.676400239383266</v>
       </c>
       <c r="T2" t="n">
-        <v>2.671892707996023</v>
+        <v>2.664746641334018</v>
       </c>
       <c r="U2" t="n">
-        <v>3.080812186207357</v>
+        <v>3.074391806773402</v>
       </c>
       <c r="V2" t="n">
-        <v>2.677336816758115</v>
+        <v>2.671075447487787</v>
       </c>
       <c r="W2" t="n">
-        <v>3.063395249776489</v>
+        <v>3.056235057932575</v>
       </c>
       <c r="X2" t="n">
-        <v>2.692104201107571</v>
+        <v>2.685047355599145</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.70585595890969</v>
+        <v>2.69236094051954</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.8321857491296</v>
+        <v>2.823589489375509</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.683044007508072</v>
+        <v>2.675691740169273</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.69387511295085</v>
+        <v>2.68882880854093</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.851280033674472</v>
+        <v>1.85377421746337</v>
       </c>
       <c r="C3" t="n">
-        <v>1.852034476028299</v>
+        <v>1.842268568747785</v>
       </c>
       <c r="D3" t="n">
-        <v>1.846037253843526</v>
+        <v>1.869181170460592</v>
       </c>
       <c r="E3" t="n">
-        <v>1.785721673290676</v>
+        <v>1.775347217004387</v>
       </c>
       <c r="F3" t="n">
-        <v>1.815684577966185</v>
+        <v>1.814673256942431</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02006167407383</v>
+        <v>1.965778843242996</v>
       </c>
       <c r="H3" t="n">
-        <v>1.861602746654363</v>
+        <v>1.855737246150848</v>
       </c>
       <c r="I3" t="n">
-        <v>1.833943739155945</v>
+        <v>1.829189088430941</v>
       </c>
       <c r="J3" t="n">
-        <v>1.93860809915929</v>
+        <v>1.916356514038503</v>
       </c>
       <c r="K3" t="n">
-        <v>1.909197404448204</v>
+        <v>1.898157925797994</v>
       </c>
       <c r="L3" t="n">
-        <v>1.921775530512291</v>
+        <v>1.936317846576264</v>
       </c>
       <c r="M3" t="n">
-        <v>2.00851449912411</v>
+        <v>1.980666135483313</v>
       </c>
       <c r="N3" t="n">
-        <v>1.859959327212068</v>
+        <v>1.853852139339696</v>
       </c>
       <c r="O3" t="n">
-        <v>2.282409301616573</v>
+        <v>2.27154471166236</v>
       </c>
       <c r="P3" t="n">
-        <v>1.955491116396283</v>
+        <v>1.925377960953017</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.819850492542678</v>
+        <v>1.813697069359274</v>
       </c>
       <c r="R3" t="n">
-        <v>1.823779611239247</v>
+        <v>1.832832307062435</v>
       </c>
       <c r="S3" t="n">
-        <v>1.944522474624713</v>
+        <v>1.92677080347792</v>
       </c>
       <c r="T3" t="n">
-        <v>1.849400746289129</v>
+        <v>1.844813249807112</v>
       </c>
       <c r="U3" t="n">
-        <v>2.600274288705444</v>
+        <v>2.602547348560221</v>
       </c>
       <c r="V3" t="n">
-        <v>1.886838044271841</v>
+        <v>1.888507661231164</v>
       </c>
       <c r="W3" t="n">
-        <v>2.59055093303678</v>
+        <v>2.587993849863943</v>
       </c>
       <c r="X3" t="n">
-        <v>1.993261589637038</v>
+        <v>1.989305694518647</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.091742755156202</v>
+        <v>2.041797919894343</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.125946839081294</v>
+        <v>2.114406647342397</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.928727663540073</v>
+        <v>1.922664381985143</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.006125843056286</v>
+        <v>2.016237545811305</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4215468614935488</v>
+        <v>0.3822361310097263</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3468210583082326</v>
+        <v>0.2919286471670149</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4121975374535026</v>
+        <v>0.4054982005745318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3170769117825061</v>
+        <v>0.2573074113966876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3639427527301686</v>
+        <v>0.3190023758312358</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6902429732607621</v>
+        <v>0.5605756460189579</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4356408451394702</v>
+        <v>0.3830294699179339</v>
       </c>
       <c r="I4" t="n">
-        <v>0.392689236573647</v>
+        <v>0.3418328888050213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5594316426588709</v>
+        <v>0.4807985700734707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5132045981610939</v>
+        <v>0.4523788720534019</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5329036284859252</v>
+        <v>0.5126776139522464</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6692156074267697</v>
+        <v>0.5818729509640393</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4339678450830554</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O4" t="n">
-        <v>0.396603053344886</v>
+        <v>0.3470793044547505</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5875153120524856</v>
+        <v>0.4963130145240098</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3709562624611219</v>
+        <v>0.3178905233996907</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3763387735794055</v>
+        <v>0.347231943313049</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5695055272962318</v>
+        <v>0.4980081652471087</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4169703350645758</v>
+        <v>0.3663754143608963</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5739230430905452</v>
+        <v>0.5340631317482722</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4762334668935017</v>
+        <v>0.4358670156862766</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6129756902457</v>
+        <v>0.5666141727054108</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6452684475056831</v>
+        <v>0.5956813207754654</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7988288485719306</v>
+        <v>0.6755134803113287</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4448030966710731</v>
+        <v>0.384751515190798</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5429293929043957</v>
+        <v>0.4900053406993378</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.663102370936414</v>
+        <v>0.6355603224375077</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.446082675318209</v>
+        <v>3.608769363067611</v>
       </c>
       <c r="C5" t="n">
-        <v>2.409325436767251</v>
+        <v>2.319422084498735</v>
       </c>
       <c r="D5" t="n">
-        <v>3.625137446373858</v>
+        <v>4.387508193130389</v>
       </c>
       <c r="E5" t="n">
-        <v>1.832131214295202</v>
+        <v>1.663161542546884</v>
       </c>
       <c r="F5" t="n">
-        <v>2.842755406793398</v>
+        <v>2.932609777314063</v>
       </c>
       <c r="G5" t="n">
-        <v>7.683136955248974</v>
+        <v>6.41091149868021</v>
       </c>
       <c r="H5" t="n">
-        <v>4.429896245784929</v>
+        <v>4.380319190464679</v>
       </c>
       <c r="I5" t="n">
-        <v>3.400758392005069</v>
+        <v>3.383223929695669</v>
       </c>
       <c r="J5" t="n">
-        <v>5.887442622390813</v>
+        <v>5.417409787730313</v>
       </c>
       <c r="K5" t="n">
-        <v>5.06892193065454</v>
+        <v>4.882491642758096</v>
       </c>
       <c r="L5" t="n">
-        <v>5.485359307335433</v>
+        <v>5.980113986696716</v>
       </c>
       <c r="M5" t="n">
-        <v>8.323123643854624</v>
+        <v>7.646563076445405</v>
       </c>
       <c r="N5" t="n">
-        <v>5.915171196201491</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O5" t="n">
-        <v>2.996598013177524</v>
+        <v>2.994383337229399</v>
       </c>
       <c r="P5" t="n">
-        <v>6.04140800152737</v>
+        <v>5.379799163065059</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.829170846647984</v>
+        <v>2.771126274220375</v>
       </c>
       <c r="R5" t="n">
-        <v>3.198081535771089</v>
+        <v>3.598849764744508</v>
       </c>
       <c r="S5" t="n">
-        <v>5.935794145139915</v>
+        <v>5.576524426529561</v>
       </c>
       <c r="T5" t="n">
-        <v>3.889787991148791</v>
+        <v>3.87789884361403</v>
       </c>
       <c r="U5" t="n">
-        <v>6.056898423638801</v>
+        <v>6.231850002486545</v>
       </c>
       <c r="V5" t="n">
-        <v>4.240551472674692</v>
+        <v>4.376094486795806</v>
       </c>
       <c r="W5" t="n">
-        <v>7.201496047013981</v>
+        <v>7.263188614450455</v>
       </c>
       <c r="X5" t="n">
-        <v>7.725721382848134</v>
+        <v>7.728975203239306</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.64621440714913</v>
+        <v>9.342850115272299</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.570678373289059</v>
+        <v>3.409333369537087</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.982603278217648</v>
+        <v>5.927384219207523</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.768634539979004</v>
+        <v>9.203003178177097</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.521175711276646</v>
+        <v>0.4054733786155179</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3707272100931839</v>
+        <v>0.3151658947728097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4361036892384537</v>
+        <v>0.4984300939279508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4167057615656031</v>
+        <v>0.3502393047501064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3878489045151198</v>
+        <v>0.3422396234370312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7898718230438604</v>
+        <v>0.583812893624753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4595469969244212</v>
+        <v>0.4759613632713529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4165953883585983</v>
+        <v>0.365070136410815</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6590604924419682</v>
+        <v>0.5737304634268886</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6128334479441897</v>
+        <v>0.5453107654068203</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6325324782690223</v>
+        <v>0.535914861558042</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6931217592117205</v>
+        <v>0.6051101985698359</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4588864631736567</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5006354895099269</v>
+        <v>0.3714659334793805</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6092086598189634</v>
+        <v>0.5935755785281523</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4705851122442187</v>
+        <v>0.4108224167531085</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4759676233625031</v>
+        <v>0.4401638366664674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6691343770793283</v>
+        <v>0.5212454128528987</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5165991848476732</v>
+        <v>0.4593073077143141</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5996012243053344</v>
+        <v>0.6297731716569744</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5001396186784528</v>
+        <v>0.4591042632920694</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7170116741800926</v>
+        <v>0.5943072841060361</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6691745992906345</v>
+        <v>0.6189185683812566</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8276742425200782</v>
+        <v>0.7048877395899523</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5444319464541699</v>
+        <v>0.4079887627965929</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6425582426874928</v>
+        <v>0.5829372340527569</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6889307704625397</v>
+        <v>0.6609976123371006</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5082469041755691</v>
+        <v>0.4673366408910056</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4335211009902533</v>
+        <v>0.3770291570482934</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4988975801355231</v>
+        <v>0.490598710455811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4037769544645262</v>
+        <v>0.3424079212779663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4506427954121892</v>
+        <v>0.4041028857125154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7769430159427821</v>
+        <v>0.6456761559002373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5223408878214905</v>
+        <v>0.4681299797992134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4793892792556677</v>
+        <v>0.4269333986862999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6461316853408913</v>
+        <v>0.5658990799547493</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5999046408431136</v>
+        <v>0.5374793819346805</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6196036711679466</v>
+        <v>0.5977781238335272</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7559156501087896</v>
+        <v>0.6669734608453165</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5206678877650758</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O7" t="n">
-        <v>0.482969425321942</v>
+        <v>0.431846057415106</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6738816840295432</v>
+        <v>0.5810797674843656</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.457656305143142</v>
+        <v>0.4029910332809694</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4630388162614265</v>
+        <v>0.4323324531943277</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6562055699782527</v>
+        <v>0.5831086751283878</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5036703777465958</v>
+        <v>0.4514759242421761</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6612410176103987</v>
+        <v>0.6212341019945702</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5629335095755215</v>
+        <v>0.5209675255675554</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6996757329277198</v>
+        <v>0.6517146825866892</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7319684901877033</v>
+        <v>0.6807818306567442</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8873009206837897</v>
+        <v>0.7633921367478924</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5315031393530931</v>
+        <v>0.4698520250720756</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6296294355864163</v>
+        <v>0.5751058505806167</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7498024136184355</v>
+        <v>0.7206608323187855</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5461200324013041</v>
+        <v>0.5031824745558057</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5714331035921998</v>
+        <v>0.5087770116530161</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6368095827374699</v>
+        <v>0.6223465650605342</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4884212074405453</v>
+        <v>0.423090778674076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5041008110768829</v>
+        <v>0.454889133403345</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9355987308324881</v>
+        <v>0.7973099192868168</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6602528904234379</v>
+        <v>0.5998778344039355</v>
       </c>
       <c r="I8" t="n">
-        <v>0.617301281857615</v>
+        <v>0.5586812532910216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7840436879428393</v>
+        <v>0.6976469345594718</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7378166434450613</v>
+        <v>0.6692272365394031</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7575156737698933</v>
+        <v>0.7295259784382493</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8938276527107084</v>
+        <v>0.7987213154502457</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5810330265644672</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5649787862831745</v>
+        <v>0.5100168664113656</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7506673138980801</v>
+        <v>0.6542428595073037</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4758695113012227</v>
+        <v>0.4199899309865481</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6009508188633732</v>
+        <v>0.5640803077990503</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7941175725802003</v>
+        <v>0.7148565297331106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6415823803485436</v>
+        <v>0.5832237788468972</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7508436676768563</v>
+        <v>0.7065913603257179</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6728020987648046</v>
+        <v>0.6261842863117272</v>
       </c>
       <c r="W8" t="n">
-        <v>0.837607395949478</v>
+        <v>0.7834813846388096</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7593504579101962</v>
+        <v>0.7065703391126082</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.123591611905384</v>
+        <v>0.9899974483483754</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.567517994134791</v>
+        <v>0.5039164294654738</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7675414381883632</v>
+        <v>0.7068537051853382</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9922133855409879</v>
+        <v>0.9525863669484902</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7156418598327792</v>
+        <v>0.6616501779456415</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7313404439789092</v>
+        <v>0.6569094306044901</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7967169231241787</v>
+        <v>0.7704789840120085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6807267258367895</v>
+        <v>0.6025397465519595</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5400092326231548</v>
+        <v>0.4867284689520754</v>
       </c>
       <c r="G9" t="n">
-        <v>1.074762369520754</v>
+        <v>0.9255564365832735</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8201602308101461</v>
+        <v>0.7480102533554082</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7772086222443222</v>
+        <v>0.7068136722424975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9439510283295469</v>
+        <v>0.8457793535109446</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8977239838317701</v>
+        <v>0.817359655490876</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9174230141566013</v>
+        <v>0.8776583973897235</v>
       </c>
       <c r="M9" t="n">
-        <v>1.053734993097445</v>
+        <v>0.9468537344015149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8184872307537303</v>
+        <v>4.039891822728022</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8110889766751808</v>
+        <v>0.7404168018174364</v>
       </c>
       <c r="P9" t="n">
-        <v>1.008518440881551</v>
+        <v>0.8958176090961852</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7554756587211129</v>
+        <v>0.6828713139640068</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7608581592500815</v>
+        <v>0.7122127267505243</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9540249129669094</v>
+        <v>0.8629889486845831</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8014897207352514</v>
+        <v>0.7313561977983721</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9602144581910598</v>
+        <v>0.9018220617410317</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9651005569392865</v>
+        <v>0.8995898840512738</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9974950759163751</v>
+        <v>0.9315949561428863</v>
       </c>
       <c r="X9" t="n">
-        <v>1.029787833176359</v>
+        <v>0.9606621042129396</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.185120263672445</v>
+        <v>1.043272410304089</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7748046218360418</v>
+        <v>0.6981431682389106</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9274487785750716</v>
+        <v>0.8549861241368137</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.047621756607089</v>
+        <v>1.000541105874983</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.614141996236274</v>
+        <v>2.607382439408013</v>
       </c>
       <c r="C2" t="n">
-        <v>2.641547679288493</v>
+        <v>2.631709186067934</v>
       </c>
       <c r="D2" t="n">
-        <v>2.619422810771437</v>
+        <v>2.612797427233207</v>
       </c>
       <c r="E2" t="n">
-        <v>2.610678444628744</v>
+        <v>2.603529189250944</v>
       </c>
       <c r="F2" t="n">
-        <v>2.61045925868026</v>
+        <v>2.603724332808019</v>
       </c>
       <c r="G2" t="n">
-        <v>2.625144227042195</v>
+        <v>2.616104402181124</v>
       </c>
       <c r="H2" t="n">
-        <v>2.615029284580122</v>
+        <v>2.608107059996717</v>
       </c>
       <c r="I2" t="n">
-        <v>2.614150261051238</v>
+        <v>2.608019723056409</v>
       </c>
       <c r="J2" t="n">
-        <v>2.620133653935317</v>
+        <v>2.612449863941507</v>
       </c>
       <c r="K2" t="n">
-        <v>2.619917048399954</v>
+        <v>2.613046955593907</v>
       </c>
       <c r="L2" t="n">
-        <v>2.611596486330555</v>
+        <v>2.605564290172252</v>
       </c>
       <c r="M2" t="n">
-        <v>2.625618822176028</v>
+        <v>2.617500101956755</v>
       </c>
       <c r="N2" t="n">
-        <v>2.616626539880058</v>
+        <v>2.609585570244394</v>
       </c>
       <c r="O2" t="n">
-        <v>2.862345376507484</v>
+        <v>2.84741789980326</v>
       </c>
       <c r="P2" t="n">
-        <v>2.615068323255491</v>
+        <v>2.607489844775565</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.613962248813449</v>
+        <v>2.606977665434417</v>
       </c>
       <c r="R2" t="n">
-        <v>2.598755426724663</v>
+        <v>2.59276795069034</v>
       </c>
       <c r="S2" t="n">
-        <v>2.617443120803427</v>
+        <v>2.609641493071008</v>
       </c>
       <c r="T2" t="n">
-        <v>2.612948531288769</v>
+        <v>2.606414000842314</v>
       </c>
       <c r="U2" t="n">
-        <v>3.015650894302451</v>
+        <v>3.007980459353699</v>
       </c>
       <c r="V2" t="n">
-        <v>2.614052441801087</v>
+        <v>2.607074430289847</v>
       </c>
       <c r="W2" t="n">
-        <v>3.009270593916464</v>
+        <v>3.001018681966039</v>
       </c>
       <c r="X2" t="n">
-        <v>2.625928805735802</v>
+        <v>2.619000030464934</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.617607230279631</v>
+        <v>2.61052308625209</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.763336026098985</v>
+        <v>2.753311417008083</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62667727303989</v>
+        <v>2.620655396929055</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.622744322974275</v>
+        <v>2.616487247712306</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.715474676283848</v>
+        <v>1.710715210052923</v>
       </c>
       <c r="C3" t="n">
-        <v>1.75302657618332</v>
+        <v>1.742096449244728</v>
       </c>
       <c r="D3" t="n">
-        <v>1.753414384701595</v>
+        <v>1.749622832506326</v>
       </c>
       <c r="E3" t="n">
-        <v>1.690878387956411</v>
+        <v>1.68334494532479</v>
       </c>
       <c r="F3" t="n">
-        <v>1.689317450894293</v>
+        <v>1.684741381367997</v>
       </c>
       <c r="G3" t="n">
-        <v>1.793335333706892</v>
+        <v>1.772424522334517</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72208605753056</v>
+        <v>1.716171237865246</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7157267971865</v>
+        <v>1.715479324999793</v>
       </c>
       <c r="J3" t="n">
-        <v>1.758039546909673</v>
+        <v>1.746729894688288</v>
       </c>
       <c r="K3" t="n">
-        <v>1.756638204589426</v>
+        <v>1.751091485065549</v>
       </c>
       <c r="L3" t="n">
-        <v>1.697425156660053</v>
+        <v>1.697816885749539</v>
       </c>
       <c r="M3" t="n">
-        <v>1.798607038908415</v>
+        <v>1.784189554199405</v>
       </c>
       <c r="N3" t="n">
-        <v>1.73330503849413</v>
+        <v>1.726543524716196</v>
       </c>
       <c r="O3" t="n">
-        <v>2.118377552760455</v>
+        <v>2.099269456388402</v>
       </c>
       <c r="P3" t="n">
-        <v>1.722077754650197</v>
+        <v>1.711497962668537</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.714288404250245</v>
+        <v>1.707928879708601</v>
       </c>
       <c r="R3" t="n">
-        <v>1.605392039405519</v>
+        <v>1.606179306999799</v>
       </c>
       <c r="S3" t="n">
-        <v>1.738723298999488</v>
+        <v>1.726590315558146</v>
       </c>
       <c r="T3" t="n">
-        <v>1.707094661101378</v>
+        <v>1.703945020422625</v>
       </c>
       <c r="U3" t="n">
-        <v>2.45280765492951</v>
+        <v>2.449916108815761</v>
       </c>
       <c r="V3" t="n">
-        <v>1.714836660759401</v>
+        <v>1.708524650582688</v>
       </c>
       <c r="W3" t="n">
-        <v>2.525068414885093</v>
+        <v>2.517511470317076</v>
       </c>
       <c r="X3" t="n">
-        <v>1.799861189876391</v>
+        <v>1.793899911994487</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.740302449011241</v>
+        <v>1.733232792842925</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.964392036866587</v>
+        <v>1.952832948221814</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.805063995953046</v>
+        <v>1.8055764414896</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.776626062159154</v>
+        <v>1.775347519489866</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1987024274226913</v>
+        <v>0.1722741691888616</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1825805812074307</v>
+        <v>0.153905476978125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2583516568920914</v>
+        <v>0.2334389476918832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1595800187031949</v>
+        <v>0.1287499360821292</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1571042125845731</v>
+        <v>0.1309541723297706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3229776856518256</v>
+        <v>0.2707927510122521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2087247574392674</v>
+        <v>0.1804590920802079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1987957823097199</v>
+        <v>0.1794725811624747</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2660674405240631</v>
+        <v>0.2292074845053215</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2639342982667222</v>
+        <v>0.236257485314725</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1699497220452098</v>
+        <v>0.1517373371809886</v>
       </c>
       <c r="M4" t="n">
-        <v>0.330757430615723</v>
+        <v>0.2890131964298719</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2267664908257822</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1846296859950953</v>
+        <v>0.1564089582570534</v>
       </c>
       <c r="P4" t="n">
-        <v>0.209165717236265</v>
+        <v>0.1734873622243033</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1966720975940089</v>
+        <v>0.167702060951896</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02490404661739624</v>
+        <v>0.007196796125784312</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2359901480010483</v>
+        <v>0.1977912195284282</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1852216918196346</v>
+        <v>0.1613352100855796</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3507012799240739</v>
+        <v>0.3286778953297822</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1955975180045394</v>
+        <v>0.1667534993776577</v>
       </c>
       <c r="W4" t="n">
-        <v>0.522344585079059</v>
+        <v>0.4952143175183372</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3318398629201405</v>
+        <v>0.303500204532726</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2358850217747154</v>
+        <v>0.203231786951504</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2042417519021026</v>
+        <v>0.1748911078280687</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3402941454317724</v>
+        <v>0.3221983302511741</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2946710740980215</v>
+        <v>0.2736885606424468</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8629444486424546</v>
+        <v>0.865813301909891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6330965517521747</v>
+        <v>0.5962518295487782</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129975620348225</v>
+        <v>2.167235692344589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1917686470000852</v>
+        <v>0.1154801352995672</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1468494719436568</v>
+        <v>0.1592080170208342</v>
       </c>
       <c r="G5" t="n">
-        <v>2.844104598636489</v>
+        <v>2.428398472715358</v>
       </c>
       <c r="H5" t="n">
-        <v>1.207478766861082</v>
+        <v>1.178728586997883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9721217844717837</v>
+        <v>1.121932159290451</v>
       </c>
       <c r="J5" t="n">
-        <v>2.032233663466548</v>
+        <v>1.863364161301649</v>
       </c>
       <c r="K5" t="n">
-        <v>2.066695689638272</v>
+        <v>2.046873245325422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3848677716941136</v>
+        <v>0.5208276748303189</v>
       </c>
       <c r="M5" t="n">
-        <v>3.30833167694606</v>
+        <v>3.034188607732593</v>
       </c>
       <c r="N5" t="n">
-        <v>3.521218544577847</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6152619755961135</v>
+        <v>0.5868223345533756</v>
       </c>
       <c r="P5" t="n">
-        <v>1.056243045852529</v>
+        <v>0.8977592107856854</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8782762945942821</v>
+        <v>0.8364042274689902</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.572224843049404</v>
+        <v>-2.384241254833486</v>
       </c>
       <c r="S5" t="n">
-        <v>1.394642311071659</v>
+        <v>1.210432067061745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6846917943322717</v>
+        <v>0.7377342758963648</v>
       </c>
       <c r="U5" t="n">
-        <v>3.647112151930283</v>
+        <v>3.775642270189544</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8423580711840848</v>
+        <v>0.8022809624133618</v>
       </c>
       <c r="W5" t="n">
-        <v>7.07355877326451</v>
+        <v>7.066993212668421</v>
       </c>
       <c r="X5" t="n">
-        <v>3.526821907545286</v>
+        <v>3.496836387101188</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.656542074676208</v>
+        <v>1.593649912955291</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9425278524834859</v>
+        <v>0.8953620907424829</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.609345938340229</v>
+        <v>3.773683430275024</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.904070016094544</v>
+        <v>3.020840275453734</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2112021048660693</v>
+        <v>0.1829796961400206</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2504708348031888</v>
+        <v>0.1646110039292827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2708513343354695</v>
+        <v>0.2938068033776957</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1720796961465729</v>
+        <v>0.1891177917679414</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2249944661803312</v>
+        <v>0.1416596992809288</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3908679392475828</v>
+        <v>0.2814982779634087</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2212244348826452</v>
+        <v>0.2408269477660218</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2112954597530977</v>
+        <v>0.2398404368482867</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2785671179674408</v>
+        <v>0.2399130114564829</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2764339757101004</v>
+        <v>0.2966253410005382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1824493994885873</v>
+        <v>0.1624428641321458</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3986476842114807</v>
+        <v>0.3493810521156848</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2396707152781656</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2577968790824821</v>
+        <v>0.222196069913697</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2196292584167587</v>
+        <v>0.2392200292421033</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2645623511897665</v>
+        <v>0.2280699166377102</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03740372406077441</v>
+        <v>0.06756465181159743</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2484898254444264</v>
+        <v>0.2084967464795874</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2531119454153923</v>
+        <v>0.1720407370367366</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3651597756215965</v>
+        <v>0.3439008553910872</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2634877716002975</v>
+        <v>0.2271213550634699</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5391152033869951</v>
+        <v>0.5610193230077946</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3443395403635185</v>
+        <v>0.3142057314838851</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2523559053279154</v>
+        <v>0.2204354514575402</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2721320054978596</v>
+        <v>0.1855966347792267</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4081843990275303</v>
+        <v>0.3825661859369873</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3079767053814838</v>
+        <v>0.2853971031238565</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2743720182544646</v>
+        <v>0.2454732008890199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.258250172039204</v>
+        <v>0.2271045086782816</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3340212477238647</v>
+        <v>0.3066379793920398</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2352496095349678</v>
+        <v>0.2019489677822855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2327738034163459</v>
+        <v>0.2041532040299263</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3986472764835982</v>
+        <v>0.343991782712407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2843943482710404</v>
+        <v>0.2536581237803643</v>
       </c>
       <c r="I7" t="n">
-        <v>0.274465373141493</v>
+        <v>0.2526716128626311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3417370313558362</v>
+        <v>0.3024065162054792</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3396038890984953</v>
+        <v>0.3094565170148823</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2456193128769826</v>
+        <v>0.2249363688811458</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4064270214474954</v>
+        <v>0.3622122281300292</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3024360816575549</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2599418799399617</v>
+        <v>0.2292506908776126</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2844779111811321</v>
+        <v>0.2463290948448628</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2723416884257823</v>
+        <v>0.2409010926520542</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1005736374491694</v>
+        <v>0.0803958278259421</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3116597388328215</v>
+        <v>0.2709902512285857</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2608912826514072</v>
+        <v>0.2345342417857343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4270502632990507</v>
+        <v>0.4052824005238171</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2712671088363125</v>
+        <v>0.2399525310778149</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5980141759108318</v>
+        <v>0.5684133492184958</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4075094537519139</v>
+        <v>0.3766992362328843</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3135134308606334</v>
+        <v>0.280948251761806</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2799113427338755</v>
+        <v>0.2480901395282254</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4159637362635457</v>
+        <v>0.3953973619513317</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.370340664929794</v>
+        <v>0.3468875923426039</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3004470179690129</v>
+        <v>0.2691395604506456</v>
       </c>
       <c r="C8" t="n">
-        <v>0.368135087824694</v>
+        <v>0.3289660437346944</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4439061635093549</v>
+        <v>0.408499514448453</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3005082172659757</v>
+        <v>0.2621738785059453</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2719054085377459</v>
+        <v>0.2400014580428148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5259107243299658</v>
+        <v>0.4620675967989025</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3942792640565304</v>
+        <v>0.3555196588367787</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3843502889269832</v>
+        <v>0.3545331479190439</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4516219471413262</v>
+        <v>0.4042680512618932</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4494888048839853</v>
+        <v>0.4113180520712947</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3555042286624732</v>
+        <v>0.3267979039375575</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5163119372328588</v>
+        <v>0.4640737631866266</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3473542913727463</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3230709014247683</v>
+        <v>0.2875125299152644</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3432306292836615</v>
+        <v>0.3005078154679581</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2819461267858536</v>
+        <v>0.2492003155180775</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2104585532346594</v>
+        <v>0.1822573628823551</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4215446546183119</v>
+        <v>0.3728517862849981</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3707761984368976</v>
+        <v>0.3363957768421483</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4965935536064311</v>
+        <v>0.4695050302874914</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3574573833985913</v>
+        <v>0.3197970804684138</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7079155626643955</v>
+        <v>0.6702902518359237</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4247952374026246</v>
+        <v>0.3921652022900499</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.50550625188734</v>
+        <v>0.4595569730859539</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3044295302359144</v>
+        <v>0.2703039835610028</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5258486520490355</v>
+        <v>0.497258897007745</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5677720460469533</v>
+        <v>0.5304305267507468</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4441226609695469</v>
+        <v>0.4080770593694242</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5042136075493966</v>
+        <v>0.4621669670390532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5799846832340575</v>
+        <v>0.5417004377528122</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4636234431612072</v>
+        <v>0.4202882761410302</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3030459513830403</v>
+        <v>0.2721788150310335</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6446107117686759</v>
+        <v>0.5790542401594001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5303577837812331</v>
+        <v>0.4887205821411385</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5204288086516851</v>
+        <v>0.4877340712234033</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5877004668660277</v>
+        <v>0.537468974566251</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5855673246086875</v>
+        <v>0.5445189753756542</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4915827483871755</v>
+        <v>0.4599988272419184</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6523904569576874</v>
+        <v>0.5972746864908024</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5483995171677467</v>
+        <v>1.394439314414711</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5315195317775053</v>
+        <v>0.4886831322252914</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5615484879618856</v>
+        <v>0.5109838831528399</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5183051237108601</v>
+        <v>0.4759635500990476</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3465370729593622</v>
+        <v>0.3154582861867135</v>
       </c>
       <c r="S9" t="n">
-        <v>0.557623174343014</v>
+        <v>0.5060527095893578</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5068547181615995</v>
+        <v>0.4695967001465067</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6742931245201842</v>
+        <v>0.6414568185008586</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6051784130581871</v>
+        <v>0.5586306030314163</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8439776114210239</v>
+        <v>0.8034758075792676</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6534728892621066</v>
+        <v>0.6117616945936551</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5594768663708255</v>
+        <v>0.5160107101225769</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4799252412051838</v>
+        <v>0.4394665050683813</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6619271717737382</v>
+        <v>0.6304598203121039</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6163041004399868</v>
+        <v>0.5819500507033769</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.585986685034265</v>
+        <v>2.578661005554993</v>
       </c>
       <c r="C2" t="n">
-        <v>2.62294715545564</v>
+        <v>2.612154650568047</v>
       </c>
       <c r="D2" t="n">
-        <v>2.597743323193721</v>
+        <v>2.59026590497706</v>
       </c>
       <c r="E2" t="n">
-        <v>2.579049448864571</v>
+        <v>2.571425869113112</v>
       </c>
       <c r="F2" t="n">
-        <v>2.581660610243694</v>
+        <v>2.5742592223301</v>
       </c>
       <c r="G2" t="n">
-        <v>2.603889112426349</v>
+        <v>2.596376206182956</v>
       </c>
       <c r="H2" t="n">
-        <v>2.595600853448177</v>
+        <v>2.588339760696088</v>
       </c>
       <c r="I2" t="n">
-        <v>2.592084471869994</v>
+        <v>2.585456862904623</v>
       </c>
       <c r="J2" t="n">
-        <v>2.597519110351288</v>
+        <v>2.590125934180029</v>
       </c>
       <c r="K2" t="n">
-        <v>2.592568568434787</v>
+        <v>2.585457835853771</v>
       </c>
       <c r="L2" t="n">
-        <v>2.578178095384615</v>
+        <v>2.570763668896675</v>
       </c>
       <c r="M2" t="n">
-        <v>2.593766425735276</v>
+        <v>2.586515632607682</v>
       </c>
       <c r="N2" t="n">
-        <v>2.600996827198443</v>
+        <v>2.593658048516239</v>
       </c>
       <c r="O2" t="n">
-        <v>2.831613109433075</v>
+        <v>2.81574299684102</v>
       </c>
       <c r="P2" t="n">
-        <v>2.585939470126089</v>
+        <v>2.578514970313353</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.595601890850383</v>
+        <v>2.588292668457665</v>
       </c>
       <c r="R2" t="n">
-        <v>2.562988558611878</v>
+        <v>2.555334530998583</v>
       </c>
       <c r="S2" t="n">
-        <v>2.591046420410602</v>
+        <v>2.583350758721187</v>
       </c>
       <c r="T2" t="n">
-        <v>2.589319986879846</v>
+        <v>2.582358142704383</v>
       </c>
       <c r="U2" t="n">
-        <v>2.975306060414016</v>
+        <v>2.963574910947648</v>
       </c>
       <c r="V2" t="n">
-        <v>2.598109113882605</v>
+        <v>2.590693934375046</v>
       </c>
       <c r="W2" t="n">
-        <v>2.967294508555575</v>
+        <v>2.95505953418782</v>
       </c>
       <c r="X2" t="n">
-        <v>2.630547523110114</v>
+        <v>2.623311659945407</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.606173869049691</v>
+        <v>2.598846766769229</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.738406615462418</v>
+        <v>2.726913032651643</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62107465791243</v>
+        <v>2.613842824574037</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.59481592113137</v>
+        <v>2.587532346809149</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.615578852881655</v>
+        <v>1.608718503244394</v>
       </c>
       <c r="C3" t="n">
-        <v>1.724873010581235</v>
+        <v>1.712318269819415</v>
       </c>
       <c r="D3" t="n">
-        <v>1.699221837906704</v>
+        <v>1.691278337092102</v>
       </c>
       <c r="E3" t="n">
-        <v>1.565901089325628</v>
+        <v>1.556913450636073</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5844340270498</v>
+        <v>1.577030198380276</v>
       </c>
       <c r="G3" t="n">
-        <v>1.742520016278084</v>
+        <v>1.734339291715073</v>
       </c>
       <c r="H3" t="n">
-        <v>1.683974426584241</v>
+        <v>1.677571540058517</v>
       </c>
       <c r="I3" t="n">
-        <v>1.658832342830574</v>
+        <v>1.656956648107838</v>
       </c>
       <c r="J3" t="n">
-        <v>1.697489544291927</v>
+        <v>1.690153426011455</v>
       </c>
       <c r="K3" t="n">
-        <v>1.662409473315777</v>
+        <v>1.657076153265413</v>
       </c>
       <c r="L3" t="n">
-        <v>1.561009042069594</v>
+        <v>1.55352679740213</v>
       </c>
       <c r="M3" t="n">
-        <v>1.672775056938129</v>
+        <v>1.666392879493504</v>
       </c>
       <c r="N3" t="n">
-        <v>1.72238406540933</v>
+        <v>1.715428722230024</v>
       </c>
       <c r="O3" t="n">
-        <v>2.067496384552572</v>
+        <v>2.046354218205086</v>
       </c>
       <c r="P3" t="n">
-        <v>1.615279715604163</v>
+        <v>1.607717814195074</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.683934795652451</v>
+        <v>1.677192115908466</v>
       </c>
       <c r="R3" t="n">
-        <v>1.450609369958317</v>
+        <v>1.441395157131156</v>
       </c>
       <c r="S3" t="n">
-        <v>1.65170069729229</v>
+        <v>1.642226697908719</v>
       </c>
       <c r="T3" t="n">
-        <v>1.639202914451991</v>
+        <v>1.634933209559036</v>
       </c>
       <c r="U3" t="n">
-        <v>2.316297383635215</v>
+        <v>2.302602644713655</v>
       </c>
       <c r="V3" t="n">
-        <v>1.701698180259372</v>
+        <v>1.694205544106299</v>
       </c>
       <c r="W3" t="n">
-        <v>2.384339204545052</v>
+        <v>2.369531998247224</v>
       </c>
       <c r="X3" t="n">
-        <v>1.93287324831922</v>
+        <v>1.926651136566437</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75941329404433</v>
+        <v>1.752540045586657</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.920930273692842</v>
+        <v>1.906834686947485</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86575666120683</v>
+        <v>1.859563481692463</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.678143870901127</v>
+        <v>1.671536383950811</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0334802562844414</v>
+        <v>0.01565514295743418</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1334361462866611</v>
+        <v>0.1156741213949941</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1662768926162706</v>
+        <v>0.1467378204471589</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04487901753854846</v>
+        <v>-0.06606905148082962</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01538474856779595</v>
+        <v>-0.03406502348806666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2356964092015349</v>
+        <v>0.2157564834451943</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1420767112555365</v>
+        <v>0.1249811347234342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1023575637145599</v>
+        <v>0.09241747797032476</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1634664327222927</v>
+        <v>0.1448806322625847</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1078256571093015</v>
+        <v>0.09242846787856202</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05472135593703657</v>
+        <v>-0.07354890755258053</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1247396873481736</v>
+        <v>0.1076606619891536</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2030267170353766</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1296107415245821</v>
+        <v>0.1114135240971107</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03294694217666175</v>
+        <v>0.01400560772359378</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1420884291907094</v>
+        <v>0.1244492062269513</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.226294161317276</v>
+        <v>-0.2478281178656667</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09063229495344928</v>
+        <v>0.06862806236264257</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07113143402492852</v>
+        <v>0.05741600782690223</v>
       </c>
       <c r="U4" t="n">
-        <v>0.152535390075348</v>
+        <v>0.1322481150766047</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1685541057280164</v>
+        <v>0.1497261972435956</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3216216504602268</v>
+        <v>0.3041222852355216</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5368154213494424</v>
+        <v>0.5200048246130025</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2603492726693409</v>
+        <v>0.2391401791383086</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1447604992477549</v>
+        <v>0.1261934922190643</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4298150512083269</v>
+        <v>0.4130499732138858</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1328167360687767</v>
+        <v>0.1153853078937689</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.471832465873534</v>
+        <v>-1.501750716855047</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1739374400041541</v>
+        <v>0.1441682653016297</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7397067988059198</v>
+        <v>0.6793788776032347</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.943959030870335</v>
+        <v>-3.033992574751441</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.475707894900345</v>
+        <v>-2.522380472279613</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67490249748892</v>
+        <v>1.615805469553945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3342304978824878</v>
+        <v>0.3154038130525527</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3918438316835179</v>
+        <v>-0.2810115351491499</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6261912206904952</v>
+        <v>0.5858781772531332</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2318515920888979</v>
+        <v>-0.2224851839095737</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.430432701632698</v>
+        <v>-2.472122805084197</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05589722513610221</v>
+        <v>0.03809753340475708</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5326594207851775</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1113772443533343</v>
+        <v>0.07646901283038755</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.461656484849128</v>
+        <v>-1.509381962453997</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3100630910448484</v>
+        <v>0.2835439564470351</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.496865163834977</v>
+        <v>-6.597783535486068</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4556869580532852</v>
+        <v>-0.5455631412593325</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8918723020434006</v>
+        <v>-0.8522474831640852</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4833226074579579</v>
+        <v>0.4681775672221225</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7413194533317666</v>
+        <v>0.6968870519000254</v>
       </c>
       <c r="W5" t="n">
-        <v>3.307051927592048</v>
+        <v>3.282176175981684</v>
       </c>
       <c r="X5" t="n">
-        <v>7.047757396519956</v>
+        <v>7.034338963267404</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.435471728761177</v>
+        <v>2.4038471110201</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3429548096015247</v>
+        <v>0.3025054250235829</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.410102820488392</v>
+        <v>5.397578164332334</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1629418082447426</v>
+        <v>0.1383595599703015</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04016403430892251</v>
+        <v>0.05709098614735862</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1401199243111412</v>
+        <v>0.1184361585146754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1729606706407509</v>
+        <v>0.1494998575668403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005883025955235294</v>
+        <v>-0.06330701436115005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03537729492599283</v>
+        <v>0.007370819701858364</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2423801872260141</v>
+        <v>0.2571923266351208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1487604892800198</v>
+        <v>0.1664169779133603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1090413417390447</v>
+        <v>0.1338533211602516</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1701502107467738</v>
+        <v>0.1863164754525111</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1145094351337822</v>
+        <v>0.1338643110684883</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.003959312443249235</v>
+        <v>-0.07078687043289916</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1755017308419561</v>
+        <v>0.1490965051790786</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2107322438612071</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1373162683503988</v>
+        <v>0.1574787425601469</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03885880261955348</v>
+        <v>0.01648054009954388</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1487722072151909</v>
+        <v>0.1658850494168761</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1755321178234914</v>
+        <v>-0.2450660807459843</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09731607297793068</v>
+        <v>0.1100639055525671</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1218934775187095</v>
+        <v>0.06017804494658265</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1603736817326354</v>
+        <v>0.139532574839162</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2193161492218009</v>
+        <v>0.152488234363276</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3318816062591937</v>
+        <v>0.310323017985291</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5434991993739231</v>
+        <v>0.5614406678029276</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2704894324669773</v>
+        <v>0.2486655576050942</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1955225427415387</v>
+        <v>0.1289555293387438</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.480577094702107</v>
+        <v>0.4544858164038121</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1404771969788438</v>
+        <v>0.1193820058211484</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09521427838684035</v>
+        <v>0.07596050630900969</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1951701683890551</v>
+        <v>0.1759794847465707</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2280109147186738</v>
+        <v>0.2070431837987362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01685500456384914</v>
+        <v>-0.005763688129253555</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04634927353460731</v>
+        <v>0.02624033986350938</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2974304313039329</v>
+        <v>0.2760618467967716</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2038107333579354</v>
+        <v>0.1852864980750111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1640915858169599</v>
+        <v>0.1527228413219026</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2252004548246927</v>
+        <v>0.2051859956141617</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169559679211699</v>
+        <v>0.1527338312301391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007012666165362516</v>
+        <v>-0.0132435442010042</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1864737094505694</v>
+        <v>0.1679660253407288</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2647607391377738</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1910120602153721</v>
+        <v>0.1713860531006023</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09434826086744834</v>
+        <v>0.07397813672708523</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2038224512931077</v>
+        <v>0.184754569578527</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1645601392148785</v>
+        <v>-0.1875227545140886</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1523663170558462</v>
+        <v>0.1289334257142181</v>
       </c>
       <c r="T7" t="n">
-        <v>0.132865456127322</v>
+        <v>0.1177213711784795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2135339347660396</v>
+        <v>0.1957578789328313</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2302881278304149</v>
+        <v>0.2100315605951719</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3833556725626247</v>
+        <v>0.3644276485870974</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5985494434518411</v>
+        <v>0.5803101879645786</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3232378084045432</v>
+        <v>0.3039679651327613</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2064945213501502</v>
+        <v>0.1864988555706405</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4915490733107211</v>
+        <v>0.4733553365654633</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1945507581711753</v>
+        <v>0.1756906712453451</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1107821511053552</v>
+        <v>0.08885017651771535</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2749132138086718</v>
+        <v>0.2477290011365305</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3077539601382865</v>
+        <v>0.2787927001886949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06242666357886864</v>
+        <v>0.0346446964216555</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07191488812278761</v>
+        <v>0.04829968619887005</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3904806168406297</v>
+        <v>0.3600163357294021</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2835537787775515</v>
+        <v>0.2570360144649705</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2438346312365753</v>
+        <v>0.2244723577118616</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3049435002443068</v>
+        <v>0.2769355120041206</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2493027246313145</v>
+        <v>0.2244833476200979</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0867557115849813</v>
+        <v>0.05850597218895595</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2662167548698696</v>
+        <v>0.2397155417306118</v>
       </c>
       <c r="N8" t="n">
-        <v>0.294757289428024</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2350120826943205</v>
+        <v>0.2103806595948909</v>
       </c>
       <c r="P8" t="n">
-        <v>0.134997247589821</v>
+        <v>0.1098992579223738</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2067784378623628</v>
+        <v>0.1860769365963976</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.08481709379526121</v>
+        <v>-0.1157732381241297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2321093624754611</v>
+        <v>0.2006829421041796</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2126085015469386</v>
+        <v>0.1894708875684387</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2626370662542959</v>
+        <v>0.2393332157906202</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2911599999616068</v>
+        <v>0.2648516794015446</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4631113301916776</v>
+        <v>0.4361887326398662</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6073872120860224</v>
+        <v>0.5870271768516451</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4647241815126316</v>
+        <v>0.4329343667275891</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2208703072921543</v>
+        <v>0.1982951739152391</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5712921187303368</v>
+        <v>0.5451048529554224</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3413301376709135</v>
+        <v>0.3089242187699145</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2211606670469803</v>
+        <v>0.1976820781823088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3795747564326498</v>
+        <v>0.3534180195438861</v>
       </c>
       <c r="D9" t="n">
-        <v>0.412415502762261</v>
+        <v>0.3844817185960507</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18776768768466</v>
+        <v>0.1588156061394956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09599174188887979</v>
+        <v>0.07523605621821697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4818350311106882</v>
+        <v>0.4535003910180437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3882153214015314</v>
+        <v>0.3627250328723259</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3484961738605543</v>
+        <v>0.330161376119218</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4096050428682836</v>
+        <v>0.3826245304114747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3539642672552917</v>
+        <v>0.3301723660274541</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1914172542089548</v>
+        <v>0.1641949905963112</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3708782974941649</v>
+        <v>0.3454045601380439</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4491653271813712</v>
+        <v>1.32621661361057</v>
       </c>
       <c r="O9" t="n">
-        <v>0.39512233806323</v>
+        <v>0.3676219633509273</v>
       </c>
       <c r="P9" t="n">
-        <v>0.302671828312954</v>
+        <v>0.2742297658200079</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3882270510998623</v>
+        <v>0.3621931137998005</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01984444882871694</v>
+        <v>-0.01008421971677377</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3367709050994387</v>
+        <v>0.3063719605115334</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3172700441709184</v>
+        <v>0.2951599059757941</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3998285138541501</v>
+        <v>0.3745144358683725</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4821522360742729</v>
+        <v>0.451766285487654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5677602606062154</v>
+        <v>0.5418661833844135</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7829540314954357</v>
+        <v>0.7577487227618941</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5076423964481367</v>
+        <v>0.4814064999300762</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3556540181424536</v>
+        <v>0.3303450200125766</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6759536613543173</v>
+        <v>0.650793871362778</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.378955346214766</v>
+        <v>0.3531292060426603</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.570525186073963</v>
+        <v>2.564359330297209</v>
       </c>
       <c r="C2" t="n">
-        <v>2.608080148830591</v>
+        <v>2.598751460949112</v>
       </c>
       <c r="D2" t="n">
-        <v>2.584687119927795</v>
+        <v>2.578607554120204</v>
       </c>
       <c r="E2" t="n">
-        <v>2.56884729902484</v>
+        <v>2.562390780005894</v>
       </c>
       <c r="F2" t="n">
-        <v>2.575898954167184</v>
+        <v>2.569774360814613</v>
       </c>
       <c r="G2" t="n">
-        <v>2.593927448032053</v>
+        <v>2.587857784515264</v>
       </c>
       <c r="H2" t="n">
-        <v>2.589368440293546</v>
+        <v>2.583284444930315</v>
       </c>
       <c r="I2" t="n">
-        <v>2.587180039436012</v>
+        <v>2.581323372700667</v>
       </c>
       <c r="J2" t="n">
-        <v>2.587984265709649</v>
+        <v>2.581879576756648</v>
       </c>
       <c r="K2" t="n">
-        <v>2.585988444838984</v>
+        <v>2.579992904057874</v>
       </c>
       <c r="L2" t="n">
-        <v>2.566575440529754</v>
+        <v>2.560380436534943</v>
       </c>
       <c r="M2" t="n">
-        <v>2.587612753188594</v>
+        <v>2.581568990664744</v>
       </c>
       <c r="N2" t="n">
-        <v>2.594410784814052</v>
+        <v>2.588344577266613</v>
       </c>
       <c r="O2" t="n">
-        <v>2.806801705414272</v>
+        <v>2.79359788084947</v>
       </c>
       <c r="P2" t="n">
-        <v>2.575527743446744</v>
+        <v>2.569302579523268</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.588147949230975</v>
+        <v>2.582095355797241</v>
       </c>
       <c r="R2" t="n">
-        <v>2.556204761767543</v>
+        <v>2.549652462379305</v>
       </c>
       <c r="S2" t="n">
-        <v>2.57934304441559</v>
+        <v>2.573082737635414</v>
       </c>
       <c r="T2" t="n">
-        <v>2.583423379344823</v>
+        <v>2.577466236137604</v>
       </c>
       <c r="U2" t="n">
-        <v>2.959586250575721</v>
+        <v>2.951968020640662</v>
       </c>
       <c r="V2" t="n">
-        <v>2.591616045965091</v>
+        <v>2.585454671792825</v>
       </c>
       <c r="W2" t="n">
-        <v>2.948304615956509</v>
+        <v>2.940460515067921</v>
       </c>
       <c r="X2" t="n">
-        <v>2.63387675772144</v>
+        <v>2.627945092346373</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.595031773897859</v>
+        <v>2.588951665718125</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.717535869177693</v>
+        <v>2.708557277297916</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.617333395931918</v>
+        <v>2.611284128089</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.588165062657946</v>
+        <v>2.582237226656121</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.555766020266634</v>
+        <v>1.549401399883442</v>
       </c>
       <c r="C3" t="n">
-        <v>1.678099187025979</v>
+        <v>1.666693312121107</v>
       </c>
       <c r="D3" t="n">
-        <v>1.656318190605468</v>
+        <v>1.650564420097018</v>
       </c>
       <c r="E3" t="n">
-        <v>1.543792191673909</v>
+        <v>1.535360017446926</v>
       </c>
       <c r="F3" t="n">
-        <v>1.59344512864363</v>
+        <v>1.587368581725817</v>
       </c>
       <c r="G3" t="n">
-        <v>1.721927146578597</v>
+        <v>1.716246480356889</v>
       </c>
       <c r="H3" t="n">
-        <v>1.689782963656186</v>
+        <v>1.683995785404143</v>
       </c>
       <c r="I3" t="n">
-        <v>1.674101372585508</v>
+        <v>1.669940656536009</v>
       </c>
       <c r="J3" t="n">
-        <v>1.679816484006319</v>
+        <v>1.673886330969188</v>
       </c>
       <c r="K3" t="n">
-        <v>1.665624702542257</v>
+        <v>1.660469995319348</v>
       </c>
       <c r="L3" t="n">
-        <v>1.528257080517992</v>
+        <v>1.521689244342171</v>
       </c>
       <c r="M3" t="n">
-        <v>1.678505015422191</v>
+        <v>1.672959337034219</v>
       </c>
       <c r="N3" t="n">
-        <v>1.725679056940065</v>
+        <v>1.720020866782082</v>
       </c>
       <c r="O3" t="n">
-        <v>1.999406473068628</v>
+        <v>1.98133869312341</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59142754960173</v>
+        <v>1.58464375100181</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.680986147402294</v>
+        <v>1.675425488803657</v>
       </c>
       <c r="R3" t="n">
-        <v>1.452299238598175</v>
+        <v>1.443158970122587</v>
       </c>
       <c r="S3" t="n">
-        <v>1.618495831594271</v>
+        <v>1.611462500318807</v>
       </c>
       <c r="T3" t="n">
-        <v>1.647277531378011</v>
+        <v>1.642397651338528</v>
       </c>
       <c r="U3" t="n">
-        <v>2.298364434517924</v>
+        <v>2.290344086806488</v>
       </c>
       <c r="V3" t="n">
-        <v>1.705573293380858</v>
+        <v>1.699241954567052</v>
       </c>
       <c r="W3" t="n">
-        <v>2.348773703158489</v>
+        <v>2.340391999027514</v>
       </c>
       <c r="X3" t="n">
-        <v>2.006467676832499</v>
+        <v>2.001767613486186</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.730177157945186</v>
+        <v>1.724419348937585</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.862429813422793</v>
+        <v>1.851469615966443</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.889354547651245</v>
+        <v>1.883817167139157</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.680408186933573</v>
+        <v>1.675694491116197</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06237793403485289</v>
+        <v>-0.07621152159661716</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06294073326863554</v>
+        <v>0.04948593251348681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09758762365562318</v>
+        <v>0.08472872099088417</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.08133044012085636</v>
+        <v>-0.09844720271491161</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.001678751366477368</v>
+        <v>-0.01504626086545037</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2019613803541699</v>
+        <v>0.1892143286192829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1504652907005213</v>
+        <v>0.1375563541671707</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1257462963005491</v>
+        <v>0.1154051411954715</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1345772693028355</v>
+        <v>0.1214379939518985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1122866871665264</v>
+        <v>0.1003768858293588</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1069921269294046</v>
+        <v>-0.1211549570229961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1330365265725812</v>
+        <v>0.1204949082387049</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2074208916527009</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04848129660506421</v>
+        <v>0.03446610838965625</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005871747219226016</v>
+        <v>-0.02037524758129934</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1366792826951509</v>
+        <v>0.1241250454010459</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2241337142965212</v>
+        <v>-0.242332360222851</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03722383234906356</v>
+        <v>0.02232337725405933</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08331309242156462</v>
+        <v>0.07183700934519811</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1446634117872867</v>
+        <v>0.1280462181297166</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1741659172170797</v>
+        <v>0.1604025055996242</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2879593593302569</v>
+        <v>0.2756863622241737</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6532072108861831</v>
+        <v>0.6420189116443702</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2135870882866687</v>
+        <v>0.1964019128025098</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06991769811235519</v>
+        <v>0.05617566987452353</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4663423291511155</v>
+        <v>0.453825655935133</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1354946815007038</v>
+        <v>0.1242676565416881</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.860131329686386</v>
+        <v>-2.897002139392414</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8990765961952492</v>
+        <v>-0.9315370349727344</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3015232420185102</v>
+        <v>-0.3237493409940608</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.194645883985961</v>
+        <v>-3.285996767439753</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.13571605938365</v>
+        <v>-2.167669741303436</v>
       </c>
       <c r="G5" t="n">
-        <v>1.368444294418042</v>
+        <v>1.349456342347001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.66166700328675</v>
+        <v>0.6376263895462891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.191892575187271</v>
+        <v>0.215343655771582</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3395110527389546</v>
+        <v>0.313783855421782</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03175617690378413</v>
+        <v>-0.03752104770857584</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.296507845174462</v>
+        <v>-3.336705826939609</v>
       </c>
       <c r="M5" t="n">
-        <v>0.326015010496028</v>
+        <v>0.3093497704758648</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5619336037453327</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.015026240207875</v>
+        <v>-1.053812150032608</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.882477110691439</v>
+        <v>-1.929068093747658</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3732140150640771</v>
+        <v>0.3566918863483195</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.374633922487035</v>
+        <v>-6.497818782328064</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.204063418803354</v>
+        <v>-1.257009984999161</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5650195405942569</v>
+        <v>-0.5627082482931587</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5000242846166736</v>
+        <v>0.4878358277855278</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9789585902310796</v>
+        <v>0.9436743534997323</v>
       </c>
       <c r="W5" t="n">
-        <v>2.947353652692523</v>
+        <v>2.935579310530637</v>
       </c>
       <c r="X5" t="n">
-        <v>9.049064582461554</v>
+        <v>9.055419062854943</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.779970204523151</v>
+        <v>1.757548916231566</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.6561104810644376</v>
+        <v>-0.6898657377904259</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.240338314595039</v>
+        <v>6.224243832723911</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3774189206143226</v>
+        <v>0.3849429989463249</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01816603417322077</v>
+        <v>-0.04008485598512593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1071526331302664</v>
+        <v>0.08561259812497783</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1417995235172558</v>
+        <v>0.120855386602377</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03711854025922482</v>
+        <v>-0.09694745260795408</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04253314849515394</v>
+        <v>0.02108040474604102</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2461732802158018</v>
+        <v>0.2253409942307736</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1553961942034618</v>
+        <v>0.1736830197786631</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306771998034899</v>
+        <v>0.1515318068069646</v>
       </c>
       <c r="J6" t="n">
-        <v>0.139508172805777</v>
+        <v>0.1229377440588551</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1564985870281586</v>
+        <v>0.101876635936316</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06278022706777314</v>
+        <v>-0.08502829141150545</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1772484264342138</v>
+        <v>0.1566215738501959</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2135013502726453</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09700404134668</v>
+        <v>0.03720176839882328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04264121131093485</v>
+        <v>0.02042436584179209</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1808911825567829</v>
+        <v>0.1602517110125365</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2192028107935813</v>
+        <v>-0.2062056946113592</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04215473585200391</v>
+        <v>0.05845004286555054</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1275249922831964</v>
+        <v>0.07333675945215447</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1897234723856727</v>
+        <v>0.1693411909545358</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1790968207200208</v>
+        <v>0.1619022557065816</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3365050883789771</v>
+        <v>0.31658709221894</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6581381143891235</v>
+        <v>0.6435186617513282</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2217123869439771</v>
+        <v>0.2054825931282646</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.07484860161529489</v>
+        <v>0.05767541998148035</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4712732326540556</v>
+        <v>0.4899523215466244</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1416167699939163</v>
+        <v>0.1272732020308294</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.003862220282146001</v>
+        <v>-0.01873213406075594</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1214564470213416</v>
+        <v>0.1069653200493471</v>
       </c>
       <c r="D7" t="n">
-        <v>0.15610333740833</v>
+        <v>0.1422081085267456</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02281472636814997</v>
+        <v>-0.04096781517905067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05683696238622793</v>
+        <v>0.04243312667041046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2604770941068764</v>
+        <v>0.2466937161551431</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2089810044532275</v>
+        <v>0.1950357417030323</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1842620100532556</v>
+        <v>0.1728845287313334</v>
       </c>
       <c r="J7" t="n">
-        <v>0.193092983055543</v>
+        <v>0.1789173814877586</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1708024009192334</v>
+        <v>0.1578562733652187</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04847641317669782</v>
+        <v>-0.06367556948713599</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1915522403252879</v>
+        <v>0.1779742957745649</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2659366054054073</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O7" t="n">
-        <v>0.106664511817191</v>
+        <v>0.09161282731248929</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05231146799290166</v>
+        <v>0.03677147134153299</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1951949964478574</v>
+        <v>0.1816044329369058</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1656180005438148</v>
+        <v>-0.184852972686991</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09573954610176993</v>
+        <v>0.07980276478991996</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1418288061742708</v>
+        <v>0.1293163968810576</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2017576112835549</v>
+        <v>0.1890829176829128</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2326816309697867</v>
+        <v>0.2178818931354849</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3464750730829634</v>
+        <v>0.3331657497600349</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7117229246388894</v>
+        <v>0.6994982991802292</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2729509627761283</v>
+        <v>0.2590496075516979</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1284334118650611</v>
+        <v>0.1136550574103844</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5248580429038212</v>
+        <v>0.511305043470994</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.19401039525341</v>
+        <v>0.1817470440775494</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008293034529091858</v>
+        <v>-0.008923999051033221</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1917376256384751</v>
+        <v>0.1705154004142396</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2263845160254638</v>
+        <v>0.2057581888916367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01651611243227343</v>
+        <v>-0.006033735437104719</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07804755679203543</v>
+        <v>0.06061362867509841</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3428110616782297</v>
+        <v>0.321387538988313</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2792621830703622</v>
+        <v>0.2585858220679229</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2545431886703893</v>
+        <v>0.2364346090962243</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2633741616726762</v>
+        <v>0.2424674618526513</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2410835795363677</v>
+        <v>0.2214063537301119</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02180476544043639</v>
+        <v>-0.000125489122243333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2618334189419945</v>
+        <v>0.2415243761392361</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2911604688129105</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1446030152027997</v>
+        <v>0.1252848323394647</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08721480931854286</v>
+        <v>0.06763723255438489</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1959271805754084</v>
+        <v>0.180851049071654</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.09533682192668128</v>
+        <v>-0.1213028923220981</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1660207247189038</v>
+        <v>0.1433528451548114</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2121099847914053</v>
+        <v>0.1928664772459508</v>
       </c>
       <c r="U8" t="n">
-        <v>0.244436713076171</v>
+        <v>0.2270225953053953</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2854202676952761</v>
+        <v>0.2656508076131927</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4167676750932293</v>
+        <v>0.3967263919987717</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7177824651712468</v>
+        <v>0.7036704714195113</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3984571981451142</v>
+        <v>0.3743393298687848</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1395089478003858</v>
+        <v>0.1224649081891581</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5951392215209549</v>
+        <v>0.5748551238358861</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3250089616826451</v>
+        <v>0.3014350802361302</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1051992444234144</v>
+        <v>0.08702088114165465</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2826173476659736</v>
+        <v>0.2626437699142882</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3172642380529624</v>
+        <v>0.297886558391687</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1263218242628249</v>
+        <v>0.1031880341128254</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0978944654716469</v>
+        <v>0.08301984727310044</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4216379782296976</v>
+        <v>0.4023721479558447</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3701419050978604</v>
+        <v>0.3507141915679725</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3454229106978887</v>
+        <v>0.3285629785962743</v>
       </c>
       <c r="J9" t="n">
-        <v>0.354253883700175</v>
+        <v>0.3345958313526998</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3319633015638664</v>
+        <v>0.3135347232301604</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1126844874679346</v>
+        <v>0.09200288037780427</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3527131409699209</v>
+        <v>0.333652745639506</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4270975060500397</v>
+        <v>1.602238015853775</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2854235738571006</v>
+        <v>0.2641691454151326</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2348255190680304</v>
+        <v>0.2129260904233848</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3563558805706799</v>
+        <v>0.3372828647376074</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.004457099899183442</v>
+        <v>-0.02917452282205031</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2569004467464021</v>
+        <v>0.2354812146548608</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3029897068189035</v>
+        <v>0.2849948467460012</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3651881869213803</v>
+        <v>0.3463723627438456</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4539641470349633</v>
+        <v>0.4311732071350701</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5076359737275958</v>
+        <v>0.4888441996249747</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8728838252835224</v>
+        <v>0.8551767490451729</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4341118634207612</v>
+        <v>0.4147280574166388</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2581829789404072</v>
+        <v>0.2392329025435754</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6860189435484534</v>
+        <v>0.666983493335934</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3551712958980424</v>
+        <v>0.3374254939424912</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.663956568447261</v>
+        <v>2.656749508374514</v>
       </c>
       <c r="C2" t="n">
-        <v>2.681823080872272</v>
+        <v>2.672969462245026</v>
       </c>
       <c r="D2" t="n">
-        <v>2.665371637540475</v>
+        <v>2.659022309050841</v>
       </c>
       <c r="E2" t="n">
-        <v>2.655046903066025</v>
+        <v>2.645977523593751</v>
       </c>
       <c r="F2" t="n">
-        <v>2.654117472032272</v>
+        <v>2.646169981595669</v>
       </c>
       <c r="G2" t="n">
-        <v>2.697039747373096</v>
+        <v>2.681225717457044</v>
       </c>
       <c r="H2" t="n">
-        <v>2.669780653794422</v>
+        <v>2.661438787827616</v>
       </c>
       <c r="I2" t="n">
-        <v>2.65559739983621</v>
+        <v>2.648138504611862</v>
       </c>
       <c r="J2" t="n">
-        <v>2.677924632695114</v>
+        <v>2.666938767554188</v>
       </c>
       <c r="K2" t="n">
-        <v>2.663661044184626</v>
+        <v>2.655825056241796</v>
       </c>
       <c r="L2" t="n">
-        <v>2.678088052499235</v>
+        <v>2.673713583224995</v>
       </c>
       <c r="M2" t="n">
-        <v>2.697181116308181</v>
+        <v>2.685207597891295</v>
       </c>
       <c r="N2" t="n">
-        <v>2.668793288751868</v>
+        <v>2.659913782881515</v>
       </c>
       <c r="O2" t="n">
-        <v>2.936110343848215</v>
+        <v>2.924176314970301</v>
       </c>
       <c r="P2" t="n">
-        <v>2.671398660085467</v>
+        <v>2.660777707085117</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.659342082786592</v>
+        <v>2.650980674499967</v>
       </c>
       <c r="R2" t="n">
-        <v>2.649854331991783</v>
+        <v>2.643236428114744</v>
       </c>
       <c r="S2" t="n">
-        <v>2.670505434534134</v>
+        <v>2.661107313852358</v>
       </c>
       <c r="T2" t="n">
-        <v>2.658150428523766</v>
+        <v>2.650072842665061</v>
       </c>
       <c r="U2" t="n">
-        <v>3.073806701792715</v>
+        <v>3.065784845837005</v>
       </c>
       <c r="V2" t="n">
-        <v>2.658373157621801</v>
+        <v>2.650327180623413</v>
       </c>
       <c r="W2" t="n">
-        <v>3.056870775563215</v>
+        <v>3.04848096613748</v>
       </c>
       <c r="X2" t="n">
-        <v>2.675009515950939</v>
+        <v>2.667047845231265</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.673526490235805</v>
+        <v>2.663822725424409</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.819227386282732</v>
+        <v>2.80938478224945</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.674207179979953</v>
+        <v>2.666321874895606</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.689208595543501</v>
+        <v>2.683872881713747</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.824416726313597</v>
+        <v>1.825363470992804</v>
       </c>
       <c r="C3" t="n">
-        <v>1.793777653122086</v>
+        <v>1.785416377748951</v>
       </c>
       <c r="D3" t="n">
-        <v>1.835338012851764</v>
+        <v>1.842483962252721</v>
       </c>
       <c r="E3" t="n">
-        <v>1.761293219131518</v>
+        <v>1.748986758801234</v>
       </c>
       <c r="F3" t="n">
-        <v>1.754770406503222</v>
+        <v>1.750473540535261</v>
       </c>
       <c r="G3" t="n">
-        <v>2.059227704759261</v>
+        <v>1.999068529579979</v>
       </c>
       <c r="H3" t="n">
-        <v>1.867219821710195</v>
+        <v>1.860100493657919</v>
       </c>
       <c r="I3" t="n">
-        <v>1.765375778980638</v>
+        <v>1.764578249622978</v>
       </c>
       <c r="J3" t="n">
-        <v>1.923870069285612</v>
+        <v>1.897980047276503</v>
       </c>
       <c r="K3" t="n">
-        <v>1.82250794968482</v>
+        <v>1.818989932353857</v>
       </c>
       <c r="L3" t="n">
-        <v>1.925316563760456</v>
+        <v>1.946454007858898</v>
       </c>
       <c r="M3" t="n">
-        <v>2.062005491788692</v>
+        <v>2.02911781695359</v>
       </c>
       <c r="N3" t="n">
-        <v>1.859581530681509</v>
+        <v>1.84862259534267</v>
       </c>
       <c r="O3" t="n">
-        <v>2.270898364720112</v>
+        <v>2.259159148231962</v>
       </c>
       <c r="P3" t="n">
-        <v>1.877482114356078</v>
+        <v>1.854155002603524</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.791973417415524</v>
+        <v>1.784717190812516</v>
       </c>
       <c r="R3" t="n">
-        <v>1.724262976083226</v>
+        <v>1.729503576045277</v>
       </c>
       <c r="S3" t="n">
-        <v>1.870726308972846</v>
+        <v>1.856120654195631</v>
       </c>
       <c r="T3" t="n">
-        <v>1.783638673875839</v>
+        <v>1.778412251596523</v>
       </c>
       <c r="U3" t="n">
-        <v>2.580630568914668</v>
+        <v>2.578443853167906</v>
       </c>
       <c r="V3" t="n">
-        <v>1.784715701096895</v>
+        <v>1.779700740290739</v>
       </c>
       <c r="W3" t="n">
-        <v>2.572216141679005</v>
+        <v>2.5658833448427</v>
       </c>
       <c r="X3" t="n">
-        <v>1.904127824337325</v>
+        <v>1.899728872296147</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.893113776046961</v>
+        <v>1.876282609543943</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.075860326434514</v>
+        <v>2.064495670147621</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.898069417664461</v>
+        <v>1.894211655937496</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.00505957483238</v>
+        <v>2.019077124578199</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.384939537474885</v>
+        <v>0.3398214111441169</v>
       </c>
       <c r="C4" t="n">
-        <v>0.259833182443277</v>
+        <v>0.2010964229896563</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4009233938466661</v>
+        <v>0.3654937403232396</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2843007683452431</v>
+        <v>0.2181468876876101</v>
       </c>
       <c r="F4" t="n">
-        <v>0.273802417259597</v>
+        <v>0.2203207893542926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7586292624563756</v>
+        <v>0.6162914523438012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4507252606826952</v>
+        <v>0.3927889797420412</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2905188826054829</v>
+        <v>0.2425561623875468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5422855520531387</v>
+        <v>0.4545146753028759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3816014549805197</v>
+        <v>0.3293792990361028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5445611506457594</v>
+        <v>0.5314384404403019</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7608688886018851</v>
+        <v>0.6621254339452989</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4395725183166986</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3794876922798552</v>
+        <v>0.3242590313866743</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4690013860596976</v>
+        <v>0.3853217686433494</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3328167991693398</v>
+        <v>0.2746597787364436</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2256482893609758</v>
+        <v>0.1871849532859723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4589119925533383</v>
+        <v>0.3890448287059342</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3193565160826634</v>
+        <v>0.2644054005379025</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5447997091232214</v>
+        <v>0.4962240038046267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.318990656179267</v>
+        <v>0.2646028706885743</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5881342251099188</v>
+        <v>0.5319738472253482</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5097876641359671</v>
+        <v>0.4561458634101432</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4891144296553779</v>
+        <v>0.4160737902837643</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3747849067592391</v>
+        <v>0.3131782681275423</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.500724910250897</v>
+        <v>0.447945694506023</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6672362193772964</v>
+        <v>0.6424628552874088</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.110519633461474</v>
+        <v>3.262224930850606</v>
       </c>
       <c r="C5" t="n">
-        <v>1.029671890462193</v>
+        <v>0.9433476989905724</v>
       </c>
       <c r="D5" t="n">
-        <v>3.869824533274174</v>
+        <v>4.247837952966089</v>
       </c>
       <c r="E5" t="n">
-        <v>1.466383884758476</v>
+        <v>1.241626303628959</v>
       </c>
       <c r="F5" t="n">
-        <v>1.329383045830831</v>
+        <v>1.345686318812127</v>
       </c>
       <c r="G5" t="n">
-        <v>9.450253273523204</v>
+        <v>7.943071028841918</v>
       </c>
       <c r="H5" t="n">
-        <v>5.041965246000505</v>
+        <v>4.96971112834515</v>
       </c>
       <c r="I5" t="n">
-        <v>1.669400934989886</v>
+        <v>1.796844818206196</v>
       </c>
       <c r="J5" t="n">
-        <v>5.961251958248535</v>
+        <v>5.379766438143134</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15885348885141</v>
+        <v>3.189543834542313</v>
       </c>
       <c r="L5" t="n">
-        <v>6.152394953331774</v>
+        <v>6.894805489508002</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28210492442113</v>
+        <v>9.457549535000776</v>
       </c>
       <c r="N5" t="n">
-        <v>6.16079836553521</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O5" t="n">
-        <v>2.946286747407991</v>
+        <v>2.922171556485146</v>
       </c>
       <c r="P5" t="n">
-        <v>4.672595363639574</v>
+        <v>4.145942341057782</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.397783503876795</v>
+        <v>2.322788290949271</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3737368245954676</v>
+        <v>0.7007779016043925</v>
       </c>
       <c r="S5" t="n">
-        <v>4.270037683223853</v>
+        <v>4.001235523521067</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2379083639066</v>
+        <v>2.22583785185435</v>
       </c>
       <c r="U5" t="n">
-        <v>6.269947333144362</v>
+        <v>6.365698228840986</v>
       </c>
       <c r="V5" t="n">
-        <v>1.997511251366765</v>
+        <v>1.98453800368403</v>
       </c>
       <c r="W5" t="n">
-        <v>7.246161791912737</v>
+        <v>7.209204295845846</v>
       </c>
       <c r="X5" t="n">
-        <v>5.93032913602512</v>
+        <v>5.943114081088913</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.37466013818405</v>
+        <v>5.01604621107187</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.959082309669633</v>
+        <v>2.825582614695042</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.574276152407164</v>
+        <v>5.601237910183863</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.567901602760097</v>
+        <v>10.18533828531488</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4858458113817983</v>
+        <v>0.3565966698512634</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2768560279786572</v>
+        <v>0.217871681696804</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5018296677535797</v>
+        <v>0.3822689990303873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3852070422521569</v>
+        <v>0.3123587852404427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3747086911665102</v>
+        <v>0.2370960480614406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7756521079917549</v>
+        <v>0.7105033498966354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5516315345896088</v>
+        <v>0.4095642384491888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3075417281408632</v>
+        <v>0.2593314210946946</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5593083975885187</v>
+        <v>0.4712899340100229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3986243005159001</v>
+        <v>0.4235911965889362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6454674245526727</v>
+        <v>0.6256503379931398</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8617751625087972</v>
+        <v>0.6789006926524475</v>
       </c>
       <c r="N6" t="n">
-        <v>0.457277707253442</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3971928812165987</v>
+        <v>0.4229007816564371</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5747084068669049</v>
+        <v>0.483912922805419</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4337230730762536</v>
+        <v>0.2914350374435908</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3265545632678896</v>
+        <v>0.281396850838808</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5598182664602518</v>
+        <v>0.405820087413081</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3363793616180434</v>
+        <v>0.2811806592450502</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6496277598327559</v>
+        <v>0.5940787626370054</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4198969300861806</v>
+        <v>0.2813781293957213</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6096185518578324</v>
+        <v>0.5531764482462247</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5268105096713473</v>
+        <v>0.5503577609629767</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5122931192213571</v>
+        <v>0.4388830291433191</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3918077522946196</v>
+        <v>0.4073901656803752</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6016311841578101</v>
+        <v>0.5421575920588568</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6865396801404323</v>
+        <v>0.6618314948880588</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4784847660866977</v>
+        <v>0.4297376170068202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.35337841105509</v>
+        <v>0.2910126288523598</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4944686224584796</v>
+        <v>0.4554099461859422</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3778459969570561</v>
+        <v>0.308063093550313</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3673476458714101</v>
+        <v>0.3102369952169958</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8521744910681892</v>
+        <v>0.7062076582065031</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5442704892945084</v>
+        <v>0.4827051856047439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3840641112172962</v>
+        <v>0.3324723682502497</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6358307806649515</v>
+        <v>0.5444308811655796</v>
       </c>
       <c r="K7" t="n">
-        <v>0.475146683592333</v>
+        <v>0.4192955048988057</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6381063792575727</v>
+        <v>0.6213546463030056</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8544141172136975</v>
+        <v>0.7520416398080005</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5331177469285121</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O7" t="n">
-        <v>0.472674533201379</v>
+        <v>0.4138169127907209</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5621882269812201</v>
+        <v>0.4748796500473972</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4263620277811527</v>
+        <v>0.3645759845991471</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3191935179727887</v>
+        <v>0.2771011591486758</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5524572211651513</v>
+        <v>0.4789610345686373</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129017446944765</v>
+        <v>0.3543216064006063</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6417718470059235</v>
+        <v>0.589424107440958</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4125358847910808</v>
+        <v>0.3545190765512774</v>
       </c>
       <c r="W7" t="n">
-        <v>0.681679453721731</v>
+        <v>0.6218900530880517</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6033328927477808</v>
+        <v>0.5460620692728467</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5865814350698135</v>
+        <v>0.5096328574260126</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4683301353710521</v>
+        <v>0.4030944739902451</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5942701388627101</v>
+        <v>0.5378619003687253</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7607814479891096</v>
+        <v>0.7323790611501129</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5190936696604831</v>
+        <v>0.4682390971806084</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5024732640640591</v>
+        <v>0.4323767771222902</v>
       </c>
       <c r="D8" t="n">
-        <v>0.643563475467449</v>
+        <v>0.5967740944558741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4691752820452097</v>
+        <v>0.3946559053303123</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4248573924540861</v>
+        <v>0.364763276890553</v>
       </c>
       <c r="G8" t="n">
-        <v>1.023764612404888</v>
+        <v>0.8689010507885142</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6933653423034771</v>
+        <v>0.6240693338746757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.533158964226265</v>
+        <v>0.4738365165201808</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7849256336739204</v>
+        <v>0.6857950294355106</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6242415366013013</v>
+        <v>0.5606596531687377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7872012322665423</v>
+        <v>0.7627187945729369</v>
       </c>
       <c r="M8" t="n">
-        <v>1.003508970222598</v>
+        <v>0.8934057880780355</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5981178397969934</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5611429839811226</v>
+        <v>0.4977156928161767</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6449918656496494</v>
+        <v>0.553407248906321</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4456509662449719</v>
+        <v>0.3828626027835108</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4682883709817572</v>
+        <v>0.4184653074186068</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7015520741741199</v>
+        <v>0.6203251828385681</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5619965977034449</v>
+        <v>0.4956857546705357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7383052549905078</v>
+        <v>0.6809408285258869</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5318632324046062</v>
+        <v>0.4677687603680043</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8307956272347583</v>
+        <v>0.7632744167528617</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6325647839848059</v>
+        <v>0.5737762553385044</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8433604591003567</v>
+        <v>0.7532701680393065</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5069238567451567</v>
+        <v>0.4396852272994951</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7433649918716786</v>
+        <v>0.6792260486386574</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.023198946543858</v>
+        <v>0.9811918674220369</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7402939086762961</v>
+        <v>0.6734910162177177</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7235805103807951</v>
+        <v>0.6363008452773694</v>
       </c>
       <c r="D9" t="n">
-        <v>0.864670721784185</v>
+        <v>0.8006981626109538</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7230314345587753</v>
+        <v>0.6299174769279323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4876744126880316</v>
+        <v>0.421459765806061</v>
       </c>
       <c r="G9" t="n">
-        <v>1.222376578126526</v>
+        <v>1.051495859827444</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9144725886202126</v>
+        <v>0.8279934020297564</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7542662105430005</v>
+        <v>0.6777605846752612</v>
       </c>
       <c r="J9" t="n">
-        <v>1.006032879990657</v>
+        <v>0.8897190975905908</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8453487829180376</v>
+        <v>0.7645837213238157</v>
       </c>
       <c r="L9" t="n">
-        <v>1.008308478583278</v>
+        <v>0.9666428627280158</v>
       </c>
       <c r="M9" t="n">
-        <v>1.224616216539402</v>
+        <v>1.097329856233015</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9033198462542164</v>
+        <v>4.313732832557108</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8791562878184981</v>
+        <v>0.7931119394405312</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9764822436643643</v>
+        <v>0.8614926482601842</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7965641148394869</v>
+        <v>0.7098641862200883</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6893956172984937</v>
+        <v>0.6223893755736846</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9226593204908563</v>
+        <v>0.8242492509936467</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7831038440201809</v>
+        <v>0.6996098228256165</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01246881386336</v>
+        <v>0.9350712873718851</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9078209596263366</v>
+        <v>0.8169761293176605</v>
       </c>
       <c r="W9" t="n">
-        <v>1.051881553047436</v>
+        <v>0.9671782695130607</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9735349920734857</v>
+        <v>0.8913502856978553</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9567835343955188</v>
+        <v>0.8549210738510223</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7731809155914362</v>
+        <v>0.6871662185848394</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9644722381884134</v>
+        <v>0.883150116793736</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.130983547314815</v>
+        <v>1.077667277575122</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.621562328267535</v>
+        <v>2.612025121316913</v>
       </c>
       <c r="C2" t="n">
-        <v>2.650796890948696</v>
+        <v>2.638677214709279</v>
       </c>
       <c r="D2" t="n">
-        <v>2.626950789725748</v>
+        <v>2.617567864550425</v>
       </c>
       <c r="E2" t="n">
-        <v>2.621201914971929</v>
+        <v>2.611489364428689</v>
       </c>
       <c r="F2" t="n">
-        <v>2.610801391120185</v>
+        <v>2.601153640775838</v>
       </c>
       <c r="G2" t="n">
-        <v>2.663692314914926</v>
+        <v>2.64798170377854</v>
       </c>
       <c r="H2" t="n">
-        <v>2.637393604085431</v>
+        <v>2.627873859121117</v>
       </c>
       <c r="I2" t="n">
-        <v>2.620399913509421</v>
+        <v>2.611353948896539</v>
       </c>
       <c r="J2" t="n">
-        <v>2.636845786131814</v>
+        <v>2.625473643986357</v>
       </c>
       <c r="K2" t="n">
-        <v>2.623107354665411</v>
+        <v>2.614626438593684</v>
       </c>
       <c r="L2" t="n">
-        <v>2.605041455460612</v>
+        <v>2.596388198412539</v>
       </c>
       <c r="M2" t="n">
-        <v>2.623953191970919</v>
+        <v>2.614092382660252</v>
       </c>
       <c r="N2" t="n">
-        <v>2.625457264137345</v>
+        <v>2.615856859862752</v>
       </c>
       <c r="O2" t="n">
-        <v>2.866399006291327</v>
+        <v>2.849451683731385</v>
       </c>
       <c r="P2" t="n">
-        <v>2.632438549472848</v>
+        <v>2.621699918692471</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.623898633346739</v>
+        <v>2.614165331036657</v>
       </c>
       <c r="R2" t="n">
-        <v>2.596262684908834</v>
+        <v>2.586778242491061</v>
       </c>
       <c r="S2" t="n">
-        <v>2.613732782278311</v>
+        <v>2.603701235933966</v>
       </c>
       <c r="T2" t="n">
-        <v>2.614656197802633</v>
+        <v>2.605780184235342</v>
       </c>
       <c r="U2" t="n">
-        <v>3.017188685539977</v>
+        <v>3.004631089747468</v>
       </c>
       <c r="V2" t="n">
-        <v>2.630044849677586</v>
+        <v>2.620445472735094</v>
       </c>
       <c r="W2" t="n">
-        <v>3.012273943640396</v>
+        <v>2.999388065181918</v>
       </c>
       <c r="X2" t="n">
-        <v>2.655420996036138</v>
+        <v>2.645891831777275</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.666188948249979</v>
+        <v>2.655351378416348</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.777753934415557</v>
+        <v>2.765847543533496</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.636322134102908</v>
+        <v>2.627408436507476</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.648473366435241</v>
+        <v>2.640012895834657</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.683037463935208</v>
+        <v>1.675014511001347</v>
       </c>
       <c r="C3" t="n">
-        <v>1.732851810341852</v>
+        <v>1.72016776345165</v>
       </c>
       <c r="D3" t="n">
-        <v>1.721458267058676</v>
+        <v>1.714536749250921</v>
       </c>
       <c r="E3" t="n">
-        <v>1.680407389389937</v>
+        <v>1.671132143561252</v>
       </c>
       <c r="F3" t="n">
-        <v>1.606090683937542</v>
+        <v>1.597277333180278</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98159708303853</v>
+        <v>1.929842508869875</v>
       </c>
       <c r="H3" t="n">
-        <v>1.796494613200936</v>
+        <v>1.788594478856093</v>
       </c>
       <c r="I3" t="n">
-        <v>1.674592500630851</v>
+        <v>1.670084752286041</v>
       </c>
       <c r="J3" t="n">
-        <v>1.791453194032336</v>
+        <v>1.770432118235289</v>
       </c>
       <c r="K3" t="n">
-        <v>1.694082360410558</v>
+        <v>1.693564322657528</v>
       </c>
       <c r="L3" t="n">
-        <v>1.565823637965684</v>
+        <v>1.56407746550255</v>
       </c>
       <c r="M3" t="n">
-        <v>1.702668649898858</v>
+        <v>1.692231781267043</v>
       </c>
       <c r="N3" t="n">
-        <v>1.710774683217471</v>
+        <v>1.70229838155069</v>
       </c>
       <c r="O3" t="n">
-        <v>2.075670659789149</v>
+        <v>2.055099462261322</v>
       </c>
       <c r="P3" t="n">
-        <v>1.760313130451901</v>
+        <v>1.743755690229131</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.699667073568405</v>
+        <v>1.690250869203948</v>
       </c>
       <c r="R3" t="n">
-        <v>1.501574390412672</v>
+        <v>1.493927414533026</v>
       </c>
       <c r="S3" t="n">
-        <v>1.627594869585659</v>
+        <v>1.616068812926883</v>
       </c>
       <c r="T3" t="n">
-        <v>1.633543510626904</v>
+        <v>1.63024810928579</v>
       </c>
       <c r="U3" t="n">
-        <v>2.378405684323112</v>
+        <v>2.365625202953191</v>
       </c>
       <c r="V3" t="n">
-        <v>1.743256593578475</v>
+        <v>1.734795400195513</v>
       </c>
       <c r="W3" t="n">
-        <v>2.460636995892238</v>
+        <v>2.447174214473795</v>
       </c>
       <c r="X3" t="n">
-        <v>1.92463404315926</v>
+        <v>1.916667826183032</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.001355507363004</v>
+        <v>1.984054660824164</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.980578862873694</v>
+        <v>1.968131847358616</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78832786016949</v>
+        <v>1.784754764642072</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.87434478143297</v>
+        <v>1.873783958580297</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1439193550509115</v>
+        <v>0.110886574539435</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1470449125615446</v>
+        <v>0.1132060381467206</v>
       </c>
       <c r="D4" t="n">
-        <v>0.204784506036171</v>
+        <v>0.1734944091498176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1398483210787149</v>
+        <v>0.1048349540265989</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02236961969595283</v>
+        <v>-0.01191179930011445</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6197969349845877</v>
+        <v>0.5170327142886526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3227408981607376</v>
+        <v>0.2899053588175399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1307893456208181</v>
+        <v>0.1033053732967496</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3161671753813717</v>
+        <v>0.2624325289238353</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1613711389621495</v>
+        <v>0.140269649845646</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.04269150328023544</v>
+        <v>-0.06573966300539433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1756918440721388</v>
+        <v>0.1387969645030976</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1879144474594618</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1198653755587041</v>
+        <v>0.08617315484197059</v>
       </c>
       <c r="P4" t="n">
-        <v>0.266771276873881</v>
+        <v>0.2201678615230622</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.170308995673943</v>
+        <v>0.1350612278690562</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1418517550965277</v>
+        <v>-0.1742885359366074</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05548103133353037</v>
+        <v>0.01686445996260507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06591143447287269</v>
+        <v>0.04034713739010611</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2287901655103393</v>
+        <v>0.1948523951935411</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2371466621111371</v>
+        <v>0.2035756886376073</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4171109111716289</v>
+        <v>0.3842618022493511</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5263685832539847</v>
+        <v>0.4934266486457383</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6453199224299579</v>
+        <v>0.5962243094468531</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2262795694046409</v>
+        <v>0.1921768760177145</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3106381518076066</v>
+        <v>0.2846481962914432</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4453292430273854</v>
+        <v>0.4239977593412521</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2513398566001752</v>
+        <v>-0.2855735580956006</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2049464329184983</v>
+        <v>-0.2526658675669184</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8060305467542006</v>
+        <v>0.8027840859200837</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3532894011481039</v>
+        <v>-0.4229971277215845</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.476515569202967</v>
+        <v>-2.533581876977078</v>
       </c>
       <c r="G5" t="n">
-        <v>7.064529688598775</v>
+        <v>5.967099154130501</v>
       </c>
       <c r="H5" t="n">
-        <v>3.154225552065774</v>
+        <v>3.122543188285328</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5606522963306317</v>
+        <v>-0.4919870341964651</v>
       </c>
       <c r="J5" t="n">
-        <v>2.457966361513275</v>
+        <v>2.1079107538037</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06663419065737175</v>
+        <v>0.2258647736930777</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.190934508780633</v>
+        <v>-3.065164186691325</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2990485278724834</v>
+        <v>0.2006750521227116</v>
       </c>
       <c r="N5" t="n">
-        <v>1.136057148287487</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5892983563938201</v>
+        <v>-0.6332222855612019</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74091520089774</v>
+        <v>1.487461105559452</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1922314528492362</v>
+        <v>0.1220821589442125</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.771172772676951</v>
+        <v>-5.795179305086728</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.588915673034625</v>
+        <v>-1.708941341131696</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.737044568693672</v>
+        <v>-1.634738695478031</v>
       </c>
       <c r="U5" t="n">
-        <v>1.179610500920488</v>
+        <v>1.153664072742528</v>
       </c>
       <c r="V5" t="n">
-        <v>1.274326565465001</v>
+        <v>1.230671288044965</v>
       </c>
       <c r="W5" t="n">
-        <v>4.562588549716123</v>
+        <v>4.53085452683943</v>
       </c>
       <c r="X5" t="n">
-        <v>6.484703757491179</v>
+        <v>6.451732126647466</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.56857083488697</v>
+        <v>8.276034833985864</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.057654205412535</v>
+        <v>1.0078042443183</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.670889458954706</v>
+        <v>2.761136851797216</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.40827295538943</v>
+        <v>5.595425760545117</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1543176475552025</v>
+        <v>0.1776069429420091</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2234994947050095</v>
+        <v>0.1799264065492945</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2151827985404617</v>
+        <v>0.2402147775523924</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2163029032221798</v>
+        <v>0.1127060602245316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09882420183941751</v>
+        <v>-0.004040693102181692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6301952274888782</v>
+        <v>0.5249038204865859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.399195480304203</v>
+        <v>0.2977764650154723</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2072439277642836</v>
+        <v>0.1700257416993247</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3265654678856627</v>
+        <v>0.3291528973264098</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2378257211056143</v>
+        <v>0.1481407560435787</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.03229321077594473</v>
+        <v>0.0009807053971804813</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2521464262156034</v>
+        <v>0.14666807070103</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1989347491060503</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1308856772053154</v>
+        <v>0.1574312316900879</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2755025726413317</v>
+        <v>0.2266277032332803</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2467635778174076</v>
+        <v>0.1429323340669889</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.06539717295306316</v>
+        <v>-0.1075681675340332</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06587932383782115</v>
+        <v>0.02473556616053706</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07630972697716396</v>
+        <v>0.04821824358803927</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2418660925967478</v>
+        <v>0.2656250336897884</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3136012442546019</v>
+        <v>0.21144679483554</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4310353461170455</v>
+        <v>0.3955150792473179</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5367668757582746</v>
+        <v>0.5601470170483124</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6602133446558026</v>
+        <v>0.6099773053904917</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2366778619089318</v>
+        <v>0.2588972444202888</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3870927339510715</v>
+        <v>0.2925193024893755</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4574198118322347</v>
+        <v>0.4337893583945159</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2167559556015595</v>
+        <v>0.1812600874653169</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2198815131121926</v>
+        <v>0.1835795510726028</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2776211065868188</v>
+        <v>0.2438679220756999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2126849216293626</v>
+        <v>0.1752084669524811</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09520622024660076</v>
+        <v>0.05846171362576791</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6926335355352349</v>
+        <v>0.5874062272145357</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3955774987113852</v>
+        <v>0.3602788717434226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2036259461714657</v>
+        <v>0.1736788862226318</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3890037759320191</v>
+        <v>0.3328060418497175</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2342077395127978</v>
+        <v>0.2106431627715281</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03014509727041198</v>
+        <v>0.004633849920487834</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2485284446227864</v>
+        <v>0.2091704774289796</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2607510480101096</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1923685179526193</v>
+        <v>0.1562132285514868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3392744192677958</v>
+        <v>0.2902079352325784</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2431455962245908</v>
+        <v>0.2054347407949382</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.06901515454588039</v>
+        <v>-0.1039150230107251</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1283176318841784</v>
+        <v>0.08723797288848636</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1387480350235206</v>
+        <v>0.1107206503159884</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3031883419069371</v>
+        <v>0.2685403567473352</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3099832626617848</v>
+        <v>0.2739492015634897</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4899475117222779</v>
+        <v>0.454635315175232</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5992051838046329</v>
+        <v>0.5638001615716209</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7208341575627223</v>
+        <v>0.6706500924664085</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2991161699552886</v>
+        <v>0.2625503889435967</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3834747523582542</v>
+        <v>0.3550217092173251</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5181658435780334</v>
+        <v>0.4943712722671339</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2427118036121972</v>
+        <v>0.2044722070758012</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3273138433297293</v>
+        <v>0.2825043269405225</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3850534368043554</v>
+        <v>0.3427926979436195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2767334284933928</v>
+        <v>0.2338184867509543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1338551519400991</v>
+        <v>0.09346898020549259</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8169605451014785</v>
+        <v>0.702030515577486</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5030098289289217</v>
+        <v>0.4592036476113421</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3110582763890025</v>
+        <v>0.2726036620905518</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4964361061495562</v>
+        <v>0.431730817717637</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3416400697303345</v>
+        <v>0.3095679386394473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1375774274879486</v>
+        <v>0.103558625788407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3559607748402229</v>
+        <v>0.3080952532970596</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3050254737780042</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2543327423694881</v>
+        <v>0.2129099833083737</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3969841852462761</v>
+        <v>0.3429512013106074</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2530894558932691</v>
+        <v>0.2137675953992809</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03841717567165677</v>
+        <v>-0.004990247142805188</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2357499621017152</v>
+        <v>0.1861627487564071</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2461803652410575</v>
+        <v>0.2096454261839085</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3713626510645478</v>
+        <v>0.3309352307565742</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3944778941278667</v>
+        <v>0.351834910917913</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5973958543228991</v>
+        <v>0.5535749707257258</v>
       </c>
       <c r="X8" t="n">
-        <v>0.616616524914628</v>
+        <v>0.5790722315509581</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9082391608866685</v>
+        <v>0.844318126305735</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3235585504858776</v>
+        <v>0.2843561070945596</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4909070825757911</v>
+        <v>0.4539464850852444</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7107071723382766</v>
+        <v>0.6723842485647922</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4067260982560931</v>
+        <v>0.3563364093817263</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4906735093506815</v>
+        <v>0.43360884029728</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5484131028253079</v>
+        <v>0.4938972113003776</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4648236106188264</v>
+        <v>0.407938956876752</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1796817060260631</v>
+        <v>0.1357038890167044</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9634255927352012</v>
+        <v>0.837435568215796</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6663694949498743</v>
+        <v>0.6103081609680994</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4744179424099544</v>
+        <v>0.4237081754473099</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6597957721705089</v>
+        <v>0.5828353310743951</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5049997357512864</v>
+        <v>0.4606724519962055</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3009370935089014</v>
+        <v>0.254663139145165</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5193204408612755</v>
+        <v>0.4591997666536571</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5315430442485984</v>
+        <v>0.4470513784209891</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4902783099624076</v>
+        <v>0.431415341151228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.643009331908834</v>
+        <v>0.5708121764542564</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5139376534245572</v>
+        <v>0.4554640817961988</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2017768416926091</v>
+        <v>0.1461142662139532</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3991096281226675</v>
+        <v>0.3372672621131645</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4095400312620103</v>
+        <v>0.3607499395406655</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5750963968815936</v>
+        <v>0.5193074674377731</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6740420065735876</v>
+        <v>0.6104726598418903</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7607395079607664</v>
+        <v>0.7046646043999089</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8699971800431208</v>
+        <v>0.8138294507962983</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9916261538012108</v>
+        <v>0.9206793816910847</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.521179799649415</v>
+        <v>0.4673897245192008</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6542667485967434</v>
+        <v>0.6050509984420027</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7889578398165223</v>
+        <v>0.7444005614918119</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -798,7 +798,7 @@
         <v>0.7739936206792769</v>
       </c>
       <c r="N4" t="n">
-        <v>8.01408394358586</v>
+        <v>0.564616270336346</v>
       </c>
       <c r="O4" t="n">
         <v>0.5163657387351357</v>
@@ -974,7 +974,7 @@
         <v>0.893659630827992</v>
       </c>
       <c r="N6" t="n">
-        <v>8.01408394358586</v>
+        <v>0.5910888615998764</v>
       </c>
       <c r="O6" t="n">
         <v>0.5428381257310242</v>
@@ -1062,7 +1062,7 @@
         <v>0.8844867091456438</v>
       </c>
       <c r="N7" t="n">
-        <v>8.01408394358586</v>
+        <v>0.6751093588027136</v>
       </c>
       <c r="O7" t="n">
         <v>0.6264753753805611</v>
@@ -1150,7 +1150,7 @@
         <v>1.06672153223512</v>
       </c>
       <c r="N8" t="n">
-        <v>8.01408394358586</v>
+        <v>0.756770702242989</v>
       </c>
       <c r="O8" t="n">
         <v>0.7361586360633455</v>
@@ -1238,7 +1238,7 @@
         <v>1.359670577894003</v>
       </c>
       <c r="N9" t="n">
-        <v>8.01408394358586</v>
+        <v>1.150293227551069</v>
       </c>
       <c r="O9" t="n">
         <v>1.147050143994055</v>
@@ -1634,7 +1634,7 @@
         <v>0.1110750852270499</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01702411745365875</v>
+        <v>-0.01702411745365874</v>
       </c>
       <c r="G4" t="n">
         <v>0.1811043387269766</v>
@@ -1658,7 +1658,7 @@
         <v>0.09814087600801574</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1432132706433129</v>
+        <v>0.108393582551083</v>
       </c>
       <c r="O4" t="n">
         <v>0.02667362989259436</v>
@@ -1670,7 +1670,7 @@
         <v>0.1303350530614293</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2581218906596082</v>
+        <v>-0.2581218906596081</v>
       </c>
       <c r="S4" t="n">
         <v>0.002519831180818853</v>
@@ -1834,7 +1834,7 @@
         <v>0.1071133200615522</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1432132706433129</v>
+        <v>0.1176727523421305</v>
       </c>
       <c r="O6" t="n">
         <v>0.07983576469089036</v>
@@ -1852,7 +1852,7 @@
         <v>0.05098086093843187</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05452230454843605</v>
+        <v>0.05452230454843604</v>
       </c>
       <c r="U6" t="n">
         <v>0.225410324964852</v>
@@ -1922,7 +1922,7 @@
         <v>0.1615019864468522</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1432132706433129</v>
+        <v>0.1717546929899203</v>
       </c>
       <c r="O7" t="n">
         <v>0.08970157674739732</v>
@@ -2010,7 +2010,7 @@
         <v>0.2393951168108953</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1432132706433129</v>
+        <v>0.2008393856702331</v>
       </c>
       <c r="O8" t="n">
         <v>0.1325324154843324</v>
@@ -2098,7 +2098,7 @@
         <v>0.3323291646077458</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1432132706433129</v>
+        <v>0.3425818711508143</v>
       </c>
       <c r="O9" t="n">
         <v>0.2791693293259368</v>
@@ -2518,7 +2518,7 @@
         <v>0.718524822685474</v>
       </c>
       <c r="N4" t="n">
-        <v>6.390361199836811</v>
+        <v>0.4929716080824226</v>
       </c>
       <c r="O4" t="n">
         <v>0.4496899016262545</v>
@@ -2694,7 +2694,7 @@
         <v>0.8232570406766121</v>
       </c>
       <c r="N6" t="n">
-        <v>6.390361199836811</v>
+        <v>0.5143327623255805</v>
       </c>
       <c r="O6" t="n">
         <v>0.4711736832018384</v>
@@ -2782,7 +2782,7 @@
         <v>0.8167754363422209</v>
       </c>
       <c r="N7" t="n">
-        <v>6.390361199836811</v>
+        <v>0.5912222217391701</v>
       </c>
       <c r="O7" t="n">
         <v>0.5475818600851873</v>
@@ -2870,7 +2870,7 @@
         <v>0.9773976815073417</v>
       </c>
       <c r="N8" t="n">
-        <v>6.390361199836811</v>
+        <v>0.6628664694068103</v>
       </c>
       <c r="O8" t="n">
         <v>0.6440366892038275</v>
@@ -2958,7 +2958,7 @@
         <v>1.19000885055331</v>
       </c>
       <c r="N9" t="n">
-        <v>6.390361199836811</v>
+        <v>0.9644556359502576</v>
       </c>
       <c r="O9" t="n">
         <v>0.9576493429281246</v>
@@ -3166,40 +3166,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672047349274314</v>
+        <v>2.672047349274317</v>
       </c>
       <c r="C2" t="n">
-        <v>2.68787739970846</v>
+        <v>2.687877399708463</v>
       </c>
       <c r="D2" t="n">
-        <v>2.680392009183838</v>
+        <v>2.680392009183839</v>
       </c>
       <c r="E2" t="n">
-        <v>2.661787447051865</v>
+        <v>2.661787447051867</v>
       </c>
       <c r="F2" t="n">
-        <v>2.66203271895922</v>
+        <v>2.662032718959222</v>
       </c>
       <c r="G2" t="n">
-        <v>2.691095152016629</v>
+        <v>2.691095152016631</v>
       </c>
       <c r="H2" t="n">
-        <v>2.671928997654845</v>
+        <v>2.671928997654847</v>
       </c>
       <c r="I2" t="n">
-        <v>2.665675243809016</v>
+        <v>2.665675243809019</v>
       </c>
       <c r="J2" t="n">
-        <v>2.68108482772379</v>
+        <v>2.681084827723792</v>
       </c>
       <c r="K2" t="n">
-        <v>2.672134965941316</v>
+        <v>2.672134965941318</v>
       </c>
       <c r="L2" t="n">
-        <v>2.686569635473952</v>
+        <v>2.686569635473954</v>
       </c>
       <c r="M2" t="n">
-        <v>2.693237291451481</v>
+        <v>2.693237291451482</v>
       </c>
       <c r="N2" t="n">
         <v>2.672293837671493</v>
@@ -3208,43 +3208,43 @@
         <v>2.943620693105744</v>
       </c>
       <c r="P2" t="n">
-        <v>2.681543926796318</v>
+        <v>2.681543926796319</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.660809367733972</v>
+        <v>2.660809367733973</v>
       </c>
       <c r="R2" t="n">
-        <v>2.668337351351107</v>
+        <v>2.668337351351108</v>
       </c>
       <c r="S2" t="n">
-        <v>2.683025969363164</v>
+        <v>2.683025969363166</v>
       </c>
       <c r="T2" t="n">
-        <v>2.669793248149384</v>
+        <v>2.669793248149385</v>
       </c>
       <c r="U2" t="n">
-        <v>3.07757320181054</v>
+        <v>3.077573201810541</v>
       </c>
       <c r="V2" t="n">
-        <v>2.665956801124032</v>
+        <v>2.665956801124034</v>
       </c>
       <c r="W2" t="n">
         <v>3.062320160911439</v>
       </c>
       <c r="X2" t="n">
-        <v>2.68700525043864</v>
+        <v>2.687005250438643</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.682830579193503</v>
+        <v>2.682830579193504</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.832022085052255</v>
+        <v>2.832022085052257</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.677650603776432</v>
+        <v>2.677650603776433</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.696698545906433</v>
+        <v>2.696698545906434</v>
       </c>
     </row>
     <row r="3">
@@ -3257,43 +3257,43 @@
         <v>1.872470112073578</v>
       </c>
       <c r="C3" t="n">
-        <v>1.83281536844156</v>
+        <v>1.832815368441561</v>
       </c>
       <c r="D3" t="n">
         <v>1.933073090733255</v>
       </c>
       <c r="E3" t="n">
-        <v>1.79975540079381</v>
+        <v>1.799755400793809</v>
       </c>
       <c r="F3" t="n">
-        <v>1.801714624197169</v>
+        <v>1.801714624197168</v>
       </c>
       <c r="G3" t="n">
         <v>2.007839976402368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87300524920383</v>
+        <v>1.873005249203829</v>
       </c>
       <c r="I3" t="n">
         <v>1.827885461459543</v>
       </c>
       <c r="J3" t="n">
-        <v>1.937127987001215</v>
+        <v>1.937127987001214</v>
       </c>
       <c r="K3" t="n">
         <v>1.873105050005258</v>
       </c>
       <c r="L3" t="n">
-        <v>1.976513359021031</v>
+        <v>1.97651335902103</v>
       </c>
       <c r="M3" t="n">
         <v>2.026547626609576</v>
       </c>
       <c r="N3" t="n">
-        <v>1.874962983847797</v>
+        <v>1.874962983847796</v>
       </c>
       <c r="O3" t="n">
-        <v>2.311646382191754</v>
+        <v>2.311646382191755</v>
       </c>
       <c r="P3" t="n">
         <v>1.93992048230803</v>
@@ -3305,25 +3305,25 @@
         <v>1.847078699616997</v>
       </c>
       <c r="S3" t="n">
-        <v>1.950589636272262</v>
+        <v>1.950589636272261</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85732232034075</v>
+        <v>1.857322320340749</v>
       </c>
       <c r="U3" t="n">
-        <v>2.591639231851396</v>
+        <v>2.591639231851397</v>
       </c>
       <c r="V3" t="n">
         <v>1.828899061331237</v>
       </c>
       <c r="W3" t="n">
-        <v>2.593792221912525</v>
+        <v>2.593792221912524</v>
       </c>
       <c r="X3" t="n">
         <v>1.980182896128464</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.949917290759077</v>
+        <v>1.949917290759078</v>
       </c>
       <c r="Z3" t="n">
         <v>2.137333682493193</v>
@@ -3332,7 +3332,7 @@
         <v>1.913044305391522</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.04922381919951</v>
+        <v>2.049223819199511</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.407581424772971</v>
+        <v>0.4075814247729721</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2708350355816703</v>
+        <v>0.2708350355816708</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501838197184277</v>
+        <v>0.5018381971842776</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2916911093822357</v>
+        <v>0.2916911093822365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2944615684064227</v>
+        <v>0.2944615684064233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6227351191696222</v>
+        <v>0.6227351191696234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4062445887866503</v>
+        <v>0.4062445887866507</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3356055622291251</v>
+        <v>0.335605562229126</v>
       </c>
       <c r="J4" t="n">
         <v>0.5092791173289669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4085710953324505</v>
+        <v>0.4085710953324507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5716173279795991</v>
+        <v>0.5716173279795982</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6492193878670401</v>
+        <v>0.649219387867042</v>
       </c>
       <c r="N4" t="n">
-        <v>4.600288343215076</v>
+        <v>0.4103656246093599</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3894871591257478</v>
+        <v>0.3894871591257487</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5148496365254933</v>
+        <v>0.5148496365254939</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.280643253547893</v>
+        <v>0.2806432535478937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3656752915470081</v>
+        <v>0.3656752915470082</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5315899890912766</v>
+        <v>0.5315899890912772</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3821203156291479</v>
+        <v>0.3821203156291493</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5066425410507474</v>
+        <v>0.5066425410507491</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3362089086008507</v>
+        <v>0.3362089086008502</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5651153745046185</v>
+        <v>0.5651153745046187</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5765377993985449</v>
+        <v>0.5765377993985455</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5261848300091474</v>
+        <v>0.5261848300091485</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4100096706653265</v>
+        <v>0.4100096706653271</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4708727619988337</v>
+        <v>0.4708727619988342</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6830462560138304</v>
+        <v>0.6830462560138308</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.170838344833232</v>
+        <v>4.170838344833221</v>
       </c>
       <c r="C5" t="n">
-        <v>2.006870883029005</v>
+        <v>2.006870883029006</v>
       </c>
       <c r="D5" t="n">
-        <v>6.380363568734685</v>
+        <v>6.380363568734682</v>
       </c>
       <c r="E5" t="n">
-        <v>2.385795812483976</v>
+        <v>2.385795812483977</v>
       </c>
       <c r="F5" t="n">
         <v>2.542952330450365</v>
       </c>
       <c r="G5" t="n">
-        <v>7.678075947073498</v>
+        <v>7.678075947073512</v>
       </c>
       <c r="H5" t="n">
-        <v>4.862250212122918</v>
+        <v>4.862250212122929</v>
       </c>
       <c r="I5" t="n">
         <v>3.360799954183372</v>
       </c>
       <c r="J5" t="n">
-        <v>6.057281150282477</v>
+        <v>6.05728115028247</v>
       </c>
       <c r="K5" t="n">
         <v>4.193324208790639</v>
       </c>
       <c r="L5" t="n">
-        <v>7.27780174617819</v>
+        <v>7.277801746178167</v>
       </c>
       <c r="M5" t="n">
-        <v>9.274190589615381</v>
+        <v>9.274190589615362</v>
       </c>
       <c r="N5" t="n">
-        <v>4.600288343215076</v>
+        <v>4.600288343215074</v>
       </c>
       <c r="O5" t="n">
-        <v>3.686737984293954</v>
+        <v>3.686737984293967</v>
       </c>
       <c r="P5" t="n">
-        <v>5.898502499935379</v>
+        <v>5.898502499935391</v>
       </c>
       <c r="Q5" t="n">
         <v>2.210860075239822</v>
       </c>
       <c r="R5" t="n">
-        <v>3.992983793333264</v>
+        <v>3.992983793333263</v>
       </c>
       <c r="S5" t="n">
-        <v>6.242126373335311</v>
+        <v>6.242126373335316</v>
       </c>
       <c r="T5" t="n">
         <v>4.207565087017858</v>
       </c>
       <c r="U5" t="n">
-        <v>6.025228910518868</v>
+        <v>6.025228910518909</v>
       </c>
       <c r="V5" t="n">
-        <v>2.898378065444698</v>
+        <v>2.898378065444704</v>
       </c>
       <c r="W5" t="n">
-        <v>7.262263708540135</v>
+        <v>7.262263708540122</v>
       </c>
       <c r="X5" t="n">
-        <v>7.655309600745091</v>
+        <v>7.655309600745118</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.577334688066912</v>
+        <v>6.577334688066913</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.01507191164377</v>
+        <v>4.015071911643761</v>
       </c>
       <c r="AA5" t="n">
         <v>5.592627239607832</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.30577393607277</v>
+        <v>10.30577393607276</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5024395574342215</v>
+        <v>0.5024395574342216</v>
       </c>
       <c r="C6" t="n">
         <v>0.2911834661992054</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5966963298455273</v>
+        <v>0.5966963298455278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3865492420434862</v>
+        <v>0.3865492420434861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3148099990239573</v>
+        <v>0.3148099990239578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6430835497871561</v>
+        <v>0.643083549787157</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4265930194041854</v>
+        <v>0.4265930194041859</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3559539928466599</v>
+        <v>0.3559539928466601</v>
       </c>
       <c r="J6" t="n">
         <v>0.6041372499902189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5034292279937013</v>
+        <v>0.5034292279937017</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6664754606408494</v>
+        <v>0.6664754606408499</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6695678184845748</v>
+        <v>0.669567818484575</v>
       </c>
       <c r="N6" t="n">
-        <v>4.600288343215076</v>
+        <v>0.4312417009033477</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4883504966487201</v>
+        <v>0.4883504966487208</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6136724186072775</v>
+        <v>0.6136724186072791</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3755013862091434</v>
+        <v>0.3755013862091437</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3860237221645427</v>
+        <v>0.3860237221645429</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6264481217525268</v>
+        <v>0.6264481217525271</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4024687462466826</v>
+        <v>0.4024687462466824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5301891089001847</v>
+        <v>0.5301891089001863</v>
       </c>
       <c r="V6" t="n">
         <v>0.4310670412621008</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6639933428894682</v>
+        <v>0.6639933428894683</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5968862300160804</v>
+        <v>0.5968862300160802</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5521731392681352</v>
+        <v>0.5521731392681393</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.504867803326577</v>
+        <v>0.5048678033265769</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5657308946600854</v>
+        <v>0.5657308946600856</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7056420265565466</v>
+        <v>0.7056420265565482</v>
       </c>
     </row>
     <row r="7">
@@ -3609,82 +3609,82 @@
         <v>0.4948793727496889</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3581329835583893</v>
+        <v>0.358132983558389</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5891361451609953</v>
+        <v>0.5891361451609958</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3789890573589539</v>
+        <v>0.3789890573589548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3817595163831406</v>
+        <v>0.3817595163831412</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100330671463398</v>
+        <v>0.7100330671463404</v>
       </c>
       <c r="H7" t="n">
-        <v>0.493542536763369</v>
+        <v>0.4935425367633692</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4229035102058445</v>
+        <v>0.4229035102058447</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5965770653056841</v>
+        <v>0.5965770653056851</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4958690433091686</v>
+        <v>0.4958690433091682</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6589152759563179</v>
+        <v>0.6589152759563178</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7365173358437573</v>
+        <v>0.736517335843759</v>
       </c>
       <c r="N7" t="n">
-        <v>4.600288343215076</v>
+        <v>0.4976635725860778</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4764512029414833</v>
+        <v>0.476451202941484</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6018136803412295</v>
+        <v>0.60181368034123</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3679412015246117</v>
+        <v>0.3679412015246122</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4529732395237261</v>
+        <v>0.452973239523726</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6188879370679953</v>
+        <v>0.6188879370679954</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4694182636058651</v>
+        <v>0.4694182636058662</v>
       </c>
       <c r="U7" t="n">
-        <v>0.596725250130305</v>
+        <v>0.5967252501303085</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4235068565775688</v>
+        <v>0.4235068565775684</v>
       </c>
       <c r="W7" t="n">
         <v>0.6524133224813364</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6638357473752647</v>
+        <v>0.6638357473752654</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6166809152177679</v>
+        <v>0.6166809152177689</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4973076186420445</v>
+        <v>0.4973076186420444</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.558170709975553</v>
+        <v>0.5581707099755534</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7703442039905498</v>
+        <v>0.7703442039905514</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5338350084806455</v>
+        <v>0.5338350084806467</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4973954961140183</v>
+        <v>0.4973954961140191</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7283986577166252</v>
+        <v>0.7283986577166258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4648411168847659</v>
+        <v>0.4648411168847657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.436341791205109</v>
+        <v>0.4363417912051096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8700948640456723</v>
+        <v>0.8700948640456729</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6328050493190001</v>
+        <v>0.6328050493190009</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5621660227614739</v>
+        <v>0.5621660227614743</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7358395778613147</v>
+        <v>0.7358395778613145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.635131555864799</v>
+        <v>0.6351315558647989</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7981777885119485</v>
+        <v>0.7981777885119482</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8757798483995787</v>
+        <v>0.875779848399579</v>
       </c>
       <c r="N8" t="n">
-        <v>4.600288343215076</v>
+        <v>0.5591714746122327</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5596606512038519</v>
+        <v>0.5596606512038529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6797854032194498</v>
+        <v>0.6797854032194512</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.387184246582239</v>
+        <v>0.3871842465822399</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5922357520793574</v>
+        <v>0.5922357520793571</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7581504496236258</v>
+        <v>0.7581504496236269</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6086807761614951</v>
+        <v>0.608680776161496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6873811021582643</v>
+        <v>0.6873811021582641</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5352860565468317</v>
+        <v>0.5352860565468328</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7916955481536033</v>
+        <v>0.791695548153604</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6922721169707042</v>
+        <v>0.6922721169707068</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8555709116930321</v>
+        <v>0.855570911693033</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5344000026431801</v>
+        <v>0.5344000026431799</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6974332225311843</v>
+        <v>0.697433222531184</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.014385636860154</v>
+        <v>1.014385636860156</v>
       </c>
     </row>
     <row r="9">
@@ -3782,82 +3782,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7133704816224133</v>
+        <v>0.713370481622414</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6699344458864066</v>
+        <v>0.6699344458864069</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9009376074890127</v>
+        <v>0.9009376074890136</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6692548845958877</v>
+        <v>0.6692548845958871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4784551236312272</v>
+        <v>0.4784551236312268</v>
       </c>
       <c r="G9" t="n">
-        <v>1.021834547519499</v>
+        <v>1.021834547519498</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8053439990913884</v>
+        <v>0.8053439990913888</v>
       </c>
       <c r="I9" t="n">
-        <v>0.734704972533863</v>
+        <v>0.7347049725338631</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9083785276337034</v>
+        <v>0.9083785276337037</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8076705056371852</v>
+        <v>0.8076705056371856</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9707167382843362</v>
+        <v>0.9707167382843354</v>
       </c>
       <c r="M9" t="n">
         <v>1.048318798171778</v>
       </c>
       <c r="N9" t="n">
-        <v>4.600288343215076</v>
+        <v>0.8094650349140966</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8195095224113714</v>
+        <v>0.8195095224113721</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9515972076114253</v>
+        <v>0.9515972076114269</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6797426818977697</v>
+        <v>0.67974268189777</v>
       </c>
       <c r="R9" t="n">
         <v>0.7647747018517435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9306893993960135</v>
+        <v>0.9306893993960142</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7812197259338844</v>
+        <v>0.781219725933885</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9089400885873852</v>
+        <v>0.9089400885873878</v>
       </c>
       <c r="V9" t="n">
-        <v>0.842986350914811</v>
+        <v>0.8429863509148106</v>
       </c>
       <c r="W9" t="n">
-        <v>0.964214784809354</v>
+        <v>0.9642147848093545</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975637209703283</v>
+        <v>0.9756372097032827</v>
       </c>
       <c r="Y9" t="n">
         <v>0.9284823775457859</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7528512424824225</v>
+        <v>0.7528512424824213</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8699721723035719</v>
+        <v>0.8699721723035727</v>
       </c>
       <c r="AB9" t="n">
         <v>1.082145666318569</v>
@@ -4038,22 +4038,22 @@
         <v>2.655090726236734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.660552652029079</v>
+        <v>2.66055265202908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.681939410045278</v>
+        <v>2.681939410045279</v>
       </c>
       <c r="H2" t="n">
-        <v>2.666221043927937</v>
+        <v>2.666221043927938</v>
       </c>
       <c r="I2" t="n">
         <v>2.662573863465164</v>
       </c>
       <c r="J2" t="n">
-        <v>2.674903125675851</v>
+        <v>2.67490312567585</v>
       </c>
       <c r="K2" t="n">
-        <v>2.672360625848101</v>
+        <v>2.672360625848102</v>
       </c>
       <c r="L2" t="n">
         <v>2.677698942461813</v>
@@ -4074,7 +4074,7 @@
         <v>2.660454218461141</v>
       </c>
       <c r="R2" t="n">
-        <v>2.66305184793832</v>
+        <v>2.663051847938319</v>
       </c>
       <c r="S2" t="n">
         <v>2.676400239383266</v>
@@ -4083,28 +4083,28 @@
         <v>2.664746641334018</v>
       </c>
       <c r="U2" t="n">
-        <v>3.074391806773402</v>
+        <v>3.074391806773401</v>
       </c>
       <c r="V2" t="n">
-        <v>2.671075447487787</v>
+        <v>2.671075447487786</v>
       </c>
       <c r="W2" t="n">
-        <v>3.056235057932575</v>
+        <v>3.056235057932574</v>
       </c>
       <c r="X2" t="n">
-        <v>2.685047355599145</v>
+        <v>2.685047355599144</v>
       </c>
       <c r="Y2" t="n">
         <v>2.69236094051954</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.823589489375509</v>
+        <v>2.823589489375508</v>
       </c>
       <c r="AA2" t="n">
         <v>2.675691740169273</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.68882880854093</v>
+        <v>2.688828808540931</v>
       </c>
     </row>
     <row r="3">
@@ -4120,7 +4120,7 @@
         <v>1.842268568747785</v>
       </c>
       <c r="D3" t="n">
-        <v>1.869181170460592</v>
+        <v>1.869181170460591</v>
       </c>
       <c r="E3" t="n">
         <v>1.775347217004387</v>
@@ -4135,10 +4135,10 @@
         <v>1.855737246150848</v>
       </c>
       <c r="I3" t="n">
-        <v>1.829189088430941</v>
+        <v>1.82918908843094</v>
       </c>
       <c r="J3" t="n">
-        <v>1.916356514038503</v>
+        <v>1.916356514038502</v>
       </c>
       <c r="K3" t="n">
         <v>1.898157925797994</v>
@@ -4150,10 +4150,10 @@
         <v>1.980666135483313</v>
       </c>
       <c r="N3" t="n">
-        <v>1.853852139339696</v>
+        <v>1.853852139339695</v>
       </c>
       <c r="O3" t="n">
-        <v>2.27154471166236</v>
+        <v>2.271544711662359</v>
       </c>
       <c r="P3" t="n">
         <v>1.925377960953017</v>
@@ -4168,13 +4168,13 @@
         <v>1.92677080347792</v>
       </c>
       <c r="T3" t="n">
-        <v>1.844813249807112</v>
+        <v>1.844813249807113</v>
       </c>
       <c r="U3" t="n">
         <v>2.602547348560221</v>
       </c>
       <c r="V3" t="n">
-        <v>1.888507661231164</v>
+        <v>1.888507661231165</v>
       </c>
       <c r="W3" t="n">
         <v>2.587993849863943</v>
@@ -4183,16 +4183,16 @@
         <v>1.989305694518647</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.041797919894343</v>
+        <v>2.041797919894341</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.114406647342397</v>
+        <v>2.114406647342396</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.922664381985143</v>
+        <v>1.922664381985142</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.016237545811305</v>
+        <v>2.016237545811304</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3822361310097263</v>
+        <v>0.3822361310097261</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2919286471670149</v>
+        <v>0.2919286471670131</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4054982005745318</v>
+        <v>0.4054982005745295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2573074113966876</v>
+        <v>0.2573074113966859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3190023758312358</v>
+        <v>0.319002375831235</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5605756460189579</v>
+        <v>0.5605756460189539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3830294699179339</v>
+        <v>0.3830294699179332</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3418328888050213</v>
+        <v>0.3418328888050202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4807985700734707</v>
+        <v>0.4807985700734682</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4523788720534019</v>
+        <v>0.4523788720534004</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5126776139522464</v>
+        <v>0.5126776139522453</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5818729509640393</v>
+        <v>0.5818729509640369</v>
       </c>
       <c r="N4" t="n">
-        <v>4.039891822728022</v>
+        <v>0.3809746747203999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3470793044547505</v>
+        <v>0.3470793044547502</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4963130145240098</v>
+        <v>0.4963130145240075</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3178905233996907</v>
+        <v>0.3178905233996899</v>
       </c>
       <c r="R4" t="n">
-        <v>0.347231943313049</v>
+        <v>0.3472319433130491</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4980081652471087</v>
+        <v>0.4980081652471061</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3663754143608963</v>
+        <v>0.366375414360894</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5340631317482722</v>
+        <v>0.5340631317482685</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4358670156862766</v>
+        <v>0.4358670156862763</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5666141727054108</v>
+        <v>0.5666141727054111</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5956813207754654</v>
+        <v>0.5956813207754645</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6755134803113287</v>
+        <v>0.6755134803113277</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.384751515190798</v>
+        <v>0.3847515151907968</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4900053406993378</v>
+        <v>0.4900053406993372</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6355603224375077</v>
+        <v>0.635560322437508</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.608769363067611</v>
+        <v>3.608769363067619</v>
       </c>
       <c r="C5" t="n">
-        <v>2.319422084498735</v>
+        <v>2.319422084498729</v>
       </c>
       <c r="D5" t="n">
-        <v>4.387508193130389</v>
+        <v>4.387508193130362</v>
       </c>
       <c r="E5" t="n">
         <v>1.663161542546884</v>
       </c>
       <c r="F5" t="n">
-        <v>2.932609777314063</v>
+        <v>2.932609777314047</v>
       </c>
       <c r="G5" t="n">
-        <v>6.41091149868021</v>
+        <v>6.410911498680199</v>
       </c>
       <c r="H5" t="n">
-        <v>4.380319190464679</v>
+        <v>4.38031919046468</v>
       </c>
       <c r="I5" t="n">
-        <v>3.383223929695669</v>
+        <v>3.383223929695665</v>
       </c>
       <c r="J5" t="n">
-        <v>5.417409787730313</v>
+        <v>5.417409787730303</v>
       </c>
       <c r="K5" t="n">
-        <v>4.882491642758096</v>
+        <v>4.882491642758101</v>
       </c>
       <c r="L5" t="n">
-        <v>5.980113986696716</v>
+        <v>5.980113986696723</v>
       </c>
       <c r="M5" t="n">
-        <v>7.646563076445405</v>
+        <v>7.646563076445401</v>
       </c>
       <c r="N5" t="n">
-        <v>4.039891822728022</v>
+        <v>4.039891822728019</v>
       </c>
       <c r="O5" t="n">
-        <v>2.994383337229399</v>
+        <v>2.994383337229386</v>
       </c>
       <c r="P5" t="n">
-        <v>5.379799163065059</v>
+        <v>5.379799163065035</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.771126274220375</v>
+        <v>2.771126274220368</v>
       </c>
       <c r="R5" t="n">
-        <v>3.598849764744508</v>
+        <v>3.598849764744505</v>
       </c>
       <c r="S5" t="n">
-        <v>5.576524426529561</v>
+        <v>5.576524426529556</v>
       </c>
       <c r="T5" t="n">
         <v>3.87789884361403</v>
       </c>
       <c r="U5" t="n">
-        <v>6.231850002486545</v>
+        <v>6.231850002486553</v>
       </c>
       <c r="V5" t="n">
-        <v>4.376094486795806</v>
+        <v>4.376094486795801</v>
       </c>
       <c r="W5" t="n">
-        <v>7.263188614450455</v>
+        <v>7.263188614450452</v>
       </c>
       <c r="X5" t="n">
-        <v>7.728975203239306</v>
+        <v>7.728975203239287</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.342850115272299</v>
+        <v>9.34285011527229</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.409333369537087</v>
+        <v>3.409333369537085</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.927384219207523</v>
+        <v>5.927384219207519</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.203003178177097</v>
+        <v>9.203003178177074</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4054733786155179</v>
+        <v>0.4054733786155116</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3151658947728097</v>
+        <v>0.3151658947727995</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4984300939279508</v>
+        <v>0.4984300939279501</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3502393047501064</v>
+        <v>0.3502393047501041</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3422396234370312</v>
+        <v>0.3422396234370207</v>
       </c>
       <c r="G6" t="n">
-        <v>0.583812893624753</v>
+        <v>0.5838128936247414</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4759613632713529</v>
+        <v>0.4759613632713515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.365070136410815</v>
+        <v>0.3650701364108047</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5737304634268886</v>
+        <v>0.5737304634268875</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5453107654068203</v>
+        <v>0.5453107654068179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.535914861558042</v>
+        <v>0.5359148615580328</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6051101985698359</v>
+        <v>0.6051101985698238</v>
       </c>
       <c r="N6" t="n">
-        <v>4.039891822728022</v>
+        <v>0.4052495837738455</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3714659334793805</v>
+        <v>0.3714659334793871</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5935755785281523</v>
+        <v>0.5935755785281509</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4108224167531085</v>
+        <v>0.410822416753106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4401638366664674</v>
+        <v>0.4401638366664642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5212454128528987</v>
+        <v>0.5212454128528926</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4593073077143141</v>
+        <v>0.4593073077143126</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6297731716569744</v>
+        <v>0.6297731716569707</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4591042632920694</v>
+        <v>0.4591042632920623</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5943072841060361</v>
+        <v>0.5943072841060356</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6189185683812566</v>
+        <v>0.6189185683812496</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7048877395899523</v>
+        <v>0.704887739589944</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4079887627965929</v>
+        <v>0.4079887627965822</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5829372340527569</v>
+        <v>0.5829372340527567</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6609976123371006</v>
+        <v>0.6609976123371007</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4673366408910056</v>
+        <v>0.4673366408910038</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3770291570482934</v>
+        <v>0.3770291570482913</v>
       </c>
       <c r="D7" t="n">
-        <v>0.490598710455811</v>
+        <v>0.4905987104558077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3424079212779663</v>
+        <v>0.3424079212779643</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4041028857125154</v>
+        <v>0.4041028857125117</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6456761559002373</v>
+        <v>0.6456761559002326</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4681299797992134</v>
+        <v>0.4681299797992117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4269333986862999</v>
+        <v>0.4269333986862981</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5658990799547493</v>
+        <v>0.5658990799547461</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5374793819346805</v>
+        <v>0.5374793819346786</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5977781238335272</v>
+        <v>0.5977781238335256</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6669734608453165</v>
+        <v>0.6669734608453138</v>
       </c>
       <c r="N7" t="n">
-        <v>4.039891822728022</v>
+        <v>0.4660751846016757</v>
       </c>
       <c r="O7" t="n">
-        <v>0.431846057415106</v>
+        <v>0.4318460574151035</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5810797674843656</v>
+        <v>0.5810797674843637</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4029910332809694</v>
+        <v>0.4029910332809684</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4323324531943277</v>
+        <v>0.4323324531943274</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5831086751283878</v>
+        <v>0.583108675128385</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4514759242421761</v>
+        <v>0.4514759242421738</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6212341019945702</v>
+        <v>0.621234101994569</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5209675255675554</v>
+        <v>0.5209675255675544</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6517146825866892</v>
+        <v>0.6517146825866871</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6807818306567442</v>
+        <v>0.6807818306567429</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7633921367478924</v>
+        <v>0.7633921367478878</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4698520250720756</v>
+        <v>0.4698520250720746</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5751058505806167</v>
+        <v>0.5751058505806155</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7206608323187855</v>
+        <v>0.7206608323187846</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5031824745558057</v>
+        <v>0.5031824745558054</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5087770116530161</v>
+        <v>0.5087770116530119</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6223465650605342</v>
+        <v>0.6223465650605324</v>
       </c>
       <c r="E8" t="n">
-        <v>0.423090778674076</v>
+        <v>0.4230907786740735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.454889133403345</v>
+        <v>0.4548891334033431</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7973099192868168</v>
+        <v>0.7973099192868132</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5998778344039355</v>
+        <v>0.5998778344039322</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5586812532910216</v>
+        <v>0.558681253291019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6976469345594718</v>
+        <v>0.69764693455947</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6692272365394031</v>
+        <v>0.6692272365393986</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7295259784382493</v>
+        <v>0.7295259784382455</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7987213154502457</v>
+        <v>0.7987213154502416</v>
       </c>
       <c r="N8" t="n">
-        <v>4.039891822728022</v>
+        <v>0.5234829289067806</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5100168664113656</v>
+        <v>0.5100168664113611</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6542428595073037</v>
+        <v>0.6542428595073024</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4199899309865481</v>
+        <v>0.4199899309865442</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5640803077990503</v>
+        <v>0.5640803077990481</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7148565297331106</v>
+        <v>0.7148565297331074</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5832237788468972</v>
+        <v>0.5832237788468945</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7065913603257179</v>
+        <v>0.7065913603257187</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6261842863117272</v>
+        <v>0.6261842863117271</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7834813846388096</v>
+        <v>0.7834813846388075</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7065703391126082</v>
+        <v>0.7065703391126047</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9899974483483754</v>
+        <v>0.9899974483483718</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5039164294654738</v>
+        <v>0.5039164294654718</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7068537051853382</v>
+        <v>0.7068537051853367</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9525863669484902</v>
+        <v>0.9525863669484875</v>
       </c>
     </row>
     <row r="9">
@@ -4642,82 +4642,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6616501779456415</v>
+        <v>0.6616501779456397</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6569094306044901</v>
+        <v>0.6569094306044877</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7704789840120085</v>
+        <v>0.7704789840120045</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6025397465519595</v>
+        <v>0.6025397465519579</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4867284689520754</v>
+        <v>0.4867284689520734</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9255564365832735</v>
+        <v>0.9255564365832702</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7480102533554082</v>
+        <v>0.7480102533554076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7068136722424975</v>
+        <v>0.7068136722424959</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8457793535109446</v>
+        <v>0.8457793535109432</v>
       </c>
       <c r="K9" t="n">
-        <v>0.817359655490876</v>
+        <v>0.8173596554908739</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8776583973897235</v>
+        <v>0.8776583973897222</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9468537344015149</v>
+        <v>0.9468537344015118</v>
       </c>
       <c r="N9" t="n">
-        <v>4.039891822728022</v>
+        <v>0.745955458157872</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7404168018174364</v>
+        <v>0.7404168018174346</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8958176090961852</v>
+        <v>0.8958176090961827</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6828713139640068</v>
+        <v>0.6828713139640038</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7122127267505243</v>
+        <v>0.7122127267505218</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8629889486845831</v>
+        <v>0.8629889486845819</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7313561977983721</v>
+        <v>0.7313561977983686</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9018220617410317</v>
+        <v>0.9018220617410294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8995898840512738</v>
+        <v>0.8995898840512728</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9315949561428863</v>
+        <v>0.9315949561428842</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9606621042129396</v>
+        <v>0.9606621042129364</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.043272410304089</v>
+        <v>1.043272410304087</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6981431682389106</v>
+        <v>0.6981431682389081</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8549861241368137</v>
+        <v>0.8549861241368106</v>
       </c>
       <c r="AB9" t="n">
         <v>1.000541105874983</v>
@@ -5098,7 +5098,7 @@
         <v>0.2890131964298719</v>
       </c>
       <c r="N4" t="n">
-        <v>1.394439314414711</v>
+        <v>0.1971595454760469</v>
       </c>
       <c r="O4" t="n">
         <v>0.1564089582570534</v>
@@ -5274,7 +5274,7 @@
         <v>0.3493810521156848</v>
       </c>
       <c r="N6" t="n">
-        <v>1.394439314414711</v>
+        <v>0.2080399988856333</v>
       </c>
       <c r="O6" t="n">
         <v>0.222196069913697</v>
@@ -5362,7 +5362,7 @@
         <v>0.3622122281300292</v>
       </c>
       <c r="N7" t="n">
-        <v>1.394439314414711</v>
+        <v>0.2703585771762045</v>
       </c>
       <c r="O7" t="n">
         <v>0.2292506908776126</v>
@@ -5450,7 +5450,7 @@
         <v>0.4640737631866266</v>
       </c>
       <c r="N8" t="n">
-        <v>1.394439314414711</v>
+        <v>0.3116057694468049</v>
       </c>
       <c r="O8" t="n">
         <v>0.2875125299152644</v>
@@ -5538,7 +5538,7 @@
         <v>0.5972746864908024</v>
       </c>
       <c r="N9" t="n">
-        <v>1.394439314414711</v>
+        <v>0.505421035536977</v>
       </c>
       <c r="O9" t="n">
         <v>0.4886831322252914</v>
@@ -5958,7 +5958,7 @@
         <v>0.1076606619891536</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32621661361057</v>
+        <v>0.185053642185349</v>
       </c>
       <c r="O4" t="n">
         <v>0.1114135240971107</v>
@@ -5973,7 +5973,7 @@
         <v>-0.2478281178656667</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06862806236264257</v>
+        <v>0.0686280623626426</v>
       </c>
       <c r="T4" t="n">
         <v>0.05741600782690223</v>
@@ -6034,7 +6034,7 @@
         <v>-0.2810115351491499</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5858781772531332</v>
+        <v>0.5858781772531331</v>
       </c>
       <c r="K5" t="n">
         <v>-0.2224851839095737</v>
@@ -6134,13 +6134,13 @@
         <v>0.1490965051790786</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32621661361057</v>
+        <v>0.1887344129924487</v>
       </c>
       <c r="O6" t="n">
         <v>0.1574787425601469</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01648054009954388</v>
+        <v>0.01648054009954387</v>
       </c>
       <c r="Q6" t="n">
         <v>0.1658850494168761</v>
@@ -6195,7 +6195,7 @@
         <v>0.2070431837987362</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005763688129253555</v>
+        <v>-0.005763688129253583</v>
       </c>
       <c r="F7" t="n">
         <v>0.02624033986350938</v>
@@ -6222,13 +6222,13 @@
         <v>0.1679660253407288</v>
       </c>
       <c r="N7" t="n">
-        <v>1.32621661361057</v>
+        <v>0.2453590055369255</v>
       </c>
       <c r="O7" t="n">
         <v>0.1713860531006023</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07397813672708523</v>
+        <v>0.07397813672708525</v>
       </c>
       <c r="Q7" t="n">
         <v>0.184754569578527</v>
@@ -6252,7 +6252,7 @@
         <v>0.3644276485870974</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5803101879645786</v>
+        <v>0.5803101879645784</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3039679651327613</v>
@@ -6277,7 +6277,7 @@
         <v>0.08885017651771535</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2477290011365305</v>
+        <v>0.2477290011365304</v>
       </c>
       <c r="D8" t="n">
         <v>0.2787927001886949</v>
@@ -6301,7 +6301,7 @@
         <v>0.2769355120041206</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2244833476200979</v>
+        <v>0.224483347620098</v>
       </c>
       <c r="L8" t="n">
         <v>0.05850597218895595</v>
@@ -6310,7 +6310,7 @@
         <v>0.2397155417306118</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32621661361057</v>
+        <v>0.2714822941019514</v>
       </c>
       <c r="O8" t="n">
         <v>0.2103806595948909</v>
@@ -6337,7 +6337,7 @@
         <v>0.2648516794015446</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4361887326398662</v>
+        <v>0.436188732639866</v>
       </c>
       <c r="X8" t="n">
         <v>0.5870271768516451</v>
@@ -6398,7 +6398,7 @@
         <v>0.3454045601380439</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32621661361057</v>
+        <v>0.4227975403342401</v>
       </c>
       <c r="O9" t="n">
         <v>0.3676219633509273</v>
@@ -6419,7 +6419,7 @@
         <v>0.2951599059757941</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3745144358683725</v>
+        <v>0.3745144358683726</v>
       </c>
       <c r="V9" t="n">
         <v>0.451766285487654</v>
@@ -6818,7 +6818,7 @@
         <v>0.1204949082387049</v>
       </c>
       <c r="N4" t="n">
-        <v>1.602238015853775</v>
+        <v>0.1947128766815314</v>
       </c>
       <c r="O4" t="n">
         <v>0.03446610838965625</v>
@@ -6994,7 +6994,7 @@
         <v>0.1566215738501959</v>
       </c>
       <c r="N6" t="n">
-        <v>1.602238015853775</v>
+        <v>0.1973358844106084</v>
       </c>
       <c r="O6" t="n">
         <v>0.03720176839882328</v>
@@ -7082,7 +7082,7 @@
         <v>0.1779742957745649</v>
       </c>
       <c r="N7" t="n">
-        <v>1.602238015853775</v>
+        <v>0.2521922642173912</v>
       </c>
       <c r="O7" t="n">
         <v>0.09161282731248929</v>
@@ -7170,7 +7170,7 @@
         <v>0.2415243761392361</v>
       </c>
       <c r="N8" t="n">
-        <v>1.602238015853775</v>
+        <v>0.274083346110228</v>
       </c>
       <c r="O8" t="n">
         <v>0.1252848323394647</v>
@@ -7258,7 +7258,7 @@
         <v>0.333652745639506</v>
       </c>
       <c r="N9" t="n">
-        <v>1.602238015853775</v>
+        <v>0.4078707140823314</v>
       </c>
       <c r="O9" t="n">
         <v>0.2641691454151326</v>
@@ -7678,7 +7678,7 @@
         <v>0.6621254339452989</v>
       </c>
       <c r="N4" t="n">
-        <v>4.313732832557108</v>
+        <v>0.3755633473388927</v>
       </c>
       <c r="O4" t="n">
         <v>0.3242590313866743</v>
@@ -7854,7 +7854,7 @@
         <v>0.6789006926524475</v>
       </c>
       <c r="N6" t="n">
-        <v>4.313732832557108</v>
+        <v>0.3930082991317371</v>
       </c>
       <c r="O6" t="n">
         <v>0.4229007816564371</v>
@@ -7942,7 +7942,7 @@
         <v>0.7520416398080005</v>
       </c>
       <c r="N7" t="n">
-        <v>4.313732832557108</v>
+        <v>0.4654795532015952</v>
       </c>
       <c r="O7" t="n">
         <v>0.4138169127907209</v>
@@ -8030,7 +8030,7 @@
         <v>0.8934057880780355</v>
       </c>
       <c r="N8" t="n">
-        <v>4.313732832557108</v>
+        <v>0.5271079251297973</v>
       </c>
       <c r="O8" t="n">
         <v>0.4977156928161767</v>
@@ -8118,7 +8118,7 @@
         <v>1.097329856233015</v>
       </c>
       <c r="N9" t="n">
-        <v>4.313732832557108</v>
+        <v>0.810767769626606</v>
       </c>
       <c r="O9" t="n">
         <v>0.7931119394405312</v>
@@ -8538,7 +8538,7 @@
         <v>0.1387969645030976</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.1541678241014948</v>
       </c>
       <c r="O4" t="n">
         <v>0.08617315484197059</v>
@@ -8714,7 +8714,7 @@
         <v>0.14666807070103</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.1625263948595985</v>
       </c>
       <c r="O6" t="n">
         <v>0.1574312316900879</v>
@@ -8802,7 +8802,7 @@
         <v>0.2091704774289796</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.224541337027377</v>
       </c>
       <c r="O7" t="n">
         <v>0.1562132285514868</v>
@@ -8890,7 +8890,7 @@
         <v>0.3080952532970596</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.2647761378375358</v>
       </c>
       <c r="O8" t="n">
         <v>0.2129099833083737</v>
@@ -8978,7 +8978,7 @@
         <v>0.4591997666536571</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.4745706262520538</v>
       </c>
       <c r="O9" t="n">
         <v>0.431415341151228</v>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -589,10 +589,10 @@
         <v>2.697725228200455</v>
       </c>
       <c r="C2" t="n">
-        <v>2.702639480244241</v>
+        <v>2.702639480244242</v>
       </c>
       <c r="D2" t="n">
-        <v>2.687978871921092</v>
+        <v>2.687978871921093</v>
       </c>
       <c r="E2" t="n">
         <v>2.675176840259549</v>
@@ -601,16 +601,16 @@
         <v>2.682975220234052</v>
       </c>
       <c r="G2" t="n">
-        <v>2.708597689297739</v>
+        <v>2.70859768929774</v>
       </c>
       <c r="H2" t="n">
-        <v>2.695839288957797</v>
+        <v>2.695839288957798</v>
       </c>
       <c r="I2" t="n">
         <v>2.683997951876753</v>
       </c>
       <c r="J2" t="n">
-        <v>2.697755753143283</v>
+        <v>2.697755753143285</v>
       </c>
       <c r="K2" t="n">
         <v>2.695246811788161</v>
@@ -622,7 +622,7 @@
         <v>2.716403956687403</v>
       </c>
       <c r="N2" t="n">
-        <v>2.698037918703968</v>
+        <v>2.698037918703969</v>
       </c>
       <c r="O2" t="n">
         <v>2.984229030873059</v>
@@ -631,40 +631,40 @@
         <v>2.692554456655992</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.688454158220473</v>
+        <v>2.688454158220474</v>
       </c>
       <c r="R2" t="n">
-        <v>2.684468101162446</v>
+        <v>2.684468101162448</v>
       </c>
       <c r="S2" t="n">
-        <v>2.701393751943495</v>
+        <v>2.701393751943497</v>
       </c>
       <c r="T2" t="n">
-        <v>2.692101922761875</v>
+        <v>2.692101922761876</v>
       </c>
       <c r="U2" t="n">
-        <v>3.113550618573962</v>
+        <v>3.113550618573963</v>
       </c>
       <c r="V2" t="n">
-        <v>2.680943831842452</v>
+        <v>2.680943831842453</v>
       </c>
       <c r="W2" t="n">
-        <v>3.087568757853364</v>
+        <v>3.087568757853365</v>
       </c>
       <c r="X2" t="n">
         <v>2.692266878223649</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.689664707120905</v>
+        <v>2.689664707120906</v>
       </c>
       <c r="Z2" t="n">
         <v>2.856443716554025</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.699495518543625</v>
+        <v>2.699495518543626</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.715143280633163</v>
+        <v>2.715143280633164</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.967620034927502</v>
+        <v>0.8309193013065054</v>
       </c>
       <c r="C3" t="n">
-        <v>1.844926382224464</v>
+        <v>0.7022403560398139</v>
       </c>
       <c r="D3" t="n">
-        <v>1.899503326408757</v>
+        <v>0.7604579757498122</v>
       </c>
       <c r="E3" t="n">
-        <v>1.807617162333339</v>
+        <v>0.6652906704874705</v>
       </c>
       <c r="F3" t="n">
-        <v>1.863870131064064</v>
+        <v>0.7235772916611553</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04536490241931</v>
+        <v>0.9113887237749245</v>
       </c>
       <c r="H3" t="n">
-        <v>1.956332484509553</v>
+        <v>0.8193374045886934</v>
       </c>
       <c r="I3" t="n">
-        <v>1.871101795707869</v>
+        <v>0.7310548691895357</v>
       </c>
       <c r="J3" t="n">
-        <v>1.968528699246639</v>
+        <v>0.8318795385908728</v>
       </c>
       <c r="K3" t="n">
-        <v>1.951426126246798</v>
+        <v>0.8142152969143559</v>
       </c>
       <c r="L3" t="n">
-        <v>2.059489417485527</v>
+        <v>0.9260494161752143</v>
       </c>
       <c r="M3" t="n">
-        <v>2.10430613853266</v>
+        <v>0.9725727512458409</v>
       </c>
       <c r="N3" t="n">
-        <v>1.971099217576704</v>
+        <v>0.8345722614775795</v>
       </c>
       <c r="O3" t="n">
-        <v>2.418695397229901</v>
+        <v>1.280996824070623</v>
       </c>
       <c r="P3" t="n">
-        <v>1.931029811373022</v>
+        <v>0.7930223476259922</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.902691209217461</v>
+        <v>0.7637509725740602</v>
       </c>
       <c r="R3" t="n">
-        <v>1.874582402609689</v>
+        <v>0.734665691515563</v>
       </c>
       <c r="S3" t="n">
-        <v>1.994122991075683</v>
+        <v>0.8583681328175875</v>
       </c>
       <c r="T3" t="n">
-        <v>1.929065258455182</v>
+        <v>0.7910713791231123</v>
       </c>
       <c r="U3" t="n">
-        <v>2.710856412520415</v>
+        <v>1.576778336812898</v>
       </c>
       <c r="V3" t="n">
-        <v>1.848388560281658</v>
+        <v>0.7074988430382317</v>
       </c>
       <c r="W3" t="n">
-        <v>2.630616642330299</v>
+        <v>1.494831767464212</v>
       </c>
       <c r="X3" t="n">
-        <v>1.930044572168908</v>
+        <v>0.7920813089227953</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.911081179989437</v>
+        <v>0.7724259139479535</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.188178851819827</v>
+        <v>1.049575164251004</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.981349966031068</v>
+        <v>0.8451692204587434</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.093317437807349</v>
+        <v>0.961108124906368</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5610842872544276</v>
+        <v>0.5610842872544253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2891746208302046</v>
+        <v>0.2891746208302026</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4509947095336142</v>
+        <v>0.4509947095336121</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3063898726909896</v>
+        <v>0.306389872690987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3944761619350109</v>
+        <v>0.3944761619350108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.683893736927475</v>
+        <v>0.683893736927476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5397817359336881</v>
+        <v>0.5397817359336861</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4060283863191232</v>
+        <v>0.4060283863191211</v>
       </c>
       <c r="J4" t="n">
-        <v>0.561027735556524</v>
+        <v>0.5610277355565231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5330894337496758</v>
+        <v>0.533089433749675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7051075919253491</v>
+        <v>0.7051075919253494</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7739936206792769</v>
+        <v>0.7739936206792741</v>
       </c>
       <c r="N4" t="n">
-        <v>0.564616270336346</v>
+        <v>0.5646162703363456</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5163657387351357</v>
+        <v>0.5163657387351352</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5026780439872969</v>
+        <v>0.5026780439872965</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4563632869276353</v>
+        <v>0.4563632869276355</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4113389387803787</v>
+        <v>0.4113389387803766</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6025219505363851</v>
+        <v>0.6025219505363868</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4975664654773624</v>
+        <v>0.4975664654773607</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6740036125027696</v>
+        <v>0.6740036125027689</v>
       </c>
       <c r="V4" t="n">
         <v>0.3688428982336557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5991453816453975</v>
+        <v>0.5991453816453972</v>
       </c>
       <c r="X4" t="n">
-        <v>0.499429713301363</v>
+        <v>0.4994297133013617</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4670874097179747</v>
+        <v>0.4670874097179744</v>
       </c>
       <c r="Z4" t="n">
         <v>0.4747928093599099</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5810805310543155</v>
+        <v>0.5810805310543149</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7549387817299072</v>
+        <v>0.7549387817299071</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.201509147590627</v>
+        <v>7.201509147590575</v>
       </c>
       <c r="C5" t="n">
-        <v>2.369017369667043</v>
+        <v>2.369017369667041</v>
       </c>
       <c r="D5" t="n">
-        <v>5.842498803471555</v>
+        <v>5.842498803471533</v>
       </c>
       <c r="E5" t="n">
-        <v>2.622936493270815</v>
+        <v>2.622936493270814</v>
       </c>
       <c r="F5" t="n">
-        <v>4.750765156733681</v>
+        <v>4.750765156733686</v>
       </c>
       <c r="G5" t="n">
-        <v>9.762335866454455</v>
+        <v>9.762335866454476</v>
       </c>
       <c r="H5" t="n">
         <v>8.063741559069625</v>
       </c>
       <c r="I5" t="n">
-        <v>4.943210946745638</v>
+        <v>4.94321094674564</v>
       </c>
       <c r="J5" t="n">
-        <v>7.618631709688998</v>
+        <v>7.618631709689</v>
       </c>
       <c r="K5" t="n">
-        <v>7.526111362832647</v>
+        <v>7.52611136283264</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6177754845596</v>
+        <v>10.61777548455959</v>
       </c>
       <c r="M5" t="n">
-        <v>12.87356285801898</v>
+        <v>12.87356285801897</v>
       </c>
       <c r="N5" t="n">
-        <v>8.01408394358586</v>
+        <v>8.014083943585852</v>
       </c>
       <c r="O5" t="n">
-        <v>6.223010248131131</v>
+        <v>6.22301024813111</v>
       </c>
       <c r="P5" t="n">
-        <v>6.21185824115284</v>
+        <v>6.211858241152847</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.829209006093925</v>
+        <v>5.829209006093929</v>
       </c>
       <c r="R5" t="n">
         <v>5.124523848171404</v>
       </c>
       <c r="S5" t="n">
-        <v>8.226475115219207</v>
+        <v>8.226475115219223</v>
       </c>
       <c r="T5" t="n">
-        <v>6.860895701021572</v>
+        <v>6.860895701021563</v>
       </c>
       <c r="U5" t="n">
-        <v>9.858296563125711</v>
+        <v>9.858296563125705</v>
       </c>
       <c r="V5" t="n">
-        <v>3.701491464772033</v>
+        <v>3.701491464772035</v>
       </c>
       <c r="W5" t="n">
-        <v>8.563322456505045</v>
+        <v>8.563322456505036</v>
       </c>
       <c r="X5" t="n">
-        <v>6.78074717401152</v>
+        <v>6.780747174011509</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.956113113626497</v>
+        <v>5.956113113626489</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.747825618427287</v>
+        <v>5.747825618427284</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.255170236172955</v>
+        <v>8.255170236172971</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.8612195711343</v>
+        <v>12.86121957113432</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5864340599113597</v>
+        <v>0.5864340599113609</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4088406309789194</v>
+        <v>0.4088406309789202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5706607196823278</v>
+        <v>0.5706607196823291</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4260558828397044</v>
+        <v>0.4260558828397049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4198259345919432</v>
+        <v>0.4198259345919433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8035597470761898</v>
+        <v>0.8035597470761895</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6594477460824023</v>
+        <v>0.6594477460824038</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4313781589760562</v>
+        <v>0.4313781589760554</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5863775082134576</v>
+        <v>0.5863775082134566</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6527554438983895</v>
+        <v>0.6527554438983889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8247736020740658</v>
+        <v>0.8247736020740707</v>
       </c>
       <c r="M6" t="n">
-        <v>0.893659630827992</v>
+        <v>0.8936596308279924</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5910888615998764</v>
+        <v>0.5910888615998675</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5428381257310242</v>
+        <v>0.5428381257310172</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6274030016379069</v>
+        <v>0.6274030016379053</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5760292970763492</v>
+        <v>0.5760292970763508</v>
       </c>
       <c r="R6" t="n">
-        <v>0.531004948929093</v>
+        <v>0.5310049489290944</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6278717231933193</v>
+        <v>0.6278717231933197</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5229162381342957</v>
+        <v>0.522916238134295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7023029690797462</v>
+        <v>0.7023029690797457</v>
       </c>
       <c r="V6" t="n">
-        <v>0.48850890838237</v>
+        <v>0.4885089083823707</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7238700327420485</v>
+        <v>0.7238700327420475</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6190957234500768</v>
+        <v>0.6190957234500742</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4987283558070083</v>
+        <v>0.4987283558070133</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5001425820168433</v>
+        <v>0.5001425820168435</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7007465412030298</v>
+        <v>0.7007465412030268</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7831516781996374</v>
+        <v>0.7831516781996369</v>
       </c>
     </row>
     <row r="7">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6715773757207947</v>
+        <v>0.671577375720793</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3996677092965722</v>
+        <v>0.3996677092965704</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5614877979999815</v>
+        <v>0.5614877979999784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4168829611573563</v>
+        <v>0.4168829611573541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5049692504013784</v>
+        <v>0.5049692504013756</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7943868253938429</v>
+        <v>0.7943868253938436</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502748244000558</v>
+        <v>0.6502748244000538</v>
       </c>
       <c r="I7" t="n">
-        <v>0.51652147478549</v>
+        <v>0.5165214747854882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6715208240228917</v>
+        <v>0.6715208240228908</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6435825222160411</v>
+        <v>0.6435825222160406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8156006803917201</v>
+        <v>0.8156006803917188</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8844867091456438</v>
+        <v>0.8844867091456403</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6751093588027136</v>
+        <v>0.6751093588027126</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6264753753805611</v>
+        <v>0.6264753753805606</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6127876806327243</v>
+        <v>0.612787680632724</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5668563753940028</v>
+        <v>0.5668563753940019</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5218320272467465</v>
+        <v>0.5218320272467442</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7130150390027546</v>
+        <v>0.713015039002755</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6080595539437308</v>
+        <v>0.6080595539437287</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7872696361533517</v>
+        <v>0.787269636153352</v>
       </c>
       <c r="V7" t="n">
         <v>0.4793359867000229</v>
       </c>
       <c r="W7" t="n">
-        <v>0.709638470111766</v>
+        <v>0.7096384701117643</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6099228017677304</v>
+        <v>0.6099228017677283</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5805300821043875</v>
+        <v>0.5805300821043863</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5852858978262775</v>
+        <v>0.5852858978262773</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6915736195206839</v>
+        <v>0.6915736195206827</v>
       </c>
       <c r="AB7" t="n">
         <v>0.8654318701962763</v>
@@ -1117,79 +1117,79 @@
         <v>0.7240679744388097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5819025323860085</v>
+        <v>0.5819025323860089</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7437226210894178</v>
+        <v>0.7437226210894176</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5300328120039962</v>
+        <v>0.5300328120039967</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5776724829119256</v>
+        <v>0.5776724829119253</v>
       </c>
       <c r="G8" t="n">
-        <v>1.003524958604737</v>
+        <v>1.003524958604738</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8325096474894929</v>
+        <v>0.8325096474894927</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6987562978749279</v>
+        <v>0.6987562978749283</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8537556471123281</v>
+        <v>0.8537556471123287</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8258173453054793</v>
+        <v>0.8258173453054788</v>
       </c>
       <c r="L8" t="n">
         <v>0.9978355034811557</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06672153223512</v>
+        <v>1.066721532235119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.756770702242989</v>
+        <v>0.7567707022429878</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7361586360633455</v>
+        <v>0.7361586360633461</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7156960856071507</v>
+        <v>0.7156960856071494</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5938492727818167</v>
+        <v>0.5938492727818157</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7040668503361827</v>
+        <v>0.7040668503361822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8952498620921898</v>
+        <v>0.8952498620921878</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7902943770331657</v>
+        <v>0.7902943770331669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9065149509951014</v>
+        <v>0.9065149509951025</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6262865270619264</v>
+        <v>0.6262865270619273</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8918987915602953</v>
+        <v>0.8918987915602944</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6488070150644972</v>
+        <v>0.6488070150644969</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8920408050357774</v>
+        <v>0.8920408050357773</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6353664309739633</v>
+        <v>0.6353664309739642</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.87380844261012</v>
+        <v>0.8738084426101194</v>
       </c>
       <c r="AB8" t="n">
         <v>1.183195384585969</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.010950742521336</v>
+        <v>1.010950742521338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8748515780449311</v>
+        <v>0.8748515780449317</v>
       </c>
       <c r="D9" t="n">
-        <v>1.03667166674834</v>
+        <v>1.036671666748339</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8607223347653183</v>
+        <v>0.8607223347653166</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6670728209309114</v>
+        <v>0.6670728209309102</v>
       </c>
       <c r="G9" t="n">
-        <v>1.269570713315539</v>
+        <v>1.269570713315541</v>
       </c>
       <c r="H9" t="n">
         <v>1.125458693148414</v>
@@ -1229,19 +1229,19 @@
         <v>1.146704692771251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.118766390964401</v>
+        <v>1.118766390964402</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29078454914008</v>
+        <v>1.290784549140077</v>
       </c>
       <c r="M9" t="n">
-        <v>1.359670577894003</v>
+        <v>1.359670577894001</v>
       </c>
       <c r="N9" t="n">
-        <v>1.150293227551069</v>
+        <v>1.15029322755107</v>
       </c>
       <c r="O9" t="n">
-        <v>1.147050143994055</v>
+        <v>1.147050143994056</v>
       </c>
       <c r="P9" t="n">
         <v>1.143150792828193</v>
@@ -1250,31 +1250,31 @@
         <v>1.042040263315698</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9970158959951051</v>
+        <v>0.9970158959951056</v>
       </c>
       <c r="S9" t="n">
-        <v>1.188198907751113</v>
+        <v>1.188198907751112</v>
       </c>
       <c r="T9" t="n">
         <v>1.083243422692089</v>
       </c>
       <c r="U9" t="n">
-        <v>1.262630153637542</v>
+        <v>1.262630153637539</v>
       </c>
       <c r="V9" t="n">
-        <v>1.111242098661583</v>
+        <v>1.111242098661584</v>
       </c>
       <c r="W9" t="n">
-        <v>1.184822338860123</v>
+        <v>1.184822338860125</v>
       </c>
       <c r="X9" t="n">
         <v>1.085106670516088</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.055713950852746</v>
+        <v>1.055713950852748</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9785881182546585</v>
+        <v>0.9785881182546592</v>
       </c>
       <c r="AA9" t="n">
         <v>1.166757488269044</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.591161317580908</v>
+        <v>2.591161317580909</v>
       </c>
       <c r="C2" t="n">
         <v>2.615593628781776</v>
@@ -1455,10 +1455,10 @@
         <v>2.594727952435032</v>
       </c>
       <c r="E2" t="n">
-        <v>2.592523871270374</v>
+        <v>2.592523871270375</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58118310228682</v>
+        <v>2.581183102286821</v>
       </c>
       <c r="G2" t="n">
         <v>2.598723641209711</v>
@@ -1473,10 +1473,10 @@
         <v>2.595516863958469</v>
       </c>
       <c r="K2" t="n">
-        <v>2.592584851912546</v>
+        <v>2.592584851912545</v>
       </c>
       <c r="L2" t="n">
-        <v>2.570182032313517</v>
+        <v>2.570182032313518</v>
       </c>
       <c r="M2" t="n">
         <v>2.591016167949279</v>
@@ -1485,7 +1485,7 @@
         <v>2.592286474770312</v>
       </c>
       <c r="O2" t="n">
-        <v>2.813460402251725</v>
+        <v>2.813460402251724</v>
       </c>
       <c r="P2" t="n">
         <v>2.591223101927591</v>
@@ -1500,25 +1500,25 @@
         <v>2.582913350421483</v>
       </c>
       <c r="T2" t="n">
-        <v>2.586722848151323</v>
+        <v>2.586722848151324</v>
       </c>
       <c r="U2" t="n">
-        <v>2.979999816597866</v>
+        <v>2.979999816597867</v>
       </c>
       <c r="V2" t="n">
-        <v>2.601771717679689</v>
+        <v>2.60177171767969</v>
       </c>
       <c r="W2" t="n">
-        <v>2.981880794231905</v>
+        <v>2.981880794231904</v>
       </c>
       <c r="X2" t="n">
-        <v>2.633860364769502</v>
+        <v>2.633860364769503</v>
       </c>
       <c r="Y2" t="n">
         <v>2.616760860298328</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.745407690195294</v>
+        <v>2.745407690195295</v>
       </c>
       <c r="AA2" t="n">
         <v>2.625615103947895</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.65879372086243</v>
+        <v>0.513027656079681</v>
       </c>
       <c r="C3" t="n">
-        <v>1.69521398675042</v>
+        <v>0.549259055212678</v>
       </c>
       <c r="D3" t="n">
-        <v>1.684169045075399</v>
+        <v>0.539299267312626</v>
       </c>
       <c r="E3" t="n">
-        <v>1.668492358684402</v>
+        <v>0.5230620536838986</v>
       </c>
       <c r="F3" t="n">
-        <v>1.587404411787472</v>
+        <v>0.4390796508924865</v>
       </c>
       <c r="G3" t="n">
-        <v>1.712454509032789</v>
+        <v>0.568579946047705</v>
       </c>
       <c r="H3" t="n">
-        <v>1.706104655481177</v>
+        <v>0.5620184850704807</v>
       </c>
       <c r="I3" t="n">
-        <v>1.670823814086225</v>
+        <v>0.5254793836681254</v>
       </c>
       <c r="J3" t="n">
-        <v>1.68970516356903</v>
+        <v>0.5450259545139013</v>
       </c>
       <c r="K3" t="n">
-        <v>1.66893775161601</v>
+        <v>0.5235241123190978</v>
       </c>
       <c r="L3" t="n">
-        <v>1.509870891607075</v>
+        <v>0.3588225130974262</v>
       </c>
       <c r="M3" t="n">
-        <v>1.659908411532485</v>
+        <v>0.5141860332605894</v>
       </c>
       <c r="N3" t="n">
-        <v>1.666711604439586</v>
+        <v>0.5212232140066387</v>
       </c>
       <c r="O3" t="n">
-        <v>1.992539869541578</v>
+        <v>0.8452485553896619</v>
       </c>
       <c r="P3" t="n">
-        <v>1.659252585560336</v>
+        <v>0.5135031267646833</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.680595812283264</v>
+        <v>0.53559889808323</v>
       </c>
       <c r="R3" t="n">
-        <v>1.434285234424961</v>
+        <v>0.2805217783561939</v>
       </c>
       <c r="S3" t="n">
-        <v>1.600284738059492</v>
+        <v>0.4524482082108457</v>
       </c>
       <c r="T3" t="n">
-        <v>1.626905344436027</v>
+        <v>0.480001657233888</v>
       </c>
       <c r="U3" t="n">
-        <v>2.339857717897884</v>
+        <v>1.195896821619609</v>
       </c>
       <c r="V3" t="n">
-        <v>1.734098272590474</v>
+        <v>0.5909885562136891</v>
       </c>
       <c r="W3" t="n">
-        <v>2.474125884561633</v>
+        <v>1.336187457491925</v>
       </c>
       <c r="X3" t="n">
-        <v>1.963057986679946</v>
+        <v>0.8281156042040233</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.841552368341715</v>
+        <v>0.7022427023188142</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.960820664607206</v>
+        <v>0.8172366688823929</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.904741954534674</v>
+        <v>0.7676609079548502</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.687247534551345</v>
+        <v>0.5424855719692772</v>
       </c>
     </row>
     <row r="4">
@@ -1625,82 +1625,82 @@
         <v>0.09568441449888429</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08766156807486819</v>
+        <v>0.08766156807486881</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1359711959093221</v>
+        <v>0.1359711959093231</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1110750852270499</v>
+        <v>0.1110750852270498</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01702411745365874</v>
+        <v>-0.01702411745365992</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1811043387269766</v>
+        <v>0.1811043387269762</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1705034458945006</v>
+        <v>0.1705034458945023</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1148731641535481</v>
+        <v>0.1148731641535494</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1446438105686483</v>
+        <v>0.1446438105686477</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1117638896328759</v>
+        <v>0.1117638896328764</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1412862635443227</v>
+        <v>-0.1412862635443218</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09814087600801574</v>
+        <v>0.09814087600801544</v>
       </c>
       <c r="N4" t="n">
-        <v>0.108393582551083</v>
+        <v>0.1083935825510842</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02667362989259436</v>
+        <v>0.02667362989259547</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09638229711686205</v>
+        <v>0.09638229711686101</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1303350530614293</v>
+        <v>0.130335053061428</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2581218906596081</v>
+        <v>-0.2581218906596056</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002519831180818853</v>
+        <v>0.00251983118082004</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04554986049489845</v>
+        <v>0.04554986049489829</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1741876946773098</v>
+        <v>0.1741876946773094</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2139436211004776</v>
+        <v>0.2139436211004772</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4467236884271242</v>
+        <v>0.4467236884271233</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5779897950262122</v>
+        <v>0.5779897950262106</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3820814253336881</v>
+        <v>0.3820814253336889</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1941846074640941</v>
+        <v>0.1941846074640937</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4848557810387746</v>
+        <v>0.4848557810387754</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1407630311804538</v>
+        <v>0.1407630311804529</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3097373850807678</v>
+        <v>-0.3097373850807689</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4701036641305643</v>
+        <v>-0.4701036641305649</v>
       </c>
       <c r="D5" t="n">
-        <v>0.361380914756843</v>
+        <v>0.3613809147568453</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05098926981614345</v>
+        <v>-0.05098926981614242</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.393494662688556</v>
+        <v>-2.393494662688555</v>
       </c>
       <c r="G5" t="n">
-        <v>1.039424504857788</v>
+        <v>1.039424504857793</v>
       </c>
       <c r="H5" t="n">
         <v>1.032445080019691</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01924255494901472</v>
+        <v>-0.01924255494901417</v>
       </c>
       <c r="J5" t="n">
-        <v>0.469838969943762</v>
+        <v>0.4698389699437623</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03353573899332363</v>
+        <v>-0.03353573899332429</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.082552921159547</v>
+        <v>-4.08255292115955</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3050563357538487</v>
+        <v>-0.3050563357538477</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1432132706433129</v>
+        <v>-0.1432132706433122</v>
       </c>
       <c r="O5" t="n">
         <v>-1.364298868113133</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2881144671126994</v>
+        <v>-0.2881144671127006</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2554625847034607</v>
+        <v>0.2554625847034616</v>
       </c>
       <c r="R5" t="n">
-        <v>-7.062576164584051</v>
+        <v>-7.062576164584053</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.772412471149399</v>
+        <v>-1.772412471149395</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.305690862716662</v>
+        <v>-1.305690862716664</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9852245974293862</v>
+        <v>0.9852245974293885</v>
       </c>
       <c r="V5" t="n">
-        <v>1.589506478177887</v>
+        <v>1.589506478177886</v>
       </c>
       <c r="W5" t="n">
-        <v>5.833329571398569</v>
+        <v>5.833329571398548</v>
       </c>
       <c r="X5" t="n">
-        <v>7.971382448702352</v>
+        <v>7.971382448702363</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.832201099424162</v>
+        <v>4.832201099424172</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.21065933860975</v>
+        <v>1.210659338609751</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.599230175613488</v>
+        <v>6.599230175613507</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4664906834129982</v>
+        <v>0.466490683412998</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1046568585524205</v>
+        <v>0.1046568585524209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1361225978324827</v>
+        <v>0.1361225978324837</v>
       </c>
       <c r="D6" t="n">
-        <v>0.144943639962861</v>
+        <v>0.1449436399628601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1595361149846649</v>
+        <v>0.1595361149846638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03143691230395497</v>
+        <v>0.03143691230395533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1900767827805146</v>
+        <v>0.190076782780515</v>
       </c>
       <c r="H6" t="n">
-        <v>0.179475889948039</v>
+        <v>0.1794758899480403</v>
       </c>
       <c r="I6" t="n">
-        <v>0.123845608207086</v>
+        <v>0.1238456082070868</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1931048403262624</v>
+        <v>0.1931048403262619</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1207363336864137</v>
+        <v>0.120736333686414</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.09282523378670786</v>
+        <v>-0.09282523378670667</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1071133200615522</v>
+        <v>0.1071133200615526</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1176727523421305</v>
+        <v>0.1176727523421319</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07983576469089036</v>
+        <v>0.0798357646908902</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1039183358113461</v>
+        <v>0.1039183358113454</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.139307497114965</v>
+        <v>0.1393074971149655</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2491494466060693</v>
+        <v>-0.2491494466060689</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05098086093843187</v>
+        <v>0.05098086093843168</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05452230454843604</v>
+        <v>0.05452230454843626</v>
       </c>
       <c r="U6" t="n">
-        <v>0.225410324964852</v>
+        <v>0.2254103249648527</v>
       </c>
       <c r="V6" t="n">
-        <v>0.222916065154015</v>
+        <v>0.2229160651540144</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4592452265264918</v>
+        <v>0.4592452265264774</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6264508247838257</v>
+        <v>0.626450824783826</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3958344431438929</v>
+        <v>0.3958344431438915</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2031570515176305</v>
+        <v>0.2031570515176309</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5333168107963878</v>
+        <v>0.5333168107963902</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1501060680556903</v>
+        <v>0.1501060680556898</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1590455249377193</v>
+        <v>0.1590455249377199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.151022678513704</v>
+        <v>0.1510226785137051</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1993323063481582</v>
+        <v>0.1993323063481586</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1744361956658859</v>
+        <v>0.1744361956658868</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04633699298517709</v>
+        <v>0.04633699298517636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2444654491658124</v>
+        <v>0.2444654491658136</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2338645563333389</v>
+        <v>0.233864556333339</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1782342745923856</v>
+        <v>0.178234274592385</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2080049210074844</v>
+        <v>0.2080049210074843</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1751250000717134</v>
+        <v>0.1751250000717129</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.07792515310548485</v>
+        <v>-0.07792515310548516</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1615019864468522</v>
+        <v>0.1615019864468518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1717546929899203</v>
+        <v>0.1717546929899202</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08970157674739732</v>
+        <v>0.0897015767473987</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1594102439716644</v>
+        <v>0.1594102439716659</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1936961635002646</v>
+        <v>0.1936961635002642</v>
       </c>
       <c r="R7" t="n">
         <v>-0.1947607802207693</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06588094161965542</v>
+        <v>0.06588094161965508</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1089109709337341</v>
+        <v>0.1089109709337345</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2392782157526664</v>
+        <v>0.2392782157526658</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2773047315393139</v>
+        <v>0.2773047315393132</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5100847988659585</v>
+        <v>0.5100847988659563</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6413509054650478</v>
+        <v>0.6413509054650482</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4482041363024508</v>
+        <v>0.4482041363024513</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.257545717902931</v>
+        <v>0.2575457179029297</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5482168914776104</v>
+        <v>0.548216891477611</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2041241416192897</v>
+        <v>0.2041241416192889</v>
       </c>
     </row>
     <row r="8">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1739736180607274</v>
+        <v>0.1739736180607275</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2289158088775472</v>
+        <v>0.2289158088775486</v>
       </c>
       <c r="D8" t="n">
         <v>0.2772254367120028</v>
@@ -1986,73 +1986,73 @@
         <v>0.2188023010504301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07107430302178812</v>
+        <v>0.07107430302178848</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3354147901803332</v>
+        <v>0.3354147901803342</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3117576866971807</v>
+        <v>0.3117576866971822</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2561274049562277</v>
+        <v>0.2561274049562289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2858980513713267</v>
+        <v>0.2858980513713275</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2530181304355564</v>
+        <v>0.2530181304355559</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.202274164215702e-05</v>
+        <v>-3.202274164158803e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2393951168108953</v>
+        <v>0.2393951168108954</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2008393856702331</v>
+        <v>0.2008393856702333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1325324154843324</v>
+        <v>0.1325324154843331</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1989532366011831</v>
+        <v>0.1989532366011853</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1962501896973009</v>
+        <v>0.1962501896973011</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1168676498569274</v>
+        <v>-0.1168676498569244</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1437740719834991</v>
+        <v>0.1437740719834993</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1868041012975784</v>
+        <v>0.1868041012975779</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2869294134879729</v>
+        <v>0.2869294134879738</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3373910574440824</v>
+        <v>0.3373910574440825</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5879903036643117</v>
+        <v>0.5879903036643113</v>
       </c>
       <c r="X8" t="n">
-        <v>0.649675802439287</v>
+        <v>0.6496758024392872</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5877752306323791</v>
+        <v>0.5877752306323806</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2713042031319067</v>
+        <v>0.2713042031319073</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6261100218414531</v>
+        <v>0.6261100218414548</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3477895184345978</v>
+        <v>0.3477895184345982</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2746299530984407</v>
+        <v>0.2746299530984416</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3218498566745983</v>
+        <v>0.3218498566745996</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3701594845090534</v>
+        <v>0.3701594845090535</v>
       </c>
       <c r="E9" t="n">
         <v>0.3325135931512143</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08981452010382455</v>
+        <v>0.08981452010382565</v>
       </c>
       <c r="G9" t="n">
         <v>0.415292654229065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4046917344942314</v>
+        <v>0.4046917344942321</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3490614527532783</v>
+        <v>0.3490614527532805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3788320991683782</v>
+        <v>0.378832099168378</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3459521782326062</v>
+        <v>0.3459521782326077</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09290202505540668</v>
+        <v>0.0929020250554094</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3323291646077458</v>
+        <v>0.3323291646077465</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3425818711508143</v>
+        <v>0.342581871150814</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2791693293259368</v>
+        <v>0.2791693293259361</v>
       </c>
       <c r="P9" t="n">
-        <v>0.35285953845344</v>
+        <v>0.3528595384534387</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3645233685635146</v>
+        <v>0.3645233685635144</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02393360205987696</v>
+        <v>-0.02393360205987582</v>
       </c>
       <c r="S9" t="n">
         <v>0.2367081197805496</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2797381490946285</v>
+        <v>0.279738149094629</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4111375838069673</v>
+        <v>0.411137583806968</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5118808974615955</v>
+        <v>0.5118808974615945</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6809119770268508</v>
+        <v>0.6809119770268525</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8121780836259412</v>
+        <v>0.8121780836259425</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6190313144633457</v>
+        <v>0.6190313144633459</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3950664408733435</v>
+        <v>0.3950664408733434</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7190440696385048</v>
+        <v>0.7190440696385055</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3749513197801826</v>
+        <v>0.3749513197801838</v>
       </c>
     </row>
   </sheetData>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.682229752605384</v>
+        <v>2.682229752605385</v>
       </c>
       <c r="C2" t="n">
         <v>2.691300341479791</v>
@@ -2333,31 +2333,31 @@
         <v>2.687292138134788</v>
       </c>
       <c r="K2" t="n">
-        <v>2.682226114281997</v>
+        <v>2.682226114281998</v>
       </c>
       <c r="L2" t="n">
-        <v>2.696846221106005</v>
+        <v>2.696846221106006</v>
       </c>
       <c r="M2" t="n">
-        <v>2.703461048296316</v>
+        <v>2.703461048296317</v>
       </c>
       <c r="N2" t="n">
-        <v>2.683647587341869</v>
+        <v>2.683647587341868</v>
       </c>
       <c r="O2" t="n">
         <v>2.96250916258444</v>
       </c>
       <c r="P2" t="n">
-        <v>2.686504644108034</v>
+        <v>2.686504644108035</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.674911672284111</v>
+        <v>2.674911672284112</v>
       </c>
       <c r="R2" t="n">
         <v>2.675570682552229</v>
       </c>
       <c r="S2" t="n">
-        <v>2.690320466637252</v>
+        <v>2.690320466637253</v>
       </c>
       <c r="T2" t="n">
         <v>2.676861538395904</v>
@@ -2369,7 +2369,7 @@
         <v>2.666291948787912</v>
       </c>
       <c r="W2" t="n">
-        <v>3.075843740811688</v>
+        <v>3.075843740811689</v>
       </c>
       <c r="X2" t="n">
         <v>2.68474516032428</v>
@@ -2384,7 +2384,7 @@
         <v>2.683317754036061</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.70443599432994</v>
+        <v>2.704435994329942</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.915552174805995</v>
+        <v>0.7772660959933259</v>
       </c>
       <c r="C3" t="n">
-        <v>1.823558637970916</v>
+        <v>0.6803771220962241</v>
       </c>
       <c r="D3" t="n">
-        <v>1.912915147802132</v>
+        <v>0.7745916374785228</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799273709662555</v>
+        <v>0.6568981586700191</v>
       </c>
       <c r="F3" t="n">
-        <v>1.830193134623629</v>
+        <v>0.6889530702247476</v>
       </c>
       <c r="G3" t="n">
-        <v>2.027749341082766</v>
+        <v>0.8934029738822887</v>
       </c>
       <c r="H3" t="n">
-        <v>1.900518103163961</v>
+        <v>0.7617833400214077</v>
       </c>
       <c r="I3" t="n">
-        <v>1.834658569534769</v>
+        <v>0.6935637579966661</v>
       </c>
       <c r="J3" t="n">
-        <v>1.952221978677433</v>
+        <v>0.8152480453597405</v>
       </c>
       <c r="K3" t="n">
-        <v>1.916132784209859</v>
+        <v>0.7779418705977816</v>
       </c>
       <c r="L3" t="n">
-        <v>2.020627366809694</v>
+        <v>0.8860615884029854</v>
       </c>
       <c r="M3" t="n">
-        <v>2.070039020280494</v>
+        <v>0.9373364207185456</v>
       </c>
       <c r="N3" t="n">
-        <v>1.926750245066961</v>
+        <v>0.7888995665102301</v>
       </c>
       <c r="O3" t="n">
-        <v>2.364811437131583</v>
+        <v>1.225915106805076</v>
       </c>
       <c r="P3" t="n">
-        <v>1.946158873447457</v>
+        <v>0.8089261694884146</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.864347914245794</v>
+        <v>0.7242965241689089</v>
       </c>
       <c r="R3" t="n">
-        <v>1.869498046765696</v>
+        <v>0.7296472690179177</v>
       </c>
       <c r="S3" t="n">
-        <v>1.973405874893537</v>
+        <v>0.8371699031013282</v>
       </c>
       <c r="T3" t="n">
-        <v>1.878513367563541</v>
+        <v>0.738973402153087</v>
       </c>
       <c r="U3" t="n">
-        <v>2.651614053287445</v>
+        <v>1.515933376179808</v>
       </c>
       <c r="V3" t="n">
-        <v>1.802236504361019</v>
+        <v>0.6599700914560653</v>
       </c>
       <c r="W3" t="n">
-        <v>2.628967396936902</v>
+        <v>1.493619997003367</v>
       </c>
       <c r="X3" t="n">
-        <v>1.934736828609618</v>
+        <v>0.7971881034754463</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.893677970463222</v>
+        <v>0.7546559938367186</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.141611137536231</v>
+        <v>1.00187712181093</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.924173161462677</v>
+        <v>0.7862211423578764</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07503213526142</v>
+        <v>0.9424192696322752</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4769565124976554</v>
+        <v>0.4769565124976547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.254591945510537</v>
+        <v>0.2545919455105378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4705848860440265</v>
+        <v>0.4705848860440282</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2916666279247302</v>
+        <v>0.291666627924731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3400265874047386</v>
+        <v>0.3400265874047393</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6546719515356285</v>
+        <v>0.6546719515356284</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4503976569797223</v>
+        <v>0.4503976569797231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3469851858408852</v>
+        <v>0.3469851858408855</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5337165795548497</v>
+        <v>0.5337165795548507</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4769154159612727</v>
+        <v>0.4769154159612736</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6420562481198525</v>
+        <v>0.6420562481198602</v>
       </c>
       <c r="M4" t="n">
-        <v>0.718524822685474</v>
+        <v>0.7185248226854745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4929716080824226</v>
+        <v>0.4929716080824234</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4496899016262545</v>
+        <v>0.4496899016262553</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5252433785673264</v>
+        <v>0.5252433785673272</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.394295428785587</v>
+        <v>0.3942954287855889</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4017392529236823</v>
+        <v>0.4017392529236826</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5683448493999173</v>
+        <v>0.568344849399917</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4163200635010239</v>
+        <v>0.4163200635010244</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5893030778733959</v>
+        <v>0.5893030778733965</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2941034100232776</v>
+        <v>0.2941034100232769</v>
       </c>
       <c r="W4" t="n">
-        <v>0.606239846265216</v>
+        <v>0.6062398462652161</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5053691998273</v>
+        <v>0.5053691998273029</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4379929924281923</v>
+        <v>0.4379929924281928</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.411277077190263</v>
+        <v>0.4112770771902644</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4892459891625247</v>
+        <v>0.4892459891625257</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7244742109301491</v>
+        <v>0.7244742109301497</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.487509371340874</v>
+        <v>5.487509371341002</v>
       </c>
       <c r="C5" t="n">
-        <v>1.771208169308962</v>
+        <v>1.77120816930896</v>
       </c>
       <c r="D5" t="n">
-        <v>6.139471097371673</v>
+        <v>6.139471097371675</v>
       </c>
       <c r="E5" t="n">
-        <v>2.427413171459129</v>
+        <v>2.427413171459162</v>
       </c>
       <c r="F5" t="n">
-        <v>3.543752586402506</v>
+        <v>3.543752586402508</v>
       </c>
       <c r="G5" t="n">
-        <v>8.796266655041482</v>
+        <v>8.796266655041483</v>
       </c>
       <c r="H5" t="n">
-        <v>5.957031160095716</v>
+        <v>5.957031160095712</v>
       </c>
       <c r="I5" t="n">
-        <v>3.713497284775157</v>
+        <v>3.713497284775167</v>
       </c>
       <c r="J5" t="n">
-        <v>6.868214991183042</v>
+        <v>6.868214991183062</v>
       </c>
       <c r="K5" t="n">
-        <v>5.824081096676911</v>
+        <v>5.824081096676908</v>
       </c>
       <c r="L5" t="n">
-        <v>9.030055196030055</v>
+        <v>9.030055196030249</v>
       </c>
       <c r="M5" t="n">
-        <v>11.17105978826167</v>
+        <v>11.17105978826166</v>
       </c>
       <c r="N5" t="n">
-        <v>6.390361199836811</v>
+        <v>6.39036119983681</v>
       </c>
       <c r="O5" t="n">
-        <v>4.88884850719993</v>
+        <v>4.888848507199928</v>
       </c>
       <c r="P5" t="n">
-        <v>6.45422871983245</v>
+        <v>6.454228719832455</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.494752982680543</v>
+        <v>4.494752982680546</v>
       </c>
       <c r="R5" t="n">
         <v>4.883957437296933</v>
       </c>
       <c r="S5" t="n">
-        <v>7.276576158064042</v>
+        <v>7.276576158064026</v>
       </c>
       <c r="T5" t="n">
-        <v>5.04976449830643</v>
+        <v>5.049764498306423</v>
       </c>
       <c r="U5" t="n">
-        <v>7.92226581792233</v>
+        <v>7.922265817922322</v>
       </c>
       <c r="V5" t="n">
-        <v>2.321730680112148</v>
+        <v>2.321730680112152</v>
       </c>
       <c r="W5" t="n">
-        <v>8.426132031688537</v>
+        <v>8.426132031688535</v>
       </c>
       <c r="X5" t="n">
-        <v>6.709948648856289</v>
+        <v>6.709948648856307</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.239543688284163</v>
+        <v>5.239543688284161</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.45846324461235</v>
+        <v>4.458463244612396</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.195869540788676</v>
+        <v>6.195869540788688</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.7205452477763</v>
+        <v>11.72054524777628</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4977235637159484</v>
+        <v>0.4977235637159514</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3593241635016765</v>
+        <v>0.3593241635016781</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4913519372623216</v>
+        <v>0.4913519372623234</v>
       </c>
       <c r="E6" t="n">
-        <v>0.396398845915869</v>
+        <v>0.3963988459158707</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3607936386230331</v>
+        <v>0.3607936386230344</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7594041695267665</v>
+        <v>0.7594041695267687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5551298749708626</v>
+        <v>0.5551298749708636</v>
       </c>
       <c r="I6" t="n">
-        <v>0.451717403832024</v>
+        <v>0.4517174038320257</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6384487975459899</v>
+        <v>0.638448797545991</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4976824671795678</v>
+        <v>0.4976824671795687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7467884661109901</v>
+        <v>0.7467884661109938</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8232570406766121</v>
+        <v>0.8232570406766122</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5143327623255805</v>
+        <v>0.5143327623255768</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4711736832018384</v>
+        <v>0.4711736832018228</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6343421531281067</v>
+        <v>0.6343421531281084</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4150624800038812</v>
+        <v>0.4150624800038826</v>
       </c>
       <c r="R6" t="n">
-        <v>0.50647147091482</v>
+        <v>0.5064714709148218</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5891119006182116</v>
+        <v>0.5891119006182123</v>
       </c>
       <c r="T6" t="n">
-        <v>0.437087114719318</v>
+        <v>0.4370871147193195</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6131915142208245</v>
+        <v>0.6131915142208265</v>
       </c>
       <c r="V6" t="n">
-        <v>0.314870461241572</v>
+        <v>0.3148704612415719</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6317407306773281</v>
+        <v>0.6317407306773284</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6101014178184399</v>
+        <v>0.6101014178184417</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4643863330422696</v>
+        <v>0.4643863330422611</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4320441284085592</v>
+        <v>0.4320441284085609</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5939782071536643</v>
+        <v>0.5939782071536658</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7478512800224888</v>
+        <v>0.7478512800224892</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5752071261544035</v>
+        <v>0.5752071261544046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3528425591672852</v>
+        <v>0.3528425591672856</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5688354997007751</v>
+        <v>0.5688354997007755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3899172415814782</v>
+        <v>0.3899172415814803</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4382772010614868</v>
+        <v>0.438277201061487</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7529225651923763</v>
+        <v>0.7529225651923762</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5486482706364704</v>
+        <v>0.5486482706364708</v>
       </c>
       <c r="I7" t="n">
-        <v>0.445235799497633</v>
+        <v>0.4452357994976337</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6319671932115987</v>
+        <v>0.6319671932116006</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5751660296180211</v>
+        <v>0.5751660296180224</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7403068617766042</v>
+        <v>0.740306861776598</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8167754363422209</v>
+        <v>0.8167754363422218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5912222217391701</v>
+        <v>0.5912222217391702</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5475818600851873</v>
+        <v>0.5475818600851876</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6231353370262592</v>
+        <v>0.6231353370262606</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4925460424423352</v>
+        <v>0.4925460424423361</v>
       </c>
       <c r="R7" t="n">
-        <v>0.49998986658043</v>
+        <v>0.4999898665804311</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6665954630566642</v>
+        <v>0.6665954630566664</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5145706771577717</v>
+        <v>0.514570677157772</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6905461035182064</v>
+        <v>0.6905461035182061</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3923540236800203</v>
+        <v>0.3923540236800254</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7044904599219636</v>
+        <v>0.7044904599219642</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6036198134840493</v>
+        <v>0.6036198134840514</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5393649912140749</v>
+        <v>0.5393649912140754</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5095276908470114</v>
+        <v>0.5095276908470127</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5874966028192732</v>
+        <v>0.587496602819274</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8227248245868999</v>
+        <v>0.8227248245869004</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6210438303216466</v>
+        <v>0.6210438303216487</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5134648043323032</v>
+        <v>0.5134648043323046</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7294577448657936</v>
+        <v>0.7294577448657938</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4894195721429417</v>
+        <v>0.4894195721429438</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5019961509794172</v>
+        <v>0.5019961509794185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9373463400352708</v>
+        <v>0.937346340035272</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7092705158014886</v>
+        <v>0.7092705158014899</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6058580446626514</v>
+        <v>0.6058580446626524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7925894383766168</v>
+        <v>0.7925894383766189</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7357882747830394</v>
+        <v>0.7357882747830408</v>
       </c>
       <c r="L8" t="n">
-        <v>0.900929106941617</v>
+        <v>0.9009291069416223</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9773976815073417</v>
+        <v>0.9773976815073442</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6628664694068103</v>
+        <v>0.6628664694068108</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6440366892038275</v>
+        <v>0.6440366892038287</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7135964081833135</v>
+        <v>0.713596408183314</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5158247679730448</v>
+        <v>0.5158247679730464</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6606121117454475</v>
+        <v>0.6606121117454484</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8272177082216837</v>
+        <v>0.8272177082216852</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6751929223227899</v>
+        <v>0.6751929223227908</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7954500291955037</v>
+        <v>0.7954500291955049</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5217999762215138</v>
+        <v>0.5217999762215169</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8651352636529316</v>
+        <v>0.8651352636529334</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6374188618793728</v>
+        <v>0.6374188618793746</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8144203897978313</v>
+        <v>0.8144203897978317</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5532321946659265</v>
+        <v>0.5532321946659273</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7481188479842904</v>
+        <v>0.7481188479842923</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.103250165459462</v>
+        <v>1.103250165459464</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8383755497573858</v>
+        <v>0.838375549757389</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7260759733783726</v>
+        <v>0.7260759733783744</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9420689139118613</v>
+        <v>0.9420689139118625</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7377481162680217</v>
+        <v>0.7377481162680247</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5577807530564887</v>
+        <v>0.5577807530564901</v>
       </c>
       <c r="G9" t="n">
-        <v>1.126155994173126</v>
+        <v>1.126155994173127</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9218816848475603</v>
+        <v>0.9218816848475615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8184692137087211</v>
+        <v>0.8184692137087232</v>
       </c>
       <c r="J9" t="n">
-        <v>1.005200607422688</v>
+        <v>1.005200607422689</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9483994438291097</v>
+        <v>0.9483994438291106</v>
       </c>
       <c r="L9" t="n">
-        <v>1.11354027598769</v>
+        <v>1.113540275987693</v>
       </c>
       <c r="M9" t="n">
         <v>1.19000885055331</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9644556359502576</v>
+        <v>0.9644556359502596</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9576493429281246</v>
+        <v>0.9576493429281262</v>
       </c>
       <c r="P9" t="n">
-        <v>1.041135593266249</v>
+        <v>1.04113559326625</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8657794714230851</v>
+        <v>0.8657794714230864</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8732232807915183</v>
+        <v>0.8732232807915205</v>
       </c>
       <c r="S9" t="n">
-        <v>1.039828877267752</v>
+        <v>1.039828877267757</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8878040913688577</v>
+        <v>0.8878040913688596</v>
       </c>
       <c r="U9" t="n">
-        <v>1.063908490870367</v>
+        <v>1.063908490870369</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8925999234451064</v>
+        <v>0.8925999234451073</v>
       </c>
       <c r="W9" t="n">
-        <v>1.077723874133052</v>
+        <v>1.077723874133054</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9768532276951376</v>
+        <v>0.9768532276951398</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9125984054251631</v>
+        <v>0.9125984054251645</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8164017089471266</v>
+        <v>0.8164017089471287</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.960730017030361</v>
+        <v>0.960730017030363</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.195958238797988</v>
+        <v>1.19595823879799</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672047349274317</v>
+        <v>2.672047349274315</v>
       </c>
       <c r="C2" t="n">
-        <v>2.687877399708463</v>
+        <v>2.687877399708461</v>
       </c>
       <c r="D2" t="n">
-        <v>2.680392009183839</v>
+        <v>2.680392009183838</v>
       </c>
       <c r="E2" t="n">
-        <v>2.661787447051867</v>
+        <v>2.661787447051866</v>
       </c>
       <c r="F2" t="n">
-        <v>2.662032718959222</v>
+        <v>2.66203271895922</v>
       </c>
       <c r="G2" t="n">
-        <v>2.691095152016631</v>
+        <v>2.69109515201663</v>
       </c>
       <c r="H2" t="n">
-        <v>2.671928997654847</v>
+        <v>2.671928997654845</v>
       </c>
       <c r="I2" t="n">
-        <v>2.665675243809019</v>
+        <v>2.665675243809016</v>
       </c>
       <c r="J2" t="n">
-        <v>2.681084827723792</v>
+        <v>2.681084827723789</v>
       </c>
       <c r="K2" t="n">
-        <v>2.672134965941318</v>
+        <v>2.672134965941316</v>
       </c>
       <c r="L2" t="n">
-        <v>2.686569635473954</v>
+        <v>2.686569635473953</v>
       </c>
       <c r="M2" t="n">
-        <v>2.693237291451482</v>
+        <v>2.693237291451481</v>
       </c>
       <c r="N2" t="n">
-        <v>2.672293837671493</v>
+        <v>2.672293837671492</v>
       </c>
       <c r="O2" t="n">
         <v>2.943620693105744</v>
       </c>
       <c r="P2" t="n">
-        <v>2.681543926796319</v>
+        <v>2.681543926796317</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.660809367733973</v>
+        <v>2.660809367733971</v>
       </c>
       <c r="R2" t="n">
-        <v>2.668337351351108</v>
+        <v>2.668337351351106</v>
       </c>
       <c r="S2" t="n">
-        <v>2.683025969363166</v>
+        <v>2.683025969363163</v>
       </c>
       <c r="T2" t="n">
-        <v>2.669793248149385</v>
+        <v>2.669793248149383</v>
       </c>
       <c r="U2" t="n">
-        <v>3.077573201810541</v>
+        <v>3.077573201810539</v>
       </c>
       <c r="V2" t="n">
-        <v>2.665956801124034</v>
+        <v>2.665956801124033</v>
       </c>
       <c r="W2" t="n">
         <v>3.062320160911439</v>
       </c>
       <c r="X2" t="n">
-        <v>2.687005250438643</v>
+        <v>2.687005250438641</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.682830579193504</v>
+        <v>2.682830579193501</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.832022085052257</v>
+        <v>2.832022085052256</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.677650603776433</v>
+        <v>2.677650603776432</v>
       </c>
       <c r="AB2" t="n">
         <v>2.696698545906434</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.872470112073578</v>
+        <v>0.732752902149676</v>
       </c>
       <c r="C3" t="n">
-        <v>1.832815368441561</v>
+        <v>0.6901049364464378</v>
       </c>
       <c r="D3" t="n">
-        <v>1.933073090733255</v>
+        <v>0.7955586888624556</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799755400793809</v>
+        <v>0.6574859696860237</v>
       </c>
       <c r="F3" t="n">
-        <v>1.801714624197168</v>
+        <v>0.6595522890174503</v>
       </c>
       <c r="G3" t="n">
-        <v>2.007839976402368</v>
+        <v>0.8728908577233212</v>
       </c>
       <c r="H3" t="n">
-        <v>1.873005249203829</v>
+        <v>0.7333784854356539</v>
       </c>
       <c r="I3" t="n">
-        <v>1.827885461459543</v>
+        <v>0.6866410695111433</v>
       </c>
       <c r="J3" t="n">
-        <v>1.937127987001214</v>
+        <v>0.7997184875429971</v>
       </c>
       <c r="K3" t="n">
-        <v>1.873105050005258</v>
+        <v>0.7334861354289698</v>
       </c>
       <c r="L3" t="n">
-        <v>1.97651335902103</v>
+        <v>0.8404838580660353</v>
       </c>
       <c r="M3" t="n">
-        <v>2.026547626609576</v>
+        <v>0.8923879831155654</v>
       </c>
       <c r="N3" t="n">
-        <v>1.874962983847796</v>
+        <v>0.7353689682572812</v>
       </c>
       <c r="O3" t="n">
-        <v>2.311646382191755</v>
+        <v>1.171523263322443</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93992048230803</v>
+        <v>0.8025624124159859</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.792814288266062</v>
+        <v>0.6503205045632663</v>
       </c>
       <c r="R3" t="n">
-        <v>1.847078699616997</v>
+        <v>0.7065209423182699</v>
       </c>
       <c r="S3" t="n">
-        <v>1.950589636272261</v>
+        <v>0.8136424618314656</v>
       </c>
       <c r="T3" t="n">
-        <v>1.857322320340749</v>
+        <v>0.7171195755705108</v>
       </c>
       <c r="U3" t="n">
-        <v>2.591639231851397</v>
+        <v>1.454226012882995</v>
       </c>
       <c r="V3" t="n">
-        <v>1.828899061331237</v>
+        <v>0.6876653917965314</v>
       </c>
       <c r="W3" t="n">
-        <v>2.593792221912524</v>
+        <v>1.457632760402536</v>
       </c>
       <c r="X3" t="n">
-        <v>1.980182896128464</v>
+        <v>0.8443389720089501</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.949917290759078</v>
+        <v>0.8129736872399738</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.137333682493193</v>
+        <v>0.9976762205936596</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.913044305391522</v>
+        <v>0.7747876254892857</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.049223819199511</v>
+        <v>0.9157858965211585</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4075814247729721</v>
+        <v>0.4075814247729728</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2708350355816708</v>
+        <v>0.2708350355816722</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5018381971842776</v>
+        <v>0.5018381971842787</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2916911093822365</v>
+        <v>0.2916911093822364</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2944615684064233</v>
+        <v>0.2944615684064221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6227351191696234</v>
+        <v>0.622735119169625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4062445887866507</v>
+        <v>0.4062445887866511</v>
       </c>
       <c r="I4" t="n">
-        <v>0.335605562229126</v>
+        <v>0.3356055622291261</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5092791173289669</v>
+        <v>0.5092791173289672</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4085710953324507</v>
+        <v>0.4085710953324511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5716173279795982</v>
+        <v>0.5716173279795996</v>
       </c>
       <c r="M4" t="n">
-        <v>0.649219387867042</v>
+        <v>0.6492193878670423</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4103656246093599</v>
+        <v>0.4103656246093589</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3894871591257487</v>
+        <v>0.3894871591257476</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5148496365254939</v>
+        <v>0.5148496365254924</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2806432535478937</v>
+        <v>0.2806432535478938</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3656752915470082</v>
+        <v>0.365675291547009</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5315899890912772</v>
+        <v>0.5315899890912786</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3821203156291493</v>
+        <v>0.3821203156291487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5066425410507491</v>
+        <v>0.5066425410507487</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3362089086008502</v>
+        <v>0.33620890860085</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5651153745046187</v>
+        <v>0.565115374504619</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5765377993985455</v>
+        <v>0.5765377993985454</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5261848300091485</v>
+        <v>0.52618483000915</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4100096706653271</v>
+        <v>0.410009670665329</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4708727619988342</v>
+        <v>0.470872761998834</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6830462560138308</v>
+        <v>0.6830462560138304</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.170838344833221</v>
+        <v>4.170838344833228</v>
       </c>
       <c r="C5" t="n">
-        <v>2.006870883029006</v>
+        <v>2.006870883029005</v>
       </c>
       <c r="D5" t="n">
-        <v>6.380363568734682</v>
+        <v>6.380363568734685</v>
       </c>
       <c r="E5" t="n">
-        <v>2.385795812483977</v>
+        <v>2.385795812483972</v>
       </c>
       <c r="F5" t="n">
-        <v>2.542952330450365</v>
+        <v>2.542952330450364</v>
       </c>
       <c r="G5" t="n">
-        <v>7.678075947073512</v>
+        <v>7.67807594707348</v>
       </c>
       <c r="H5" t="n">
-        <v>4.862250212122929</v>
+        <v>4.862250212122921</v>
       </c>
       <c r="I5" t="n">
-        <v>3.360799954183372</v>
+        <v>3.360799954183375</v>
       </c>
       <c r="J5" t="n">
-        <v>6.05728115028247</v>
+        <v>6.057281150282471</v>
       </c>
       <c r="K5" t="n">
-        <v>4.193324208790639</v>
+        <v>4.193324208790643</v>
       </c>
       <c r="L5" t="n">
-        <v>7.277801746178167</v>
+        <v>7.277801746178177</v>
       </c>
       <c r="M5" t="n">
-        <v>9.274190589615362</v>
+        <v>9.274190589615378</v>
       </c>
       <c r="N5" t="n">
-        <v>4.600288343215074</v>
+        <v>4.600288343215079</v>
       </c>
       <c r="O5" t="n">
-        <v>3.686737984293967</v>
+        <v>3.686737984293956</v>
       </c>
       <c r="P5" t="n">
-        <v>5.898502499935391</v>
+        <v>5.89850249993539</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.210860075239822</v>
+        <v>2.210860075239819</v>
       </c>
       <c r="R5" t="n">
-        <v>3.992983793333263</v>
+        <v>3.99298379333326</v>
       </c>
       <c r="S5" t="n">
-        <v>6.242126373335316</v>
+        <v>6.242126373335308</v>
       </c>
       <c r="T5" t="n">
-        <v>4.207565087017858</v>
+        <v>4.207565087017865</v>
       </c>
       <c r="U5" t="n">
-        <v>6.025228910518909</v>
+        <v>6.025228910518879</v>
       </c>
       <c r="V5" t="n">
-        <v>2.898378065444704</v>
+        <v>2.898378065444697</v>
       </c>
       <c r="W5" t="n">
-        <v>7.262263708540122</v>
+        <v>7.26226370854013</v>
       </c>
       <c r="X5" t="n">
-        <v>7.655309600745118</v>
+        <v>7.655309600745098</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.577334688066913</v>
+        <v>6.577334688066923</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.015071911643761</v>
+        <v>4.015071911643773</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.592627239607832</v>
+        <v>5.592627239607834</v>
       </c>
       <c r="AB5" t="n">
         <v>10.30577393607276</v>
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5024395574342216</v>
+        <v>0.5024395574342219</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2911834661992054</v>
+        <v>0.2911834661992044</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5966963298455278</v>
+        <v>0.5966963298455285</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3865492420434861</v>
+        <v>0.3865492420434868</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3148099990239578</v>
+        <v>0.3148099990239574</v>
       </c>
       <c r="G6" t="n">
-        <v>0.643083549787157</v>
+        <v>0.6430835497871598</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4265930194041859</v>
+        <v>0.4265930194041855</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3559539928466601</v>
+        <v>0.3559539928466614</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6041372499902189</v>
+        <v>0.6041372499902219</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5034292279937017</v>
+        <v>0.5034292279937013</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6664754606408499</v>
+        <v>0.6664754606408508</v>
       </c>
       <c r="M6" t="n">
-        <v>0.669567818484575</v>
+        <v>0.6695678184845743</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4312417009033477</v>
+        <v>0.4312417009033451</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4883504966487208</v>
+        <v>0.4883504966487229</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6136724186072791</v>
+        <v>0.6136724186072777</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3755013862091437</v>
+        <v>0.3755013862091456</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3860237221645429</v>
+        <v>0.3860237221645425</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6264481217525271</v>
+        <v>0.6264481217525278</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4024687462466824</v>
+        <v>0.4024687462466846</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5301891089001863</v>
+        <v>0.5301891089001876</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4310670412621008</v>
+        <v>0.4310670412621005</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6639933428894683</v>
+        <v>0.6639933428894689</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5968862300160802</v>
+        <v>0.5968862300160815</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5521731392681393</v>
+        <v>0.5521731392681362</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5048678033265769</v>
+        <v>0.5048678033265794</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5657308946600856</v>
+        <v>0.5657308946600873</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7056420265565482</v>
+        <v>0.7056420265565488</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4948793727496889</v>
+        <v>0.4948793727496895</v>
       </c>
       <c r="C7" t="n">
-        <v>0.358132983558389</v>
+        <v>0.3581329835583895</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5891361451609958</v>
+        <v>0.5891361451609965</v>
       </c>
       <c r="E7" t="n">
         <v>0.3789890573589548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3817595163831412</v>
+        <v>0.3817595163831423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100330671463404</v>
+        <v>0.7100330671463425</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4935425367633692</v>
+        <v>0.4935425367633702</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4229035102058447</v>
+        <v>0.4229035102058452</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5965770653056851</v>
+        <v>0.5965770653056855</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4958690433091682</v>
+        <v>0.4958690433091695</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6589152759563178</v>
+        <v>0.6589152759563176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.736517335843759</v>
+        <v>0.7365173358437593</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4976635725860778</v>
+        <v>0.497663572586078</v>
       </c>
       <c r="O7" t="n">
-        <v>0.476451202941484</v>
+        <v>0.4764512029414834</v>
       </c>
       <c r="P7" t="n">
-        <v>0.60181368034123</v>
+        <v>0.6018136803412297</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3679412015246122</v>
+        <v>0.3679412015246131</v>
       </c>
       <c r="R7" t="n">
-        <v>0.452973239523726</v>
+        <v>0.4529732395237274</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6188879370679954</v>
+        <v>0.6188879370679957</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4694182636058662</v>
+        <v>0.4694182636058659</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5967252501303085</v>
+        <v>0.5967252501303065</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4235068565775684</v>
+        <v>0.4235068565775683</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6524133224813364</v>
+        <v>0.652413322481337</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6638357473752654</v>
+        <v>0.6638357473752636</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6166809152177689</v>
+        <v>0.61668091521777</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4973076186420444</v>
+        <v>0.4973076186420461</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5581707099755534</v>
+        <v>0.5581707099755527</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7703442039905514</v>
+        <v>0.7703442039905523</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5338350084806467</v>
+        <v>0.5338350084806477</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4973954961140191</v>
+        <v>0.4973954961140207</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7283986577166258</v>
+        <v>0.7283986577166273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4648411168847657</v>
+        <v>0.4648411168847668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4363417912051096</v>
+        <v>0.4363417912051092</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8700948640456729</v>
+        <v>0.8700948640456718</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6328050493190009</v>
+        <v>0.6328050493190014</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5621660227614743</v>
+        <v>0.5621660227614746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7358395778613145</v>
+        <v>0.7358395778613146</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6351315558647989</v>
+        <v>0.6351315558648005</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7981777885119482</v>
+        <v>0.7981777885119506</v>
       </c>
       <c r="M8" t="n">
-        <v>0.875779848399579</v>
+        <v>0.8757798483995815</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5591714746122327</v>
+        <v>0.5591714746122347</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5596606512038529</v>
+        <v>0.5596606512038554</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6797854032194512</v>
+        <v>0.6797854032194538</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3871842465822399</v>
+        <v>0.3871842465822415</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5922357520793571</v>
+        <v>0.5922357520793592</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7581504496236269</v>
+        <v>0.7581504496236275</v>
       </c>
       <c r="T8" t="n">
-        <v>0.608680776161496</v>
+        <v>0.6086807761614972</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6873811021582641</v>
+        <v>0.6873811021582648</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5352860565468328</v>
+        <v>0.5352860565468313</v>
       </c>
       <c r="W8" t="n">
-        <v>0.791695548153604</v>
+        <v>0.7916955481536037</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6922721169707068</v>
+        <v>0.6922721169707049</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.855570911693033</v>
+        <v>0.8555709116930333</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5344000026431799</v>
+        <v>0.5344000026431814</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.697433222531184</v>
+        <v>0.6974332225311849</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.014385636860156</v>
+        <v>1.014385636860159</v>
       </c>
     </row>
     <row r="9">
@@ -3782,82 +3782,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.713370481622414</v>
+        <v>0.713370481622413</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6699344458864069</v>
+        <v>0.6699344458864073</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9009376074890136</v>
+        <v>0.9009376074890147</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6692548845958871</v>
+        <v>0.6692548845958886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4784551236312268</v>
+        <v>0.4784551236312273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.021834547519498</v>
+        <v>1.0218345475195</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8053439990913888</v>
+        <v>0.8053439990913883</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7347049725338631</v>
+        <v>0.734704972533863</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9083785276337037</v>
+        <v>0.908378527633703</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8076705056371856</v>
+        <v>0.8076705056371853</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9707167382843354</v>
+        <v>0.9707167382843365</v>
       </c>
       <c r="M9" t="n">
         <v>1.048318798171778</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8094650349140966</v>
+        <v>0.809465034914096</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8195095224113721</v>
+        <v>0.8195095224113753</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9515972076114269</v>
+        <v>0.9515972076114282</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.67974268189777</v>
+        <v>0.6797426818977697</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7647747018517435</v>
+        <v>0.7647747018517441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9306893993960142</v>
+        <v>0.9306893993960131</v>
       </c>
       <c r="T9" t="n">
-        <v>0.781219725933885</v>
+        <v>0.7812197259338859</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9089400885873878</v>
+        <v>0.9089400885873853</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8429863509148106</v>
+        <v>0.8429863509148107</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9642147848093545</v>
+        <v>0.9642147848093537</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9756372097032827</v>
+        <v>0.9756372097032844</v>
       </c>
       <c r="Y9" t="n">
         <v>0.9284823775457859</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7528512424824213</v>
+        <v>0.7528512424824231</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8699721723035727</v>
+        <v>0.8699721723035703</v>
       </c>
       <c r="AB9" t="n">
         <v>1.082145666318569</v>
@@ -4038,13 +4038,13 @@
         <v>2.655090726236734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.66055265202908</v>
+        <v>2.660552652029078</v>
       </c>
       <c r="G2" t="n">
-        <v>2.681939410045279</v>
+        <v>2.681939410045278</v>
       </c>
       <c r="H2" t="n">
-        <v>2.666221043927938</v>
+        <v>2.666221043927937</v>
       </c>
       <c r="I2" t="n">
         <v>2.662573863465164</v>
@@ -4053,7 +4053,7 @@
         <v>2.67490312567585</v>
       </c>
       <c r="K2" t="n">
-        <v>2.672360625848102</v>
+        <v>2.672360625848101</v>
       </c>
       <c r="L2" t="n">
         <v>2.677698942461813</v>
@@ -4074,7 +4074,7 @@
         <v>2.660454218461141</v>
       </c>
       <c r="R2" t="n">
-        <v>2.663051847938319</v>
+        <v>2.66305184793832</v>
       </c>
       <c r="S2" t="n">
         <v>2.676400239383266</v>
@@ -4089,22 +4089,22 @@
         <v>2.671075447487786</v>
       </c>
       <c r="W2" t="n">
-        <v>3.056235057932574</v>
+        <v>3.056235057932573</v>
       </c>
       <c r="X2" t="n">
-        <v>2.685047355599144</v>
+        <v>2.685047355599145</v>
       </c>
       <c r="Y2" t="n">
         <v>2.69236094051954</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.823589489375508</v>
+        <v>2.823589489375509</v>
       </c>
       <c r="AA2" t="n">
         <v>2.675691740169273</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.688828808540931</v>
+        <v>2.68882880854093</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.85377421746337</v>
+        <v>0.7134259237817842</v>
       </c>
       <c r="C3" t="n">
-        <v>1.842268568747785</v>
+        <v>0.6999610099029786</v>
       </c>
       <c r="D3" t="n">
-        <v>1.869181170460591</v>
+        <v>0.729430050691026</v>
       </c>
       <c r="E3" t="n">
-        <v>1.775347217004387</v>
+        <v>0.6322415504697777</v>
       </c>
       <c r="F3" t="n">
-        <v>1.814673256942431</v>
+        <v>0.6729942363526672</v>
       </c>
       <c r="G3" t="n">
-        <v>1.965778843242996</v>
+        <v>0.8293829593102383</v>
       </c>
       <c r="H3" t="n">
-        <v>1.855737246150848</v>
+        <v>0.7155138275543692</v>
       </c>
       <c r="I3" t="n">
-        <v>1.82918908843094</v>
+        <v>0.6880140096764116</v>
       </c>
       <c r="J3" t="n">
-        <v>1.916356514038502</v>
+        <v>0.7782462901972031</v>
       </c>
       <c r="K3" t="n">
-        <v>1.898157925797994</v>
+        <v>0.7594517005684778</v>
       </c>
       <c r="L3" t="n">
-        <v>1.936317846576264</v>
+        <v>0.7989050853251495</v>
       </c>
       <c r="M3" t="n">
-        <v>1.980666135483313</v>
+        <v>0.8449156288803787</v>
       </c>
       <c r="N3" t="n">
-        <v>1.853852139339695</v>
+        <v>0.7135295192832366</v>
       </c>
       <c r="O3" t="n">
-        <v>2.271544711662359</v>
+        <v>1.130413902420713</v>
       </c>
       <c r="P3" t="n">
-        <v>1.925377960953017</v>
+        <v>0.7875404283289658</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.813697069359274</v>
+        <v>0.6719678020314004</v>
       </c>
       <c r="R3" t="n">
-        <v>1.832832307062435</v>
+        <v>0.6917872201216863</v>
       </c>
       <c r="S3" t="n">
-        <v>1.92677080347792</v>
+        <v>0.7890077695608937</v>
       </c>
       <c r="T3" t="n">
-        <v>1.844813249807113</v>
+        <v>0.7041854263556119</v>
       </c>
       <c r="U3" t="n">
-        <v>2.602547348560221</v>
+        <v>1.465664636942849</v>
       </c>
       <c r="V3" t="n">
-        <v>1.888507661231165</v>
+        <v>0.7494006008170206</v>
       </c>
       <c r="W3" t="n">
-        <v>2.587993849863943</v>
+        <v>1.451797364028459</v>
       </c>
       <c r="X3" t="n">
-        <v>1.989305694518647</v>
+        <v>0.8538209281790469</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.041797919894341</v>
+        <v>0.9081116195265423</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.114406647342396</v>
+        <v>0.9741193544051817</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.922664381985142</v>
+        <v>0.7847644316598454</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.016237545811304</v>
+        <v>0.8816609609394558</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3822361310097261</v>
+        <v>0.3822361310097255</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2919286471670131</v>
+        <v>0.2919286471670136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4054982005745295</v>
+        <v>0.4054982005745293</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2573074113966859</v>
+        <v>0.2573074113966863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.319002375831235</v>
+        <v>0.3190023758312343</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5605756460189539</v>
+        <v>0.5605756460189549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3830294699179332</v>
+        <v>0.3830294699179336</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3418328888050202</v>
+        <v>0.3418328888050201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4807985700734682</v>
+        <v>0.4807985700734685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4523788720534004</v>
+        <v>0.4523788720534011</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5126776139522453</v>
+        <v>0.5126776139522459</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5818729509640369</v>
+        <v>0.581872950964038</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3809746747203999</v>
+        <v>0.3809746747203975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3470793044547502</v>
+        <v>0.3470793044547483</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4963130145240075</v>
+        <v>0.4963130145240078</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3178905233996899</v>
+        <v>0.3178905233996895</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3472319433130491</v>
+        <v>0.3472319433130485</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4980081652471061</v>
+        <v>0.4980081652471073</v>
       </c>
       <c r="T4" t="n">
-        <v>0.366375414360894</v>
+        <v>0.3663754143608946</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5340631317482685</v>
+        <v>0.5340631317482712</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4358670156862763</v>
+        <v>0.4358670156862756</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5666141727054111</v>
+        <v>0.5666141727054085</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5956813207754645</v>
+        <v>0.5956813207754643</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6755134803113277</v>
+        <v>0.6755134803113262</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3847515151907968</v>
+        <v>0.3847515151907975</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4900053406993372</v>
+        <v>0.490005340699337</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.635560322437508</v>
+        <v>0.635560322437506</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.608769363067619</v>
+        <v>3.608769363067622</v>
       </c>
       <c r="C5" t="n">
-        <v>2.319422084498729</v>
+        <v>2.319422084498731</v>
       </c>
       <c r="D5" t="n">
-        <v>4.387508193130362</v>
+        <v>4.387508193130366</v>
       </c>
       <c r="E5" t="n">
-        <v>1.663161542546884</v>
+        <v>1.663161542546886</v>
       </c>
       <c r="F5" t="n">
-        <v>2.932609777314047</v>
+        <v>2.932609777314057</v>
       </c>
       <c r="G5" t="n">
-        <v>6.410911498680199</v>
+        <v>6.410911498680195</v>
       </c>
       <c r="H5" t="n">
-        <v>4.38031919046468</v>
+        <v>4.380319190464686</v>
       </c>
       <c r="I5" t="n">
-        <v>3.383223929695665</v>
+        <v>3.383223929695666</v>
       </c>
       <c r="J5" t="n">
-        <v>5.417409787730303</v>
+        <v>5.417409787730306</v>
       </c>
       <c r="K5" t="n">
-        <v>4.882491642758101</v>
+        <v>4.882491642758091</v>
       </c>
       <c r="L5" t="n">
-        <v>5.980113986696723</v>
+        <v>5.980113986696726</v>
       </c>
       <c r="M5" t="n">
-        <v>7.646563076445401</v>
+        <v>7.646563076445406</v>
       </c>
       <c r="N5" t="n">
-        <v>4.039891822728019</v>
+        <v>4.039891822728016</v>
       </c>
       <c r="O5" t="n">
-        <v>2.994383337229386</v>
+        <v>2.994383337229383</v>
       </c>
       <c r="P5" t="n">
-        <v>5.379799163065035</v>
+        <v>5.379799163065063</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.771126274220368</v>
+        <v>2.771126274220377</v>
       </c>
       <c r="R5" t="n">
-        <v>3.598849764744505</v>
+        <v>3.598849764744504</v>
       </c>
       <c r="S5" t="n">
         <v>5.576524426529556</v>
       </c>
       <c r="T5" t="n">
-        <v>3.87789884361403</v>
+        <v>3.877898843614026</v>
       </c>
       <c r="U5" t="n">
-        <v>6.231850002486553</v>
+        <v>6.23185000248654</v>
       </c>
       <c r="V5" t="n">
-        <v>4.376094486795801</v>
+        <v>4.376094486795797</v>
       </c>
       <c r="W5" t="n">
-        <v>7.263188614450452</v>
+        <v>7.263188614450454</v>
       </c>
       <c r="X5" t="n">
-        <v>7.728975203239287</v>
+        <v>7.728975203239291</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.34285011527229</v>
+        <v>9.342850115272281</v>
       </c>
       <c r="Z5" t="n">
         <v>3.409333369537085</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.927384219207519</v>
+        <v>5.927384219207526</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.203003178177074</v>
+        <v>9.203003178177084</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4054733786155116</v>
+        <v>0.4054733786155124</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3151658947727995</v>
+        <v>0.3151658947728004</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4984300939279501</v>
+        <v>0.4984300939279483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3502393047501041</v>
+        <v>0.3502393047501052</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3422396234370207</v>
+        <v>0.3422396234370206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5838128936247414</v>
+        <v>0.5838128936247425</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4759613632713515</v>
+        <v>0.4759613632713511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3650701364108047</v>
+        <v>0.3650701364108064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5737304634268875</v>
+        <v>0.5737304634268877</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5453107654068179</v>
+        <v>0.545310765406819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5359148615580328</v>
+        <v>0.5359148615580333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6051101985698238</v>
+        <v>0.6051101985698247</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4052495837738455</v>
+        <v>0.4052495837738551</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3714659334793871</v>
+        <v>0.3714659334793922</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5935755785281509</v>
+        <v>0.5935755785281502</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.410822416753106</v>
+        <v>0.4108224167531075</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4401638366664642</v>
+        <v>0.4401638366664669</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5212454128528926</v>
+        <v>0.5212454128528943</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4593073077143126</v>
+        <v>0.4593073077143122</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6297731716569707</v>
+        <v>0.6297731716569734</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4591042632920623</v>
+        <v>0.4591042632920622</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5943072841060356</v>
+        <v>0.5943072841060355</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6189185683812496</v>
+        <v>0.618918568381251</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.704887739589944</v>
+        <v>0.7048877395899459</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4079887627965822</v>
+        <v>0.4079887627965834</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5829372340527567</v>
+        <v>0.5829372340527554</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6609976123371007</v>
+        <v>0.6609976123371001</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4673366408910038</v>
+        <v>0.4673366408910047</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3770291570482913</v>
+        <v>0.3770291570482918</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4905987104558077</v>
+        <v>0.4905987104558078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3424079212779643</v>
+        <v>0.3424079212779648</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4041028857125117</v>
+        <v>0.4041028857125139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6456761559002326</v>
+        <v>0.6456761559002336</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4681299797992117</v>
+        <v>0.4681299797992126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4269333986862981</v>
+        <v>0.4269333986862974</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5658990799547461</v>
+        <v>0.5658990799547472</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5374793819346786</v>
+        <v>0.5374793819346788</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5977781238335256</v>
+        <v>0.5977781238335262</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6669734608453138</v>
+        <v>0.6669734608453143</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4660751846016757</v>
+        <v>0.4660751846016759</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4318460574151035</v>
+        <v>0.4318460574151042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5810797674843637</v>
+        <v>0.5810797674843646</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4029910332809684</v>
+        <v>0.402991033280968</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4323324531943274</v>
+        <v>0.4323324531943266</v>
       </c>
       <c r="S7" t="n">
-        <v>0.583108675128385</v>
+        <v>0.5831086751283864</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4514759242421738</v>
+        <v>0.4514759242421736</v>
       </c>
       <c r="U7" t="n">
-        <v>0.621234101994569</v>
+        <v>0.6212341019945682</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5209675255675544</v>
+        <v>0.5209675255675543</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6517146825866871</v>
+        <v>0.6517146825866873</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6807818306567429</v>
+        <v>0.6807818306567436</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7633921367478878</v>
+        <v>0.7633921367478896</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4698520250720746</v>
+        <v>0.469852025072075</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5751058505806155</v>
+        <v>0.5751058505806159</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7206608323187846</v>
+        <v>0.7206608323187841</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5031824745558054</v>
+        <v>0.5031824745558039</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5087770116530119</v>
+        <v>0.5087770116530134</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6223465650605324</v>
+        <v>0.6223465650605297</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4230907786740735</v>
+        <v>0.4230907786740732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4548891334033431</v>
+        <v>0.4548891334033425</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7973099192868132</v>
+        <v>0.7973099192868122</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5998778344039322</v>
+        <v>0.5998778344039338</v>
       </c>
       <c r="I8" t="n">
-        <v>0.558681253291019</v>
+        <v>0.5586812532910195</v>
       </c>
       <c r="J8" t="n">
-        <v>0.69764693455947</v>
+        <v>0.697646934559469</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6692272365393986</v>
+        <v>0.6692272365394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7295259784382455</v>
+        <v>0.7295259784382466</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7987213154502416</v>
+        <v>0.7987213154502435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5234829289067806</v>
+        <v>0.5234829289067792</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5100168664113611</v>
+        <v>0.5100168664113622</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6542428595073024</v>
+        <v>0.6542428595073008</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4199899309865442</v>
+        <v>0.4199899309865465</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5640803077990481</v>
+        <v>0.5640803077990477</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7148565297331074</v>
+        <v>0.7148565297331081</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5832237788468945</v>
+        <v>0.5832237788468946</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7065913603257187</v>
+        <v>0.7065913603257161</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6261842863117271</v>
+        <v>0.626184286311726</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7834813846388075</v>
+        <v>0.7834813846388072</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7065703391126047</v>
+        <v>0.7065703391126066</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9899974483483718</v>
+        <v>0.9899974483483712</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5039164294654718</v>
+        <v>0.5039164294654725</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7068537051853367</v>
+        <v>0.7068537051853357</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9525863669484875</v>
+        <v>0.9525863669484879</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6616501779456397</v>
+        <v>0.6616501779456395</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6569094306044877</v>
+        <v>0.6569094306044888</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7704789840120045</v>
+        <v>0.7704789840120047</v>
       </c>
       <c r="E9" t="n">
         <v>0.6025397465519579</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4867284689520734</v>
+        <v>0.4867284689520738</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9255564365832702</v>
+        <v>0.9255564365832706</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7480102533554076</v>
+        <v>0.7480102533554074</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7068136722424959</v>
+        <v>0.7068136722424953</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8457793535109432</v>
+        <v>0.8457793535109419</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8173596554908739</v>
+        <v>0.8173596554908736</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8776583973897222</v>
+        <v>0.8776583973897227</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9468537344015118</v>
+        <v>0.9468537344015119</v>
       </c>
       <c r="N9" t="n">
-        <v>0.745955458157872</v>
+        <v>0.7459554581578723</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7404168018174346</v>
+        <v>0.7404168018174343</v>
       </c>
       <c r="P9" t="n">
         <v>0.8958176090961827</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6828713139640038</v>
+        <v>0.6828713139640045</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7122127267505218</v>
+        <v>0.7122127267505228</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8629889486845819</v>
+        <v>0.8629889486845808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7313561977983686</v>
+        <v>0.7313561977983697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9018220617410294</v>
+        <v>0.9018220617410302</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8995898840512728</v>
+        <v>0.8995898840512717</v>
       </c>
       <c r="W9" t="n">
         <v>0.9315949561428842</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9606621042129364</v>
+        <v>0.9606621042129396</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.043272410304087</v>
+        <v>1.043272410304086</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6981431682389081</v>
+        <v>0.6981431682389088</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8549861241368106</v>
+        <v>0.8549861241368111</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.000541105874983</v>
+        <v>1.000541105874982</v>
       </c>
     </row>
   </sheetData>
@@ -4892,31 +4892,31 @@
         <v>2.631709186067934</v>
       </c>
       <c r="D2" t="n">
-        <v>2.612797427233207</v>
+        <v>2.612797427233206</v>
       </c>
       <c r="E2" t="n">
-        <v>2.603529189250944</v>
+        <v>2.603529189250943</v>
       </c>
       <c r="F2" t="n">
         <v>2.603724332808019</v>
       </c>
       <c r="G2" t="n">
-        <v>2.616104402181124</v>
+        <v>2.616104402181125</v>
       </c>
       <c r="H2" t="n">
-        <v>2.608107059996717</v>
+        <v>2.608107059996716</v>
       </c>
       <c r="I2" t="n">
-        <v>2.608019723056409</v>
+        <v>2.60801972305641</v>
       </c>
       <c r="J2" t="n">
-        <v>2.612449863941507</v>
+        <v>2.612449863941506</v>
       </c>
       <c r="K2" t="n">
         <v>2.613046955593907</v>
       </c>
       <c r="L2" t="n">
-        <v>2.605564290172252</v>
+        <v>2.605564290172253</v>
       </c>
       <c r="M2" t="n">
         <v>2.617500101956755</v>
@@ -4928,19 +4928,19 @@
         <v>2.84741789980326</v>
       </c>
       <c r="P2" t="n">
-        <v>2.607489844775565</v>
+        <v>2.607489844775564</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.606977665434417</v>
+        <v>2.606977665434418</v>
       </c>
       <c r="R2" t="n">
         <v>2.59276795069034</v>
       </c>
       <c r="S2" t="n">
-        <v>2.609641493071008</v>
+        <v>2.609641493071009</v>
       </c>
       <c r="T2" t="n">
-        <v>2.606414000842314</v>
+        <v>2.606414000842315</v>
       </c>
       <c r="U2" t="n">
         <v>3.007980459353699</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.710715210052923</v>
+        <v>0.5665067105740583</v>
       </c>
       <c r="C3" t="n">
-        <v>1.742096449244728</v>
+        <v>0.5974891051574704</v>
       </c>
       <c r="D3" t="n">
-        <v>1.749622832506326</v>
+        <v>0.6068041476068686</v>
       </c>
       <c r="E3" t="n">
-        <v>1.68334494532479</v>
+        <v>0.5381691344187821</v>
       </c>
       <c r="F3" t="n">
-        <v>1.684741381367997</v>
+        <v>0.5396188254949599</v>
       </c>
       <c r="G3" t="n">
-        <v>1.772424522334517</v>
+        <v>0.6303984858322973</v>
       </c>
       <c r="H3" t="n">
-        <v>1.716171237865246</v>
+        <v>0.5721692366058242</v>
       </c>
       <c r="I3" t="n">
-        <v>1.715479324999793</v>
+        <v>0.5714494945726111</v>
       </c>
       <c r="J3" t="n">
-        <v>1.746729894688288</v>
+        <v>0.603800999076991</v>
       </c>
       <c r="K3" t="n">
-        <v>1.751091485065549</v>
+        <v>0.6083327744245848</v>
       </c>
       <c r="L3" t="n">
-        <v>1.697816885749539</v>
+        <v>0.5531568789452922</v>
       </c>
       <c r="M3" t="n">
-        <v>1.784189554199405</v>
+        <v>0.6426339031512442</v>
       </c>
       <c r="N3" t="n">
-        <v>1.726543524716196</v>
+        <v>0.5829028375493693</v>
       </c>
       <c r="O3" t="n">
-        <v>2.099269456388402</v>
+        <v>0.9547091345398065</v>
       </c>
       <c r="P3" t="n">
-        <v>1.711497962668537</v>
+        <v>0.5673144043598169</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.707928879708601</v>
+        <v>0.563630153796202</v>
       </c>
       <c r="R3" t="n">
-        <v>1.606179306999799</v>
+        <v>0.4582634692112388</v>
       </c>
       <c r="S3" t="n">
-        <v>1.726590315558146</v>
+        <v>0.582951307385683</v>
       </c>
       <c r="T3" t="n">
-        <v>1.703945020422625</v>
+        <v>0.5595057889739735</v>
       </c>
       <c r="U3" t="n">
-        <v>2.449916108815761</v>
+        <v>1.309293550466883</v>
       </c>
       <c r="V3" t="n">
-        <v>1.708524650582688</v>
+        <v>0.5642405463266704</v>
       </c>
       <c r="W3" t="n">
-        <v>2.517511470317076</v>
+        <v>1.380516004749474</v>
       </c>
       <c r="X3" t="n">
-        <v>1.793899911994487</v>
+        <v>0.6526525512245807</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.733232792842925</v>
+        <v>0.5898261693650177</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.952832948221814</v>
+        <v>0.8086834846094677</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8055764414896</v>
+        <v>0.6647241058040985</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.775347519489866</v>
+        <v>0.6334344409479657</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1722741691888616</v>
+        <v>0.1722741691888618</v>
       </c>
       <c r="C4" t="n">
-        <v>0.153905476978125</v>
+        <v>0.1539054769781236</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2334389476918832</v>
+        <v>0.2334389476918821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1287499360821292</v>
+        <v>0.1287499360821281</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1309541723297706</v>
+        <v>0.1309541723297686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2707927510122521</v>
+        <v>0.2707927510122493</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1804590920802079</v>
+        <v>0.1804590920802072</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1794725811624747</v>
+        <v>0.1794725811624731</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2292074845053215</v>
+        <v>0.2292074845053214</v>
       </c>
       <c r="K4" t="n">
-        <v>0.236257485314725</v>
+        <v>0.2362574853147237</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1517373371809886</v>
+        <v>0.1517373371809879</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2890131964298719</v>
+        <v>0.2890131964298716</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1971595454760469</v>
+        <v>0.1971595454760474</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1564089582570534</v>
+        <v>0.1564089582570529</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1734873622243033</v>
+        <v>0.173487362224304</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.167702060951896</v>
+        <v>0.1677020609518958</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007196796125784312</v>
+        <v>0.007196796125783354</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1977912195284282</v>
+        <v>0.1977912195284279</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1613352100855796</v>
+        <v>0.1613352100855776</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3286778953297822</v>
+        <v>0.3286778953297809</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1667534993776577</v>
+        <v>0.1667534993776581</v>
       </c>
       <c r="W4" t="n">
         <v>0.4952143175183372</v>
       </c>
       <c r="X4" t="n">
-        <v>0.303500204532726</v>
+        <v>0.3035002045327258</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.203231786951504</v>
+        <v>0.2032317869515027</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1748911078280687</v>
+        <v>0.1748911078280672</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3221983302511741</v>
+        <v>0.3221983302511733</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2736885606424468</v>
+        <v>0.2736885606424465</v>
       </c>
     </row>
     <row r="5">
@@ -5150,82 +5150,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.865813301909891</v>
+        <v>0.8658133019098903</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5962518295487782</v>
+        <v>0.5962518295487775</v>
       </c>
       <c r="D5" t="n">
-        <v>2.167235692344589</v>
+        <v>2.167235692344581</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1154801352995672</v>
+        <v>0.1154801352995651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1592080170208342</v>
+        <v>0.1592080170208345</v>
       </c>
       <c r="G5" t="n">
-        <v>2.428398472715358</v>
+        <v>2.42839847271537</v>
       </c>
       <c r="H5" t="n">
-        <v>1.178728586997883</v>
+        <v>1.178728586997874</v>
       </c>
       <c r="I5" t="n">
-        <v>1.121932159290451</v>
+        <v>1.121932159290449</v>
       </c>
       <c r="J5" t="n">
-        <v>1.863364161301649</v>
+        <v>1.863364161301652</v>
       </c>
       <c r="K5" t="n">
         <v>2.046873245325422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5208276748303189</v>
+        <v>0.5208276748303202</v>
       </c>
       <c r="M5" t="n">
         <v>3.034188607732593</v>
       </c>
       <c r="N5" t="n">
-        <v>1.394439314414711</v>
+        <v>1.394439314414721</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5868223345533756</v>
+        <v>0.5868223345533621</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8977592107856854</v>
+        <v>0.8977592107856879</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8364042274689902</v>
+        <v>0.836404227468986</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.384241254833486</v>
+        <v>-2.384241254833483</v>
       </c>
       <c r="S5" t="n">
-        <v>1.210432067061745</v>
+        <v>1.210432067061751</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7377342758963648</v>
+        <v>0.7377342758963634</v>
       </c>
       <c r="U5" t="n">
-        <v>3.775642270189544</v>
+        <v>3.775642270189531</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8022809624133618</v>
+        <v>0.8022809624133611</v>
       </c>
       <c r="W5" t="n">
-        <v>7.066993212668421</v>
+        <v>7.06699321266843</v>
       </c>
       <c r="X5" t="n">
-        <v>3.496836387101188</v>
+        <v>3.496836387101193</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.593649912955291</v>
+        <v>1.593649912955278</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8953620907424829</v>
+        <v>0.89536209074248</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.773683430275024</v>
+        <v>3.77368343027502</v>
       </c>
       <c r="AB5" t="n">
         <v>3.020840275453734</v>
@@ -5241,82 +5241,82 @@
         <v>0.1829796961400206</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1646110039292827</v>
+        <v>0.1646110039292829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2938068033776957</v>
+        <v>0.2938068033776944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1891177917679414</v>
+        <v>0.1891177917679403</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1416596992809288</v>
+        <v>0.1416596992809277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2814982779634087</v>
+        <v>0.2814982779634086</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2408269477660218</v>
+        <v>0.2408269477660198</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2398404368482867</v>
+        <v>0.2398404368482858</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2399130114564829</v>
+        <v>0.2399130114564805</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2966253410005382</v>
+        <v>0.2966253410005364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1624428641321458</v>
+        <v>0.162442864132147</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3493810521156848</v>
+        <v>0.349381052115684</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2080399988856333</v>
+        <v>0.2080399988856405</v>
       </c>
       <c r="O6" t="n">
-        <v>0.222196069913697</v>
+        <v>0.2221960699136948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2392200292421033</v>
+        <v>0.239220029242103</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2280699166377102</v>
+        <v>0.2280699166377086</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06756465181159743</v>
+        <v>0.06756465181159645</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2084967464795874</v>
+        <v>0.2084967464795867</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1720407370367366</v>
+        <v>0.1720407370367365</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3439008553910872</v>
+        <v>0.3439008553910862</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2271213550634699</v>
+        <v>0.2271213550634706</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5610193230077946</v>
+        <v>0.5610193230077933</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3142057314838851</v>
+        <v>0.3142057314838846</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2204354514575402</v>
+        <v>0.2204354514575417</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1855966347792267</v>
+        <v>0.1855966347792265</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3825661859369873</v>
+        <v>0.382566185936986</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2853971031238565</v>
+        <v>0.2853971031238539</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2454732008890199</v>
+        <v>0.2454732008890183</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2271045086782816</v>
+        <v>0.2271045086782802</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3066379793920398</v>
+        <v>0.3066379793920384</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2019489677822855</v>
+        <v>0.2019489677822844</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2041532040299263</v>
+        <v>0.2041532040299253</v>
       </c>
       <c r="G7" t="n">
-        <v>0.343991782712407</v>
+        <v>0.3439917827124058</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2536581237803643</v>
+        <v>0.2536581237803635</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2526716128626311</v>
+        <v>0.2526716128626295</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3024065162054792</v>
+        <v>0.3024065162054783</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3094565170148823</v>
+        <v>0.3094565170148807</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2249363688811458</v>
+        <v>0.224936368881145</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3622122281300292</v>
+        <v>0.3622122281300284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2703585771762045</v>
+        <v>0.2703585771762042</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2292506908776126</v>
+        <v>0.2292506908776107</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2463290948448628</v>
+        <v>0.2463290948448618</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2409010926520542</v>
+        <v>0.2409010926520524</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0803958278259421</v>
+        <v>0.08039582782594079</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2709902512285857</v>
+        <v>0.2709902512285844</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2345342417857343</v>
+        <v>0.234534241785734</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4052824005238171</v>
+        <v>0.4052824005238156</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2399525310778149</v>
+        <v>0.239952531077815</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5684133492184958</v>
+        <v>0.5684133492184938</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3766992362328843</v>
+        <v>0.3766992362328829</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.280948251761806</v>
+        <v>0.2809482517618044</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2480901395282254</v>
+        <v>0.2480901395282239</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3953973619513317</v>
+        <v>0.3953973619513301</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3468875923426039</v>
+        <v>0.3468875923426027</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2691395604506456</v>
+        <v>0.2691395604506446</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3289660437346944</v>
+        <v>0.3289660437346945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.408499514448453</v>
+        <v>0.4084995144484528</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2621738785059453</v>
+        <v>0.2621738785059455</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2400014580428148</v>
+        <v>0.2400014580428139</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4620675967989025</v>
+        <v>0.4620675967989016</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3555196588367787</v>
+        <v>0.3555196588367782</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3545331479190439</v>
+        <v>0.3545331479190432</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4042680512618932</v>
+        <v>0.4042680512618922</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4113180520712947</v>
+        <v>0.4113180520712948</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3267979039375575</v>
+        <v>0.3267979039375583</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4640737631866266</v>
+        <v>0.4640737631866265</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3116057694468049</v>
+        <v>0.3116057694468034</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2875125299152644</v>
+        <v>0.2875125299152645</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3005078154679581</v>
+        <v>0.3005078154679584</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2492003155180775</v>
+        <v>0.2492003155180758</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1822573628823551</v>
+        <v>0.1822573628823543</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3728517862849981</v>
+        <v>0.3728517862849982</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3363957768421483</v>
+        <v>0.3363957768421481</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4695050302874914</v>
+        <v>0.4695050302874897</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3197970804684138</v>
+        <v>0.3197970804684143</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6702902518359237</v>
+        <v>0.6702902518359229</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3921652022900499</v>
+        <v>0.3921652022900508</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4595569730859539</v>
+        <v>0.4595569730859524</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2703039835610028</v>
+        <v>0.2703039835610035</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.497258897007745</v>
+        <v>0.4972588970077441</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5304305267507468</v>
+        <v>0.5304305267507461</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4080770593694242</v>
+        <v>0.4080770593694229</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4621669670390532</v>
+        <v>0.4621669670390519</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5417004377528122</v>
+        <v>0.541700437752811</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4202882761410302</v>
+        <v>0.420288276141029</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2721788150310335</v>
+        <v>0.2721788150310323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5790542401594001</v>
+        <v>0.5790542401593989</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4887205821411385</v>
+        <v>0.4887205821411365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4877340712234033</v>
+        <v>0.4877340712234021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.537468974566251</v>
+        <v>0.5374689745662496</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5445189753756542</v>
+        <v>0.5445189753756527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4599988272419184</v>
+        <v>0.4599988272419172</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5972746864908024</v>
+        <v>0.5972746864908006</v>
       </c>
       <c r="N9" t="n">
-        <v>0.505421035536977</v>
+        <v>0.5054210355369757</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4886831322252914</v>
+        <v>0.48868313222529</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5109838831528399</v>
+        <v>0.5109838831528383</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4759635500990476</v>
+        <v>0.4759635500990461</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3154582861867135</v>
+        <v>0.3154582861867126</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5060527095893578</v>
+        <v>0.5060527095893563</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4695967001465067</v>
+        <v>0.4695967001465058</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6414568185008586</v>
+        <v>0.6414568185008567</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5586306030314163</v>
+        <v>0.5586306030314167</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8034758075792676</v>
+        <v>0.8034758075792661</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6117616945936551</v>
+        <v>0.6117616945936538</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5160107101225769</v>
+        <v>0.5160107101225772</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4394665050683813</v>
+        <v>0.4394665050683816</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6304598203121039</v>
+        <v>0.6304598203121026</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5819500507033769</v>
+        <v>0.5819500507033754</v>
       </c>
     </row>
   </sheetData>
@@ -5755,19 +5755,19 @@
         <v>2.59026590497706</v>
       </c>
       <c r="E2" t="n">
-        <v>2.571425869113112</v>
+        <v>2.571425869113111</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5742592223301</v>
+        <v>2.574259222330099</v>
       </c>
       <c r="G2" t="n">
         <v>2.596376206182956</v>
       </c>
       <c r="H2" t="n">
-        <v>2.588339760696088</v>
+        <v>2.588339760696087</v>
       </c>
       <c r="I2" t="n">
-        <v>2.585456862904623</v>
+        <v>2.585456862904622</v>
       </c>
       <c r="J2" t="n">
         <v>2.590125934180029</v>
@@ -5779,13 +5779,13 @@
         <v>2.570763668896675</v>
       </c>
       <c r="M2" t="n">
-        <v>2.586515632607682</v>
+        <v>2.586515632607683</v>
       </c>
       <c r="N2" t="n">
         <v>2.593658048516239</v>
       </c>
       <c r="O2" t="n">
-        <v>2.81574299684102</v>
+        <v>2.815742996841019</v>
       </c>
       <c r="P2" t="n">
         <v>2.578514970313353</v>
@@ -5797,7 +5797,7 @@
         <v>2.555334530998583</v>
       </c>
       <c r="S2" t="n">
-        <v>2.583350758721187</v>
+        <v>2.583350758721186</v>
       </c>
       <c r="T2" t="n">
         <v>2.582358142704383</v>
@@ -5806,25 +5806,25 @@
         <v>2.963574910947648</v>
       </c>
       <c r="V2" t="n">
-        <v>2.590693934375046</v>
+        <v>2.590693934375045</v>
       </c>
       <c r="W2" t="n">
         <v>2.95505953418782</v>
       </c>
       <c r="X2" t="n">
-        <v>2.623311659945407</v>
+        <v>2.623311659945406</v>
       </c>
       <c r="Y2" t="n">
         <v>2.598846766769229</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.726913032651643</v>
+        <v>2.726913032651644</v>
       </c>
       <c r="AA2" t="n">
         <v>2.613842824574037</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.587532346809149</v>
+        <v>2.587532346809148</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.608718503244394</v>
+        <v>0.4613260790616813</v>
       </c>
       <c r="C3" t="n">
-        <v>1.712318269819415</v>
+        <v>0.5671400946418738</v>
       </c>
       <c r="D3" t="n">
-        <v>1.691278337092102</v>
+        <v>0.546798544329805</v>
       </c>
       <c r="E3" t="n">
-        <v>1.556913450636073</v>
+        <v>0.4076828398218185</v>
       </c>
       <c r="F3" t="n">
-        <v>1.577030198380276</v>
+        <v>0.4284692914803493</v>
       </c>
       <c r="G3" t="n">
-        <v>1.734339291715073</v>
+        <v>0.5913773891880783</v>
       </c>
       <c r="H3" t="n">
-        <v>1.677571540058517</v>
+        <v>0.5326041967937253</v>
       </c>
       <c r="I3" t="n">
-        <v>1.656956648107838</v>
+        <v>0.5112547142677463</v>
       </c>
       <c r="J3" t="n">
-        <v>1.690153426011455</v>
+        <v>0.5456271042085689</v>
       </c>
       <c r="K3" t="n">
-        <v>1.657076153265413</v>
+        <v>0.5113761155273444</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55352679740213</v>
+        <v>0.4041335112529164</v>
       </c>
       <c r="M3" t="n">
-        <v>1.666392879493504</v>
+        <v>0.5210339714098549</v>
       </c>
       <c r="N3" t="n">
-        <v>1.715428722230024</v>
+        <v>0.5718036630285898</v>
       </c>
       <c r="O3" t="n">
-        <v>2.046354218205086</v>
+        <v>0.901081500701805</v>
       </c>
       <c r="P3" t="n">
-        <v>1.607717814195074</v>
+        <v>0.4602932779944635</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.677192115908466</v>
+        <v>0.5322106829341605</v>
       </c>
       <c r="R3" t="n">
-        <v>1.441395157131156</v>
+        <v>0.2880126987369397</v>
       </c>
       <c r="S3" t="n">
-        <v>1.642226697908719</v>
+        <v>0.4960036797210632</v>
       </c>
       <c r="T3" t="n">
-        <v>1.634933209559036</v>
+        <v>0.4884445125919507</v>
       </c>
       <c r="U3" t="n">
-        <v>2.302602644713655</v>
+        <v>1.157893724928285</v>
       </c>
       <c r="V3" t="n">
-        <v>1.694205544106299</v>
+        <v>0.5498230291841324</v>
       </c>
       <c r="W3" t="n">
-        <v>2.369531998247224</v>
+        <v>1.228558372696038</v>
       </c>
       <c r="X3" t="n">
-        <v>1.926651136566437</v>
+        <v>0.7905541779566589</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.752540045586657</v>
+        <v>0.6102220864695833</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.906834686947485</v>
+        <v>0.7618893302836671</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.859563481692463</v>
+        <v>0.7210256863554814</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.671536383950811</v>
+        <v>0.5263517397069203</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01565514295743418</v>
+        <v>0.01565514295743296</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1156741213949941</v>
+        <v>0.1156741213949938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1467378204471589</v>
+        <v>0.1467378204471594</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06606905148082962</v>
+        <v>-0.06606905148083021</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03406502348806666</v>
+        <v>-0.03406502348806685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2157564834451943</v>
+        <v>0.2157564834451942</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1249811347234342</v>
+        <v>0.1249811347234346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09241747797032476</v>
+        <v>0.0924174779703254</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1448806322625847</v>
+        <v>0.1448806322625866</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09242846787856202</v>
+        <v>0.09242846787856271</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07354890755258053</v>
+        <v>-0.07354890755257965</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1076606619891536</v>
+        <v>0.107660661989153</v>
       </c>
       <c r="N4" t="n">
-        <v>0.185053642185349</v>
+        <v>0.1850536421853499</v>
       </c>
       <c r="O4" t="n">
         <v>0.1114135240971107</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01400560772359378</v>
+        <v>0.0140056077235931</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1244492062269513</v>
+        <v>0.1244492062269506</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2478281178656667</v>
+        <v>-0.2478281178656652</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0686280623626426</v>
+        <v>0.06862806236264143</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05741600782690223</v>
+        <v>0.0574160078269033</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1322481150766047</v>
+        <v>0.1322481150766044</v>
       </c>
       <c r="V4" t="n">
         <v>0.1497261972435956</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3041222852355216</v>
+        <v>0.3041222852355215</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5200048246130025</v>
+        <v>0.520004824613002</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2391401791383086</v>
+        <v>0.2391401791383077</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1261934922190643</v>
+        <v>0.1261934922190631</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4130499732138858</v>
+        <v>0.4130499732138859</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1153853078937689</v>
+        <v>0.1153853078937688</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.501750716855047</v>
+        <v>-1.501750716855053</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1441682653016297</v>
+        <v>0.1441682653016302</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6793788776032347</v>
+        <v>0.6793788776032358</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.033992574751441</v>
+        <v>-3.03399257475144</v>
       </c>
       <c r="F5" t="n">
         <v>-2.522380472279613</v>
       </c>
       <c r="G5" t="n">
-        <v>1.615805469553945</v>
+        <v>1.61580546955395</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3154038130525527</v>
+        <v>0.3154038130525535</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2810115351491499</v>
+        <v>-0.2810115351491494</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5858781772531331</v>
+        <v>0.5858781772531367</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2224851839095737</v>
+        <v>-0.2224851839095733</v>
       </c>
       <c r="L5" t="n">
         <v>-2.472122805084197</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03809753340475708</v>
+        <v>0.03809753340475772</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32621661361057</v>
+        <v>1.326216613610575</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07646901283038755</v>
+        <v>0.07646901283038565</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.509381962453997</v>
+        <v>-1.509381962454001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2835439564470351</v>
+        <v>0.2835439564470337</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.597783535486068</v>
+        <v>-6.597783535486075</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5455631412593325</v>
+        <v>-0.5455631412593333</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8522474831640852</v>
+        <v>-0.8522474831640847</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4681775672221225</v>
+        <v>0.4681775672221247</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6968870519000254</v>
+        <v>0.6968870519000264</v>
       </c>
       <c r="W5" t="n">
-        <v>3.282176175981684</v>
+        <v>3.282176175981679</v>
       </c>
       <c r="X5" t="n">
-        <v>7.034338963267404</v>
+        <v>7.034338963267405</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.4038471110201</v>
+        <v>2.403847111020102</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3025054250235829</v>
+        <v>0.3025054250235817</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.397578164332334</v>
+        <v>5.397578164332328</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1383595599703015</v>
+        <v>0.1383595599703023</v>
       </c>
     </row>
     <row r="6">
@@ -6098,82 +6098,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05709098614735862</v>
+        <v>0.05709098614735904</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1184361585146754</v>
+        <v>0.1184361585146744</v>
       </c>
       <c r="D6" t="n">
         <v>0.1494998575668403</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06330701436115005</v>
+        <v>-0.06330701436115024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007370819701858364</v>
+        <v>0.007370819701858974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2571923266351208</v>
+        <v>0.2571923266351204</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1664169779133603</v>
+        <v>0.1664169779133599</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1338533211602516</v>
+        <v>0.1338533211602506</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1863164754525111</v>
+        <v>0.1863164754525107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1338643110684883</v>
+        <v>0.1338643110684881</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07078687043289916</v>
+        <v>-0.0707868704329</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1490965051790786</v>
+        <v>0.1490965051790784</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1887344129924487</v>
+        <v>0.1887344129924498</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1574787425601469</v>
+        <v>0.1574787425601493</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01648054009954387</v>
+        <v>0.01648054009954421</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1658850494168761</v>
+        <v>0.1658850494168763</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2450660807459843</v>
+        <v>-0.2450660807459853</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1100639055525671</v>
+        <v>0.1100639055525681</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06017804494658265</v>
+        <v>0.0601780449465824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.139532574839162</v>
+        <v>0.139532574839161</v>
       </c>
       <c r="V6" t="n">
-        <v>0.152488234363276</v>
+        <v>0.1524882343632757</v>
       </c>
       <c r="W6" t="n">
-        <v>0.310323017985291</v>
+        <v>0.3103230179852898</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5614406678029276</v>
+        <v>0.5614406678029255</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2486655576050942</v>
+        <v>0.2486655576050945</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1289555293387438</v>
+        <v>0.1289555293387436</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4544858164038121</v>
+        <v>0.4544858164038131</v>
       </c>
       <c r="AB6" t="n">
         <v>0.1193820058211484</v>
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07596050630900969</v>
+        <v>0.07596050630900843</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1759794847465707</v>
+        <v>0.1759794847465698</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2070431837987362</v>
+        <v>0.2070431837987347</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005763688129253583</v>
+        <v>-0.00576368812925343</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02624033986350938</v>
+        <v>0.0262403398635086</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2760618467967716</v>
+        <v>0.27606184679677</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1852864980750111</v>
+        <v>0.1852864980750097</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1527228413219026</v>
+        <v>0.1527228413219019</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2051859956141617</v>
+        <v>0.2051859956141616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1527338312301391</v>
+        <v>0.1527338312301388</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0132435442010042</v>
+        <v>-0.01324354420100421</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1679660253407288</v>
+        <v>0.1679660253407285</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2453590055369255</v>
+        <v>0.245359005536925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1713860531006023</v>
+        <v>0.171386053100602</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07397813672708525</v>
+        <v>0.07397813672708534</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.184754569578527</v>
+        <v>0.1847545695785259</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1875227545140886</v>
+        <v>-0.187522754514089</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1289334257142181</v>
+        <v>0.1289334257142171</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1177213711784795</v>
+        <v>0.1177213711784789</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1957578789328313</v>
+        <v>0.1957578789328308</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2100315605951719</v>
+        <v>0.210031560595172</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3644276485870974</v>
+        <v>0.3644276485870959</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5803101879645784</v>
+        <v>0.5803101879645796</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3039679651327613</v>
+        <v>0.3039679651327601</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1864988555706405</v>
+        <v>0.186498855570639</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4733553365654633</v>
+        <v>0.4733553365654616</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1756906712453451</v>
+        <v>0.1756906712453435</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08885017651771535</v>
+        <v>0.08885017651771401</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2477290011365304</v>
+        <v>0.2477290011365311</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2787927001886949</v>
+        <v>0.2787927001886961</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0346446964216555</v>
+        <v>0.03464469642165535</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04829968619887005</v>
+        <v>0.0482996861988698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3600163357294021</v>
+        <v>0.3600163357294019</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2570360144649705</v>
+        <v>0.2570360144649709</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2244723577118616</v>
+        <v>0.2244723577118624</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2769355120041206</v>
+        <v>0.2769355120041218</v>
       </c>
       <c r="K8" t="n">
-        <v>0.224483347620098</v>
+        <v>0.2244833476200989</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05850597218895595</v>
+        <v>0.05850597218895615</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2397155417306118</v>
+        <v>0.2397155417306117</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2714822941019514</v>
+        <v>0.2714822941019519</v>
       </c>
       <c r="O8" t="n">
         <v>0.2103806595948909</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1098992579223738</v>
+        <v>0.1098992579223735</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1860769365963976</v>
+        <v>0.1860769365963961</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1157732381241297</v>
+        <v>-0.1157732381241287</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2006829421041796</v>
+        <v>0.200682942104179</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1894708875684387</v>
+        <v>0.1894708875684384</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2393332157906202</v>
+        <v>0.2393332157906191</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2648516794015446</v>
+        <v>0.2648516794015445</v>
       </c>
       <c r="W8" t="n">
-        <v>0.436188732639866</v>
+        <v>0.4361887326398656</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5870271768516451</v>
+        <v>0.5870271768516453</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4329343667275891</v>
+        <v>0.4329343667275893</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1982951739152391</v>
+        <v>0.1982951739152387</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5451048529554224</v>
+        <v>0.5451048529554233</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3089242187699145</v>
+        <v>0.3089242187699161</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1976820781823088</v>
+        <v>0.1976820781823091</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3534180195438861</v>
+        <v>0.3534180195438845</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3844817185960507</v>
+        <v>0.3844817185960503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1588156061394956</v>
+        <v>0.1588156061394963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07523605621821697</v>
+        <v>0.07523605621821644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4535003910180437</v>
+        <v>0.4535003910180453</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3627250328723259</v>
+        <v>0.362725032872325</v>
       </c>
       <c r="I9" t="n">
-        <v>0.330161376119218</v>
+        <v>0.330161376119217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3826245304114747</v>
+        <v>0.3826245304114752</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3301723660274541</v>
+        <v>0.3301723660274531</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1641949905963112</v>
+        <v>0.1641949905963105</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3454045601380439</v>
+        <v>0.3454045601380443</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4227975403342401</v>
+        <v>0.4227975403342396</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3676219633509273</v>
+        <v>0.3676219633509267</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2742297658200079</v>
+        <v>0.2742297658200071</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3621931137998005</v>
+        <v>0.3621931137998015</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.01008421971677377</v>
+        <v>-0.01008421971677484</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3063719605115334</v>
+        <v>0.3063719605115324</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2951599059757941</v>
+        <v>0.2951599059757934</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3745144358683726</v>
+        <v>0.374514435868372</v>
       </c>
       <c r="V9" t="n">
-        <v>0.451766285487654</v>
+        <v>0.4517662854876544</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5418661833844135</v>
+        <v>0.5418661833844117</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7577487227618941</v>
+        <v>0.7577487227618932</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4814064999300762</v>
+        <v>0.4814064999300756</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3303450200125766</v>
+        <v>0.3303450200125769</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.650793871362778</v>
+        <v>0.6507938713627762</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3531292060426603</v>
+        <v>0.353129206042659</v>
       </c>
     </row>
   </sheetData>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.564359330297209</v>
+        <v>2.564359330297208</v>
       </c>
       <c r="C2" t="n">
         <v>2.598751460949112</v>
@@ -6615,16 +6615,16 @@
         <v>2.578607554120204</v>
       </c>
       <c r="E2" t="n">
-        <v>2.562390780005894</v>
+        <v>2.562390780005893</v>
       </c>
       <c r="F2" t="n">
-        <v>2.569774360814613</v>
+        <v>2.569774360814612</v>
       </c>
       <c r="G2" t="n">
-        <v>2.587857784515264</v>
+        <v>2.587857784515265</v>
       </c>
       <c r="H2" t="n">
-        <v>2.583284444930315</v>
+        <v>2.583284444930316</v>
       </c>
       <c r="I2" t="n">
         <v>2.581323372700667</v>
@@ -6636,16 +6636,16 @@
         <v>2.579992904057874</v>
       </c>
       <c r="L2" t="n">
-        <v>2.560380436534943</v>
+        <v>2.560380436534944</v>
       </c>
       <c r="M2" t="n">
         <v>2.581568990664744</v>
       </c>
       <c r="N2" t="n">
-        <v>2.588344577266613</v>
+        <v>2.588344577266614</v>
       </c>
       <c r="O2" t="n">
-        <v>2.79359788084947</v>
+        <v>2.793597880849471</v>
       </c>
       <c r="P2" t="n">
         <v>2.569302579523268</v>
@@ -6654,7 +6654,7 @@
         <v>2.582095355797241</v>
       </c>
       <c r="R2" t="n">
-        <v>2.549652462379305</v>
+        <v>2.549652462379306</v>
       </c>
       <c r="S2" t="n">
         <v>2.573082737635414</v>
@@ -6666,25 +6666,25 @@
         <v>2.951968020640662</v>
       </c>
       <c r="V2" t="n">
-        <v>2.585454671792825</v>
+        <v>2.585454671792824</v>
       </c>
       <c r="W2" t="n">
-        <v>2.940460515067921</v>
+        <v>2.940460515067922</v>
       </c>
       <c r="X2" t="n">
         <v>2.627945092346373</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.588951665718125</v>
+        <v>2.588951665718124</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.708557277297916</v>
+        <v>2.708557277297917</v>
       </c>
       <c r="AA2" t="n">
         <v>2.611284128089</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.582237226656121</v>
+        <v>2.58223722665612</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.549401399883442</v>
+        <v>0.4000487489435975</v>
       </c>
       <c r="C3" t="n">
-        <v>1.666693312121107</v>
+        <v>0.5201036335509608</v>
       </c>
       <c r="D3" t="n">
-        <v>1.650564420097018</v>
+        <v>0.5047654762661968</v>
       </c>
       <c r="E3" t="n">
-        <v>1.535360017446926</v>
+        <v>0.3854821842279328</v>
       </c>
       <c r="F3" t="n">
-        <v>1.587368581725817</v>
+        <v>0.4393127708688767</v>
       </c>
       <c r="G3" t="n">
-        <v>1.716246480356889</v>
+        <v>0.5727700519118938</v>
       </c>
       <c r="H3" t="n">
-        <v>1.683995785404143</v>
+        <v>0.5393887022506931</v>
       </c>
       <c r="I3" t="n">
-        <v>1.669940656536009</v>
+        <v>0.5248315941548717</v>
       </c>
       <c r="J3" t="n">
-        <v>1.673886330969188</v>
+        <v>0.5289141390947195</v>
       </c>
       <c r="K3" t="n">
-        <v>1.660469995319348</v>
+        <v>0.5150231503674257</v>
       </c>
       <c r="L3" t="n">
-        <v>1.521689244342171</v>
+        <v>0.3713094579763085</v>
       </c>
       <c r="M3" t="n">
-        <v>1.672959337034219</v>
+        <v>0.5279653733874726</v>
       </c>
       <c r="N3" t="n">
-        <v>1.720020866782082</v>
+        <v>0.5766865010052959</v>
       </c>
       <c r="O3" t="n">
-        <v>1.98133869312341</v>
+        <v>0.8344377270489746</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58464375100181</v>
+        <v>0.4365327407240328</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.675425488803657</v>
+        <v>0.5305114190374638</v>
       </c>
       <c r="R3" t="n">
-        <v>1.443158970122587</v>
+        <v>0.289975881393761</v>
       </c>
       <c r="S3" t="n">
-        <v>1.611462500318807</v>
+        <v>0.4642849293264363</v>
       </c>
       <c r="T3" t="n">
-        <v>1.642397651338528</v>
+        <v>0.4963083387392141</v>
       </c>
       <c r="U3" t="n">
-        <v>2.290344086806488</v>
+        <v>1.145629852752289</v>
       </c>
       <c r="V3" t="n">
-        <v>1.699241954567052</v>
+        <v>0.5551656390818641</v>
       </c>
       <c r="W3" t="n">
-        <v>2.340391999027514</v>
+        <v>1.198858005503273</v>
       </c>
       <c r="X3" t="n">
-        <v>2.001767613486186</v>
+        <v>0.8684858772777715</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.724419348937585</v>
+        <v>0.5812349690652845</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.851469615966443</v>
+        <v>0.7050460583978431</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.883817167139157</v>
+        <v>0.7462640922512145</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.675694491116197</v>
+        <v>0.5307845103749096</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07621152159661716</v>
+        <v>-0.07621152159661804</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04948593251348681</v>
+        <v>0.04948593251348592</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08472872099088417</v>
+        <v>0.08472872099088391</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09844720271491161</v>
+        <v>-0.09844720271491021</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01504626086545037</v>
+        <v>-0.01504626086545219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1892143286192829</v>
+        <v>0.1892143286192823</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1375563541671707</v>
+        <v>0.1375563541671711</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1154051411954715</v>
+        <v>0.1154051411954716</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1214379939518985</v>
+        <v>0.1214379939518983</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1003768858293588</v>
+        <v>0.1003768858293585</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1211549570229961</v>
+        <v>-0.1211549570229976</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1204949082387049</v>
+        <v>0.120494908238704</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1947128766815314</v>
+        <v>0.194712876681529</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03446610838965625</v>
+        <v>0.0344661083896563</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.02037524758129934</v>
+        <v>-0.02037524758129961</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1241250454010459</v>
+        <v>0.1241250454010443</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.242332360222851</v>
+        <v>-0.2423323602228514</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02232337725405933</v>
+        <v>0.02232337725405865</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07183700934519811</v>
+        <v>0.07183700934519639</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1280462181297166</v>
+        <v>0.1280462181297161</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1604025055996242</v>
+        <v>0.1604025055996244</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2756863622241737</v>
+        <v>0.2756863622241734</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6420189116443702</v>
+        <v>0.6420189116443696</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1964019128025098</v>
+        <v>0.1964019128025082</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05617566987452353</v>
+        <v>0.0561756698745227</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.453825655935133</v>
+        <v>0.4538256559351313</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1242676565416881</v>
+        <v>0.1242676565416889</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.897002139392414</v>
+        <v>-2.897002139392419</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9315370349727344</v>
+        <v>-0.9315370349727353</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3237493409940608</v>
+        <v>-0.3237493409940606</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.285996767439753</v>
+        <v>-3.285996767439747</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.167669741303436</v>
+        <v>-2.167669741303441</v>
       </c>
       <c r="G5" t="n">
-        <v>1.349456342347001</v>
+        <v>1.349456342347003</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6376263895462891</v>
+        <v>0.6376263895462901</v>
       </c>
       <c r="I5" t="n">
-        <v>0.215343655771582</v>
+        <v>0.2153436557715822</v>
       </c>
       <c r="J5" t="n">
-        <v>0.313783855421782</v>
+        <v>0.3137838554217808</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03752104770857584</v>
+        <v>-0.03752104770857645</v>
       </c>
       <c r="L5" t="n">
         <v>-3.336705826939609</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3093497704758648</v>
+        <v>0.309349770475864</v>
       </c>
       <c r="N5" t="n">
-        <v>1.602238015853775</v>
+        <v>1.602238015853779</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.053812150032608</v>
+        <v>-1.05381215003261</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.929068093747658</v>
+        <v>-1.929068093747664</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3566918863483195</v>
+        <v>0.35669188634832</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.497818782328064</v>
+        <v>-6.497818782328072</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.257009984999161</v>
+        <v>-1.257009984999162</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5627082482931587</v>
+        <v>-0.562708248293161</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4878358277855278</v>
+        <v>0.4878358277855282</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9436743534997323</v>
+        <v>0.9436743534997321</v>
       </c>
       <c r="W5" t="n">
-        <v>2.935579310530637</v>
+        <v>2.935579310530633</v>
       </c>
       <c r="X5" t="n">
-        <v>9.055419062854943</v>
+        <v>9.055419062854938</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.757548916231566</v>
+        <v>1.757548916231565</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.6898657377904259</v>
+        <v>-0.6898657377904291</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.224243832723911</v>
+        <v>6.224243832723917</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3849429989463249</v>
+        <v>0.3849429989463251</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04008485598512593</v>
+        <v>-0.0400848559851258</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08561259812497783</v>
+        <v>0.08561259812497864</v>
       </c>
       <c r="D6" t="n">
-        <v>0.120855386602377</v>
+        <v>0.1208553866023764</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.09694745260795408</v>
+        <v>-0.09694745260795395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02108040474604102</v>
+        <v>0.02108040474604099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2253409942307736</v>
+        <v>0.2253409942307742</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1736830197786631</v>
+        <v>0.1736830197786625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1515318068069646</v>
+        <v>0.1515318068069637</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1229377440588551</v>
+        <v>0.1229377440588557</v>
       </c>
       <c r="K6" t="n">
-        <v>0.101876635936316</v>
+        <v>0.1018766359363151</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.08502829141150545</v>
+        <v>-0.08502829141150531</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1566215738501959</v>
+        <v>0.1566215738501961</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1973358844106084</v>
+        <v>0.1973358844106078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03720176839882328</v>
+        <v>0.03720176839882239</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02042436584179209</v>
+        <v>0.02042436584179057</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1602517110125365</v>
+        <v>0.1602517110125362</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2062056946113592</v>
+        <v>-0.2062056946113587</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05845004286555054</v>
+        <v>0.05845004286554992</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07333675945215447</v>
+        <v>0.07333675945215498</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1693411909545358</v>
+        <v>0.1693411909545354</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1619022557065816</v>
+        <v>0.161902255706582</v>
       </c>
       <c r="W6" t="n">
-        <v>0.31658709221894</v>
+        <v>0.3165870922189386</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6435186617513282</v>
+        <v>0.6435186617513268</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2054825931282646</v>
+        <v>0.2054825931282633</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05767541998148035</v>
+        <v>0.05767541998148017</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4899523215466244</v>
+        <v>0.4899523215466247</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1272732020308294</v>
+        <v>0.1272732020308286</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01873213406075594</v>
+        <v>-0.01873213406075602</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1069653200493471</v>
+        <v>0.1069653200493483</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1422081085267456</v>
+        <v>0.1422081085267465</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04096781517905067</v>
+        <v>-0.04096781517905286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04243312667041046</v>
+        <v>0.0424331266704088</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2466937161551431</v>
+        <v>0.2466937161551422</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1950357417030323</v>
+        <v>0.1950357417030308</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1728845287313334</v>
+        <v>0.1728845287313344</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1789173814877586</v>
+        <v>0.1789173814877589</v>
       </c>
       <c r="K7" t="n">
         <v>0.1578562733652187</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06367556948713599</v>
+        <v>-0.06367556948713508</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1779742957745649</v>
+        <v>0.1779742957745656</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2521922642173912</v>
+        <v>0.2521922642173902</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09161282731248929</v>
+        <v>0.09161282731248822</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03677147134153299</v>
+        <v>0.03677147134153261</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1816044329369058</v>
+        <v>0.1816044329369059</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.184852972686991</v>
+        <v>-0.1848529726869899</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07980276478991996</v>
+        <v>0.07980276478992046</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1293163968810576</v>
+        <v>0.1293163968810574</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1890829176829128</v>
+        <v>0.1890829176829112</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2178818931354849</v>
+        <v>0.2178818931354854</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3331657497600349</v>
+        <v>0.3331657497600352</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6994982991802292</v>
+        <v>0.6994982991802319</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2590496075516979</v>
+        <v>0.2590496075516975</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1136550574103844</v>
+        <v>0.1136550574103846</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.511305043470994</v>
+        <v>0.511305043470995</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1817470440775494</v>
+        <v>0.1817470440775503</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.008923999051033221</v>
+        <v>-0.008923999051033971</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1705154004142396</v>
+        <v>0.1705154004142383</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2057581888916367</v>
+        <v>0.2057581888916369</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.006033735437104719</v>
+        <v>-0.006033735437105413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06061362867509841</v>
+        <v>0.06061362867509817</v>
       </c>
       <c r="G8" t="n">
-        <v>0.321387538988313</v>
+        <v>0.321387538988311</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2585858220679229</v>
+        <v>0.2585858220679228</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2364346090962243</v>
+        <v>0.2364346090962242</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2424674618526513</v>
+        <v>0.2424674618526505</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2214063537301119</v>
+        <v>0.2214063537301113</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.000125489122243333</v>
+        <v>-0.0001254891222437354</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2415243761392361</v>
+        <v>0.2415243761392348</v>
       </c>
       <c r="N8" t="n">
-        <v>0.274083346110228</v>
+        <v>0.2740833461102273</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1252848323394647</v>
+        <v>0.1252848323394639</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06763723255438489</v>
+        <v>0.06763723255438421</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.180851049071654</v>
+        <v>0.1808510490716536</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1213028923220981</v>
+        <v>-0.121302892322099</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1433528451548114</v>
+        <v>0.1433528451548119</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1928664772459508</v>
+        <v>0.1928664772459501</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2270225953053953</v>
+        <v>0.2270225953053946</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2656508076131927</v>
+        <v>0.265650807613193</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3967263919987717</v>
+        <v>0.3967263919987716</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7036704714195113</v>
+        <v>0.7036704714195099</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3743393298687848</v>
+        <v>0.3743393298687846</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1224649081891581</v>
+        <v>0.1224649081891564</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5748551238358861</v>
+        <v>0.5748551238358843</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3014350802361302</v>
+        <v>0.3014350802361293</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08702088114165465</v>
+        <v>0.08702088114165291</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2626437699142882</v>
+        <v>0.2626437699142892</v>
       </c>
       <c r="D9" t="n">
-        <v>0.297886558391687</v>
+        <v>0.2978865583916875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1031880341128254</v>
+        <v>0.1031880341128256</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08301984727310044</v>
+        <v>0.08301984727309794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4023721479558447</v>
+        <v>0.4023721479558451</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3507141915679725</v>
+        <v>0.3507141915679714</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3285629785962743</v>
+        <v>0.3285629785962749</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3345958313526998</v>
+        <v>0.3345958313526991</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3135347232301604</v>
+        <v>0.3135347232301599</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09200288037780427</v>
+        <v>0.09200288037780432</v>
       </c>
       <c r="M9" t="n">
-        <v>0.333652745639506</v>
+        <v>0.3336527456395073</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4078707140823314</v>
+        <v>0.4078707140823317</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2641691454151326</v>
+        <v>0.2641691454151329</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2129260904233848</v>
+        <v>0.2129260904233849</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3372828647376074</v>
+        <v>0.3372828647376067</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02917452282205031</v>
+        <v>-0.02917452282204892</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2354812146548608</v>
+        <v>0.235481214654861</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2849948467460012</v>
+        <v>0.2849948467459988</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3463723627438456</v>
+        <v>0.3463723627438442</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4311732071350701</v>
+        <v>0.4311732071350708</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4888441996249747</v>
+        <v>0.4888441996249765</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8551767490451729</v>
+        <v>0.8551767490451725</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4147280574166388</v>
+        <v>0.414728057416638</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2392329025435754</v>
+        <v>0.2392329025435744</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.666983493335934</v>
+        <v>0.6669834933359351</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3374254939424912</v>
+        <v>0.3374254939424916</v>
       </c>
     </row>
   </sheetData>
@@ -7475,13 +7475,13 @@
         <v>2.659022309050841</v>
       </c>
       <c r="E2" t="n">
-        <v>2.645977523593751</v>
+        <v>2.64597752359375</v>
       </c>
       <c r="F2" t="n">
         <v>2.646169981595669</v>
       </c>
       <c r="G2" t="n">
-        <v>2.681225717457044</v>
+        <v>2.681225717457045</v>
       </c>
       <c r="H2" t="n">
         <v>2.661438787827616</v>
@@ -7496,10 +7496,10 @@
         <v>2.655825056241796</v>
       </c>
       <c r="L2" t="n">
-        <v>2.673713583224995</v>
+        <v>2.673713583224993</v>
       </c>
       <c r="M2" t="n">
-        <v>2.685207597891295</v>
+        <v>2.685207597891296</v>
       </c>
       <c r="N2" t="n">
         <v>2.659913782881515</v>
@@ -7511,7 +7511,7 @@
         <v>2.660777707085117</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.650980674499967</v>
+        <v>2.650980674499966</v>
       </c>
       <c r="R2" t="n">
         <v>2.643236428114744</v>
@@ -7523,7 +7523,7 @@
         <v>2.650072842665061</v>
       </c>
       <c r="U2" t="n">
-        <v>3.065784845837005</v>
+        <v>3.065784845837004</v>
       </c>
       <c r="V2" t="n">
         <v>2.650327180623413</v>
@@ -7532,7 +7532,7 @@
         <v>3.04848096613748</v>
       </c>
       <c r="X2" t="n">
-        <v>2.667047845231265</v>
+        <v>2.667047845231264</v>
       </c>
       <c r="Y2" t="n">
         <v>2.663822725424409</v>
@@ -7541,10 +7541,10 @@
         <v>2.80938478224945</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.666321874895606</v>
+        <v>2.666321874895605</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.683872881713747</v>
+        <v>2.683872881713748</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.825363470992804</v>
+        <v>0.6842541941661949</v>
       </c>
       <c r="C3" t="n">
-        <v>1.785416377748951</v>
+        <v>0.6412493943902149</v>
       </c>
       <c r="D3" t="n">
-        <v>1.842483962252721</v>
+        <v>0.7020139290910754</v>
       </c>
       <c r="E3" t="n">
-        <v>1.748986758801234</v>
+        <v>0.6051876128786339</v>
       </c>
       <c r="F3" t="n">
-        <v>1.750473540535261</v>
+        <v>0.6067463981464857</v>
       </c>
       <c r="G3" t="n">
-        <v>1.999068529579979</v>
+        <v>0.8640845756592573</v>
       </c>
       <c r="H3" t="n">
-        <v>1.860100493657919</v>
+        <v>0.7202795524597764</v>
       </c>
       <c r="I3" t="n">
-        <v>1.764578249622978</v>
+        <v>0.6213478568325873</v>
       </c>
       <c r="J3" t="n">
-        <v>1.897980047276503</v>
+        <v>0.7594535033520344</v>
       </c>
       <c r="K3" t="n">
-        <v>1.818989932353857</v>
+        <v>0.6777026195047352</v>
       </c>
       <c r="L3" t="n">
-        <v>1.946454007858898</v>
+        <v>0.809638055265428</v>
       </c>
       <c r="M3" t="n">
-        <v>2.02911781695359</v>
+        <v>0.8953594595335964</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84862259534267</v>
+        <v>0.708358575666273</v>
       </c>
       <c r="O3" t="n">
-        <v>2.259159148231962</v>
+        <v>1.117701452847592</v>
       </c>
       <c r="P3" t="n">
-        <v>1.854155002603524</v>
+        <v>0.7140430598296806</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.784717190812516</v>
+        <v>0.6421985313702354</v>
       </c>
       <c r="R3" t="n">
-        <v>1.729503576045277</v>
+        <v>0.5850272693968334</v>
       </c>
       <c r="S3" t="n">
-        <v>1.856120654195631</v>
+        <v>0.7161166116894947</v>
       </c>
       <c r="T3" t="n">
-        <v>1.778412251596523</v>
+        <v>0.6356710872781413</v>
       </c>
       <c r="U3" t="n">
-        <v>2.578443853167906</v>
+        <v>1.440917106594371</v>
       </c>
       <c r="V3" t="n">
-        <v>1.779700740290739</v>
+        <v>0.6369895936616078</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5658833448427</v>
+        <v>1.429093146250606</v>
       </c>
       <c r="X3" t="n">
-        <v>1.899728872296147</v>
+        <v>0.76129044358008</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.876282609543943</v>
+        <v>0.7369970616351518</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.064495670147621</v>
+        <v>0.9228003905360703</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.894211655937496</v>
+        <v>0.7555518230998053</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.019077124578199</v>
+        <v>0.8848362384286819</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3398214111441169</v>
+        <v>0.3398214111441124</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2010964229896563</v>
+        <v>0.2010964229896566</v>
       </c>
       <c r="D4" t="n">
         <v>0.3654937403232396</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2181468876876101</v>
+        <v>0.2181468876876092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2203207893542926</v>
+        <v>0.2203207893542931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6162914523438012</v>
+        <v>0.6162914523438018</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3927889797420412</v>
+        <v>0.3927889797420417</v>
       </c>
       <c r="I4" t="n">
         <v>0.2425561623875468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4545146753028759</v>
+        <v>0.4545146753028761</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3293792990361028</v>
+        <v>0.3293792990361037</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5314384404403019</v>
+        <v>0.5314384404402922</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6621254339452989</v>
+        <v>0.6621254339452993</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3755633473388927</v>
+        <v>0.375563347338893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3242590313866743</v>
+        <v>0.3242590313866744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3853217686433494</v>
+        <v>0.3853217686433483</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2746597787364436</v>
+        <v>0.2746597787364438</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1871849532859723</v>
+        <v>0.1871849532859725</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3890448287059342</v>
+        <v>0.3890448287059334</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2644054005379025</v>
+        <v>0.2644054005379027</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4962240038046267</v>
+        <v>0.4962240038046256</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2646028706885743</v>
+        <v>0.2646028706885745</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5319738472253482</v>
+        <v>0.5319738472253479</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4561458634101432</v>
+        <v>0.4561458634101399</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4160737902837643</v>
+        <v>0.4160737902837649</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3131782681275423</v>
+        <v>0.3131782681275409</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.447945694506023</v>
+        <v>0.4479456945060231</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6424628552874088</v>
+        <v>0.64246285528741</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.262224930850606</v>
+        <v>3.26222493085057</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9433476989905724</v>
+        <v>0.9433476989905729</v>
       </c>
       <c r="D5" t="n">
-        <v>4.247837952966089</v>
+        <v>4.247837952966086</v>
       </c>
       <c r="E5" t="n">
-        <v>1.241626303628959</v>
+        <v>1.241626303628952</v>
       </c>
       <c r="F5" t="n">
         <v>1.345686318812127</v>
       </c>
       <c r="G5" t="n">
-        <v>7.943071028841918</v>
+        <v>7.943071028841917</v>
       </c>
       <c r="H5" t="n">
-        <v>4.96971112834515</v>
+        <v>4.969711128345156</v>
       </c>
       <c r="I5" t="n">
-        <v>1.796844818206196</v>
+        <v>1.796844818206197</v>
       </c>
       <c r="J5" t="n">
-        <v>5.379766438143134</v>
+        <v>5.379766438143128</v>
       </c>
       <c r="K5" t="n">
         <v>3.189543834542313</v>
       </c>
       <c r="L5" t="n">
-        <v>6.894805489508002</v>
+        <v>6.894805489507837</v>
       </c>
       <c r="M5" t="n">
         <v>9.457549535000776</v>
       </c>
       <c r="N5" t="n">
-        <v>4.313732832557108</v>
+        <v>4.313732832557112</v>
       </c>
       <c r="O5" t="n">
-        <v>2.922171556485146</v>
+        <v>2.922171556485147</v>
       </c>
       <c r="P5" t="n">
-        <v>4.145942341057782</v>
+        <v>4.145942341057779</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.322788290949271</v>
+        <v>2.322788290949253</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7007779016043925</v>
+        <v>0.7007779016043996</v>
       </c>
       <c r="S5" t="n">
-        <v>4.001235523521067</v>
+        <v>4.001235523521046</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22583785185435</v>
+        <v>2.225837851854342</v>
       </c>
       <c r="U5" t="n">
-        <v>6.365698228840986</v>
+        <v>6.365698228840984</v>
       </c>
       <c r="V5" t="n">
-        <v>1.98453800368403</v>
+        <v>1.984538003684035</v>
       </c>
       <c r="W5" t="n">
-        <v>7.209204295845846</v>
+        <v>7.209204295845826</v>
       </c>
       <c r="X5" t="n">
-        <v>5.943114081088913</v>
+        <v>5.943114081088903</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.01604621107187</v>
+        <v>5.016046211071864</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.825582614695042</v>
+        <v>2.825582614695005</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.601237910183863</v>
+        <v>5.601237910183857</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.18533828531488</v>
+        <v>10.18533828531486</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3565966698512634</v>
+        <v>0.3565966698512611</v>
       </c>
       <c r="C6" t="n">
-        <v>0.217871681696804</v>
+        <v>0.2178716816968038</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3822689990303873</v>
+        <v>0.3822689990303877</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3123587852404427</v>
+        <v>0.3123587852404435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2370960480614406</v>
+        <v>0.2370960480614389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7105033498966354</v>
+        <v>0.7105033498966343</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4095642384491888</v>
+        <v>0.409564238449189</v>
       </c>
       <c r="I6" t="n">
         <v>0.2593314210946946</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4712899340100229</v>
+        <v>0.4712899340100232</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4235911965889362</v>
+        <v>0.4235911965889371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6256503379931398</v>
+        <v>0.6256503379931224</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6789006926524475</v>
+        <v>0.678900692652447</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3930082991317371</v>
+        <v>0.3930082991317349</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4229007816564371</v>
+        <v>0.4229007816564372</v>
       </c>
       <c r="P6" t="n">
-        <v>0.483912922805419</v>
+        <v>0.4839129228054181</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2914350374435908</v>
+        <v>0.2914350374435912</v>
       </c>
       <c r="R6" t="n">
-        <v>0.281396850838808</v>
+        <v>0.2813968508388062</v>
       </c>
       <c r="S6" t="n">
-        <v>0.405820087413081</v>
+        <v>0.4058200874130805</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2811806592450502</v>
+        <v>0.2811806592450499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5940787626370054</v>
+        <v>0.5940787626370071</v>
       </c>
       <c r="V6" t="n">
         <v>0.2813781293957213</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5531764482462247</v>
+        <v>0.5531764482462254</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5503577609629767</v>
+        <v>0.5503577609629742</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4388830291433191</v>
+        <v>0.438883029143322</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4073901656803752</v>
+        <v>0.4073901656803738</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5421575920588568</v>
+        <v>0.5421575920588563</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6618314948880588</v>
+        <v>0.6618314948880597</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4297376170068202</v>
+        <v>0.429737617006817</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2910126288523598</v>
+        <v>0.2910126288523597</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4554099461859422</v>
+        <v>0.4554099461859432</v>
       </c>
       <c r="E7" t="n">
-        <v>0.308063093550313</v>
+        <v>0.308063093550312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3102369952169958</v>
+        <v>0.310236995216996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7062076582065031</v>
+        <v>0.706207658206504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4827051856047439</v>
+        <v>0.4827051856047446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3324723682502497</v>
+        <v>0.3324723682502498</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5444308811655796</v>
+        <v>0.5444308811655798</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4192955048988057</v>
+        <v>0.4192955048988065</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6213546463030056</v>
+        <v>0.6213546463029912</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7520416398080005</v>
+        <v>0.7520416398080009</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4654795532015952</v>
+        <v>0.4654795532015959</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4138169127907209</v>
+        <v>0.4138169127907225</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4748796500473972</v>
+        <v>0.4748796500473985</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3645759845991471</v>
+        <v>0.3645759845991464</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2771011591486758</v>
+        <v>0.2771011591486756</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4789610345686373</v>
+        <v>0.4789610345686364</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3543216064006063</v>
+        <v>0.354321606400606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.589424107440958</v>
+        <v>0.589424107440959</v>
       </c>
       <c r="V7" t="n">
         <v>0.3545190765512774</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6218900530880517</v>
+        <v>0.6218900530880513</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5460620692728467</v>
+        <v>0.546062069272843</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5096328574260126</v>
+        <v>0.5096328574260128</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4030944739902451</v>
+        <v>0.4030944739902441</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5378619003687253</v>
+        <v>0.5378619003687259</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7323790611501129</v>
+        <v>0.7323790611501131</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4682390971806084</v>
+        <v>0.468239097180605</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4323767771222902</v>
+        <v>0.4323767771222907</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5967740944558741</v>
+        <v>0.5967740944558733</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3946559053303123</v>
+        <v>0.3946559053303108</v>
       </c>
       <c r="F8" t="n">
-        <v>0.364763276890553</v>
+        <v>0.3647632768905539</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8689010507885142</v>
+        <v>0.8689010507885132</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6240693338746757</v>
+        <v>0.6240693338746768</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4738365165201808</v>
+        <v>0.473836516520181</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6857950294355106</v>
+        <v>0.6857950294355112</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5606596531687377</v>
+        <v>0.5606596531687376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7627187945729369</v>
+        <v>0.762718794572928</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8934057880780355</v>
+        <v>0.8934057880780359</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5271079251297973</v>
+        <v>0.5271079251297981</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4977156928161767</v>
+        <v>0.497715692816178</v>
       </c>
       <c r="P8" t="n">
-        <v>0.553407248906321</v>
+        <v>0.5534072489063206</v>
       </c>
       <c r="Q8" t="n">
         <v>0.3828626027835108</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4184653074186068</v>
+        <v>0.4184653074186064</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6203251828385681</v>
+        <v>0.6203251828385671</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4956857546705357</v>
+        <v>0.495685754670536</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6809408285258869</v>
+        <v>0.6809408285258867</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4677687603680043</v>
+        <v>0.467768760368004</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7632744167528617</v>
+        <v>0.7632744167528625</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5737762553385044</v>
+        <v>0.5737762553385021</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7532701680393065</v>
+        <v>0.7532701680393066</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4396852272994951</v>
+        <v>0.4396852272994936</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6792260486386574</v>
+        <v>0.6792260486386569</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9811918674220369</v>
+        <v>0.9811918674220382</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6734910162177177</v>
+        <v>0.6734910162177113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6363008452773694</v>
+        <v>0.6363008452773687</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8006981626109538</v>
+        <v>0.8006981626109543</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6299174769279323</v>
+        <v>0.6299174769279309</v>
       </c>
       <c r="F9" t="n">
-        <v>0.421459765806061</v>
+        <v>0.4214597658060619</v>
       </c>
       <c r="G9" t="n">
-        <v>1.051495859827444</v>
+        <v>1.051495859827446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8279934020297564</v>
+        <v>0.8279934020297566</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6777605846752612</v>
+        <v>0.6777605846752603</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8897190975905908</v>
+        <v>0.8897190975905903</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7645837213238157</v>
+        <v>0.7645837213238166</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9666428627280158</v>
+        <v>0.966642862728</v>
       </c>
       <c r="M9" t="n">
-        <v>1.097329856233015</v>
+        <v>1.097329856233014</v>
       </c>
       <c r="N9" t="n">
-        <v>0.810767769626606</v>
+        <v>0.8107677696266054</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7931119394405312</v>
+        <v>0.7931119394405317</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8614926482601842</v>
+        <v>0.8614926482601837</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7098641862200883</v>
+        <v>0.7098641862200888</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6223893755736846</v>
+        <v>0.6223893755736847</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8242492509936467</v>
+        <v>0.8242492509936445</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6996098228256165</v>
+        <v>0.6996098228256158</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9350712873718851</v>
+        <v>0.9350712873718848</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8169761293176605</v>
+        <v>0.8169761293176607</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9671782695130607</v>
+        <v>0.96717826951306</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8913502856978553</v>
+        <v>0.8913502856978502</v>
       </c>
       <c r="Y9" t="n">
         <v>0.8549210738510223</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6871662185848394</v>
+        <v>0.6871662185848373</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.883150116793736</v>
+        <v>0.8831501167937359</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.077667277575122</v>
+        <v>1.077667277575121</v>
       </c>
     </row>
   </sheetData>
@@ -8326,13 +8326,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.612025121316913</v>
+        <v>2.612025121316911</v>
       </c>
       <c r="C2" t="n">
-        <v>2.638677214709279</v>
+        <v>2.638677214709278</v>
       </c>
       <c r="D2" t="n">
-        <v>2.617567864550425</v>
+        <v>2.617567864550424</v>
       </c>
       <c r="E2" t="n">
         <v>2.611489364428689</v>
@@ -8341,67 +8341,67 @@
         <v>2.601153640775838</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64798170377854</v>
+        <v>2.647981703778538</v>
       </c>
       <c r="H2" t="n">
-        <v>2.627873859121117</v>
+        <v>2.627873859121116</v>
       </c>
       <c r="I2" t="n">
-        <v>2.611353948896539</v>
+        <v>2.611353948896538</v>
       </c>
       <c r="J2" t="n">
         <v>2.625473643986357</v>
       </c>
       <c r="K2" t="n">
-        <v>2.614626438593684</v>
+        <v>2.614626438593682</v>
       </c>
       <c r="L2" t="n">
-        <v>2.596388198412539</v>
+        <v>2.596388198412538</v>
       </c>
       <c r="M2" t="n">
         <v>2.614092382660252</v>
       </c>
       <c r="N2" t="n">
-        <v>2.615856859862752</v>
+        <v>2.615856859862751</v>
       </c>
       <c r="O2" t="n">
         <v>2.849451683731385</v>
       </c>
       <c r="P2" t="n">
-        <v>2.621699918692471</v>
+        <v>2.62169991869247</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.614165331036657</v>
+        <v>2.614165331036656</v>
       </c>
       <c r="R2" t="n">
-        <v>2.586778242491061</v>
+        <v>2.586778242491062</v>
       </c>
       <c r="S2" t="n">
-        <v>2.603701235933966</v>
+        <v>2.603701235933965</v>
       </c>
       <c r="T2" t="n">
-        <v>2.605780184235342</v>
+        <v>2.605780184235341</v>
       </c>
       <c r="U2" t="n">
         <v>3.004631089747468</v>
       </c>
       <c r="V2" t="n">
-        <v>2.620445472735094</v>
+        <v>2.620445472735093</v>
       </c>
       <c r="W2" t="n">
         <v>2.999388065181918</v>
       </c>
       <c r="X2" t="n">
-        <v>2.645891831777275</v>
+        <v>2.645891831777274</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.655351378416348</v>
+        <v>2.655351378416347</v>
       </c>
       <c r="Z2" t="n">
         <v>2.765847543533496</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.627408436507476</v>
+        <v>2.627408436507477</v>
       </c>
       <c r="AB2" t="n">
         <v>2.640012895834657</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.675014511001347</v>
+        <v>0.5293114160996238</v>
       </c>
       <c r="C3" t="n">
-        <v>1.72016776345165</v>
+        <v>0.5745084502352048</v>
       </c>
       <c r="D3" t="n">
-        <v>1.714536749250921</v>
+        <v>0.5702321920771261</v>
       </c>
       <c r="E3" t="n">
-        <v>1.671132143561252</v>
+        <v>0.5252866580145426</v>
       </c>
       <c r="F3" t="n">
-        <v>1.597277333180278</v>
+        <v>0.4487881760388615</v>
       </c>
       <c r="G3" t="n">
-        <v>1.929842508869875</v>
+        <v>0.7931342090446497</v>
       </c>
       <c r="H3" t="n">
-        <v>1.788594478856093</v>
+        <v>0.6469303817500632</v>
       </c>
       <c r="I3" t="n">
-        <v>1.670084752286041</v>
+        <v>0.5242008291507138</v>
       </c>
       <c r="J3" t="n">
-        <v>1.770432118235289</v>
+        <v>0.6280942224721918</v>
       </c>
       <c r="K3" t="n">
-        <v>1.693564322657528</v>
+        <v>0.5485127144002095</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56407746550255</v>
+        <v>0.4144364044407537</v>
       </c>
       <c r="M3" t="n">
-        <v>1.692231781267043</v>
+        <v>0.5471473440622296</v>
       </c>
       <c r="N3" t="n">
-        <v>1.70229838155069</v>
+        <v>0.557557691029148</v>
       </c>
       <c r="O3" t="n">
-        <v>2.055099462261322</v>
+        <v>0.9088505504645584</v>
       </c>
       <c r="P3" t="n">
-        <v>1.743755690229131</v>
+        <v>0.6004679123829767</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.690250869203948</v>
+        <v>0.5450823774803608</v>
       </c>
       <c r="R3" t="n">
-        <v>1.493927414533026</v>
+        <v>0.3417765161467682</v>
       </c>
       <c r="S3" t="n">
-        <v>1.616068812926883</v>
+        <v>0.4682762997674378</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63024810928579</v>
+        <v>0.482948827277569</v>
       </c>
       <c r="U3" t="n">
-        <v>2.365625202953191</v>
+        <v>1.22187770353142</v>
       </c>
       <c r="V3" t="n">
-        <v>1.734795400195513</v>
+        <v>0.5912001747520989</v>
       </c>
       <c r="W3" t="n">
-        <v>2.447174214473795</v>
+        <v>1.307566127903972</v>
       </c>
       <c r="X3" t="n">
-        <v>1.916667826183032</v>
+        <v>0.779548111035993</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.984054660824164</v>
+        <v>0.8492830615718125</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.968131847358616</v>
+        <v>0.8242294864435538</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.784754764642072</v>
+        <v>0.6429267650582385</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.873783958580297</v>
+        <v>0.7351125582158146</v>
       </c>
     </row>
     <row r="4">
@@ -8508,79 +8508,79 @@
         <v>0.1132060381467206</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1734944091498176</v>
+        <v>0.1734944091498175</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1048349540265989</v>
+        <v>0.104834954026599</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01191179930011445</v>
+        <v>-0.01191179930011398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5170327142886526</v>
+        <v>0.5170327142886524</v>
       </c>
       <c r="H4" t="n">
         <v>0.2899053588175399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1033053732967496</v>
+        <v>0.1033053732967495</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2624325289238353</v>
+        <v>0.2624325289238354</v>
       </c>
       <c r="K4" t="n">
-        <v>0.140269649845646</v>
+        <v>0.1402696498456458</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.06573966300539433</v>
+        <v>-0.06573966300539462</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1387969645030976</v>
+        <v>0.1387969645030977</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1541678241014948</v>
+        <v>0.154167824101495</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08617315484197059</v>
+        <v>0.08617315484197087</v>
       </c>
       <c r="P4" t="n">
         <v>0.2201678615230622</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1350612278690562</v>
+        <v>0.1350612278690565</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1742885359366074</v>
+        <v>-0.1742885359366071</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01686445996260507</v>
+        <v>0.016864459962605</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04034713739010611</v>
+        <v>0.04034713739010616</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1948523951935411</v>
+        <v>0.1948523951935414</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2035756886376073</v>
+        <v>0.2035756886376074</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3842618022493511</v>
+        <v>0.38426180224935</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4934266486457383</v>
+        <v>0.4934266486457392</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5962243094468531</v>
+        <v>0.596224309446853</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1921768760177145</v>
+        <v>0.1921768760177143</v>
       </c>
       <c r="AA4" t="n">
         <v>0.2846481962914432</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4239977593412521</v>
+        <v>0.4239977593412524</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2855735580956006</v>
+        <v>-0.2855735580955999</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2526658675669184</v>
+        <v>-0.2526658675669188</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8027840859200837</v>
+        <v>0.8027840859200832</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4229971277215845</v>
+        <v>-0.4229971277215846</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.533581876977078</v>
+        <v>-2.533581876977076</v>
       </c>
       <c r="G5" t="n">
-        <v>5.967099154130501</v>
+        <v>5.967099154130493</v>
       </c>
       <c r="H5" t="n">
-        <v>3.122543188285328</v>
+        <v>3.122543188285326</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4919870341964651</v>
+        <v>-0.4919870341964642</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1079107538037</v>
+        <v>2.107910753803695</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2258647736930777</v>
+        <v>0.2258647736930782</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.065164186691325</v>
+        <v>-3.065164186691327</v>
       </c>
       <c r="M5" t="n">
         <v>0.2006750521227116</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4470513784209891</v>
+        <v>0.4470513784209882</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6332222855612019</v>
+        <v>-0.633222285561202</v>
       </c>
       <c r="P5" t="n">
-        <v>1.487461105559452</v>
+        <v>1.48746110555945</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1220821589442125</v>
+        <v>0.1220821589442121</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.795179305086728</v>
+        <v>-5.795179305086734</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.708941341131696</v>
+        <v>-1.708941341131699</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.634738695478031</v>
+        <v>-1.634738695478033</v>
       </c>
       <c r="U5" t="n">
-        <v>1.153664072742528</v>
+        <v>1.153664072742531</v>
       </c>
       <c r="V5" t="n">
-        <v>1.230671288044965</v>
+        <v>1.230671288044964</v>
       </c>
       <c r="W5" t="n">
-        <v>4.53085452683943</v>
+        <v>4.530854526839421</v>
       </c>
       <c r="X5" t="n">
-        <v>6.451732126647466</v>
+        <v>6.451732126647462</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.276034833985864</v>
+        <v>8.276034833985857</v>
       </c>
       <c r="Z5" t="n">
         <v>1.0078042443183</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.761136851797216</v>
+        <v>2.761136851797212</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.595425760545117</v>
+        <v>5.595425760545125</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1776069429420091</v>
+        <v>0.177606942942009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1799264065492945</v>
+        <v>0.1799264065492949</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2402147775523924</v>
+        <v>0.2402147775523918</v>
       </c>
       <c r="E6" t="n">
         <v>0.1127060602245316</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.004040693102181692</v>
+        <v>-0.004040693102181372</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5249038204865859</v>
+        <v>0.5249038204865849</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2977764650154723</v>
+        <v>0.2977764650154724</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1700257416993247</v>
+        <v>0.1700257416993238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3291528973264098</v>
+        <v>0.3291528973264093</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1481407560435787</v>
+        <v>0.1481407560435789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009807053971804813</v>
+        <v>0.0009807053971801205</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14666807070103</v>
+        <v>0.1466680707010303</v>
       </c>
       <c r="N6" t="n">
         <v>0.1625263948595985</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1574312316900879</v>
+        <v>0.1574312316900878</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2266277032332803</v>
+        <v>0.2266277032332806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1429323340669889</v>
+        <v>0.1429323340669888</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1075681675340332</v>
+        <v>-0.1075681675340334</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02473556616053706</v>
+        <v>0.02473556616053716</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04821824358803927</v>
+        <v>0.0482182435880393</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2656250336897884</v>
+        <v>0.2656250336897878</v>
       </c>
       <c r="V6" t="n">
-        <v>0.21144679483554</v>
+        <v>0.2114467948355399</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3955150792473179</v>
+        <v>0.3955150792473116</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5601470170483124</v>
+        <v>0.5601470170483125</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6099773053904917</v>
+        <v>0.6099773053904919</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2588972444202888</v>
+        <v>0.2588972444202886</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2925193024893755</v>
+        <v>0.2925193024893759</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4337893583945159</v>
+        <v>0.4337893583945154</v>
       </c>
     </row>
     <row r="7">
@@ -8766,49 +8766,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1812600874653169</v>
+        <v>0.1812600874653171</v>
       </c>
       <c r="C7" t="n">
         <v>0.1835795510726028</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2438679220756999</v>
+        <v>0.2438679220757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1752084669524811</v>
+        <v>0.1752084669524812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05846171362576791</v>
+        <v>0.05846171362576803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5874062272145357</v>
+        <v>0.5874062272145348</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3602788717434226</v>
+        <v>0.3602788717434225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1736788862226318</v>
+        <v>0.1736788862226319</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3328060418497175</v>
+        <v>0.3328060418497172</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2106431627715281</v>
+        <v>0.2106431627715283</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004633849920487834</v>
+        <v>0.004633849920488292</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2091704774289796</v>
+        <v>0.2091704774289797</v>
       </c>
       <c r="N7" t="n">
-        <v>0.224541337027377</v>
+        <v>0.2245413370273769</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1562132285514868</v>
+        <v>0.1562132285514869</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2902079352325784</v>
+        <v>0.2902079352325785</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2054347407949382</v>
@@ -8817,34 +8817,34 @@
         <v>-0.1039150230107251</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08723797288848636</v>
+        <v>0.08723797288848648</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1107206503159884</v>
+        <v>0.1107206503159888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2685403567473352</v>
+        <v>0.2685403567473353</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2739492015634897</v>
+        <v>0.2739492015634895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.454635315175232</v>
+        <v>0.4546353151752324</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5638001615716209</v>
+        <v>0.5638001615716211</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6706500924664085</v>
+        <v>0.6706500924664083</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2625503889435967</v>
+        <v>0.2625503889435968</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3550217092173251</v>
+        <v>0.3550217092173248</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4943712722671339</v>
+        <v>0.4943712722671342</v>
       </c>
     </row>
     <row r="8">
@@ -8857,82 +8857,82 @@
         <v>0.2044722070758012</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2825043269405225</v>
+        <v>0.2825043269405221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3427926979436195</v>
+        <v>0.3427926979436191</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2338184867509543</v>
+        <v>0.2338184867509542</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09346898020549259</v>
+        <v>0.09346898020549234</v>
       </c>
       <c r="G8" t="n">
-        <v>0.702030515577486</v>
+        <v>0.7020305155774841</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4592036476113421</v>
+        <v>0.4592036476113414</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2726036620905518</v>
+        <v>0.2726036620905511</v>
       </c>
       <c r="J8" t="n">
-        <v>0.431730817717637</v>
+        <v>0.4317308177176368</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3095679386394473</v>
+        <v>0.309567938639447</v>
       </c>
       <c r="L8" t="n">
-        <v>0.103558625788407</v>
+        <v>0.1035586257884069</v>
       </c>
       <c r="M8" t="n">
         <v>0.3080952532970596</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2647761378375358</v>
+        <v>0.2647761378375361</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2129099833083737</v>
+        <v>0.2129099833083736</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3429512013106074</v>
+        <v>0.342951201310607</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2137675953992809</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.004990247142805188</v>
+        <v>-0.00499024714280577</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1861627487564071</v>
+        <v>0.1861627487564065</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2096454261839085</v>
+        <v>0.2096454261839079</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3309352307565742</v>
+        <v>0.3309352307565739</v>
       </c>
       <c r="V8" t="n">
-        <v>0.351834910917913</v>
+        <v>0.3518349109179131</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5535749707257258</v>
+        <v>0.5535749707257251</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5790722315509581</v>
+        <v>0.5790722315509587</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.844318126305735</v>
+        <v>0.8443181263057353</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2843561070945596</v>
+        <v>0.2843561070945594</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4539464850852444</v>
+        <v>0.4539464850852442</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6723842485647922</v>
+        <v>0.6723842485647916</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3563364093817263</v>
+        <v>0.3563364093817265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.43360884029728</v>
+        <v>0.4336088402972798</v>
       </c>
       <c r="D9" t="n">
         <v>0.4938972113003776</v>
       </c>
       <c r="E9" t="n">
-        <v>0.407938956876752</v>
+        <v>0.4079389568767521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1357038890167044</v>
+        <v>0.1357038890167047</v>
       </c>
       <c r="G9" t="n">
-        <v>0.837435568215796</v>
+        <v>0.8374355682157948</v>
       </c>
       <c r="H9" t="n">
         <v>0.6103081609680994</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4237081754473099</v>
+        <v>0.4237081754473094</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5828353310743951</v>
+        <v>0.5828353310743956</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4606724519962055</v>
+        <v>0.4606724519962054</v>
       </c>
       <c r="L9" t="n">
-        <v>0.254663139145165</v>
+        <v>0.2546631391451658</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4591997666536571</v>
+        <v>0.4591997666536574</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4745706262520538</v>
+        <v>0.4745706262520545</v>
       </c>
       <c r="O9" t="n">
-        <v>0.431415341151228</v>
+        <v>0.4314153411512294</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5708121764542564</v>
+        <v>0.5708121764542574</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4554640817961988</v>
+        <v>0.4554640817961989</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1461142662139532</v>
+        <v>0.1461142662139529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3372672621131645</v>
+        <v>0.3372672621131644</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3607499395406655</v>
+        <v>0.3607499395406657</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5193074674377731</v>
+        <v>0.5193074674377732</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6104726598418903</v>
+        <v>0.6104726598418909</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7046646043999089</v>
+        <v>0.7046646043999086</v>
       </c>
       <c r="X9" t="n">
         <v>0.8138294507962983</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9206793816910847</v>
+        <v>0.9206793816910841</v>
       </c>
       <c r="Z9" t="n">
         <v>0.4673897245192008</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6050509984420027</v>
+        <v>0.6050509984420023</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7444005614918119</v>
+        <v>0.7444005614918124</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3E2EF4-128D-43E1-8DC9-C81A5F7930A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D1B86-4CDA-4D57-8C4B-3C685E066077}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="image SSP2-Base 2020" sheetId="1" r:id="rId1"/>
@@ -155,6 +155,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1283,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.7109375" bestFit="1" customWidth="1"/>
@@ -2061,1550 +2062,6 @@
       </c>
       <c r="AB9">
         <v>0.37495131978018381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>2.6977252282004551</v>
-      </c>
-      <c r="C11">
-        <v>2.7026394802442422</v>
-      </c>
-      <c r="D11">
-        <v>2.6879788719210929</v>
-      </c>
-      <c r="E11">
-        <v>2.675176840259549</v>
-      </c>
-      <c r="F11">
-        <v>2.6829752202340522</v>
-      </c>
-      <c r="G11">
-        <v>2.7085976892977399</v>
-      </c>
-      <c r="H11">
-        <v>2.695839288957798</v>
-      </c>
-      <c r="I11">
-        <v>2.6839979518767532</v>
-      </c>
-      <c r="J11">
-        <v>2.697755753143285</v>
-      </c>
-      <c r="K11">
-        <v>2.6952468117881612</v>
-      </c>
-      <c r="L11">
-        <v>2.7104757761534479</v>
-      </c>
-      <c r="M11">
-        <v>2.7164039566874032</v>
-      </c>
-      <c r="N11">
-        <v>2.6980379187039691</v>
-      </c>
-      <c r="O11">
-        <v>2.9842290308730588</v>
-      </c>
-      <c r="P11">
-        <v>2.692554456655992</v>
-      </c>
-      <c r="Q11">
-        <v>2.6884541582204742</v>
-      </c>
-      <c r="R11">
-        <v>2.6844681011624481</v>
-      </c>
-      <c r="S11">
-        <v>2.7013937519434972</v>
-      </c>
-      <c r="T11">
-        <v>2.6921019227618759</v>
-      </c>
-      <c r="U11">
-        <v>3.1135506185739632</v>
-      </c>
-      <c r="V11">
-        <v>2.6809438318424532</v>
-      </c>
-      <c r="W11">
-        <v>3.087568757853365</v>
-      </c>
-      <c r="X11">
-        <v>2.692266878223649</v>
-      </c>
-      <c r="Y11">
-        <v>2.6896647071209059</v>
-      </c>
-      <c r="Z11">
-        <v>2.8564437165540251</v>
-      </c>
-      <c r="AA11">
-        <v>2.699495518543626</v>
-      </c>
-      <c r="AB11">
-        <v>2.7151432806331641</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>0.83091930130650538</v>
-      </c>
-      <c r="C12">
-        <v>0.70224035603981394</v>
-      </c>
-      <c r="D12">
-        <v>0.76045797574981222</v>
-      </c>
-      <c r="E12">
-        <v>0.66529067048747048</v>
-      </c>
-      <c r="F12">
-        <v>0.72357729166115525</v>
-      </c>
-      <c r="G12">
-        <v>0.91138872377492453</v>
-      </c>
-      <c r="H12">
-        <v>0.81933740458869342</v>
-      </c>
-      <c r="I12">
-        <v>0.73105486918953566</v>
-      </c>
-      <c r="J12">
-        <v>0.83187953859087282</v>
-      </c>
-      <c r="K12">
-        <v>0.8142152969143559</v>
-      </c>
-      <c r="L12">
-        <v>0.9260494161752143</v>
-      </c>
-      <c r="M12">
-        <v>0.97257275124584086</v>
-      </c>
-      <c r="N12">
-        <v>0.83457226147757946</v>
-      </c>
-      <c r="O12">
-        <v>1.2809968240706231</v>
-      </c>
-      <c r="P12">
-        <v>0.79302234762599222</v>
-      </c>
-      <c r="Q12">
-        <v>0.76375097257406022</v>
-      </c>
-      <c r="R12">
-        <v>0.73466569151556305</v>
-      </c>
-      <c r="S12">
-        <v>0.8583681328175875</v>
-      </c>
-      <c r="T12">
-        <v>0.79107137912311232</v>
-      </c>
-      <c r="U12">
-        <v>1.576778336812898</v>
-      </c>
-      <c r="V12">
-        <v>0.70749884303823174</v>
-      </c>
-      <c r="W12">
-        <v>1.494831767464212</v>
-      </c>
-      <c r="X12">
-        <v>0.79208130892279527</v>
-      </c>
-      <c r="Y12">
-        <v>0.77242591394795346</v>
-      </c>
-      <c r="Z12">
-        <v>1.0495751642510041</v>
-      </c>
-      <c r="AA12">
-        <v>0.84516922045874343</v>
-      </c>
-      <c r="AB12">
-        <v>0.96110812490636799</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>0.56108428725442527</v>
-      </c>
-      <c r="C13">
-        <v>0.28917462083020262</v>
-      </c>
-      <c r="D13">
-        <v>0.45099470953361209</v>
-      </c>
-      <c r="E13">
-        <v>0.306389872690987</v>
-      </c>
-      <c r="F13">
-        <v>0.39447616193501078</v>
-      </c>
-      <c r="G13">
-        <v>0.68389373692747601</v>
-      </c>
-      <c r="H13">
-        <v>0.53978173593368606</v>
-      </c>
-      <c r="I13">
-        <v>0.40602838631912108</v>
-      </c>
-      <c r="J13">
-        <v>0.56102773555652308</v>
-      </c>
-      <c r="K13">
-        <v>0.53308943374967499</v>
-      </c>
-      <c r="L13">
-        <v>0.70510759192534944</v>
-      </c>
-      <c r="M13">
-        <v>0.77399362067927413</v>
-      </c>
-      <c r="N13">
-        <v>0.56461627033634565</v>
-      </c>
-      <c r="O13">
-        <v>0.51636573873513525</v>
-      </c>
-      <c r="P13">
-        <v>0.50267804398729654</v>
-      </c>
-      <c r="Q13">
-        <v>0.4563632869276355</v>
-      </c>
-      <c r="R13">
-        <v>0.41133893878037658</v>
-      </c>
-      <c r="S13">
-        <v>0.6025219505363868</v>
-      </c>
-      <c r="T13">
-        <v>0.49756646547736072</v>
-      </c>
-      <c r="U13">
-        <v>0.67400361250276886</v>
-      </c>
-      <c r="V13">
-        <v>0.36884289823365568</v>
-      </c>
-      <c r="W13">
-        <v>0.59914538164539721</v>
-      </c>
-      <c r="X13">
-        <v>0.49942971330136171</v>
-      </c>
-      <c r="Y13">
-        <v>0.46708740971797441</v>
-      </c>
-      <c r="Z13">
-        <v>0.47479280935990992</v>
-      </c>
-      <c r="AA13">
-        <v>0.5810805310543149</v>
-      </c>
-      <c r="AB13">
-        <v>0.75493878172990714</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>7.201509147590575</v>
-      </c>
-      <c r="C14">
-        <v>2.3690173696670409</v>
-      </c>
-      <c r="D14">
-        <v>5.8424988034715328</v>
-      </c>
-      <c r="E14">
-        <v>2.6229364932708141</v>
-      </c>
-      <c r="F14">
-        <v>4.7507651567336859</v>
-      </c>
-      <c r="G14">
-        <v>9.7623358664544764</v>
-      </c>
-      <c r="H14">
-        <v>8.0637415590696246</v>
-      </c>
-      <c r="I14">
-        <v>4.9432109467456398</v>
-      </c>
-      <c r="J14">
-        <v>7.6186317096889997</v>
-      </c>
-      <c r="K14">
-        <v>7.5261113628326397</v>
-      </c>
-      <c r="L14">
-        <v>10.617775484559591</v>
-      </c>
-      <c r="M14">
-        <v>12.873562858018969</v>
-      </c>
-      <c r="N14">
-        <v>8.0140839435858524</v>
-      </c>
-      <c r="O14">
-        <v>6.2230102481311098</v>
-      </c>
-      <c r="P14">
-        <v>6.2118582411528473</v>
-      </c>
-      <c r="Q14">
-        <v>5.8292090060939286</v>
-      </c>
-      <c r="R14">
-        <v>5.1245238481714042</v>
-      </c>
-      <c r="S14">
-        <v>8.2264751152192233</v>
-      </c>
-      <c r="T14">
-        <v>6.8608957010215628</v>
-      </c>
-      <c r="U14">
-        <v>9.8582965631257053</v>
-      </c>
-      <c r="V14">
-        <v>3.7014914647720349</v>
-      </c>
-      <c r="W14">
-        <v>8.5633224565050359</v>
-      </c>
-      <c r="X14">
-        <v>6.7807471740115091</v>
-      </c>
-      <c r="Y14">
-        <v>5.9561131136264889</v>
-      </c>
-      <c r="Z14">
-        <v>5.7478256184272842</v>
-      </c>
-      <c r="AA14">
-        <v>8.2551702361729706</v>
-      </c>
-      <c r="AB14">
-        <v>12.86121957113432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>0.58643405991136088</v>
-      </c>
-      <c r="C15">
-        <v>0.40884063097892021</v>
-      </c>
-      <c r="D15">
-        <v>0.57066071968232912</v>
-      </c>
-      <c r="E15">
-        <v>0.42605588283970491</v>
-      </c>
-      <c r="F15">
-        <v>0.41982593459194328</v>
-      </c>
-      <c r="G15">
-        <v>0.80355974707618949</v>
-      </c>
-      <c r="H15">
-        <v>0.65944774608240375</v>
-      </c>
-      <c r="I15">
-        <v>0.43137815897605541</v>
-      </c>
-      <c r="J15">
-        <v>0.58637750821345658</v>
-      </c>
-      <c r="K15">
-        <v>0.65275544389838891</v>
-      </c>
-      <c r="L15">
-        <v>0.82477360207407069</v>
-      </c>
-      <c r="M15">
-        <v>0.89365963082799238</v>
-      </c>
-      <c r="N15">
-        <v>0.59108886159986751</v>
-      </c>
-      <c r="O15">
-        <v>0.5428381257310172</v>
-      </c>
-      <c r="P15">
-        <v>0.6274030016379053</v>
-      </c>
-      <c r="Q15">
-        <v>0.57602929707635075</v>
-      </c>
-      <c r="R15">
-        <v>0.53100494892909444</v>
-      </c>
-      <c r="S15">
-        <v>0.62787172319331974</v>
-      </c>
-      <c r="T15">
-        <v>0.522916238134295</v>
-      </c>
-      <c r="U15">
-        <v>0.70230296907974565</v>
-      </c>
-      <c r="V15">
-        <v>0.48850890838237071</v>
-      </c>
-      <c r="W15">
-        <v>0.72387003274204753</v>
-      </c>
-      <c r="X15">
-        <v>0.61909572345007424</v>
-      </c>
-      <c r="Y15">
-        <v>0.4987283558070133</v>
-      </c>
-      <c r="Z15">
-        <v>0.50014258201684347</v>
-      </c>
-      <c r="AA15">
-        <v>0.70074654120302682</v>
-      </c>
-      <c r="AB15">
-        <v>0.78315167819963694</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>0.67157737572079301</v>
-      </c>
-      <c r="C16">
-        <v>0.39966770929657042</v>
-      </c>
-      <c r="D16">
-        <v>0.56148779799997839</v>
-      </c>
-      <c r="E16">
-        <v>0.41688296115735413</v>
-      </c>
-      <c r="F16">
-        <v>0.50496925040137564</v>
-      </c>
-      <c r="G16">
-        <v>0.79438682539384364</v>
-      </c>
-      <c r="H16">
-        <v>0.6502748244000538</v>
-      </c>
-      <c r="I16">
-        <v>0.51652147478548815</v>
-      </c>
-      <c r="J16">
-        <v>0.67152082402289082</v>
-      </c>
-      <c r="K16">
-        <v>0.64358252221604062</v>
-      </c>
-      <c r="L16">
-        <v>0.81560068039171885</v>
-      </c>
-      <c r="M16">
-        <v>0.88448670914564032</v>
-      </c>
-      <c r="N16">
-        <v>0.67510935880271261</v>
-      </c>
-      <c r="O16">
-        <v>0.62647537538056064</v>
-      </c>
-      <c r="P16">
-        <v>0.61278768063272404</v>
-      </c>
-      <c r="Q16">
-        <v>0.56685637539400191</v>
-      </c>
-      <c r="R16">
-        <v>0.52183202724674416</v>
-      </c>
-      <c r="S16">
-        <v>0.71301503900275498</v>
-      </c>
-      <c r="T16">
-        <v>0.60805955394372868</v>
-      </c>
-      <c r="U16">
-        <v>0.78726963615335199</v>
-      </c>
-      <c r="V16">
-        <v>0.47933598670002292</v>
-      </c>
-      <c r="W16">
-        <v>0.70963847011176429</v>
-      </c>
-      <c r="X16">
-        <v>0.60992280176772828</v>
-      </c>
-      <c r="Y16">
-        <v>0.58053008210438628</v>
-      </c>
-      <c r="Z16">
-        <v>0.58528589782627727</v>
-      </c>
-      <c r="AA16">
-        <v>0.69157361952068275</v>
-      </c>
-      <c r="AB16">
-        <v>0.86543187019627632</v>
-      </c>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>0.72406797443880966</v>
-      </c>
-      <c r="C17">
-        <v>0.58190253238600886</v>
-      </c>
-      <c r="D17">
-        <v>0.74372262108941756</v>
-      </c>
-      <c r="E17">
-        <v>0.53003281200399666</v>
-      </c>
-      <c r="F17">
-        <v>0.5776724829119253</v>
-      </c>
-      <c r="G17">
-        <v>1.0035249586047379</v>
-      </c>
-      <c r="H17">
-        <v>0.83250964748949274</v>
-      </c>
-      <c r="I17">
-        <v>0.69875629787492832</v>
-      </c>
-      <c r="J17">
-        <v>0.85375564711232865</v>
-      </c>
-      <c r="K17">
-        <v>0.82581734530547879</v>
-      </c>
-      <c r="L17">
-        <v>0.99783550348115568</v>
-      </c>
-      <c r="M17">
-        <v>1.0667215322351189</v>
-      </c>
-      <c r="N17">
-        <v>0.75677070224298781</v>
-      </c>
-      <c r="O17">
-        <v>0.73615863606334608</v>
-      </c>
-      <c r="P17">
-        <v>0.71569608560714937</v>
-      </c>
-      <c r="Q17">
-        <v>0.59384927278181565</v>
-      </c>
-      <c r="R17">
-        <v>0.70406685033618222</v>
-      </c>
-      <c r="S17">
-        <v>0.89524986209218782</v>
-      </c>
-      <c r="T17">
-        <v>0.79029437703316685</v>
-      </c>
-      <c r="U17">
-        <v>0.90651495099510249</v>
-      </c>
-      <c r="V17">
-        <v>0.62628652706192733</v>
-      </c>
-      <c r="W17">
-        <v>0.89189879156029439</v>
-      </c>
-      <c r="X17">
-        <v>0.64880701506449689</v>
-      </c>
-      <c r="Y17">
-        <v>0.89204080503577732</v>
-      </c>
-      <c r="Z17">
-        <v>0.63536643097396417</v>
-      </c>
-      <c r="AA17">
-        <v>0.87380844261011936</v>
-      </c>
-      <c r="AB17">
-        <v>1.1831953845859691</v>
-      </c>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B18">
-        <v>1.010950742521338</v>
-      </c>
-      <c r="C18">
-        <v>0.87485157804493174</v>
-      </c>
-      <c r="D18">
-        <v>1.0366716667483391</v>
-      </c>
-      <c r="E18">
-        <v>0.86072233476531657</v>
-      </c>
-      <c r="F18">
-        <v>0.66707282093091025</v>
-      </c>
-      <c r="G18">
-        <v>1.2695707133155409</v>
-      </c>
-      <c r="H18">
-        <v>1.1254586931484141</v>
-      </c>
-      <c r="I18">
-        <v>0.99170534353384898</v>
-      </c>
-      <c r="J18">
-        <v>1.146704692771251</v>
-      </c>
-      <c r="K18">
-        <v>1.1187663909644019</v>
-      </c>
-      <c r="L18">
-        <v>1.2907845491400769</v>
-      </c>
-      <c r="M18">
-        <v>1.359670577894001</v>
-      </c>
-      <c r="N18">
-        <v>1.15029322755107</v>
-      </c>
-      <c r="O18">
-        <v>1.1470501439940559</v>
-      </c>
-      <c r="P18">
-        <v>1.143150792828193</v>
-      </c>
-      <c r="Q18">
-        <v>1.042040263315698</v>
-      </c>
-      <c r="R18">
-        <v>0.99701589599510565</v>
-      </c>
-      <c r="S18">
-        <v>1.1881989077511119</v>
-      </c>
-      <c r="T18">
-        <v>1.0832434226920891</v>
-      </c>
-      <c r="U18">
-        <v>1.2626301536375391</v>
-      </c>
-      <c r="V18">
-        <v>1.1112420986615841</v>
-      </c>
-      <c r="W18">
-        <v>1.1848223388601249</v>
-      </c>
-      <c r="X18">
-        <v>1.0851066705160879</v>
-      </c>
-      <c r="Y18">
-        <v>1.055713950852748</v>
-      </c>
-      <c r="Z18">
-        <v>0.97858811825465919</v>
-      </c>
-      <c r="AA18">
-        <v>1.1667574882690439</v>
-      </c>
-      <c r="AB18">
-        <v>1.3406157389446349</v>
-      </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <f>(B11-B2)/B11*100</f>
-        <v>3.9501395288737569</v>
-      </c>
-      <c r="C22">
-        <f t="shared" ref="C22:AB22" si="0">(C11-C2)/C11*100</f>
-        <v>3.2207718454035037</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>3.4691834991773827</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>3.0896263658276544</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>3.7940014197503937</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>4.0564919818902982</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="0"/>
-        <v>3.6372404438812662</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="0"/>
-        <v>3.395599920989357</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="0"/>
-        <v>3.7897755964635564</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>3.8090003270425963</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>5.1759822048299844</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>4.6159478022198064</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>3.9195684834724602</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="0"/>
-        <v>5.7223700612340442</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="0"/>
-        <v>3.7633910979185559</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>3.5048088758549332</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="0"/>
-        <v>4.6426202846665188</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
-        <v>4.3858989988695427</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>3.9143790849657649</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="0"/>
-        <v>4.2893409594626677</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="0"/>
-        <v>2.9531433378950265</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="0"/>
-        <v>3.423015709452268</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="0"/>
-        <v>2.1694176727636494</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="0"/>
-        <v>2.7105180296103288</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="0"/>
-        <v>3.8872121202752976</v>
-      </c>
-      <c r="AA22">
-        <f t="shared" si="0"/>
-        <v>2.736823013345449</v>
-      </c>
-      <c r="AB22">
-        <f t="shared" si="0"/>
-        <v>4.4189057846628685</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <f t="shared" ref="B23:AB29" si="1">(B12-B3)/B12*100</f>
-        <v>38.257824162585202</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
-        <v>21.784749268733645</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="1"/>
-        <v>29.082305070063015</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>21.378417451631844</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>39.318210237849257</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>37.613892819226848</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>31.405733227495769</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>28.120390710114002</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>34.482586813335374</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>35.702004825614907</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="1"/>
-        <v>61.252336340814153</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="1"/>
-        <v>47.131355201764578</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="1"/>
-        <v>37.546065443891912</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="1"/>
-        <v>34.016342624198245</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="1"/>
-        <v>35.247332146197806</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="1"/>
-        <v>29.872574004310877</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="1"/>
-        <v>61.816404169153806</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="1"/>
-        <v>47.289724430275903</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="1"/>
-        <v>39.322585811919936</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="1"/>
-        <v>24.155679102184717</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="1"/>
-        <v>16.467911993213917</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="1"/>
-        <v>10.612853795675377</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="1"/>
-        <v>-4.5493177121214359</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="1"/>
-        <v>9.0860767824871544</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="1"/>
-        <v>22.136432271090577</v>
-      </c>
-      <c r="AA23">
-        <f t="shared" si="1"/>
-        <v>9.1707448198152601</v>
-      </c>
-      <c r="AB23">
-        <f t="shared" si="1"/>
-        <v>43.556239104510055</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <f t="shared" si="1"/>
-        <v>82.946516829565766</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="1"/>
-        <v>69.685594184165339</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="1"/>
-        <v>69.85082240766522</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="1"/>
-        <v>63.747142080288064</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="1"/>
-        <v>104.31562641710772</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>73.518643475136614</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="1"/>
-        <v>68.412520368149472</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="1"/>
-        <v>71.708095289853944</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="1"/>
-        <v>74.218064205833727</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>79.034683008675458</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="1"/>
-        <v>120.03754677474525</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="1"/>
-        <v>87.320195750207247</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="1"/>
-        <v>80.802256639449396</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="1"/>
-        <v>94.834353271010201</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="1"/>
-        <v>80.826236938389783</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="1"/>
-        <v>71.440504353695971</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="1"/>
-        <v>162.75163042549269</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="1"/>
-        <v>99.581785994920722</v>
-      </c>
-      <c r="T24">
-        <f t="shared" si="1"/>
-        <v>90.84547218205347</v>
-      </c>
-      <c r="U24">
-        <f t="shared" si="1"/>
-        <v>74.156266903303305</v>
-      </c>
-      <c r="V24">
-        <f t="shared" si="1"/>
-        <v>41.996003684759145</v>
-      </c>
-      <c r="W24">
-        <f t="shared" si="1"/>
-        <v>25.439851142587017</v>
-      </c>
-      <c r="X24">
-        <f t="shared" si="1"/>
-        <v>-15.729957516052881</v>
-      </c>
-      <c r="Y24">
-        <f t="shared" si="1"/>
-        <v>18.199159860808884</v>
-      </c>
-      <c r="Z24">
-        <f t="shared" si="1"/>
-        <v>59.101190322178034</v>
-      </c>
-      <c r="AA24">
-        <f t="shared" si="1"/>
-        <v>16.559623816848397</v>
-      </c>
-      <c r="AB24">
-        <f t="shared" si="1"/>
-        <v>81.354378051965895</v>
-      </c>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25">
-        <f t="shared" si="1"/>
-        <v>104.30100661865296</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="1"/>
-        <v>119.84382512976835</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="1"/>
-        <v>93.81461722264936</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="1"/>
-        <v>101.94397652962456</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="1"/>
-        <v>150.38124562516083</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="1"/>
-        <v>89.35270698450887</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="1"/>
-        <v>87.196451269467374</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="1"/>
-        <v>100.38927238097502</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="1"/>
-        <v>93.833026876122076</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="1"/>
-        <v>100.44559185184183</v>
-      </c>
-      <c r="L25">
-        <f t="shared" si="1"/>
-        <v>138.45017185658534</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="1"/>
-        <v>102.36963410299293</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="1"/>
-        <v>101.78701984720205</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="1"/>
-        <v>121.92345526865971</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="1"/>
-        <v>104.63813654348992</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="1"/>
-        <v>95.617542887270005</v>
-      </c>
-      <c r="R25">
-        <f t="shared" si="1"/>
-        <v>237.81916864537979</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="1"/>
-        <v>121.54522376017863</v>
-      </c>
-      <c r="T25">
-        <f t="shared" si="1"/>
-        <v>119.03090965983132</v>
-      </c>
-      <c r="U25">
-        <f t="shared" si="1"/>
-        <v>90.006137560168824</v>
-      </c>
-      <c r="V25">
-        <f t="shared" si="1"/>
-        <v>57.057675445003916</v>
-      </c>
-      <c r="W25">
-        <f t="shared" si="1"/>
-        <v>31.880066399142521</v>
-      </c>
-      <c r="X25">
-        <f t="shared" si="1"/>
-        <v>-17.559057197327569</v>
-      </c>
-      <c r="Y25">
-        <f t="shared" si="1"/>
-        <v>18.869890359049982</v>
-      </c>
-      <c r="Z25">
-        <f t="shared" si="1"/>
-        <v>78.937089971407133</v>
-      </c>
-      <c r="AA25">
-        <f t="shared" si="1"/>
-        <v>20.059429583939671</v>
-      </c>
-      <c r="AB25">
-        <f t="shared" si="1"/>
-        <v>96.372889205157591</v>
-      </c>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B26">
-        <f t="shared" si="1"/>
-        <v>82.153686883698455</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="1"/>
-        <v>66.70521775036049</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="1"/>
-        <v>74.60073298131573</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="1"/>
-        <v>62.555119783503585</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="1"/>
-        <v>92.51191750826186</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="1"/>
-        <v>76.345656502565845</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="1"/>
-        <v>72.783910322803152</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="1"/>
-        <v>71.290709640688803</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="1"/>
-        <v>67.06817065432756</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="1"/>
-        <v>81.503588393633009</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="1"/>
-        <v>111.25463200486504</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="1"/>
-        <v>88.014080935679033</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="1"/>
-        <v>80.092206098481782</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="1"/>
-        <v>85.292896554865465</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="1"/>
-        <v>83.436748702181049</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="1"/>
-        <v>75.81590071511576</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="1"/>
-        <v>146.92036243890789</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="1"/>
-        <v>91.880369977621228</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="1"/>
-        <v>89.57341528674543</v>
-      </c>
-      <c r="U26">
-        <f t="shared" si="1"/>
-        <v>67.904119035661154</v>
-      </c>
-      <c r="V26">
-        <f t="shared" si="1"/>
-        <v>54.36806548888331</v>
-      </c>
-      <c r="W26">
-        <f t="shared" si="1"/>
-        <v>36.556950038829648</v>
-      </c>
-      <c r="X26">
-        <f t="shared" si="1"/>
-        <v>-1.1880394348007255</v>
-      </c>
-      <c r="Y26">
-        <f t="shared" si="1"/>
-        <v>20.631253760702027</v>
-      </c>
-      <c r="Z26">
-        <f t="shared" si="1"/>
-        <v>59.380173010185914</v>
-      </c>
-      <c r="AA26">
-        <f t="shared" si="1"/>
-        <v>23.893051276314097</v>
-      </c>
-      <c r="AB26">
-        <f t="shared" si="1"/>
-        <v>80.833078414546208</v>
-      </c>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B27">
-        <f t="shared" si="1"/>
-        <v>76.317617196824287</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="1"/>
-        <v>62.212939649412647</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="1"/>
-        <v>64.499263019039603</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="1"/>
-        <v>58.157034007430887</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="1"/>
-        <v>90.823799083143115</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="1"/>
-        <v>69.225893311534747</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="1"/>
-        <v>64.036043291526255</v>
-      </c>
-      <c r="I27">
-        <f t="shared" si="1"/>
-        <v>65.49334668681378</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="1"/>
-        <v>69.024799594242552</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="1"/>
-        <v>72.789037298790078</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="1"/>
-        <v>109.55432664279523</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="1"/>
-        <v>81.740597707471181</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="1"/>
-        <v>74.558982074471274</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="1"/>
-        <v>85.681547867239274</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="1"/>
-        <v>73.986056017466041</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="1"/>
-        <v>65.829763603587793</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="1"/>
-        <v>137.32250418747836</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="1"/>
-        <v>90.76023112895372</v>
-      </c>
-      <c r="T27">
-        <f t="shared" si="1"/>
-        <v>82.088765775101464</v>
-      </c>
-      <c r="U27">
-        <f t="shared" si="1"/>
-        <v>69.606573813541956</v>
-      </c>
-      <c r="V27">
-        <f t="shared" si="1"/>
-        <v>42.148150935127795</v>
-      </c>
-      <c r="W27">
-        <f t="shared" si="1"/>
-        <v>28.120469739243337</v>
-      </c>
-      <c r="X27">
-        <f t="shared" si="1"/>
-        <v>-5.1528002570542464</v>
-      </c>
-      <c r="Y27">
-        <f t="shared" si="1"/>
-        <v>22.793986027780239</v>
-      </c>
-      <c r="Z27">
-        <f t="shared" si="1"/>
-        <v>55.996596046574552</v>
-      </c>
-      <c r="AA27">
-        <f t="shared" si="1"/>
-        <v>20.729062531683862</v>
-      </c>
-      <c r="AB27">
-        <f t="shared" si="1"/>
-        <v>76.413609360954723</v>
-      </c>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B28">
-        <f t="shared" si="1"/>
-        <v>75.972750597681639</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="1"/>
-        <v>60.660798649747797</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="1"/>
-        <v>62.724619522004289</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="1"/>
-        <v>58.719102648916724</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="1"/>
-        <v>87.696436107962441</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
-        <v>66.576338006910973</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="1"/>
-        <v>62.552063193824189</v>
-      </c>
-      <c r="I28">
-        <f t="shared" si="1"/>
-        <v>63.345245583450385</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="1"/>
-        <v>66.512894838432388</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="1"/>
-        <v>69.361489937952115</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="1"/>
-        <v>100.00320922051078</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="1"/>
-        <v>77.557862143338667</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="1"/>
-        <v>73.460998810476312</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="1"/>
-        <v>81.996758715885164</v>
-      </c>
-      <c r="P28">
-        <f t="shared" si="1"/>
-        <v>72.201435692860244</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="1"/>
-        <v>66.952861830075051</v>
-      </c>
-      <c r="R28">
-        <f t="shared" si="1"/>
-        <v>116.59894224548731</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="1"/>
-        <v>83.940341342527418</v>
-      </c>
-      <c r="T28">
-        <f t="shared" si="1"/>
-        <v>76.362719168159003</v>
-      </c>
-      <c r="U28">
-        <f t="shared" si="1"/>
-        <v>68.34807708653841</v>
-      </c>
-      <c r="V28">
-        <f t="shared" si="1"/>
-        <v>46.128322602296507</v>
-      </c>
-      <c r="W28">
-        <f t="shared" si="1"/>
-        <v>34.074324438126361</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="1"/>
-        <v>-0.13390536085741653</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="1"/>
-        <v>34.10893007200422</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="1"/>
-        <v>57.299569208272402</v>
-      </c>
-      <c r="AA28">
-        <f t="shared" si="1"/>
-        <v>28.346993309972401</v>
-      </c>
-      <c r="AB28">
-        <f t="shared" si="1"/>
-        <v>70.605909812917417</v>
-      </c>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <f t="shared" si="1"/>
-        <v>72.834487226003986</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="1"/>
-        <v>63.210918885938206</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="1"/>
-        <v>64.293469535044906</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="1"/>
-        <v>61.368076588615885</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="1"/>
-        <v>86.536024660922621</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="1"/>
-        <v>67.288733910338124</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="1"/>
-        <v>64.042062409049649</v>
-      </c>
-      <c r="I29">
-        <f t="shared" si="1"/>
-        <v>64.80189856500796</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="1"/>
-        <v>66.9634125022327</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="1"/>
-        <v>69.077353321778901</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="1"/>
-        <v>92.802669886519723</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="1"/>
-        <v>75.558111647713062</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="1"/>
-        <v>70.217865936657077</v>
-      </c>
-      <c r="O29">
-        <f t="shared" si="1"/>
-        <v>75.661976872792863</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="1"/>
-        <v>69.132721538822324</v>
-      </c>
-      <c r="Q29">
-        <f t="shared" si="1"/>
-        <v>65.018302900923715</v>
-      </c>
-      <c r="R29">
-        <f t="shared" si="1"/>
-        <v>102.40052361813028</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="1"/>
-        <v>80.078409579708847</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="1"/>
-        <v>74.17587374780264</v>
-      </c>
-      <c r="U29">
-        <f t="shared" si="1"/>
-        <v>67.438003708171181</v>
-      </c>
-      <c r="V29">
-        <f t="shared" si="1"/>
-        <v>53.936149640288065</v>
-      </c>
-      <c r="W29">
-        <f t="shared" si="1"/>
-        <v>42.530457546746334</v>
-      </c>
-      <c r="X29">
-        <f t="shared" si="1"/>
-        <v>25.15223565627311</v>
-      </c>
-      <c r="Y29">
-        <f t="shared" si="1"/>
-        <v>41.363726986526387</v>
-      </c>
-      <c r="Z29">
-        <f t="shared" si="1"/>
-        <v>59.62893545264415</v>
-      </c>
-      <c r="AA29">
-        <f t="shared" si="1"/>
-        <v>38.372448699236429</v>
-      </c>
-      <c r="AB29">
-        <f t="shared" si="1"/>
-        <v>72.031409979167151</v>
       </c>
     </row>
   </sheetData>
@@ -5182,7 +3639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.7109375" bestFit="1" customWidth="1"/>
@@ -5960,1550 +4417,6 @@
       </c>
       <c r="AB9">
         <v>1.000541105874982</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>2.6977252282004551</v>
-      </c>
-      <c r="C11">
-        <v>2.7026394802442422</v>
-      </c>
-      <c r="D11">
-        <v>2.6879788719210929</v>
-      </c>
-      <c r="E11">
-        <v>2.675176840259549</v>
-      </c>
-      <c r="F11">
-        <v>2.6829752202340522</v>
-      </c>
-      <c r="G11">
-        <v>2.7085976892977399</v>
-      </c>
-      <c r="H11">
-        <v>2.695839288957798</v>
-      </c>
-      <c r="I11">
-        <v>2.6839979518767532</v>
-      </c>
-      <c r="J11">
-        <v>2.697755753143285</v>
-      </c>
-      <c r="K11">
-        <v>2.6952468117881612</v>
-      </c>
-      <c r="L11">
-        <v>2.7104757761534479</v>
-      </c>
-      <c r="M11">
-        <v>2.7164039566874032</v>
-      </c>
-      <c r="N11">
-        <v>2.6980379187039691</v>
-      </c>
-      <c r="O11">
-        <v>2.9842290308730588</v>
-      </c>
-      <c r="P11">
-        <v>2.692554456655992</v>
-      </c>
-      <c r="Q11">
-        <v>2.6884541582204742</v>
-      </c>
-      <c r="R11">
-        <v>2.6844681011624481</v>
-      </c>
-      <c r="S11">
-        <v>2.7013937519434972</v>
-      </c>
-      <c r="T11">
-        <v>2.6921019227618759</v>
-      </c>
-      <c r="U11">
-        <v>3.1135506185739632</v>
-      </c>
-      <c r="V11">
-        <v>2.6809438318424532</v>
-      </c>
-      <c r="W11">
-        <v>3.087568757853365</v>
-      </c>
-      <c r="X11">
-        <v>2.692266878223649</v>
-      </c>
-      <c r="Y11">
-        <v>2.6896647071209059</v>
-      </c>
-      <c r="Z11">
-        <v>2.8564437165540251</v>
-      </c>
-      <c r="AA11">
-        <v>2.699495518543626</v>
-      </c>
-      <c r="AB11">
-        <v>2.7151432806331641</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>0.83091930130650538</v>
-      </c>
-      <c r="C12">
-        <v>0.70224035603981394</v>
-      </c>
-      <c r="D12">
-        <v>0.76045797574981222</v>
-      </c>
-      <c r="E12">
-        <v>0.66529067048747048</v>
-      </c>
-      <c r="F12">
-        <v>0.72357729166115525</v>
-      </c>
-      <c r="G12">
-        <v>0.91138872377492453</v>
-      </c>
-      <c r="H12">
-        <v>0.81933740458869342</v>
-      </c>
-      <c r="I12">
-        <v>0.73105486918953566</v>
-      </c>
-      <c r="J12">
-        <v>0.83187953859087282</v>
-      </c>
-      <c r="K12">
-        <v>0.8142152969143559</v>
-      </c>
-      <c r="L12">
-        <v>0.9260494161752143</v>
-      </c>
-      <c r="M12">
-        <v>0.97257275124584086</v>
-      </c>
-      <c r="N12">
-        <v>0.83457226147757946</v>
-      </c>
-      <c r="O12">
-        <v>1.2809968240706231</v>
-      </c>
-      <c r="P12">
-        <v>0.79302234762599222</v>
-      </c>
-      <c r="Q12">
-        <v>0.76375097257406022</v>
-      </c>
-      <c r="R12">
-        <v>0.73466569151556305</v>
-      </c>
-      <c r="S12">
-        <v>0.8583681328175875</v>
-      </c>
-      <c r="T12">
-        <v>0.79107137912311232</v>
-      </c>
-      <c r="U12">
-        <v>1.576778336812898</v>
-      </c>
-      <c r="V12">
-        <v>0.70749884303823174</v>
-      </c>
-      <c r="W12">
-        <v>1.494831767464212</v>
-      </c>
-      <c r="X12">
-        <v>0.79208130892279527</v>
-      </c>
-      <c r="Y12">
-        <v>0.77242591394795346</v>
-      </c>
-      <c r="Z12">
-        <v>1.0495751642510041</v>
-      </c>
-      <c r="AA12">
-        <v>0.84516922045874343</v>
-      </c>
-      <c r="AB12">
-        <v>0.96110812490636799</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>0.56108428725442527</v>
-      </c>
-      <c r="C13">
-        <v>0.28917462083020262</v>
-      </c>
-      <c r="D13">
-        <v>0.45099470953361209</v>
-      </c>
-      <c r="E13">
-        <v>0.306389872690987</v>
-      </c>
-      <c r="F13">
-        <v>0.39447616193501078</v>
-      </c>
-      <c r="G13">
-        <v>0.68389373692747601</v>
-      </c>
-      <c r="H13">
-        <v>0.53978173593368606</v>
-      </c>
-      <c r="I13">
-        <v>0.40602838631912108</v>
-      </c>
-      <c r="J13">
-        <v>0.56102773555652308</v>
-      </c>
-      <c r="K13">
-        <v>0.53308943374967499</v>
-      </c>
-      <c r="L13">
-        <v>0.70510759192534944</v>
-      </c>
-      <c r="M13">
-        <v>0.77399362067927413</v>
-      </c>
-      <c r="N13">
-        <v>0.56461627033634565</v>
-      </c>
-      <c r="O13">
-        <v>0.51636573873513525</v>
-      </c>
-      <c r="P13">
-        <v>0.50267804398729654</v>
-      </c>
-      <c r="Q13">
-        <v>0.4563632869276355</v>
-      </c>
-      <c r="R13">
-        <v>0.41133893878037658</v>
-      </c>
-      <c r="S13">
-        <v>0.6025219505363868</v>
-      </c>
-      <c r="T13">
-        <v>0.49756646547736072</v>
-      </c>
-      <c r="U13">
-        <v>0.67400361250276886</v>
-      </c>
-      <c r="V13">
-        <v>0.36884289823365568</v>
-      </c>
-      <c r="W13">
-        <v>0.59914538164539721</v>
-      </c>
-      <c r="X13">
-        <v>0.49942971330136171</v>
-      </c>
-      <c r="Y13">
-        <v>0.46708740971797441</v>
-      </c>
-      <c r="Z13">
-        <v>0.47479280935990992</v>
-      </c>
-      <c r="AA13">
-        <v>0.5810805310543149</v>
-      </c>
-      <c r="AB13">
-        <v>0.75493878172990714</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>7.201509147590575</v>
-      </c>
-      <c r="C14">
-        <v>2.3690173696670409</v>
-      </c>
-      <c r="D14">
-        <v>5.8424988034715328</v>
-      </c>
-      <c r="E14">
-        <v>2.6229364932708141</v>
-      </c>
-      <c r="F14">
-        <v>4.7507651567336859</v>
-      </c>
-      <c r="G14">
-        <v>9.7623358664544764</v>
-      </c>
-      <c r="H14">
-        <v>8.0637415590696246</v>
-      </c>
-      <c r="I14">
-        <v>4.9432109467456398</v>
-      </c>
-      <c r="J14">
-        <v>7.6186317096889997</v>
-      </c>
-      <c r="K14">
-        <v>7.5261113628326397</v>
-      </c>
-      <c r="L14">
-        <v>10.617775484559591</v>
-      </c>
-      <c r="M14">
-        <v>12.873562858018969</v>
-      </c>
-      <c r="N14">
-        <v>8.0140839435858524</v>
-      </c>
-      <c r="O14">
-        <v>6.2230102481311098</v>
-      </c>
-      <c r="P14">
-        <v>6.2118582411528473</v>
-      </c>
-      <c r="Q14">
-        <v>5.8292090060939286</v>
-      </c>
-      <c r="R14">
-        <v>5.1245238481714042</v>
-      </c>
-      <c r="S14">
-        <v>8.2264751152192233</v>
-      </c>
-      <c r="T14">
-        <v>6.8608957010215628</v>
-      </c>
-      <c r="U14">
-        <v>9.8582965631257053</v>
-      </c>
-      <c r="V14">
-        <v>3.7014914647720349</v>
-      </c>
-      <c r="W14">
-        <v>8.5633224565050359</v>
-      </c>
-      <c r="X14">
-        <v>6.7807471740115091</v>
-      </c>
-      <c r="Y14">
-        <v>5.9561131136264889</v>
-      </c>
-      <c r="Z14">
-        <v>5.7478256184272842</v>
-      </c>
-      <c r="AA14">
-        <v>8.2551702361729706</v>
-      </c>
-      <c r="AB14">
-        <v>12.86121957113432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>0.58643405991136088</v>
-      </c>
-      <c r="C15">
-        <v>0.40884063097892021</v>
-      </c>
-      <c r="D15">
-        <v>0.57066071968232912</v>
-      </c>
-      <c r="E15">
-        <v>0.42605588283970491</v>
-      </c>
-      <c r="F15">
-        <v>0.41982593459194328</v>
-      </c>
-      <c r="G15">
-        <v>0.80355974707618949</v>
-      </c>
-      <c r="H15">
-        <v>0.65944774608240375</v>
-      </c>
-      <c r="I15">
-        <v>0.43137815897605541</v>
-      </c>
-      <c r="J15">
-        <v>0.58637750821345658</v>
-      </c>
-      <c r="K15">
-        <v>0.65275544389838891</v>
-      </c>
-      <c r="L15">
-        <v>0.82477360207407069</v>
-      </c>
-      <c r="M15">
-        <v>0.89365963082799238</v>
-      </c>
-      <c r="N15">
-        <v>0.59108886159986751</v>
-      </c>
-      <c r="O15">
-        <v>0.5428381257310172</v>
-      </c>
-      <c r="P15">
-        <v>0.6274030016379053</v>
-      </c>
-      <c r="Q15">
-        <v>0.57602929707635075</v>
-      </c>
-      <c r="R15">
-        <v>0.53100494892909444</v>
-      </c>
-      <c r="S15">
-        <v>0.62787172319331974</v>
-      </c>
-      <c r="T15">
-        <v>0.522916238134295</v>
-      </c>
-      <c r="U15">
-        <v>0.70230296907974565</v>
-      </c>
-      <c r="V15">
-        <v>0.48850890838237071</v>
-      </c>
-      <c r="W15">
-        <v>0.72387003274204753</v>
-      </c>
-      <c r="X15">
-        <v>0.61909572345007424</v>
-      </c>
-      <c r="Y15">
-        <v>0.4987283558070133</v>
-      </c>
-      <c r="Z15">
-        <v>0.50014258201684347</v>
-      </c>
-      <c r="AA15">
-        <v>0.70074654120302682</v>
-      </c>
-      <c r="AB15">
-        <v>0.78315167819963694</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>0.67157737572079301</v>
-      </c>
-      <c r="C16">
-        <v>0.39966770929657042</v>
-      </c>
-      <c r="D16">
-        <v>0.56148779799997839</v>
-      </c>
-      <c r="E16">
-        <v>0.41688296115735413</v>
-      </c>
-      <c r="F16">
-        <v>0.50496925040137564</v>
-      </c>
-      <c r="G16">
-        <v>0.79438682539384364</v>
-      </c>
-      <c r="H16">
-        <v>0.6502748244000538</v>
-      </c>
-      <c r="I16">
-        <v>0.51652147478548815</v>
-      </c>
-      <c r="J16">
-        <v>0.67152082402289082</v>
-      </c>
-      <c r="K16">
-        <v>0.64358252221604062</v>
-      </c>
-      <c r="L16">
-        <v>0.81560068039171885</v>
-      </c>
-      <c r="M16">
-        <v>0.88448670914564032</v>
-      </c>
-      <c r="N16">
-        <v>0.67510935880271261</v>
-      </c>
-      <c r="O16">
-        <v>0.62647537538056064</v>
-      </c>
-      <c r="P16">
-        <v>0.61278768063272404</v>
-      </c>
-      <c r="Q16">
-        <v>0.56685637539400191</v>
-      </c>
-      <c r="R16">
-        <v>0.52183202724674416</v>
-      </c>
-      <c r="S16">
-        <v>0.71301503900275498</v>
-      </c>
-      <c r="T16">
-        <v>0.60805955394372868</v>
-      </c>
-      <c r="U16">
-        <v>0.78726963615335199</v>
-      </c>
-      <c r="V16">
-        <v>0.47933598670002292</v>
-      </c>
-      <c r="W16">
-        <v>0.70963847011176429</v>
-      </c>
-      <c r="X16">
-        <v>0.60992280176772828</v>
-      </c>
-      <c r="Y16">
-        <v>0.58053008210438628</v>
-      </c>
-      <c r="Z16">
-        <v>0.58528589782627727</v>
-      </c>
-      <c r="AA16">
-        <v>0.69157361952068275</v>
-      </c>
-      <c r="AB16">
-        <v>0.86543187019627632</v>
-      </c>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>0.72406797443880966</v>
-      </c>
-      <c r="C17">
-        <v>0.58190253238600886</v>
-      </c>
-      <c r="D17">
-        <v>0.74372262108941756</v>
-      </c>
-      <c r="E17">
-        <v>0.53003281200399666</v>
-      </c>
-      <c r="F17">
-        <v>0.5776724829119253</v>
-      </c>
-      <c r="G17">
-        <v>1.0035249586047379</v>
-      </c>
-      <c r="H17">
-        <v>0.83250964748949274</v>
-      </c>
-      <c r="I17">
-        <v>0.69875629787492832</v>
-      </c>
-      <c r="J17">
-        <v>0.85375564711232865</v>
-      </c>
-      <c r="K17">
-        <v>0.82581734530547879</v>
-      </c>
-      <c r="L17">
-        <v>0.99783550348115568</v>
-      </c>
-      <c r="M17">
-        <v>1.0667215322351189</v>
-      </c>
-      <c r="N17">
-        <v>0.75677070224298781</v>
-      </c>
-      <c r="O17">
-        <v>0.73615863606334608</v>
-      </c>
-      <c r="P17">
-        <v>0.71569608560714937</v>
-      </c>
-      <c r="Q17">
-        <v>0.59384927278181565</v>
-      </c>
-      <c r="R17">
-        <v>0.70406685033618222</v>
-      </c>
-      <c r="S17">
-        <v>0.89524986209218782</v>
-      </c>
-      <c r="T17">
-        <v>0.79029437703316685</v>
-      </c>
-      <c r="U17">
-        <v>0.90651495099510249</v>
-      </c>
-      <c r="V17">
-        <v>0.62628652706192733</v>
-      </c>
-      <c r="W17">
-        <v>0.89189879156029439</v>
-      </c>
-      <c r="X17">
-        <v>0.64880701506449689</v>
-      </c>
-      <c r="Y17">
-        <v>0.89204080503577732</v>
-      </c>
-      <c r="Z17">
-        <v>0.63536643097396417</v>
-      </c>
-      <c r="AA17">
-        <v>0.87380844261011936</v>
-      </c>
-      <c r="AB17">
-        <v>1.1831953845859691</v>
-      </c>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B18">
-        <v>1.010950742521338</v>
-      </c>
-      <c r="C18">
-        <v>0.87485157804493174</v>
-      </c>
-      <c r="D18">
-        <v>1.0366716667483391</v>
-      </c>
-      <c r="E18">
-        <v>0.86072233476531657</v>
-      </c>
-      <c r="F18">
-        <v>0.66707282093091025</v>
-      </c>
-      <c r="G18">
-        <v>1.2695707133155409</v>
-      </c>
-      <c r="H18">
-        <v>1.1254586931484141</v>
-      </c>
-      <c r="I18">
-        <v>0.99170534353384898</v>
-      </c>
-      <c r="J18">
-        <v>1.146704692771251</v>
-      </c>
-      <c r="K18">
-        <v>1.1187663909644019</v>
-      </c>
-      <c r="L18">
-        <v>1.2907845491400769</v>
-      </c>
-      <c r="M18">
-        <v>1.359670577894001</v>
-      </c>
-      <c r="N18">
-        <v>1.15029322755107</v>
-      </c>
-      <c r="O18">
-        <v>1.1470501439940559</v>
-      </c>
-      <c r="P18">
-        <v>1.143150792828193</v>
-      </c>
-      <c r="Q18">
-        <v>1.042040263315698</v>
-      </c>
-      <c r="R18">
-        <v>0.99701589599510565</v>
-      </c>
-      <c r="S18">
-        <v>1.1881989077511119</v>
-      </c>
-      <c r="T18">
-        <v>1.0832434226920891</v>
-      </c>
-      <c r="U18">
-        <v>1.2626301536375391</v>
-      </c>
-      <c r="V18">
-        <v>1.1112420986615841</v>
-      </c>
-      <c r="W18">
-        <v>1.1848223388601249</v>
-      </c>
-      <c r="X18">
-        <v>1.0851066705160879</v>
-      </c>
-      <c r="Y18">
-        <v>1.055713950852748</v>
-      </c>
-      <c r="Z18">
-        <v>0.97858811825465919</v>
-      </c>
-      <c r="AA18">
-        <v>1.1667574882690439</v>
-      </c>
-      <c r="AB18">
-        <v>1.3406157389446349</v>
-      </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <f>(B11-B2)/B11*100</f>
-        <v>1.1704090225251473</v>
-      </c>
-      <c r="C22">
-        <f t="shared" ref="C22:AB22" si="0">(C11-C2)/C11*100</f>
-        <v>0.64048877501112289</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>0.73544646373772715</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>0.75083313074983327</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>0.8357351956093837</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>0.98420962839164217</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="0"/>
-        <v>1.0986650855330216</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="0"/>
-        <v>0.7982155275717977</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="0"/>
-        <v>0.84709771968081526</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>0.84913136117861288</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>1.2092649556215544</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>1.2077010216649249</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>1.1860021656524418</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="0"/>
-        <v>1.8313781450240045</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="0"/>
-        <v>0.60553244765459724</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>1.0414884581058621</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="0"/>
-        <v>0.79778385948614505</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
-        <v>0.9252080538888332</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>1.0161309717350393</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="0"/>
-        <v>1.2576899044762431</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="0"/>
-        <v>0.36809366303975266</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="0"/>
-        <v>1.0148340774952274</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="0"/>
-        <v>0.26815776262371072</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="0"/>
-        <v>-0.1002442197161494</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="0"/>
-        <v>1.1501793992339129</v>
-      </c>
-      <c r="AA22">
-        <f t="shared" si="0"/>
-        <v>0.88178617859662523</v>
-      </c>
-      <c r="AB22">
-        <f t="shared" si="0"/>
-        <v>0.96917434449711459</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <f t="shared" ref="B23:AB23" si="1">(B12-B3)/B12*100</f>
-        <v>14.140167082408507</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
-        <v>0.32458204904220961</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="1"/>
-        <v>4.0801630133726592</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>4.9676211442251388</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>6.9906913734622353</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>8.9978910563017092</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>12.671651074741735</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>5.8875005594094709</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>6.4472373589714032</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>6.7259355791295699</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="1"/>
-        <v>13.729756601456389</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="1"/>
-        <v>13.125714472458395</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="1"/>
-        <v>14.503566411378344</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="1"/>
-        <v>11.755136220510124</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="1"/>
-        <v>0.69126920741102005</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="1"/>
-        <v>12.017421101713845</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="1"/>
-        <v>5.8364602960322749</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="1"/>
-        <v>8.0804914121192848</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="1"/>
-        <v>10.98332654428882</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="1"/>
-        <v>7.0468814338634527</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="1"/>
-        <v>-5.9225196183853868</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="1"/>
-        <v>2.8788793744165151</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="1"/>
-        <v>-7.7946062557915248</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="1"/>
-        <v>-17.566177303022414</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="1"/>
-        <v>7.1891763844916232</v>
-      </c>
-      <c r="AA23">
-        <f t="shared" si="1"/>
-        <v>7.1470644383040005</v>
-      </c>
-      <c r="AB23">
-        <f t="shared" si="1"/>
-        <v>8.2662045932295101</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <f t="shared" ref="B24:AB24" si="2">(B13-B4)/B13*100</f>
-        <v>31.875452638295069</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="2"/>
-        <v>-0.95237484150730367</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="2"/>
-        <v>10.088036067237281</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="2"/>
-        <v>16.019609546234381</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="2"/>
-        <v>19.132660826336735</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="2"/>
-        <v>18.03176199018159</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="2"/>
-        <v>29.039935140563927</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="2"/>
-        <v>15.810593465168724</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="2"/>
-        <v>14.300392012432257</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="2"/>
-        <v>15.140154087948678</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="2"/>
-        <v>27.290867404740176</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="2"/>
-        <v>24.821996536176449</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="2"/>
-        <v>32.525027220089079</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="2"/>
-        <v>32.784211186253927</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="2"/>
-        <v>1.2662238861281192</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="2"/>
-        <v>30.34266065970888</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="2"/>
-        <v>15.584956692261093</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="2"/>
-        <v>17.346054396231967</v>
-      </c>
-      <c r="T24">
-        <f t="shared" si="2"/>
-        <v>26.366537984147026</v>
-      </c>
-      <c r="U24">
-        <f t="shared" si="2"/>
-        <v>20.76257132136999</v>
-      </c>
-      <c r="V24">
-        <f t="shared" si="2"/>
-        <v>-18.17145396416479</v>
-      </c>
-      <c r="W24">
-        <f t="shared" si="2"/>
-        <v>5.4296018857143178</v>
-      </c>
-      <c r="X24">
-        <f t="shared" si="2"/>
-        <v>-19.272302970893378</v>
-      </c>
-      <c r="Y24">
-        <f t="shared" si="2"/>
-        <v>-44.622498114260587</v>
-      </c>
-      <c r="Z24">
-        <f t="shared" si="2"/>
-        <v>18.964333998760694</v>
-      </c>
-      <c r="AA24">
-        <f t="shared" si="2"/>
-        <v>15.67341968758284</v>
-      </c>
-      <c r="AB24">
-        <f t="shared" si="2"/>
-        <v>15.812998640611747</v>
-      </c>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25">
-        <f t="shared" ref="B25:AB25" si="3">(B14-B5)/B14*100</f>
-        <v>49.888706809807829</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="3"/>
-        <v>2.0934960546650783</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="3"/>
-        <v>24.903567108591123</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="3"/>
-        <v>36.5916198576003</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="3"/>
-        <v>38.270790481878358</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="3"/>
-        <v>34.330148169666124</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="3"/>
-        <v>45.678824669945442</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="3"/>
-        <v>31.558172084017382</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="3"/>
-        <v>28.892614918756188</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="3"/>
-        <v>35.125971336671221</v>
-      </c>
-      <c r="L25">
-        <f t="shared" si="3"/>
-        <v>43.678278040508289</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="3"/>
-        <v>40.602588725604072</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="3"/>
-        <v>49.590098492025632</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="3"/>
-        <v>51.882076071967674</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="3"/>
-        <v>13.394688767613665</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="3"/>
-        <v>52.461367034130937</v>
-      </c>
-      <c r="R25">
-        <f t="shared" si="3"/>
-        <v>29.772016457125279</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="3"/>
-        <v>32.212468299906241</v>
-      </c>
-      <c r="T25">
-        <f t="shared" si="3"/>
-        <v>43.478242308265656</v>
-      </c>
-      <c r="U25">
-        <f t="shared" si="3"/>
-        <v>36.785732072654866</v>
-      </c>
-      <c r="V25">
-        <f t="shared" si="3"/>
-        <v>-18.225167569454566</v>
-      </c>
-      <c r="W25">
-        <f t="shared" si="3"/>
-        <v>15.182586532951934</v>
-      </c>
-      <c r="X25">
-        <f t="shared" si="3"/>
-        <v>-13.98412306039141</v>
-      </c>
-      <c r="Y25">
-        <f t="shared" si="3"/>
-        <v>-56.861529273135567</v>
-      </c>
-      <c r="Z25">
-        <f t="shared" si="3"/>
-        <v>40.684815513419416</v>
-      </c>
-      <c r="AA25">
-        <f t="shared" si="3"/>
-        <v>28.197916582815225</v>
-      </c>
-      <c r="AB25">
-        <f t="shared" si="3"/>
-        <v>28.443775279039052</v>
-      </c>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B26">
-        <f t="shared" ref="B26:AB26" si="4">(B15-B6)/B15*100</f>
-        <v>30.857805449294766</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="4"/>
-        <v>22.912286379616141</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="4"/>
-        <v>12.657367725360455</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="4"/>
-        <v>17.794984447644449</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="4"/>
-        <v>18.480590349982545</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="4"/>
-        <v>27.346672633990423</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="4"/>
-        <v>27.824248987291927</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="4"/>
-        <v>15.371205330061603</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="4"/>
-        <v>2.1568093266573607</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="4"/>
-        <v>16.460173483944974</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="4"/>
-        <v>35.022791683637791</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="4"/>
-        <v>32.288515929808895</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="4"/>
-        <v>31.440158984388827</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="4"/>
-        <v>31.569667664894631</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="4"/>
-        <v>5.3916578373780188</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="4"/>
-        <v>28.680291291042725</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="4"/>
-        <v>17.107394657212062</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="4"/>
-        <v>16.982180659152817</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="4"/>
-        <v>12.164267578863514</v>
-      </c>
-      <c r="U26">
-        <f t="shared" si="4"/>
-        <v>10.32742286677369</v>
-      </c>
-      <c r="V26">
-        <f t="shared" si="4"/>
-        <v>6.019264866157279</v>
-      </c>
-      <c r="W26">
-        <f t="shared" si="4"/>
-        <v>17.898620301385229</v>
-      </c>
-      <c r="X26">
-        <f t="shared" si="4"/>
-        <v>2.8615133672054125E-2</v>
-      </c>
-      <c r="Y26">
-        <f t="shared" si="4"/>
-        <v>-41.337008690700458</v>
-      </c>
-      <c r="Z26">
-        <f t="shared" si="4"/>
-        <v>18.425509551425591</v>
-      </c>
-      <c r="AA26">
-        <f t="shared" si="4"/>
-        <v>16.811971265390603</v>
-      </c>
-      <c r="AB26">
-        <f t="shared" si="4"/>
-        <v>15.597753189184635</v>
-      </c>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B27">
-        <f t="shared" ref="B27:AB27" si="5">(B16-B7)/B16*100</f>
-        <v>30.412092815154786</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="5"/>
-        <v>5.6643435838545138</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="5"/>
-        <v>12.625223165432589</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="5"/>
-        <v>17.864735865584684</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="5"/>
-        <v>19.974753830790277</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="5"/>
-        <v>18.720183258311433</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="5"/>
-        <v>28.010440780771233</v>
-      </c>
-      <c r="I27">
-        <f t="shared" si="5"/>
-        <v>17.344501724037077</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="5"/>
-        <v>15.728736963865646</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="5"/>
-        <v>16.486330286909912</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="5"/>
-        <v>26.707010157663944</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="5"/>
-        <v>24.592031293543172</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="5"/>
-        <v>30.96300939624847</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="5"/>
-        <v>31.067353261447245</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="5"/>
-        <v>5.1743718339147939</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="5"/>
-        <v>28.907735579252659</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="5"/>
-        <v>17.151031247474272</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="5"/>
-        <v>18.219302085978395</v>
-      </c>
-      <c r="T27">
-        <f t="shared" si="5"/>
-        <v>25.751364103399276</v>
-      </c>
-      <c r="U27">
-        <f t="shared" si="5"/>
-        <v>21.090046730373558</v>
-      </c>
-      <c r="V27">
-        <f t="shared" si="5"/>
-        <v>-8.6852521034656149</v>
-      </c>
-      <c r="W27">
-        <f t="shared" si="5"/>
-        <v>8.1624362213556854</v>
-      </c>
-      <c r="X27">
-        <f t="shared" si="5"/>
-        <v>-11.617704516644704</v>
-      </c>
-      <c r="Y27">
-        <f t="shared" si="5"/>
-        <v>-31.499152288653075</v>
-      </c>
-      <c r="Z27">
-        <f t="shared" si="5"/>
-        <v>19.722647202489917</v>
-      </c>
-      <c r="AA27">
-        <f t="shared" si="5"/>
-        <v>16.840979131157223</v>
-      </c>
-      <c r="AB27">
-        <f t="shared" si="5"/>
-        <v>16.728184258416409</v>
-      </c>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B28">
-        <f t="shared" ref="B28:AB28" si="6">(B17-B8)/B17*100</f>
-        <v>30.506182800613924</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="6"/>
-        <v>12.566626997334874</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="6"/>
-        <v>16.320070492288398</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="6"/>
-        <v>20.176493022306907</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="6"/>
-        <v>21.254837843349879</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="6"/>
-        <v>20.549069313098013</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="6"/>
-        <v>27.943437506950332</v>
-      </c>
-      <c r="I28">
-        <f t="shared" si="6"/>
-        <v>20.046337329610893</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="6"/>
-        <v>18.284940554228672</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="6"/>
-        <v>18.961833346834638</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="6"/>
-        <v>26.889153984484992</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="6"/>
-        <v>25.123728047687404</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="6"/>
-        <v>30.82674483099947</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="6"/>
-        <v>30.719162769221995</v>
-      </c>
-      <c r="P28">
-        <f t="shared" si="6"/>
-        <v>8.5864974443329167</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="6"/>
-        <v>29.276678403738021</v>
-      </c>
-      <c r="R28">
-        <f t="shared" si="6"/>
-        <v>19.882564059122064</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="6"/>
-        <v>20.150054191296132</v>
-      </c>
-      <c r="T28">
-        <f t="shared" si="6"/>
-        <v>26.201704605774008</v>
-      </c>
-      <c r="U28">
-        <f t="shared" si="6"/>
-        <v>22.05408641632723</v>
-      </c>
-      <c r="V28">
-        <f t="shared" si="6"/>
-        <v>1.6324916118029009E-2</v>
-      </c>
-      <c r="W28">
-        <f t="shared" si="6"/>
-        <v>12.155797041929043</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="6"/>
-        <v>-8.9030054711056916</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="6"/>
-        <v>-10.981184129650339</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="6"/>
-        <v>20.688849001195994</v>
-      </c>
-      <c r="AA28">
-        <f t="shared" si="6"/>
-        <v>19.1065603493232</v>
-      </c>
-      <c r="AB28">
-        <f t="shared" si="6"/>
-        <v>19.490358113438493</v>
-      </c>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <f t="shared" ref="B29:AB29" si="7">(B18-B9)/B18*100</f>
-        <v>34.551689798904903</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="7"/>
-        <v>24.9118996764557</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="7"/>
-        <v>25.677626897172157</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="7"/>
-        <v>29.996036792022419</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="7"/>
-        <v>27.035182115074512</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="7"/>
-        <v>27.096897646123359</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="7"/>
-        <v>33.537298355847575</v>
-      </c>
-      <c r="I29">
-        <f t="shared" si="7"/>
-        <v>28.727451470228949</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="7"/>
-        <v>26.242618623375495</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="7"/>
-        <v>26.94098946015967</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="7"/>
-        <v>32.005817859036163</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="7"/>
-        <v>30.36153390418308</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="7"/>
-        <v>35.150843255333875</v>
-      </c>
-      <c r="O29">
-        <f t="shared" si="7"/>
-        <v>35.450354485874058</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="7"/>
-        <v>21.636094317889576</v>
-      </c>
-      <c r="Q29">
-        <f t="shared" si="7"/>
-        <v>34.467857144871111</v>
-      </c>
-      <c r="R29">
-        <f t="shared" si="7"/>
-        <v>28.565559525038996</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="7"/>
-        <v>27.369993100065347</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="7"/>
-        <v>32.484593723099209</v>
-      </c>
-      <c r="U29">
-        <f t="shared" si="7"/>
-        <v>28.575912816357889</v>
-      </c>
-      <c r="V29">
-        <f t="shared" si="7"/>
-        <v>19.046453951414648</v>
-      </c>
-      <c r="W29">
-        <f t="shared" si="7"/>
-        <v>21.372603673295156</v>
-      </c>
-      <c r="X29">
-        <f t="shared" si="7"/>
-        <v>11.46841777720905</v>
-      </c>
-      <c r="Y29">
-        <f t="shared" si="7"/>
-        <v>1.1784954190112182</v>
-      </c>
-      <c r="Z29">
-        <f t="shared" si="7"/>
-        <v>28.658119262262481</v>
-      </c>
-      <c r="AA29">
-        <f t="shared" si="7"/>
-        <v>26.721179616748351</v>
-      </c>
-      <c r="AB29">
-        <f t="shared" si="7"/>
-        <v>25.367047632707035</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D1B86-4CDA-4D57-8C4B-3C685E066077}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DAA9C0-1E0B-47B9-B4C6-1607C8E8CF7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="image SSP2-Base 2020" sheetId="1" r:id="rId1"/>
@@ -5996,6 +5996,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="58.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -595,10 +595,10 @@
         <v>2.687978871921092</v>
       </c>
       <c r="E2" t="n">
-        <v>2.675176840259549</v>
+        <v>2.675176840259548</v>
       </c>
       <c r="F2" t="n">
-        <v>2.682975220234051</v>
+        <v>2.682975220234052</v>
       </c>
       <c r="G2" t="n">
         <v>2.708597689297739</v>
@@ -631,25 +631,25 @@
         <v>2.692554456655992</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.688454158220473</v>
+        <v>2.688454158220474</v>
       </c>
       <c r="R2" t="n">
         <v>2.684468101162447</v>
       </c>
       <c r="S2" t="n">
-        <v>2.701393751943496</v>
+        <v>2.701393751943495</v>
       </c>
       <c r="T2" t="n">
         <v>2.692101922761875</v>
       </c>
       <c r="U2" t="n">
-        <v>3.113550618573962</v>
+        <v>3.113550618573961</v>
       </c>
       <c r="V2" t="n">
-        <v>2.680943831842453</v>
+        <v>2.680943831842452</v>
       </c>
       <c r="W2" t="n">
-        <v>3.087568757853364</v>
+        <v>3.087568757853365</v>
       </c>
       <c r="X2" t="n">
         <v>2.692266878223649</v>
@@ -661,7 +661,7 @@
         <v>2.856443716554024</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.699495518543625</v>
+        <v>2.699495518543626</v>
       </c>
       <c r="AB2" t="n">
         <v>2.715143280633164</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.293573998311548</v>
+        <v>0.919037594972943</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7710374888781516</v>
+        <v>0.7639434923307629</v>
       </c>
       <c r="D3" t="n">
-        <v>1.076774728549627</v>
+        <v>0.8523018554938656</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6732935898995865</v>
+        <v>0.6436785705769053</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9617525146588018</v>
+        <v>0.8129137532584743</v>
       </c>
       <c r="G3" t="n">
-        <v>1.544792598796785</v>
+        <v>1.007066868391658</v>
       </c>
       <c r="H3" t="n">
-        <v>1.264640252771907</v>
+        <v>0.920818255993013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9845778443440452</v>
+        <v>0.8205561967678987</v>
       </c>
       <c r="J3" t="n">
-        <v>1.298036154075481</v>
+        <v>0.9246210070061189</v>
       </c>
       <c r="K3" t="n">
-        <v>1.245583734971959</v>
+        <v>0.9108054719143576</v>
       </c>
       <c r="L3" t="n">
-        <v>1.593458522689595</v>
+        <v>1.027678516960402</v>
       </c>
       <c r="M3" t="n">
-        <v>1.748031149281003</v>
+        <v>1.087683777099</v>
       </c>
       <c r="N3" t="n">
-        <v>1.308703829672049</v>
+        <v>0.9312044994928721</v>
       </c>
       <c r="O3" t="n">
-        <v>1.492081867591025</v>
+        <v>1.176846472485359</v>
       </c>
       <c r="P3" t="n">
-        <v>1.17371617274</v>
+        <v>0.8800846679811848</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.086569343472962</v>
+        <v>0.8545204612754762</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9964255034761896</v>
+        <v>0.8252882385401963</v>
       </c>
       <c r="S3" t="n">
-        <v>1.380464554812898</v>
+        <v>0.9508471853431525</v>
       </c>
       <c r="T3" t="n">
-        <v>1.173396594882046</v>
+        <v>0.886319954360705</v>
       </c>
       <c r="U3" t="n">
-        <v>1.940203388970966</v>
+        <v>1.410830773680003</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9077249219366931</v>
+        <v>0.7890357080600784</v>
       </c>
       <c r="W3" t="n">
-        <v>1.763850755357105</v>
+        <v>1.340199088347982</v>
       </c>
       <c r="X3" t="n">
-        <v>1.176259397017422</v>
+        <v>0.8861111291758029</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.112990613968058</v>
+        <v>0.8622618287639392</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.284794643463427</v>
+        <v>1.027997285190209</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.340880945368945</v>
+        <v>0.9416638093524805</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.706412038167079</v>
+        <v>1.079309635116534</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.201509147590619</v>
+        <v>7.201509147590636</v>
       </c>
       <c r="C4" t="n">
-        <v>2.369017369667042</v>
+        <v>2.369017369667043</v>
       </c>
       <c r="D4" t="n">
-        <v>5.842498803471538</v>
+        <v>5.84249880347155</v>
       </c>
       <c r="E4" t="n">
-        <v>2.622936493270815</v>
+        <v>2.622936493270806</v>
       </c>
       <c r="F4" t="n">
-        <v>4.750765156733681</v>
+        <v>4.750765156733676</v>
       </c>
       <c r="G4" t="n">
-        <v>9.762335866454469</v>
+        <v>9.762335866454466</v>
       </c>
       <c r="H4" t="n">
-        <v>8.063741559069614</v>
+        <v>8.063741559069621</v>
       </c>
       <c r="I4" t="n">
-        <v>4.943210946745641</v>
+        <v>4.943210946745638</v>
       </c>
       <c r="J4" t="n">
-        <v>7.618631709688994</v>
+        <v>7.618631709688993</v>
       </c>
       <c r="K4" t="n">
-        <v>7.526111362832665</v>
+        <v>7.526111362832643</v>
       </c>
       <c r="L4" t="n">
-        <v>10.61777548455963</v>
+        <v>10.6177754845596</v>
       </c>
       <c r="M4" t="n">
-        <v>12.87356285801897</v>
+        <v>12.873562858019</v>
       </c>
       <c r="N4" t="n">
-        <v>8.014083943585863</v>
+        <v>8.01408394358587</v>
       </c>
       <c r="O4" t="n">
-        <v>6.223010248131098</v>
+        <v>6.223010248131103</v>
       </c>
       <c r="P4" t="n">
-        <v>6.211858241152841</v>
+        <v>6.211858241152838</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.829209006093929</v>
+        <v>5.829209006093933</v>
       </c>
       <c r="R4" t="n">
-        <v>5.124523848171405</v>
+        <v>5.124523848171408</v>
       </c>
       <c r="S4" t="n">
-        <v>8.226475115219213</v>
+        <v>8.22647511521922</v>
       </c>
       <c r="T4" t="n">
-        <v>6.860895701021572</v>
+        <v>6.860895701021563</v>
       </c>
       <c r="U4" t="n">
         <v>9.858296563125711</v>
       </c>
       <c r="V4" t="n">
-        <v>3.701491464772029</v>
+        <v>3.701491464772027</v>
       </c>
       <c r="W4" t="n">
-        <v>8.563322456505039</v>
+        <v>8.563322456505048</v>
       </c>
       <c r="X4" t="n">
-        <v>6.780747174011522</v>
+        <v>6.780747174011524</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.956113113626468</v>
+        <v>5.956113113626483</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.747825618427277</v>
+        <v>5.74782561842729</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.255170236172969</v>
+        <v>8.255170236172958</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.86121957113432</v>
+        <v>12.86121957113431</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7240679744388107</v>
+        <v>0.7240679744388077</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5819025323860083</v>
+        <v>0.5819025323860065</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7437226210894173</v>
+        <v>0.7437226210894166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5300328120039963</v>
+        <v>0.530032812003995</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5776724829119253</v>
+        <v>0.5776724829119236</v>
       </c>
       <c r="G5" t="n">
-        <v>1.003524958604737</v>
+        <v>1.003524958604735</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8325096474894924</v>
+        <v>0.8325096474894911</v>
       </c>
       <c r="I5" t="n">
-        <v>0.698756297874927</v>
+        <v>0.6987562978749254</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8537556471123272</v>
+        <v>0.8537556471123267</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8258173453054792</v>
+        <v>0.8258173453054811</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9978355034811577</v>
+        <v>0.997835503481156</v>
       </c>
       <c r="M5" t="n">
-        <v>1.066721532235118</v>
+        <v>1.066721532235119</v>
       </c>
       <c r="N5" t="n">
-        <v>8.014083943585863</v>
+        <v>0.7567707022429879</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7361586360633452</v>
+        <v>0.736158636063343</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7156960856071494</v>
+        <v>0.7156960856071465</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5938492727818162</v>
+        <v>0.593849272781815</v>
       </c>
       <c r="R5" t="n">
-        <v>0.704066850336182</v>
+        <v>0.7040668503361812</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8952498620921892</v>
+        <v>0.895249862092189</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7902943770331665</v>
+        <v>0.7902943770331682</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9065149509951004</v>
+        <v>0.9065149509950996</v>
       </c>
       <c r="V5" t="n">
         <v>0.6262865270619262</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8918987915602952</v>
+        <v>0.8918987915602923</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6488070150644974</v>
+        <v>0.6488070150644953</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8920408050357769</v>
+        <v>0.8920408050357782</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6353664309739627</v>
+        <v>0.6353664309739602</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8738084426101198</v>
+        <v>0.8738084426101211</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.183195384585969</v>
+        <v>1.183195384585968</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.010950742521337</v>
+        <v>1.010950742521338</v>
       </c>
       <c r="C6" t="n">
-        <v>0.874851578044932</v>
+        <v>0.8748515780449302</v>
       </c>
       <c r="D6" t="n">
-        <v>1.03667166674834</v>
+        <v>1.036671666748338</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8607223347653196</v>
+        <v>0.8607223347653202</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6670728209309118</v>
+        <v>0.6670728209309112</v>
       </c>
       <c r="G6" t="n">
-        <v>1.26957071331554</v>
+        <v>1.269570713315539</v>
       </c>
       <c r="H6" t="n">
         <v>1.125458693148415</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9917053435338504</v>
+        <v>0.9917053435338509</v>
       </c>
       <c r="J6" t="n">
-        <v>1.146704692771252</v>
+        <v>1.146704692771251</v>
       </c>
       <c r="K6" t="n">
-        <v>1.118766390964402</v>
+        <v>1.118766390964403</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29078454914008</v>
+        <v>1.290784549140077</v>
       </c>
       <c r="M6" t="n">
-        <v>1.359670577894003</v>
+        <v>1.359670577894001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.014083943585863</v>
+        <v>1.150293227551069</v>
       </c>
       <c r="O6" t="n">
-        <v>1.147050143994056</v>
+        <v>1.147050143994055</v>
       </c>
       <c r="P6" t="n">
-        <v>1.143150792828193</v>
+        <v>1.143150792828192</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.0420402633157</v>
+        <v>1.042040263315696</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9970158959951066</v>
+        <v>0.9970158959951033</v>
       </c>
       <c r="S6" t="n">
         <v>1.188198907751113</v>
       </c>
       <c r="T6" t="n">
-        <v>1.08324342269209</v>
+        <v>1.083243422692089</v>
       </c>
       <c r="U6" t="n">
-        <v>1.262630153637541</v>
+        <v>1.262630153637542</v>
       </c>
       <c r="V6" t="n">
-        <v>1.111242098661584</v>
+        <v>1.111242098661583</v>
       </c>
       <c r="W6" t="n">
         <v>1.184822338860124</v>
       </c>
       <c r="X6" t="n">
-        <v>1.085106670516089</v>
+        <v>1.085106670516087</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.055713950852747</v>
+        <v>1.055713950852743</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9785881182546592</v>
+        <v>0.9785881182546557</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.166757488269045</v>
+        <v>1.166757488269043</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.340615738944636</v>
+        <v>1.340615738944634</v>
       </c>
     </row>
   </sheetData>
@@ -1185,7 +1185,7 @@
         <v>2.591161317580907</v>
       </c>
       <c r="C2" t="n">
-        <v>2.615593628781775</v>
+        <v>2.615593628781777</v>
       </c>
       <c r="D2" t="n">
         <v>2.594727952435032</v>
@@ -1200,13 +1200,13 @@
         <v>2.59872364120971</v>
       </c>
       <c r="H2" t="n">
-        <v>2.597785132037784</v>
+        <v>2.597785132037785</v>
       </c>
       <c r="I2" t="n">
-        <v>2.59286011954347</v>
+        <v>2.592860119543472</v>
       </c>
       <c r="J2" t="n">
-        <v>2.595516863958471</v>
+        <v>2.595516863958469</v>
       </c>
       <c r="K2" t="n">
         <v>2.592584851912545</v>
@@ -1218,22 +1218,22 @@
         <v>2.591016167949278</v>
       </c>
       <c r="N2" t="n">
-        <v>2.592286474770313</v>
+        <v>2.592286474770312</v>
       </c>
       <c r="O2" t="n">
-        <v>2.813460402251724</v>
+        <v>2.813460402251725</v>
       </c>
       <c r="P2" t="n">
-        <v>2.591223101927594</v>
+        <v>2.591223101927593</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.594228978259872</v>
+        <v>2.594228978259873</v>
       </c>
       <c r="R2" t="n">
-        <v>2.559838440562479</v>
+        <v>2.559838440562478</v>
       </c>
       <c r="S2" t="n">
-        <v>2.582913350421483</v>
+        <v>2.582913350421484</v>
       </c>
       <c r="T2" t="n">
         <v>2.586722848151323</v>
@@ -1245,16 +1245,16 @@
         <v>2.601771717679689</v>
       </c>
       <c r="W2" t="n">
-        <v>2.981880794231905</v>
+        <v>2.981880794231904</v>
       </c>
       <c r="X2" t="n">
-        <v>2.633860364769502</v>
+        <v>2.633860364769503</v>
       </c>
       <c r="Y2" t="n">
         <v>2.616760860298328</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.745407690195294</v>
+        <v>2.745407690195296</v>
       </c>
       <c r="AA2" t="n">
         <v>2.625615103947895</v>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4081029658783051</v>
+        <v>0.5797931044775508</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4160439459241248</v>
+        <v>0.5989694707355258</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4905608052013315</v>
+        <v>0.6076953588325148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3456708403240991</v>
+        <v>0.4970030143532489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1734424350420015</v>
+        <v>0.4986159930676781</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5821744393604382</v>
+        <v>0.6378535779513194</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5624966128621054</v>
+        <v>0.6330466951848065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4469537231293707</v>
+        <v>0.5926454513232178</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5081867562328466</v>
+        <v>0.6132698394333544</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4406596890472216</v>
+        <v>0.5910440457192809</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.07730150576242298</v>
+        <v>0.4182260774375355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4119323414981343</v>
+        <v>0.5805810259671321</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4336742202346489</v>
+        <v>0.5879220651332568</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4961494722816163</v>
+        <v>0.761820820250475</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4096260426529795</v>
+        <v>0.5804253278490608</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4788798456714538</v>
+        <v>0.6036119896608476</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.3265134543515023</v>
+        <v>0.3219064928357973</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2177443541372435</v>
+        <v>0.5165864670245703</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3036256973140375</v>
+        <v>0.5426683046379246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9557697113540029</v>
+        <v>1.016850550477679</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6525169953768253</v>
+        <v>0.661375323192461</v>
       </c>
       <c r="W3" t="n">
-        <v>1.488056413192009</v>
+        <v>1.186936213939955</v>
       </c>
       <c r="X3" t="n">
-        <v>1.402276151341616</v>
+        <v>0.9176113491493632</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.002197890793459</v>
+        <v>0.7848826792004776</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7543523383461411</v>
+        <v>0.7917512389247244</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.207345123445843</v>
+        <v>0.8556425782180381</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5005177929969772</v>
+        <v>0.6113997563238704</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.30973738508077</v>
+        <v>-0.3097373850807679</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4701036641305647</v>
+        <v>-0.4701036641305667</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3613809147568448</v>
+        <v>0.3613809147568444</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05098926981614411</v>
+        <v>-0.05098926981614428</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.393494662688552</v>
+        <v>-2.393494662688556</v>
       </c>
       <c r="G4" t="n">
-        <v>1.039424504857789</v>
+        <v>1.03942450485779</v>
       </c>
       <c r="H4" t="n">
-        <v>1.032445080019692</v>
+        <v>1.032445080019694</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01924255494901383</v>
+        <v>-0.01924255494901461</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4698389699437635</v>
+        <v>0.4698389699437626</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03353573899332218</v>
+        <v>-0.03353573899332596</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.08255292115955</v>
+        <v>-4.082552921159548</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3050563357538484</v>
+        <v>-0.3050563357538488</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1432132706433138</v>
+        <v>-0.1432132706433147</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.364298868113137</v>
+        <v>-1.364298868113139</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2881144671127025</v>
+        <v>-0.2881144671126993</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2554625847034619</v>
+        <v>0.2554625847034617</v>
       </c>
       <c r="R4" t="n">
-        <v>-7.062576164584046</v>
+        <v>-7.062576164584051</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.772412471149402</v>
+        <v>-1.7724124711494</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.305690862716663</v>
+        <v>-1.305690862716664</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9852245974293851</v>
+        <v>0.9852245974293889</v>
       </c>
       <c r="V4" t="n">
-        <v>1.589506478177886</v>
+        <v>1.589506478177892</v>
       </c>
       <c r="W4" t="n">
-        <v>5.833329571398556</v>
+        <v>5.833329571398559</v>
       </c>
       <c r="X4" t="n">
-        <v>7.971382448702354</v>
+        <v>7.971382448702359</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.832201099424167</v>
+        <v>4.832201099424169</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.210659338609751</v>
+        <v>1.210659338609752</v>
       </c>
       <c r="AA4" t="n">
         <v>6.599230175613494</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4664906834129977</v>
+        <v>0.466490683412997</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1739736180607257</v>
+        <v>0.1739736180607271</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2289158088775491</v>
+        <v>0.2289158088775485</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2772254367120032</v>
+        <v>0.277225436712002</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2188023010504296</v>
+        <v>0.2188023010504284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0710743030217876</v>
+        <v>0.07107430302178817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3354147901803355</v>
+        <v>0.3354147901803352</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3117576866971822</v>
+        <v>0.31175768669718</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2561274049562294</v>
+        <v>0.2561274049562287</v>
       </c>
       <c r="J5" t="n">
-        <v>0.285898051371327</v>
+        <v>0.2858980513713277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2530181304355527</v>
+        <v>0.2530181304355539</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.202274164179619e-05</v>
+        <v>-3.202274164200436e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2393951168108955</v>
+        <v>0.2393951168108932</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1432132706433138</v>
+        <v>0.2008393856702321</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1325324154843336</v>
+        <v>0.1325324154843335</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1989532366011842</v>
+        <v>0.1989532366011841</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1962501896973011</v>
+        <v>0.1962501896972998</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1168676498569248</v>
+        <v>-0.1168676498569277</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1437740719834976</v>
+        <v>0.1437740719834981</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1868041012975786</v>
+        <v>0.1868041012975783</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2869294134879727</v>
+        <v>0.2869294134879748</v>
       </c>
       <c r="V5" t="n">
-        <v>0.337391057444082</v>
+        <v>0.3373910574440854</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5879903036643122</v>
+        <v>0.587990303664312</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6496758024392867</v>
+        <v>0.6496758024392878</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5877752306323799</v>
+        <v>0.587775230632378</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2713042031319063</v>
+        <v>0.2713042031319065</v>
       </c>
       <c r="AA5" t="n">
         <v>0.626110021841455</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3477895184345985</v>
+        <v>0.3477895184345969</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2746299530984415</v>
+        <v>0.2746299530984416</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3218498566745972</v>
+        <v>0.3218498566745985</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3701594845090514</v>
+        <v>0.3701594845090524</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3325135931512162</v>
+        <v>0.3325135931512146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08981452010382428</v>
+        <v>0.08981452010382511</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4152926542290639</v>
+        <v>0.4152926542290637</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4046917344942307</v>
+        <v>0.404691734494232</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3490614527532788</v>
+        <v>0.349061452753279</v>
       </c>
       <c r="J6" t="n">
-        <v>0.378832099168379</v>
+        <v>0.3788320991683785</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3459521782326076</v>
+        <v>0.3459521782326062</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09290202505540747</v>
+        <v>0.09290202505540868</v>
       </c>
       <c r="M6" t="n">
-        <v>0.332329164607744</v>
+        <v>0.3323291646077455</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1432132706433138</v>
+        <v>0.3425818711508146</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2791693293259365</v>
+        <v>0.2791693293259356</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3528595384534375</v>
+        <v>0.3528595384534401</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3645233685635137</v>
+        <v>0.3645233685635144</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.02393360205987596</v>
+        <v>-0.02393360205987585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.23670811978055</v>
+        <v>0.2367081197805493</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2797381490946274</v>
+        <v>0.2797381490946284</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4111375838069658</v>
+        <v>0.4111375838069661</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5118808974615947</v>
+        <v>0.5118808974615972</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6809119770268508</v>
+        <v>0.6809119770268522</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8121780836259402</v>
+        <v>0.8121780836259409</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6190313144633421</v>
+        <v>0.6190313144633451</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3950664408733428</v>
+        <v>0.3950664408733445</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7190440696385033</v>
+        <v>0.7190440696385056</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3749513197801814</v>
+        <v>0.374951319780183</v>
       </c>
     </row>
   </sheetData>
@@ -1778,22 +1778,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.682229752605385</v>
+        <v>2.682229752605383</v>
       </c>
       <c r="C2" t="n">
         <v>2.691300341479792</v>
       </c>
       <c r="D2" t="n">
-        <v>2.681665665225076</v>
+        <v>2.681665665225075</v>
       </c>
       <c r="E2" t="n">
-        <v>2.665825827116728</v>
+        <v>2.665825827116727</v>
       </c>
       <c r="F2" t="n">
-        <v>2.670107189662629</v>
+        <v>2.670107189662628</v>
       </c>
       <c r="G2" t="n">
-        <v>2.697963103764205</v>
+        <v>2.697963103764204</v>
       </c>
       <c r="H2" t="n">
         <v>2.679878466737921</v>
@@ -1802,13 +1802,13 @@
         <v>2.67072324234416</v>
       </c>
       <c r="J2" t="n">
-        <v>2.687292138134789</v>
+        <v>2.687292138134787</v>
       </c>
       <c r="K2" t="n">
-        <v>2.682226114281998</v>
+        <v>2.682226114281997</v>
       </c>
       <c r="L2" t="n">
-        <v>2.696846221106005</v>
+        <v>2.696846221106004</v>
       </c>
       <c r="M2" t="n">
         <v>2.703461048296316</v>
@@ -1817,43 +1817,43 @@
         <v>2.683647587341869</v>
       </c>
       <c r="O2" t="n">
-        <v>2.96250916258444</v>
+        <v>2.962509162584441</v>
       </c>
       <c r="P2" t="n">
-        <v>2.686504644108035</v>
+        <v>2.686504644108034</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.674911672284112</v>
+        <v>2.674911672284111</v>
       </c>
       <c r="R2" t="n">
-        <v>2.67557068255223</v>
+        <v>2.675570682552229</v>
       </c>
       <c r="S2" t="n">
         <v>2.690320466637253</v>
       </c>
       <c r="T2" t="n">
-        <v>2.676861538395905</v>
+        <v>2.676861538395904</v>
       </c>
       <c r="U2" t="n">
-        <v>3.09388242342168</v>
+        <v>3.093882423421679</v>
       </c>
       <c r="V2" t="n">
-        <v>2.666291948787912</v>
+        <v>2.666291948787911</v>
       </c>
       <c r="W2" t="n">
-        <v>3.075843740811689</v>
+        <v>3.075843740811688</v>
       </c>
       <c r="X2" t="n">
-        <v>2.684745160324282</v>
+        <v>2.684745160324281</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.679056607388795</v>
+        <v>2.679056607388794</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.838272881279905</v>
+        <v>2.838272881279904</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.683317754036063</v>
+        <v>2.68331775403606</v>
       </c>
       <c r="AB2" t="n">
         <v>2.704435994329943</v>
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.140120526305009</v>
+        <v>0.8610215861796742</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7177902440356173</v>
+        <v>0.7391826580618438</v>
       </c>
       <c r="D3" t="n">
-        <v>1.135738601888801</v>
+        <v>0.8672725534991891</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6630658178017322</v>
+        <v>0.6354925682968564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8671946692850024</v>
+        <v>0.7731101816552444</v>
       </c>
       <c r="G3" t="n">
-        <v>1.503142778908771</v>
+        <v>0.9860673713582356</v>
       </c>
       <c r="H3" t="n">
-        <v>1.097381735347201</v>
+        <v>0.8557785112308193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8808523752530512</v>
+        <v>0.7785435495881191</v>
       </c>
       <c r="J3" t="n">
-        <v>1.260602839616695</v>
+        <v>0.9056681866039387</v>
       </c>
       <c r="K3" t="n">
-        <v>1.147350534333827</v>
+        <v>0.8657714501888223</v>
       </c>
       <c r="L3" t="n">
-        <v>1.482422551826982</v>
+        <v>0.9837145912459326</v>
       </c>
       <c r="M3" t="n">
-        <v>1.651487202555862</v>
+        <v>1.047469191571945</v>
       </c>
       <c r="N3" t="n">
-        <v>1.179532806247416</v>
+        <v>0.8807116377260052</v>
       </c>
       <c r="O3" t="n">
-        <v>1.366548201542346</v>
+        <v>1.123271883484728</v>
       </c>
       <c r="P3" t="n">
-        <v>1.237686316838608</v>
+        <v>0.8958994425593492</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9769390260048051</v>
+        <v>0.8104579330234689</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9950801313309293</v>
+        <v>0.8191895155921367</v>
       </c>
       <c r="S3" t="n">
-        <v>1.328644658225927</v>
+        <v>0.926564418171684</v>
       </c>
       <c r="T3" t="n">
-        <v>1.023807229611965</v>
+        <v>0.8279799843830318</v>
       </c>
       <c r="U3" t="n">
-        <v>1.781117305071772</v>
+        <v>1.347678974451668</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7734546263577274</v>
+        <v>0.7369574568837203</v>
       </c>
       <c r="W3" t="n">
-        <v>1.792405525835504</v>
+        <v>1.341564080352442</v>
       </c>
       <c r="X3" t="n">
-        <v>1.206910224478887</v>
+        <v>0.8906953044341508</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07175539580214</v>
+        <v>0.8416469797523185</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.168726853737806</v>
+        <v>0.9793365463253307</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.170388527665668</v>
+        <v>0.8763442023075317</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66193370470598</v>
+        <v>1.05805543264278</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.487509371340867</v>
+        <v>5.487509371340852</v>
       </c>
       <c r="C4" t="n">
-        <v>1.771208169308958</v>
+        <v>1.771208169308959</v>
       </c>
       <c r="D4" t="n">
-        <v>6.139471097371681</v>
+        <v>6.139471097371659</v>
       </c>
       <c r="E4" t="n">
-        <v>2.427413171459142</v>
+        <v>2.427413171459187</v>
       </c>
       <c r="F4" t="n">
-        <v>3.543752586402499</v>
+        <v>3.543752586402505</v>
       </c>
       <c r="G4" t="n">
-        <v>8.796266655041483</v>
+        <v>8.796266655041467</v>
       </c>
       <c r="H4" t="n">
-        <v>5.957031160095713</v>
+        <v>5.957031160095715</v>
       </c>
       <c r="I4" t="n">
-        <v>3.713497284775155</v>
+        <v>3.713497284775156</v>
       </c>
       <c r="J4" t="n">
-        <v>6.868214991183051</v>
+        <v>6.868214991183055</v>
       </c>
       <c r="K4" t="n">
-        <v>5.824081096676911</v>
+        <v>5.824081096676917</v>
       </c>
       <c r="L4" t="n">
-        <v>9.030055196030069</v>
+        <v>9.030055196030402</v>
       </c>
       <c r="M4" t="n">
-        <v>11.17105978826165</v>
+        <v>11.17105978826166</v>
       </c>
       <c r="N4" t="n">
-        <v>6.390361199836809</v>
+        <v>6.39036119983681</v>
       </c>
       <c r="O4" t="n">
-        <v>4.888848507199926</v>
+        <v>4.88884850719994</v>
       </c>
       <c r="P4" t="n">
-        <v>6.454228719832454</v>
+        <v>6.454228719832448</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.494752982680538</v>
+        <v>4.494752982680518</v>
       </c>
       <c r="R4" t="n">
-        <v>4.883957437296939</v>
+        <v>4.883957437296929</v>
       </c>
       <c r="S4" t="n">
-        <v>7.276576158064038</v>
+        <v>7.276576158064036</v>
       </c>
       <c r="T4" t="n">
-        <v>5.049764498306426</v>
+        <v>5.049764498306429</v>
       </c>
       <c r="U4" t="n">
-        <v>7.922265817922328</v>
+        <v>7.922265817922324</v>
       </c>
       <c r="V4" t="n">
-        <v>2.321730680112153</v>
+        <v>2.321730680112151</v>
       </c>
       <c r="W4" t="n">
-        <v>8.426132031688525</v>
+        <v>8.426132031688532</v>
       </c>
       <c r="X4" t="n">
-        <v>6.709948648856277</v>
+        <v>6.709948648856273</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.239543688284162</v>
+        <v>5.239543688284169</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.458463244612345</v>
+        <v>4.458463244612379</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.195869540788691</v>
+        <v>6.195869540788692</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.72054524777623</v>
+        <v>11.7205452477763</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6210438303216445</v>
+        <v>0.6210438303216415</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5134648043323037</v>
+        <v>0.5134648043323036</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7294577448657928</v>
+        <v>0.7294577448657927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4894195721429417</v>
+        <v>0.489419572142946</v>
       </c>
       <c r="F5" t="n">
-        <v>0.501996150979418</v>
+        <v>0.5019961509794177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9373463400352713</v>
+        <v>0.9373463400352716</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7092705158014894</v>
+        <v>0.7092705158014893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.605858044662652</v>
+        <v>0.6058580446626514</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7925894383766177</v>
+        <v>0.7925894383766169</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7357882747830398</v>
+        <v>0.7357882747830392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.90092910694162</v>
+        <v>0.9009291069416343</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9773976815073429</v>
+        <v>0.9773976815073421</v>
       </c>
       <c r="N5" t="n">
-        <v>6.390361199836809</v>
+        <v>0.6628664694068106</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6440366892038283</v>
+        <v>0.6440366892038275</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7135964081833137</v>
+        <v>0.7135964081833145</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.515824767973045</v>
+        <v>0.5158247679730453</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6606121117454478</v>
+        <v>0.6606121117454475</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8272177082216838</v>
+        <v>0.8272177082216834</v>
       </c>
       <c r="T5" t="n">
-        <v>0.675192922322789</v>
+        <v>0.6751929223227899</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7954500291955033</v>
+        <v>0.7954500291955037</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5217999762215167</v>
+        <v>0.5217999762215172</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8651352636529323</v>
+        <v>0.8651352636529308</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6374188618793727</v>
+        <v>0.637418861879374</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8144203897978313</v>
+        <v>0.8144203897978308</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.553232194665927</v>
+        <v>0.5532321946659271</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7481188479842906</v>
+        <v>0.7481188479842911</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.103250165459464</v>
+        <v>1.103250165459465</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8383755497573858</v>
+        <v>0.8383755497573856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7260759733783729</v>
+        <v>0.7260759733783722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9420689139118612</v>
+        <v>0.9420689139118609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7377481162680224</v>
+        <v>0.7377481162680236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5577807530564888</v>
+        <v>0.5577807530564883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.126155994173126</v>
+        <v>1.126155994173125</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9218816848475601</v>
+        <v>0.9218816848475594</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8184692137087218</v>
+        <v>0.8184692137087214</v>
       </c>
       <c r="J6" t="n">
-        <v>1.005200607422688</v>
+        <v>1.005200607422686</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9483994438291106</v>
+        <v>0.9483994438291102</v>
       </c>
       <c r="L6" t="n">
-        <v>1.11354027598769</v>
+        <v>1.113540275987685</v>
       </c>
       <c r="M6" t="n">
-        <v>1.19000885055331</v>
+        <v>1.190008850553309</v>
       </c>
       <c r="N6" t="n">
-        <v>6.390361199836809</v>
+        <v>0.964455635950258</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9576493429281254</v>
+        <v>0.9576493429281243</v>
       </c>
       <c r="P6" t="n">
-        <v>1.04113559326625</v>
+        <v>1.041135593266249</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8657794714230854</v>
+        <v>0.8657794714230839</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8732232807915192</v>
+        <v>0.8732232807915189</v>
       </c>
       <c r="S6" t="n">
-        <v>1.039828877267753</v>
+        <v>1.039828877267752</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8878040913688585</v>
+        <v>0.8878040913688573</v>
       </c>
       <c r="U6" t="n">
-        <v>1.063908490870368</v>
+        <v>1.063908490870367</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8925999234451064</v>
+        <v>0.8925999234451065</v>
       </c>
       <c r="W6" t="n">
-        <v>1.077723874133053</v>
+        <v>1.077723874133052</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9768532276951373</v>
+        <v>0.9768532276951428</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9125984054251638</v>
+        <v>0.9125984054251631</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8164017089471266</v>
+        <v>0.816401708947126</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9607300170303615</v>
+        <v>0.9607300170303609</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.195958238797989</v>
+        <v>1.19595823879799</v>
       </c>
     </row>
   </sheetData>
@@ -2374,82 +2374,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.672047349274316</v>
+        <v>2.672047349274317</v>
       </c>
       <c r="C2" t="n">
-        <v>2.687877399708461</v>
+        <v>2.687877399708463</v>
       </c>
       <c r="D2" t="n">
-        <v>2.680392009183838</v>
+        <v>2.68039200918384</v>
       </c>
       <c r="E2" t="n">
-        <v>2.661787447051866</v>
+        <v>2.661787447051867</v>
       </c>
       <c r="F2" t="n">
         <v>2.662032718959221</v>
       </c>
       <c r="G2" t="n">
-        <v>2.69109515201663</v>
+        <v>2.691095152016632</v>
       </c>
       <c r="H2" t="n">
-        <v>2.671928997654846</v>
+        <v>2.671928997654847</v>
       </c>
       <c r="I2" t="n">
-        <v>2.665675243809018</v>
+        <v>2.665675243809019</v>
       </c>
       <c r="J2" t="n">
-        <v>2.681084827723791</v>
+        <v>2.681084827723792</v>
       </c>
       <c r="K2" t="n">
-        <v>2.672134965941316</v>
+        <v>2.672134965941318</v>
       </c>
       <c r="L2" t="n">
-        <v>2.686569635473953</v>
+        <v>2.686569635473955</v>
       </c>
       <c r="M2" t="n">
-        <v>2.693237291451481</v>
+        <v>2.693237291451482</v>
       </c>
       <c r="N2" t="n">
-        <v>2.672293837671492</v>
+        <v>2.672293837671494</v>
       </c>
       <c r="O2" t="n">
-        <v>2.943620693105744</v>
+        <v>2.943620693105745</v>
       </c>
       <c r="P2" t="n">
-        <v>2.681543926796317</v>
+        <v>2.681543926796319</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.660809367733972</v>
+        <v>2.660809367733973</v>
       </c>
       <c r="R2" t="n">
-        <v>2.668337351351107</v>
+        <v>2.668337351351108</v>
       </c>
       <c r="S2" t="n">
-        <v>2.683025969363165</v>
+        <v>2.683025969363166</v>
       </c>
       <c r="T2" t="n">
-        <v>2.669793248149384</v>
+        <v>2.669793248149387</v>
       </c>
       <c r="U2" t="n">
-        <v>3.07757320181054</v>
+        <v>3.077573201810541</v>
       </c>
       <c r="V2" t="n">
-        <v>2.665956801124033</v>
+        <v>2.665956801124035</v>
       </c>
       <c r="W2" t="n">
-        <v>3.062320160911438</v>
+        <v>3.062320160911441</v>
       </c>
       <c r="X2" t="n">
-        <v>2.687005250438642</v>
+        <v>2.687005250438643</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.682830579193503</v>
+        <v>2.682830579193504</v>
       </c>
       <c r="Z2" t="n">
         <v>2.832022085052257</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.677650603776432</v>
+        <v>2.677650603776433</v>
       </c>
       <c r="AB2" t="n">
         <v>2.696698545906433</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.006306300927394</v>
+        <v>0.8140692125159072</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7579983300413619</v>
+        <v>0.749052195618946</v>
       </c>
       <c r="D3" t="n">
-        <v>1.207849368332499</v>
+        <v>0.8889294720840278</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6717537622308868</v>
+        <v>0.6365357279312429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7802644041162226</v>
+        <v>0.739612535707641</v>
       </c>
       <c r="G3" t="n">
-        <v>1.445231181502139</v>
+        <v>0.9619212541661866</v>
       </c>
       <c r="H3" t="n">
-        <v>1.013337966909747</v>
+        <v>0.8238391881482795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8649128281128056</v>
+        <v>0.770062439061027</v>
       </c>
       <c r="J3" t="n">
-        <v>1.218161368648327</v>
+        <v>0.8875706696859518</v>
       </c>
       <c r="K3" t="n">
-        <v>1.013668691264318</v>
+        <v>0.8149630787413779</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3454460434412</v>
+        <v>0.9332505916106235</v>
       </c>
       <c r="M3" t="n">
-        <v>1.515445192197986</v>
+        <v>0.9973792798214125</v>
       </c>
       <c r="N3" t="n">
-        <v>1.017020348730291</v>
+        <v>0.8217334048080231</v>
       </c>
       <c r="O3" t="n">
-        <v>1.241860084961567</v>
+        <v>1.072017949328526</v>
       </c>
       <c r="P3" t="n">
-        <v>1.223837624347083</v>
+        <v>0.8874466642508173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7501076978515245</v>
+        <v>0.7285041361655062</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9279444267384136</v>
+        <v>0.7928487208830266</v>
       </c>
       <c r="S3" t="n">
-        <v>1.260911388900975</v>
+        <v>0.9000547344725752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9607315331654239</v>
+        <v>0.8033473015762319</v>
       </c>
       <c r="U3" t="n">
-        <v>1.614393400982204</v>
+        <v>1.283632896784622</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8662366232262358</v>
+        <v>0.7646209248852265</v>
       </c>
       <c r="W3" t="n">
-        <v>1.709668955452535</v>
+        <v>1.306462489110656</v>
       </c>
       <c r="X3" t="n">
-        <v>1.361400756309618</v>
+        <v>0.9411291578644839</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.260789112525045</v>
+        <v>0.9040852000606451</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.17105732819291</v>
+        <v>0.9726311146053055</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.140219639760518</v>
+        <v>0.8633962609118244</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.583898794147158</v>
+        <v>1.02811630568665</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.170838344833223</v>
+        <v>4.170838344833241</v>
       </c>
       <c r="C4" t="n">
         <v>2.006870883029004</v>
       </c>
       <c r="D4" t="n">
-        <v>6.380363568734667</v>
+        <v>6.380363568734687</v>
       </c>
       <c r="E4" t="n">
-        <v>2.385795812483975</v>
+        <v>2.385795812483972</v>
       </c>
       <c r="F4" t="n">
-        <v>2.542952330450364</v>
+        <v>2.542952330450367</v>
       </c>
       <c r="G4" t="n">
-        <v>7.678075947073514</v>
+        <v>7.678075947073521</v>
       </c>
       <c r="H4" t="n">
-        <v>4.862250212122925</v>
+        <v>4.862250212122932</v>
       </c>
       <c r="I4" t="n">
-        <v>3.360799954183374</v>
+        <v>3.36079995418337</v>
       </c>
       <c r="J4" t="n">
-        <v>6.057281150282477</v>
+        <v>6.057281150282474</v>
       </c>
       <c r="K4" t="n">
-        <v>4.193324208790642</v>
+        <v>4.193324208790648</v>
       </c>
       <c r="L4" t="n">
-        <v>7.277801746178191</v>
+        <v>7.27780174617818</v>
       </c>
       <c r="M4" t="n">
-        <v>9.274190589615394</v>
+        <v>9.274190589615372</v>
       </c>
       <c r="N4" t="n">
-        <v>4.600288343215079</v>
+        <v>4.60028834321508</v>
       </c>
       <c r="O4" t="n">
-        <v>3.686737984293952</v>
+        <v>3.686737984293955</v>
       </c>
       <c r="P4" t="n">
-        <v>5.898502499935381</v>
+        <v>5.898502499935386</v>
       </c>
       <c r="Q4" t="n">
         <v>2.210860075239812</v>
       </c>
       <c r="R4" t="n">
-        <v>3.992983793333262</v>
+        <v>3.992983793333256</v>
       </c>
       <c r="S4" t="n">
-        <v>6.242126373335301</v>
+        <v>6.242126373335306</v>
       </c>
       <c r="T4" t="n">
-        <v>4.207565087017858</v>
+        <v>4.207565087017869</v>
       </c>
       <c r="U4" t="n">
-        <v>6.025228910518868</v>
+        <v>6.025228910518865</v>
       </c>
       <c r="V4" t="n">
-        <v>2.898378065444692</v>
+        <v>2.898378065444691</v>
       </c>
       <c r="W4" t="n">
-        <v>7.262263708540126</v>
+        <v>7.262263708540112</v>
       </c>
       <c r="X4" t="n">
-        <v>7.655309600745086</v>
+        <v>7.655309600745096</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.577334688066905</v>
+        <v>6.577334688066926</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.015071911643768</v>
+        <v>4.015071911643761</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.592627239607833</v>
+        <v>5.59262723960784</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.30577393607278</v>
+        <v>10.30577393607279</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5338350084806454</v>
+        <v>0.5338350084806467</v>
       </c>
       <c r="C5" t="n">
         <v>0.4973954961140187</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7283986577166246</v>
+        <v>0.7283986577166267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4648411168847657</v>
+        <v>0.4648411168847655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.436341791205109</v>
+        <v>0.4363417912051091</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8700948640456717</v>
+        <v>0.8700948640456724</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6328050493190001</v>
+        <v>0.6328050493190002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5621660227614738</v>
+        <v>0.5621660227614733</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7358395778613148</v>
+        <v>0.7358395778613149</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6351315558647987</v>
+        <v>0.6351315558647982</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7981777885119489</v>
+        <v>0.7981777885119484</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8757798483995793</v>
+        <v>0.875779848399578</v>
       </c>
       <c r="N5" t="n">
-        <v>4.600288343215079</v>
+        <v>0.559171474612232</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5596606512038517</v>
+        <v>0.5596606512038522</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6797854032194505</v>
+        <v>0.6797854032194511</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3871842465822392</v>
+        <v>0.3871842465822395</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5922357520793569</v>
+        <v>0.5922357520793566</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7581504496236254</v>
+        <v>0.758150449623626</v>
       </c>
       <c r="T5" t="n">
-        <v>0.608680776161496</v>
+        <v>0.6086807761614959</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6873811021582641</v>
+        <v>0.6873811021582639</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5352860565468321</v>
+        <v>0.535286056546832</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7916955481536027</v>
+        <v>0.7916955481536029</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6922721169707049</v>
+        <v>0.6922721169707053</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.855570911693031</v>
+        <v>0.8555709116930328</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5344000026431786</v>
+        <v>0.5344000026431796</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.697433222531184</v>
+        <v>0.6974332225311836</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.014385636860154</v>
+        <v>1.014385636860155</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7133704816224127</v>
+        <v>0.7133704816224142</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6699344458864072</v>
+        <v>0.6699344458864066</v>
       </c>
       <c r="D6" t="n">
         <v>0.9009376074890132</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6692548845958878</v>
+        <v>0.6692548845958872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4784551236312269</v>
+        <v>0.4784551236312268</v>
       </c>
       <c r="G6" t="n">
-        <v>1.021834547519498</v>
+        <v>1.021834547519499</v>
       </c>
       <c r="H6" t="n">
         <v>0.8053439990913878</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7347049725338635</v>
+        <v>0.734704972533863</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9083785276337039</v>
+        <v>0.9083785276337035</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8076705056371855</v>
+        <v>0.8076705056371849</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9707167382843368</v>
+        <v>0.9707167382843362</v>
       </c>
       <c r="M6" t="n">
-        <v>1.048318798171778</v>
+        <v>1.048318798171777</v>
       </c>
       <c r="N6" t="n">
-        <v>4.600288343215079</v>
+        <v>0.8094650349140958</v>
       </c>
       <c r="O6" t="n">
         <v>0.8195095224113728</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9515972076114264</v>
+        <v>0.9515972076114262</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6797426818977687</v>
+        <v>0.6797426818977703</v>
       </c>
       <c r="R6" t="n">
         <v>0.7647747018517437</v>
       </c>
       <c r="S6" t="n">
-        <v>0.930689399396013</v>
+        <v>0.9306893993960133</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7812197259338843</v>
+        <v>0.7812197259338846</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9089400885873857</v>
+        <v>0.9089400885873848</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8429863509148114</v>
+        <v>0.8429863509148122</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9642147848093532</v>
+        <v>0.9642147848093531</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9756372097032832</v>
+        <v>0.9756372097032826</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9284823775457854</v>
+        <v>0.9284823775457869</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7528512424824214</v>
+        <v>0.752851242482422</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8699721723035725</v>
+        <v>0.8699721723035723</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.082145666318568</v>
+        <v>1.082145666318569</v>
       </c>
     </row>
   </sheetData>
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.666150808726661</v>
+        <v>2.66615080872666</v>
       </c>
       <c r="C2" t="n">
-        <v>2.685329377744259</v>
+        <v>2.68532937774426</v>
       </c>
       <c r="D2" t="n">
         <v>2.668210226361532</v>
       </c>
       <c r="E2" t="n">
-        <v>2.655090726236735</v>
+        <v>2.655090726236734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.66055265202908</v>
+        <v>2.660552652029079</v>
       </c>
       <c r="G2" t="n">
         <v>2.681939410045279</v>
@@ -2991,10 +2991,10 @@
         <v>2.666221043927938</v>
       </c>
       <c r="I2" t="n">
-        <v>2.662573863465164</v>
+        <v>2.662573863465163</v>
       </c>
       <c r="J2" t="n">
-        <v>2.674903125675852</v>
+        <v>2.67490312567585</v>
       </c>
       <c r="K2" t="n">
         <v>2.672360625848101</v>
@@ -3003,10 +3003,10 @@
         <v>2.677698942461813</v>
       </c>
       <c r="M2" t="n">
-        <v>2.683597918349943</v>
+        <v>2.683597918349944</v>
       </c>
       <c r="N2" t="n">
-        <v>2.666039130558017</v>
+        <v>2.666039130558016</v>
       </c>
       <c r="O2" t="n">
         <v>2.929576512604189</v>
@@ -3018,7 +3018,7 @@
         <v>2.660454218461141</v>
       </c>
       <c r="R2" t="n">
-        <v>2.663051847938321</v>
+        <v>2.66305184793832</v>
       </c>
       <c r="S2" t="n">
         <v>2.676400239383266</v>
@@ -3033,13 +3033,13 @@
         <v>2.671075447487787</v>
       </c>
       <c r="W2" t="n">
-        <v>3.056235057932573</v>
+        <v>3.056235057932574</v>
       </c>
       <c r="X2" t="n">
-        <v>2.685047355599146</v>
+        <v>2.685047355599145</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.692360940519541</v>
+        <v>2.69236094051954</v>
       </c>
       <c r="Z2" t="n">
         <v>2.823589489375508</v>
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9481284534059123</v>
+        <v>0.7918008414569021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7943575086518191</v>
+        <v>0.7596726072199461</v>
       </c>
       <c r="D3" t="n">
-        <v>1.002055959009698</v>
+        <v>0.8137968786631924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5945790119109157</v>
+        <v>0.6076597930984116</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8247424856378933</v>
+        <v>0.7536788566567401</v>
       </c>
       <c r="G3" t="n">
-        <v>1.311759678867961</v>
+        <v>0.9128091643496121</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9587013099834213</v>
+        <v>0.8036831047623559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8713288416960064</v>
+        <v>0.7705195974867736</v>
       </c>
       <c r="J3" t="n">
-        <v>1.153485059498486</v>
+        <v>0.8627179081859904</v>
       </c>
       <c r="K3" t="n">
-        <v>1.097591402575583</v>
+        <v>0.8420589044592336</v>
       </c>
       <c r="L3" t="n">
-        <v>1.217834863367034</v>
+        <v>0.8851167056202983</v>
       </c>
       <c r="M3" t="n">
-        <v>1.368800282810187</v>
+        <v>0.9405705628747187</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9501706464361832</v>
+        <v>0.7976680028105427</v>
       </c>
       <c r="O3" t="n">
-        <v>1.142628208880246</v>
+        <v>1.033566276993093</v>
       </c>
       <c r="P3" t="n">
-        <v>1.179470435725815</v>
+        <v>0.8688627884704372</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8204099291594669</v>
+        <v>0.7507639893695106</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8833114405811995</v>
+        <v>0.7761247881310834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.185833266016445</v>
+        <v>0.8725751660333662</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9218140725910567</v>
+        <v>0.7887830824388464</v>
       </c>
       <c r="U3" t="n">
-        <v>1.661028923537464</v>
+        <v>1.294174040967793</v>
       </c>
       <c r="V3" t="n">
-        <v>1.061931046642876</v>
+        <v>0.8280166068467206</v>
       </c>
       <c r="W3" t="n">
-        <v>1.703872663189219</v>
+        <v>1.301920948420068</v>
       </c>
       <c r="X3" t="n">
-        <v>1.394110743165671</v>
+        <v>0.9481226469413534</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.56090176822422</v>
+        <v>1.008775195729786</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.110379093750714</v>
+        <v>0.9472139849804534</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.173258875183242</v>
+        <v>0.8742251236169024</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.47901304728226</v>
+        <v>0.9879466106336092</v>
       </c>
     </row>
     <row r="4">
@@ -3146,82 +3146,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.60876936306762</v>
+        <v>3.608769363067621</v>
       </c>
       <c r="C4" t="n">
-        <v>2.319422084498727</v>
+        <v>2.319422084498731</v>
       </c>
       <c r="D4" t="n">
-        <v>4.387508193130365</v>
+        <v>4.387508193130378</v>
       </c>
       <c r="E4" t="n">
-        <v>1.663161542546885</v>
+        <v>1.663161542546884</v>
       </c>
       <c r="F4" t="n">
-        <v>2.932609777314061</v>
+        <v>2.93260977731406</v>
       </c>
       <c r="G4" t="n">
-        <v>6.410911498680209</v>
+        <v>6.410911498680181</v>
       </c>
       <c r="H4" t="n">
         <v>4.380319190464685</v>
       </c>
       <c r="I4" t="n">
-        <v>3.383223929695665</v>
+        <v>3.383223929695669</v>
       </c>
       <c r="J4" t="n">
-        <v>5.417409787730309</v>
+        <v>5.417409787730307</v>
       </c>
       <c r="K4" t="n">
-        <v>4.882491642758104</v>
+        <v>4.882491642758106</v>
       </c>
       <c r="L4" t="n">
-        <v>5.980113986696724</v>
+        <v>5.980113986696725</v>
       </c>
       <c r="M4" t="n">
-        <v>7.646563076445404</v>
+        <v>7.646563076445402</v>
       </c>
       <c r="N4" t="n">
-        <v>4.039891822728028</v>
+        <v>4.039891822728027</v>
       </c>
       <c r="O4" t="n">
-        <v>2.994383337229394</v>
+        <v>2.994383337229396</v>
       </c>
       <c r="P4" t="n">
-        <v>5.379799163065051</v>
+        <v>5.379799163065063</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.771126274220373</v>
+        <v>2.77112627422037</v>
       </c>
       <c r="R4" t="n">
-        <v>3.598849764744511</v>
+        <v>3.59884976474451</v>
       </c>
       <c r="S4" t="n">
-        <v>5.576524426529561</v>
+        <v>5.57652442652956</v>
       </c>
       <c r="T4" t="n">
-        <v>3.877898843614025</v>
+        <v>3.877898843614029</v>
       </c>
       <c r="U4" t="n">
-        <v>6.231850002486561</v>
+        <v>6.231850002486541</v>
       </c>
       <c r="V4" t="n">
-        <v>4.376094486795806</v>
+        <v>4.37609448679581</v>
       </c>
       <c r="W4" t="n">
         <v>7.26318861445046</v>
       </c>
       <c r="X4" t="n">
-        <v>7.728975203239303</v>
+        <v>7.728975203239308</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.342850115272304</v>
+        <v>9.342850115272299</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.409333369537089</v>
+        <v>3.409333369537083</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.927384219207516</v>
+        <v>5.927384219207525</v>
       </c>
       <c r="AB4" t="n">
         <v>9.203003178177092</v>
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5031824745558032</v>
+        <v>0.5031824745558053</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5087770116530146</v>
+        <v>0.5087770116530151</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6223465650605307</v>
+        <v>0.6223465650605327</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4230907786740773</v>
+        <v>0.4230907786740754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4548891334033435</v>
+        <v>0.454889133403344</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7973099192868126</v>
+        <v>0.7973099192868137</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5998778344039351</v>
+        <v>0.5998778344039359</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5586812532910209</v>
+        <v>0.5586812532910206</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6976469345594682</v>
+        <v>0.6976469345594712</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6692272365394013</v>
+        <v>0.6692272365394022</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7295259784382487</v>
+        <v>0.7295259784382491</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7987213154502442</v>
+        <v>0.7987213154502441</v>
       </c>
       <c r="N5" t="n">
-        <v>4.039891822728028</v>
+        <v>0.5234829289067805</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5100168664113666</v>
+        <v>0.5100168664113642</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6542428595073041</v>
+        <v>0.654242859507303</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4199899309865475</v>
+        <v>0.419989930986547</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5640803077990507</v>
+        <v>0.5640803077990497</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7148565297331103</v>
+        <v>0.7148565297331098</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5832237788468952</v>
+        <v>0.5832237788468959</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7065913603257159</v>
+        <v>0.706591360325717</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6261842863117272</v>
+        <v>0.6261842863117285</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7834813846388112</v>
+        <v>0.7834813846388081</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7065703391126058</v>
+        <v>0.706570339112608</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9899974483483732</v>
+        <v>0.9899974483483744</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.503916429465475</v>
+        <v>0.5039164294654738</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7068537051853367</v>
+        <v>0.7068537051853381</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9525863669484922</v>
+        <v>0.9525863669484896</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6616501779456424</v>
+        <v>0.6616501779456408</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6569094306044894</v>
+        <v>0.6569094306044899</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7704789840120071</v>
+        <v>0.7704789840120068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6025397465519592</v>
+        <v>0.602539746551959</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4867284689520758</v>
+        <v>0.4867284689520743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.925556436583272</v>
+        <v>0.9255564365832719</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7480102533554085</v>
+        <v>0.7480102533554093</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7068136722424964</v>
+        <v>0.7068136722424967</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8457793535109427</v>
+        <v>0.845779353510943</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8173596554908737</v>
+        <v>0.8173596554908747</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8776583973897234</v>
+        <v>0.877658397389725</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9468537344015129</v>
+        <v>0.9468537344015133</v>
       </c>
       <c r="N6" t="n">
-        <v>4.039891822728028</v>
+        <v>0.7459554581578736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7404168018174374</v>
+        <v>0.7404168018174356</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8958176090961862</v>
+        <v>0.8958176090961854</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6828713139640061</v>
+        <v>0.6828713139640058</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7122127267505243</v>
+        <v>0.7122127267505236</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8629889486845803</v>
+        <v>0.8629889486845823</v>
       </c>
       <c r="T6" t="n">
-        <v>0.731356197798371</v>
+        <v>0.7313561977983714</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9018220617410313</v>
+        <v>0.9018220617410309</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8995898840512735</v>
+        <v>0.8995898840512747</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9315949561428842</v>
+        <v>0.9315949561428846</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9606621042129397</v>
+        <v>0.9606621042129411</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.043272410304086</v>
+        <v>1.043272410304088</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6981431682389112</v>
+        <v>0.69814316823891</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8549861241368119</v>
+        <v>0.8549861241368127</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.000541105874984</v>
+        <v>1.000541105874983</v>
       </c>
     </row>
   </sheetData>
@@ -3569,16 +3569,16 @@
         <v>2.607382439408013</v>
       </c>
       <c r="C2" t="n">
-        <v>2.631709186067935</v>
+        <v>2.631709186067934</v>
       </c>
       <c r="D2" t="n">
-        <v>2.612797427233206</v>
+        <v>2.612797427233207</v>
       </c>
       <c r="E2" t="n">
         <v>2.603529189250944</v>
       </c>
       <c r="F2" t="n">
-        <v>2.603724332808019</v>
+        <v>2.60372433280802</v>
       </c>
       <c r="G2" t="n">
         <v>2.616104402181125</v>
@@ -3608,7 +3608,7 @@
         <v>2.84741789980326</v>
       </c>
       <c r="P2" t="n">
-        <v>2.607489844775564</v>
+        <v>2.607489844775565</v>
       </c>
       <c r="Q2" t="n">
         <v>2.606977665434418</v>
@@ -3623,13 +3623,13 @@
         <v>2.606414000842316</v>
       </c>
       <c r="U2" t="n">
-        <v>3.007980459353699</v>
+        <v>3.0079804593537</v>
       </c>
       <c r="V2" t="n">
-        <v>2.607074430289847</v>
+        <v>2.607074430289848</v>
       </c>
       <c r="W2" t="n">
-        <v>3.001018681966039</v>
+        <v>3.001018681966038</v>
       </c>
       <c r="X2" t="n">
         <v>2.619000030464934</v>
@@ -3638,10 +3638,10 @@
         <v>2.61052308625209</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.753311417008083</v>
+        <v>2.753311417008084</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.620655396929055</v>
+        <v>2.620655396929056</v>
       </c>
       <c r="AB2" t="n">
         <v>2.616487247712306</v>
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5591292475442378</v>
+        <v>0.6361935368024458</v>
       </c>
       <c r="C3" t="n">
-        <v>0.548267685589391</v>
+        <v>0.6502285109151389</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6867289419521083</v>
+        <v>0.6815152411469566</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3755478557240768</v>
+        <v>0.5117766633118216</v>
       </c>
       <c r="F3" t="n">
-        <v>0.47497317066691</v>
+        <v>0.6079827852895303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75977699987264</v>
+        <v>0.7017850472266653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.577886165297449</v>
+        <v>0.6441941848775462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5753858469659852</v>
+        <v>0.6429635002382471</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6766768460472113</v>
+        <v>0.6755548112951671</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6920004880797531</v>
+        <v>0.681123539642529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5175084444675191</v>
+        <v>0.6222618522285757</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8018986838606188</v>
+        <v>0.7181493151376277</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6112070612119443</v>
+        <v>0.6546248335717109</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7681827701086223</v>
+        <v>0.866695021734724</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5614878928751074</v>
+        <v>0.6371724737225027</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5506669943099586</v>
+        <v>0.6337582886227658</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2182683903153104</v>
+        <v>0.5175425022625922</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6112849841546362</v>
+        <v>0.6523643993745871</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5377416475152719</v>
+        <v>0.629551962273717</v>
       </c>
       <c r="U3" t="n">
-        <v>1.275336300726505</v>
+        <v>1.134619926698629</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5521251704893402</v>
+        <v>0.6337929856935978</v>
       </c>
       <c r="W3" t="n">
-        <v>1.587952030307876</v>
+        <v>1.231141498572048</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8311574712866752</v>
+        <v>0.7311864010322152</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.632793938319519</v>
+        <v>0.6621030514752193</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7102089846423993</v>
+        <v>0.7834707719176441</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8678638446321606</v>
+        <v>0.7433344640593277</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.770193848121639</v>
+        <v>0.7114132478914482</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8658133019098884</v>
+        <v>0.8658133019098903</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5962518295487768</v>
+        <v>0.5962518295487783</v>
       </c>
       <c r="D4" t="n">
-        <v>2.167235692344586</v>
+        <v>2.167235692344583</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1154801352995675</v>
+        <v>0.115480135299565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1592080170208349</v>
+        <v>0.1592080170208335</v>
       </c>
       <c r="G4" t="n">
-        <v>2.428398472715363</v>
+        <v>2.428398472715358</v>
       </c>
       <c r="H4" t="n">
-        <v>1.178728586997881</v>
+        <v>1.178728586997875</v>
       </c>
       <c r="I4" t="n">
-        <v>1.121932159290449</v>
+        <v>1.121932159290447</v>
       </c>
       <c r="J4" t="n">
-        <v>1.863364161301652</v>
+        <v>1.86336416130165</v>
       </c>
       <c r="K4" t="n">
-        <v>2.046873245325419</v>
+        <v>2.046873245325418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5208276748303267</v>
+        <v>0.5208276748303158</v>
       </c>
       <c r="M4" t="n">
-        <v>3.034188607732592</v>
+        <v>3.034188607732591</v>
       </c>
       <c r="N4" t="n">
-        <v>1.394439314414733</v>
+        <v>1.394439314414703</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5868223345533697</v>
+        <v>0.5868223345533543</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8977592107856834</v>
+        <v>0.8977592107856814</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8364042274689785</v>
+        <v>0.8364042274689818</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.384241254833486</v>
+        <v>-2.384241254833485</v>
       </c>
       <c r="S4" t="n">
-        <v>1.210432067061753</v>
+        <v>1.210432067061756</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7377342758963636</v>
+        <v>0.7377342758963605</v>
       </c>
       <c r="U4" t="n">
-        <v>3.775642270189541</v>
+        <v>3.77564227018955</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8022809624133611</v>
+        <v>0.8022809624133569</v>
       </c>
       <c r="W4" t="n">
-        <v>7.066993212668418</v>
+        <v>7.06699321266842</v>
       </c>
       <c r="X4" t="n">
-        <v>3.496836387101191</v>
+        <v>3.496836387101195</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.593649912955309</v>
+        <v>1.593649912955284</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8953620907424821</v>
+        <v>0.8953620907424804</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.773683430275025</v>
+        <v>3.773683430275014</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.020840275453736</v>
+        <v>3.020840275453735</v>
       </c>
     </row>
     <row r="5">
@@ -3833,82 +3833,82 @@
         <v>0.2691395604506444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3289660437346942</v>
+        <v>0.3289660437346941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4084995144484534</v>
+        <v>0.4084995144484526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2621738785059462</v>
+        <v>0.2621738785059454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2400014580428138</v>
+        <v>0.2400014580428141</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4620675967989013</v>
+        <v>0.4620675967989012</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3555196588367787</v>
+        <v>0.3555196588367773</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3545331479190438</v>
+        <v>0.3545331479190429</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4042680512618921</v>
+        <v>0.4042680512618917</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4113180520712945</v>
+        <v>0.4113180520712946</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3267979039375592</v>
+        <v>0.3267979039375579</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4640737631866274</v>
+        <v>0.464073763186626</v>
       </c>
       <c r="N5" t="n">
-        <v>1.394439314414733</v>
+        <v>0.3116057694468026</v>
       </c>
       <c r="O5" t="n">
         <v>0.2875125299152647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3005078154679567</v>
+        <v>0.3005078154679575</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2492003155180755</v>
+        <v>0.2492003155180751</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1822573628823542</v>
+        <v>0.1822573628823545</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3728517862849986</v>
+        <v>0.3728517862849982</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3363957768421477</v>
+        <v>0.3363957768421478</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4695050302874914</v>
+        <v>0.4695050302874885</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3197970804684141</v>
+        <v>0.3197970804684137</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6702902518359219</v>
+        <v>0.6702902518359228</v>
       </c>
       <c r="X5" t="n">
         <v>0.3921652022900506</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4595569730859529</v>
+        <v>0.4595569730859517</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2703039835610035</v>
+        <v>0.2703039835610037</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4972588970077456</v>
+        <v>0.497258897007744</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5304305267507466</v>
+        <v>0.5304305267507462</v>
       </c>
     </row>
     <row r="6">
@@ -3918,85 +3918,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4080770593694242</v>
+        <v>0.4080770593694227</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4621669670390506</v>
+        <v>0.4621669670390516</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5417004377528105</v>
+        <v>0.541700437752811</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4202882761410286</v>
+        <v>0.4202882761410289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2721788150310334</v>
+        <v>0.2721788150310323</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5790542401593977</v>
+        <v>0.5790542401593988</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4887205821411361</v>
+        <v>0.4887205821411363</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4877340712234017</v>
+        <v>0.4877340712234016</v>
       </c>
       <c r="J6" t="n">
         <v>0.5374689745662495</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5445189753756542</v>
+        <v>0.5445189753756532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4599988272419169</v>
+        <v>0.459998827241917</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5972746864908008</v>
+        <v>0.5972746864908007</v>
       </c>
       <c r="N6" t="n">
-        <v>1.394439314414733</v>
+        <v>0.5054210355369761</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4886831322252909</v>
+        <v>0.4886831322252906</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5109838831528373</v>
+        <v>0.5109838831528377</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4759635500990451</v>
+        <v>0.4759635500990457</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3154582861867125</v>
+        <v>0.3154582861867126</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5060527095893556</v>
+        <v>0.5060527095893567</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4695967001465056</v>
+        <v>0.4695967001465061</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6414568185008568</v>
+        <v>0.6414568185008566</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5586306030314171</v>
+        <v>0.558630603031417</v>
       </c>
       <c r="W6" t="n">
-        <v>0.803475807579265</v>
+        <v>0.8034758075792661</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6117616945936531</v>
+        <v>0.6117616945936535</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5160107101225776</v>
+        <v>0.516010710122577</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4394665050683805</v>
+        <v>0.4394665050683816</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6304598203121026</v>
+        <v>0.6304598203121025</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5819500507033748</v>
+        <v>0.5819500507033751</v>
       </c>
     </row>
   </sheetData>
@@ -4162,22 +4162,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.578661005554993</v>
+        <v>2.578661005554992</v>
       </c>
       <c r="C2" t="n">
         <v>2.612154650568046</v>
       </c>
       <c r="D2" t="n">
-        <v>2.59026590497706</v>
+        <v>2.590265904977059</v>
       </c>
       <c r="E2" t="n">
         <v>2.571425869113111</v>
       </c>
       <c r="F2" t="n">
-        <v>2.574259222330099</v>
+        <v>2.5742592223301</v>
       </c>
       <c r="G2" t="n">
-        <v>2.596376206182956</v>
+        <v>2.596376206182955</v>
       </c>
       <c r="H2" t="n">
         <v>2.588339760696087</v>
@@ -4195,13 +4195,13 @@
         <v>2.570763668896675</v>
       </c>
       <c r="M2" t="n">
-        <v>2.586515632607682</v>
+        <v>2.586515632607683</v>
       </c>
       <c r="N2" t="n">
-        <v>2.593658048516239</v>
+        <v>2.593658048516238</v>
       </c>
       <c r="O2" t="n">
-        <v>2.815742996841018</v>
+        <v>2.815742996841019</v>
       </c>
       <c r="P2" t="n">
         <v>2.578514970313353</v>
@@ -4216,28 +4216,28 @@
         <v>2.583350758721186</v>
       </c>
       <c r="T2" t="n">
-        <v>2.582358142704383</v>
+        <v>2.582358142704382</v>
       </c>
       <c r="U2" t="n">
-        <v>2.963574910947649</v>
+        <v>2.963574910947648</v>
       </c>
       <c r="V2" t="n">
-        <v>2.590693934375046</v>
+        <v>2.590693934375045</v>
       </c>
       <c r="W2" t="n">
-        <v>2.95505953418782</v>
+        <v>2.955059534187819</v>
       </c>
       <c r="X2" t="n">
         <v>2.623311659945407</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.598846766769228</v>
+        <v>2.598846766769229</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.726913032651644</v>
+        <v>2.726913032651643</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.613842824574037</v>
+        <v>2.613842824574036</v>
       </c>
       <c r="AB2" t="n">
         <v>2.587532346809148</v>
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2545021837284155</v>
+        <v>0.5231263593167896</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4830480136869053</v>
+        <v>0.6167221002539748</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5225386215154829</v>
+        <v>0.613870250180234</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.008781888029217116</v>
+        <v>0.3696919723125198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1480140546462781</v>
+        <v>0.4857605487316363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6621623402502526</v>
+        <v>0.6585037369224913</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4777592928084001</v>
+        <v>0.5987735518057834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4102979488362838</v>
+        <v>0.5754100409663363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5183808261049229</v>
+        <v>0.611772672780345</v>
       </c>
       <c r="K3" t="n">
-        <v>0.410548329463173</v>
+        <v>0.5762791653306009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07178033357299748</v>
+        <v>0.4689098540080167</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4416047104167668</v>
+        <v>0.5866423072136117</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6011391379653008</v>
+        <v>0.640536961498537</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6783227592949809</v>
+        <v>0.8177854073958447</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2514844457019464</v>
+        <v>0.5222833181149571</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4764687101567049</v>
+        <v>0.5980630112455281</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2950980024774763</v>
+        <v>0.3300333346288328</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3624313769955805</v>
+        <v>0.5608860919813065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3381179428941709</v>
+        <v>0.5513299089113861</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8757270486186609</v>
+        <v>0.9804819567620308</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5315868841802963</v>
+        <v>0.6163018258013735</v>
       </c>
       <c r="W3" t="n">
-        <v>1.195822405804348</v>
+        <v>1.073461286579422</v>
       </c>
       <c r="X3" t="n">
-        <v>1.29227630933798</v>
+        <v>0.8745303216830032</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7215162653285961</v>
+        <v>0.6826251936659811</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6182939284369975</v>
+        <v>0.7375841027890591</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.069361479732131</v>
+        <v>0.8024916847189455</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4578671600388286</v>
+        <v>0.5919105823167611</v>
       </c>
     </row>
     <row r="4">
@@ -4338,16 +4338,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.501750716855047</v>
+        <v>-1.501750716855049</v>
       </c>
       <c r="C4" t="n">
         <v>0.1441682653016315</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6793788776032371</v>
+        <v>0.6793788776032357</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.033992574751435</v>
+        <v>-3.03399257475144</v>
       </c>
       <c r="F4" t="n">
         <v>-2.522380472279614</v>
@@ -4356,67 +4356,67 @@
         <v>1.615805469553951</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3154038130525512</v>
+        <v>0.3154038130525549</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2810115351491461</v>
+        <v>-0.2810115351491467</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5858781772531378</v>
+        <v>0.5858781772531355</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2224851839095727</v>
+        <v>-0.2224851839095728</v>
       </c>
       <c r="L4" t="n">
         <v>-2.472122805084195</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03809753340475819</v>
+        <v>0.03809753340475733</v>
       </c>
       <c r="N4" t="n">
-        <v>1.326216613610578</v>
+        <v>1.326216613610575</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07646901283038979</v>
+        <v>0.07646901283038672</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.509381962453994</v>
+        <v>-1.509381962454001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2835439564470377</v>
+        <v>0.2835439564470356</v>
       </c>
       <c r="R4" t="n">
-        <v>-6.59778353548607</v>
+        <v>-6.597783535486069</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5455631412593328</v>
+        <v>-0.545563141259333</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8522474831640819</v>
+        <v>-0.8522474831640849</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4681775672221261</v>
+        <v>0.4681775672221241</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6968870519000285</v>
+        <v>0.6968870519000249</v>
       </c>
       <c r="W4" t="n">
-        <v>3.282176175981685</v>
+        <v>3.282176175981682</v>
       </c>
       <c r="X4" t="n">
-        <v>7.034338963267399</v>
+        <v>7.034338963267413</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.403847111020106</v>
+        <v>2.403847111020099</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3025054250235849</v>
+        <v>0.3025054250235831</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.397578164332328</v>
+        <v>5.39757816433232</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1383595599703032</v>
+        <v>0.1383595599703026</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08885017651771629</v>
+        <v>0.08885017651771522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2477290011365327</v>
+        <v>0.2477290011365317</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2787927001886966</v>
+        <v>0.2787927001886965</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03464469642165687</v>
+        <v>0.03464469642165573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04829968619887123</v>
+        <v>0.04829968619887041</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3600163357294024</v>
+        <v>0.3600163357294013</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2570360144649718</v>
+        <v>0.2570360144649717</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2244723577118634</v>
+        <v>0.2244723577118627</v>
       </c>
       <c r="J5" t="n">
-        <v>0.276935512004123</v>
+        <v>0.2769355120041219</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2244833476200995</v>
+        <v>0.2244833476200994</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05850597218895776</v>
+        <v>0.05850597218895745</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2397155417306136</v>
+        <v>0.2397155417306122</v>
       </c>
       <c r="N5" t="n">
-        <v>1.326216613610578</v>
+        <v>0.2714822941019522</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2103806595948916</v>
+        <v>0.2103806595948912</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1098992579223745</v>
+        <v>0.1098992579223734</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1860769365963971</v>
+        <v>0.1860769365963972</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1157732381241273</v>
+        <v>-0.1157732381241289</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2006829421041805</v>
+        <v>0.2006829421041794</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1894708875684401</v>
+        <v>0.1894708875684394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2393332157906215</v>
+        <v>0.2393332157906203</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2648516794015475</v>
+        <v>0.2648516794015447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4361887326398675</v>
+        <v>0.436188732639866</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5870271768516472</v>
+        <v>0.587027176851646</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4329343667275923</v>
+        <v>0.4329343667275896</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1982951739152402</v>
+        <v>0.1982951739152395</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5451048529554249</v>
+        <v>0.5451048529554238</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3089242187699174</v>
+        <v>0.3089242187699157</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1976820781823099</v>
+        <v>0.1976820781823095</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3534180195438862</v>
+        <v>0.3534180195438855</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3844817185960522</v>
+        <v>0.3844817185960502</v>
       </c>
       <c r="E6" t="n">
-        <v>0.158815606139497</v>
+        <v>0.1588156061394958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0752360562182179</v>
+        <v>0.07523605621821698</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4535003910180461</v>
+        <v>0.4535003910180448</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3627250328723268</v>
+        <v>0.3627250328723256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3301613761192178</v>
+        <v>0.3301613761192175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3826245304114769</v>
+        <v>0.3826245304114756</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3301723660274551</v>
+        <v>0.3301723660274533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1641949905963124</v>
+        <v>0.1641949905963107</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3454045601380451</v>
+        <v>0.3454045601380439</v>
       </c>
       <c r="N6" t="n">
-        <v>1.326216613610578</v>
+        <v>0.4227975403342396</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3676219633509261</v>
+        <v>0.3676219633509265</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2742297658200069</v>
+        <v>0.2742297658200074</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3621931137998014</v>
+        <v>0.3621931137998011</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.01008421971677356</v>
+        <v>-0.01008421971677435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3063719605115336</v>
+        <v>0.3063719605115333</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2951599059757958</v>
+        <v>0.2951599059757941</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3745144358683732</v>
+        <v>0.3745144358683719</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4517662854876565</v>
+        <v>0.4517662854876537</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5418661833844139</v>
+        <v>0.5418661833844124</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7577487227618946</v>
+        <v>0.7577487227618935</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4814064999300751</v>
+        <v>0.4814064999300755</v>
       </c>
       <c r="Z6" t="n">
         <v>0.330345020012577</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6507938713627787</v>
+        <v>0.6507938713627772</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3531292060426609</v>
+        <v>0.3531292060426597</v>
       </c>
     </row>
   </sheetData>
@@ -4758,40 +4758,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.564359330297209</v>
+        <v>2.564359330297208</v>
       </c>
       <c r="C2" t="n">
-        <v>2.598751460949111</v>
+        <v>2.598751460949112</v>
       </c>
       <c r="D2" t="n">
         <v>2.578607554120204</v>
       </c>
       <c r="E2" t="n">
-        <v>2.562390780005894</v>
+        <v>2.562390780005893</v>
       </c>
       <c r="F2" t="n">
         <v>2.569774360814613</v>
       </c>
       <c r="G2" t="n">
-        <v>2.587857784515265</v>
+        <v>2.587857784515264</v>
       </c>
       <c r="H2" t="n">
-        <v>2.583284444930316</v>
+        <v>2.583284444930315</v>
       </c>
       <c r="I2" t="n">
-        <v>2.581323372700668</v>
+        <v>2.581323372700667</v>
       </c>
       <c r="J2" t="n">
         <v>2.581879576756648</v>
       </c>
       <c r="K2" t="n">
-        <v>2.579992904057875</v>
+        <v>2.579992904057874</v>
       </c>
       <c r="L2" t="n">
-        <v>2.560380436534944</v>
+        <v>2.560380436534943</v>
       </c>
       <c r="M2" t="n">
-        <v>2.581568990664744</v>
+        <v>2.581568990664745</v>
       </c>
       <c r="N2" t="n">
         <v>2.588344577266613</v>
@@ -4800,7 +4800,7 @@
         <v>2.79359788084947</v>
       </c>
       <c r="P2" t="n">
-        <v>2.569302579523269</v>
+        <v>2.569302579523268</v>
       </c>
       <c r="Q2" t="n">
         <v>2.582095355797242</v>
@@ -4818,13 +4818,13 @@
         <v>2.951968020640662</v>
       </c>
       <c r="V2" t="n">
-        <v>2.585454671792825</v>
+        <v>2.585454671792824</v>
       </c>
       <c r="W2" t="n">
-        <v>2.940460515067921</v>
+        <v>2.940460515067922</v>
       </c>
       <c r="X2" t="n">
-        <v>2.627945092346374</v>
+        <v>2.627945092346373</v>
       </c>
       <c r="Y2" t="n">
         <v>2.588951665718125</v>
@@ -4833,10 +4833,10 @@
         <v>2.708557277297917</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.611284128089001</v>
+        <v>2.611284128089</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.58223722665612</v>
+        <v>2.582237226656121</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07072643472514772</v>
+        <v>0.4575063001979591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3486718485702647</v>
+        <v>0.5658831569895237</v>
       </c>
       <c r="D3" t="n">
-        <v>0.398052710875469</v>
+        <v>0.5673431552004041</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0699911258906615</v>
+        <v>0.3487427928776702</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1908947650961189</v>
+        <v>0.4955048440799732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6116377818626295</v>
+        <v>0.6387138996358828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5074925100670385</v>
+        <v>0.6051547198387246</v>
       </c>
       <c r="I3" t="n">
-        <v>0.461411298278054</v>
+        <v>0.5890142432443018</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4740561710356407</v>
+        <v>0.593273063067533</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4304069556397756</v>
+        <v>0.578563354704971</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02256859149929982</v>
+        <v>0.4308848064921135</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4717720634458595</v>
+        <v>0.5924730243644782</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6245809617082207</v>
+        <v>0.6449261173098333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5159549300980807</v>
+        <v>0.7535761073023075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1850425101380324</v>
+        <v>0.4967333139042611</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4793208692613472</v>
+        <v>0.5949975369133181</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2802927291046192</v>
+        <v>0.3299701631138225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2712088131445237</v>
+        <v>0.5257023495521841</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3713712088032317</v>
+        <v>0.5580525764711171</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8667873628277994</v>
+        <v>0.9700585774261649</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5564391619527577</v>
+        <v>0.6206280021201623</v>
       </c>
       <c r="W3" t="n">
-        <v>1.135155698333357</v>
+        <v>1.045724108798657</v>
       </c>
       <c r="X3" t="n">
-        <v>1.547176565415244</v>
+        <v>0.954910741562643</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6385159433549255</v>
+        <v>0.6502761305235029</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4730409695429221</v>
+        <v>0.6816744080770872</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.156676644957366</v>
+        <v>0.828909941816836</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4798636518246919</v>
+        <v>0.5956079263665366</v>
       </c>
     </row>
     <row r="4">
@@ -4934,85 +4934,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.897002139392423</v>
+        <v>-2.897002139392419</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.9315370349727344</v>
+        <v>-0.9315370349727359</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3237493409940601</v>
+        <v>-0.3237493409940612</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.285996767439755</v>
+        <v>-3.285996767439753</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.167669741303437</v>
+        <v>-2.16766974130344</v>
       </c>
       <c r="G4" t="n">
-        <v>1.349456342346996</v>
+        <v>1.349456342347002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6376263895462896</v>
+        <v>0.6376263895462906</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2153436557715831</v>
+        <v>0.2153436557715829</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3137838554217822</v>
+        <v>0.3137838554217815</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03752104770857728</v>
+        <v>-0.03752104770857656</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.33670582693961</v>
+        <v>-3.336705826939614</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3093497704758644</v>
+        <v>0.3093497704758643</v>
       </c>
       <c r="N4" t="n">
-        <v>1.602238015853774</v>
+        <v>1.602238015853776</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.053812150032607</v>
+        <v>-1.053812150032609</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.929068093747659</v>
+        <v>-1.92906809374766</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3566918863483198</v>
+        <v>0.35669188634832</v>
       </c>
       <c r="R4" t="n">
-        <v>-6.497818782328071</v>
+        <v>-6.497818782328066</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.257009984999161</v>
+        <v>-1.257009984999164</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5627082482931597</v>
+        <v>-0.5627082482931594</v>
       </c>
       <c r="U4" t="n">
-        <v>0.487835827785528</v>
+        <v>0.4878358277855274</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9436743534997321</v>
+        <v>0.9436743534997317</v>
       </c>
       <c r="W4" t="n">
-        <v>2.93557931053063</v>
+        <v>2.935579310530634</v>
       </c>
       <c r="X4" t="n">
-        <v>9.055419062854934</v>
+        <v>9.055419062854932</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.757548916231562</v>
+        <v>1.757548916231565</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6898657377904268</v>
+        <v>-0.6898657377904276</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.2242438327239</v>
+        <v>6.224243832723901</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.384942998946326</v>
+        <v>0.3849429989463261</v>
       </c>
     </row>
     <row r="5">
@@ -5022,85 +5022,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.008923999051033499</v>
+        <v>-0.00892399905103361</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1705154004142393</v>
+        <v>0.1705154004142392</v>
       </c>
       <c r="D5" t="n">
         <v>0.2057581888916376</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.006033735437105128</v>
+        <v>-0.006033735437105829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06061362867509831</v>
+        <v>0.06061362867509798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3213875389883118</v>
+        <v>0.3213875389883116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.258585822067923</v>
+        <v>0.2585858220679228</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2364346090962248</v>
+        <v>0.2364346090962241</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2424674618526512</v>
+        <v>0.2424674618526509</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2214063537301111</v>
+        <v>0.221406353730111</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0001254891222440269</v>
+        <v>-0.0001254891222437632</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2415243761392353</v>
+        <v>0.2415243761392354</v>
       </c>
       <c r="N5" t="n">
-        <v>1.602238015853774</v>
+        <v>0.2740833461102278</v>
       </c>
       <c r="O5" t="n">
         <v>0.1252848323394646</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06763723255438384</v>
+        <v>0.06763723255438434</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.180851049071654</v>
+        <v>0.1808510490716533</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1213028923220988</v>
+        <v>-0.1213028923220993</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1433528451548119</v>
+        <v>0.1433528451548123</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1928664772459503</v>
+        <v>0.1928664772459502</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2270225953053951</v>
+        <v>0.2270225953053953</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2656508076131929</v>
+        <v>0.2656508076131932</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3967263919987722</v>
+        <v>0.3967263919987734</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7036704714195104</v>
+        <v>0.7036704714195107</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3743393298687847</v>
+        <v>0.3743393298687853</v>
       </c>
       <c r="Z5" t="n">
         <v>0.1224649081891568</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5748551238358848</v>
+        <v>0.5748551238358859</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3014350802361303</v>
+        <v>0.3014350802361299</v>
       </c>
     </row>
     <row r="6">
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08702088114165374</v>
+        <v>0.08702088114165502</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2626437699142884</v>
+        <v>0.2626437699142881</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2978865583916869</v>
+        <v>0.2978865583916868</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1031880341128265</v>
+        <v>0.1031880341128262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08301984727309868</v>
+        <v>0.08301984727309875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4023721479558437</v>
+        <v>0.4023721479558446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3507141915679731</v>
+        <v>0.3507141915679727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.328562978596274</v>
+        <v>0.3285629785962745</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3345958313527</v>
+        <v>0.3345958313526997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3135347232301607</v>
+        <v>0.3135347232301598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09200288037780477</v>
+        <v>0.09200288037780432</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3336527456395063</v>
+        <v>0.3336527456395055</v>
       </c>
       <c r="N6" t="n">
-        <v>1.602238015853774</v>
+        <v>0.4078707140823309</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2641691454151326</v>
+        <v>0.2641691454151328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2129260904233859</v>
+        <v>0.2129260904233856</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3372828647376071</v>
+        <v>0.3372828647376074</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.02917452282205006</v>
+        <v>-0.0291745228220502</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2354812146548612</v>
+        <v>0.2354812146548607</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2849948467459994</v>
+        <v>0.2849948467459988</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3463723627438455</v>
+        <v>0.3463723627438449</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4311732071350706</v>
+        <v>0.4311732071350703</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4888441996249758</v>
+        <v>0.4888441996249752</v>
       </c>
       <c r="X6" t="n">
         <v>0.8551767490451718</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4147280574166388</v>
+        <v>0.4147280574166386</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2392329025435755</v>
+        <v>0.2392329025435757</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6669834933359338</v>
+        <v>0.6669834933359329</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3374254939424908</v>
+        <v>0.3374254939424911</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.656749508374514</v>
+        <v>2.656749508374513</v>
       </c>
       <c r="C2" t="n">
-        <v>2.672969462245022</v>
+        <v>2.672969462245026</v>
       </c>
       <c r="D2" t="n">
-        <v>2.659022309050838</v>
+        <v>2.65902230905084</v>
       </c>
       <c r="E2" t="n">
-        <v>2.645977523593752</v>
+        <v>2.645977523593749</v>
       </c>
       <c r="F2" t="n">
-        <v>2.646169981595667</v>
+        <v>2.646169981595668</v>
       </c>
       <c r="G2" t="n">
-        <v>2.681225717457041</v>
+        <v>2.681225717457045</v>
       </c>
       <c r="H2" t="n">
-        <v>2.661438787827615</v>
+        <v>2.661438787827616</v>
       </c>
       <c r="I2" t="n">
-        <v>2.648138504611862</v>
+        <v>2.648138504611863</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66693876755419</v>
+        <v>2.666938767554188</v>
       </c>
       <c r="K2" t="n">
-        <v>2.655825056241798</v>
+        <v>2.655825056241796</v>
       </c>
       <c r="L2" t="n">
         <v>2.673713583224997</v>
       </c>
       <c r="M2" t="n">
-        <v>2.685207597891299</v>
+        <v>2.685207597891296</v>
       </c>
       <c r="N2" t="n">
-        <v>2.659913782881508</v>
+        <v>2.659913782881515</v>
       </c>
       <c r="O2" t="n">
-        <v>2.924176314970302</v>
+        <v>2.924176314970301</v>
       </c>
       <c r="P2" t="n">
         <v>2.660777707085116</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.650980674499963</v>
+        <v>2.650980674499968</v>
       </c>
       <c r="R2" t="n">
-        <v>2.643236428114745</v>
+        <v>2.643236428114744</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66110731385236</v>
+        <v>2.661107313852359</v>
       </c>
       <c r="T2" t="n">
-        <v>2.650072842665059</v>
+        <v>2.650072842665062</v>
       </c>
       <c r="U2" t="n">
-        <v>3.065784845837002</v>
+        <v>3.065784845837007</v>
       </c>
       <c r="V2" t="n">
-        <v>2.650327180623412</v>
+        <v>2.650327180623411</v>
       </c>
       <c r="W2" t="n">
-        <v>3.048480966137482</v>
+        <v>3.048480966137481</v>
       </c>
       <c r="X2" t="n">
-        <v>2.66704784523126</v>
+        <v>2.667047845231265</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.663822725424414</v>
+        <v>2.663822725424408</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.809384782249446</v>
+        <v>2.809384782249449</v>
       </c>
       <c r="AA2" t="n">
         <v>2.666321874895606</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.683872881713746</v>
+        <v>2.683872881713748</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8698492769474475</v>
+        <v>0.7613233176646573</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6166812757026836</v>
+        <v>0.6958622877717484</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9280988813331035</v>
+        <v>0.7864611820029365</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5233610244680074</v>
+        <v>0.5801745073858204</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6284829301884878</v>
+        <v>0.6815184494295461</v>
       </c>
       <c r="G3" t="n">
-        <v>1.433505827790061</v>
+        <v>0.9494499446798368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9873108992472012</v>
+        <v>0.808667424255144</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6742371551759283</v>
+        <v>0.6976798678180125</v>
       </c>
       <c r="J3" t="n">
-        <v>1.107090295350969</v>
+        <v>0.8420136194555626</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8524694966865654</v>
+        <v>0.755730010667466</v>
       </c>
       <c r="L3" t="n">
-        <v>1.264557583017842</v>
+        <v>0.8971138537632433</v>
       </c>
       <c r="M3" t="n">
-        <v>1.542871882578135</v>
+        <v>0.9910233145276719</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472477201433747</v>
+        <v>0.7918514869927629</v>
       </c>
       <c r="O3" t="n">
-        <v>1.106534951775888</v>
+        <v>1.018482227291572</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9620672496992514</v>
+        <v>0.7938226091071875</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7396895035670557</v>
+        <v>0.7192844399516672</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5597270526379297</v>
+        <v>0.6577963700075041</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9710584007538499</v>
+        <v>0.7935462816653412</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7192482204609059</v>
+        <v>0.713365785545151</v>
       </c>
       <c r="U3" t="n">
-        <v>1.594277033031671</v>
+        <v>1.270553595001589</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7222359959277463</v>
+        <v>0.7113270815401825</v>
       </c>
       <c r="W3" t="n">
-        <v>1.641887978592482</v>
+        <v>1.276408523320738</v>
       </c>
       <c r="X3" t="n">
-        <v>1.114822827801266</v>
+        <v>0.8503839913285218</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.037200912247656</v>
+        <v>0.8212758594498193</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9708496036840023</v>
+        <v>0.8983926848918418</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.094966168788812</v>
+        <v>0.8419562929306716</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.501824764370945</v>
+        <v>0.992526198049735</v>
       </c>
     </row>
     <row r="4">
@@ -5530,55 +5530,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.262224930850599</v>
+        <v>3.262224930850613</v>
       </c>
       <c r="C4" t="n">
-        <v>0.943347698990574</v>
+        <v>0.9433476989905747</v>
       </c>
       <c r="D4" t="n">
-        <v>4.247837952966089</v>
+        <v>4.247837952966091</v>
       </c>
       <c r="E4" t="n">
-        <v>1.241626303628953</v>
+        <v>1.241626303628963</v>
       </c>
       <c r="F4" t="n">
-        <v>1.345686318812127</v>
+        <v>1.345686318812128</v>
       </c>
       <c r="G4" t="n">
-        <v>7.943071028841914</v>
+        <v>7.943071028841917</v>
       </c>
       <c r="H4" t="n">
-        <v>4.969711128345152</v>
+        <v>4.969711128345151</v>
       </c>
       <c r="I4" t="n">
-        <v>1.796844818206194</v>
+        <v>1.796844818206195</v>
       </c>
       <c r="J4" t="n">
-        <v>5.379766438143126</v>
+        <v>5.379766438143132</v>
       </c>
       <c r="K4" t="n">
-        <v>3.189543834542313</v>
+        <v>3.189543834542317</v>
       </c>
       <c r="L4" t="n">
-        <v>6.894805489507935</v>
+        <v>6.89480548950799</v>
       </c>
       <c r="M4" t="n">
-        <v>9.457549535000766</v>
+        <v>9.457549535000775</v>
       </c>
       <c r="N4" t="n">
-        <v>4.313732832557116</v>
+        <v>4.313732832557113</v>
       </c>
       <c r="O4" t="n">
-        <v>2.922171556485143</v>
+        <v>2.922171556485141</v>
       </c>
       <c r="P4" t="n">
         <v>4.145942341057783</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.322788290949274</v>
+        <v>2.322788290949273</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7007779016043921</v>
+        <v>0.7007779016043902</v>
       </c>
       <c r="S4" t="n">
         <v>4.001235523521062</v>
@@ -5587,28 +5587,28 @@
         <v>2.225837851854348</v>
       </c>
       <c r="U4" t="n">
-        <v>6.365698228840985</v>
+        <v>6.365698228840975</v>
       </c>
       <c r="V4" t="n">
-        <v>1.984538003684036</v>
+        <v>1.984538003684041</v>
       </c>
       <c r="W4" t="n">
-        <v>7.209204295845844</v>
+        <v>7.20920429584585</v>
       </c>
       <c r="X4" t="n">
-        <v>5.943114081088915</v>
+        <v>5.943114081088916</v>
       </c>
       <c r="Y4" t="n">
         <v>5.016046211071871</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.825582614695041</v>
+        <v>2.825582614695035</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.601237910183864</v>
+        <v>5.601237910183874</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.18533828531488</v>
+        <v>10.18533828531486</v>
       </c>
     </row>
     <row r="5">
@@ -5618,67 +5618,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4682390971806104</v>
+        <v>0.4682390971806097</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4323767771222913</v>
+        <v>0.4323767771222915</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5967740944558738</v>
+        <v>0.5967740944558748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3946559053303112</v>
+        <v>0.3946559053303125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3647632768905529</v>
+        <v>0.3647632768905538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8689010507885128</v>
+        <v>0.8689010507885132</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6240693338746761</v>
+        <v>0.6240693338746767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4738365165201811</v>
+        <v>0.473836516520182</v>
       </c>
       <c r="J5" t="n">
-        <v>0.685795029435511</v>
+        <v>0.6857950294355116</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5606596531687369</v>
+        <v>0.5606596531687387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7627187945729383</v>
+        <v>0.762718794572938</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8934057880780361</v>
+        <v>0.8934057880780362</v>
       </c>
       <c r="N5" t="n">
-        <v>4.313732832557116</v>
+        <v>0.5271079251297982</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4977156928161777</v>
+        <v>0.4977156928161786</v>
       </c>
       <c r="P5" t="n">
         <v>0.5534072489063218</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3828626027835108</v>
+        <v>0.3828626027835113</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4184653074186084</v>
+        <v>0.4184653074186068</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6203251828385665</v>
+        <v>0.6203251828385679</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4956857546705355</v>
+        <v>0.4956857546705364</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6809408285258873</v>
+        <v>0.6809408285258869</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4677687603680043</v>
+        <v>0.4677687603680044</v>
       </c>
       <c r="W5" t="n">
         <v>0.7632744167528628</v>
@@ -5687,16 +5687,16 @@
         <v>0.5737762553385051</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7532701680393058</v>
+        <v>0.7532701680393066</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.439685227299494</v>
+        <v>0.4396852272994955</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.679226048638658</v>
+        <v>0.6792260486386585</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9811918674220378</v>
+        <v>0.9811918674220371</v>
       </c>
     </row>
     <row r="6">
@@ -5715,76 +5715,76 @@
         <v>0.8006981626109537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6299174769279317</v>
+        <v>0.6299174769279328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4214597658060631</v>
+        <v>0.4214597658060621</v>
       </c>
       <c r="G6" t="n">
-        <v>1.051495859827445</v>
+        <v>1.051495859827446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8279934020297566</v>
+        <v>0.8279934020297567</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6777605846752608</v>
+        <v>0.6777605846752611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8897190975905902</v>
+        <v>0.889719097590591</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7645837213238156</v>
+        <v>0.7645837213238167</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9666428627280144</v>
+        <v>0.9666428627280168</v>
       </c>
       <c r="M6" t="n">
         <v>1.097329856233014</v>
       </c>
       <c r="N6" t="n">
-        <v>4.313732832557116</v>
+        <v>0.8107677696266058</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7931119394405315</v>
+        <v>0.7931119394405314</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8614926482601841</v>
+        <v>0.8614926482601847</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7098641862200894</v>
+        <v>0.7098641862200897</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6223893755736837</v>
+        <v>0.6223893755736849</v>
       </c>
       <c r="S6" t="n">
-        <v>0.824249250993646</v>
+        <v>0.8242492509936465</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6996098228256143</v>
+        <v>0.6996098228256165</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9350712873718864</v>
+        <v>0.9350712873718854</v>
       </c>
       <c r="V6" t="n">
         <v>0.8169761293176605</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9671782695130591</v>
+        <v>0.9671782695130602</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8913502856978547</v>
+        <v>0.891350285697856</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8549210738510212</v>
+        <v>0.8549210738510221</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6871662185848399</v>
+        <v>0.6871662185848398</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8831501167937357</v>
+        <v>0.8831501167937362</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.077667277575122</v>
+        <v>1.077667277575121</v>
       </c>
     </row>
   </sheetData>
@@ -5953,16 +5953,16 @@
         <v>2.612025121316912</v>
       </c>
       <c r="C2" t="n">
-        <v>2.638677214709279</v>
+        <v>2.638677214709278</v>
       </c>
       <c r="D2" t="n">
-        <v>2.617567864550426</v>
+        <v>2.617567864550424</v>
       </c>
       <c r="E2" t="n">
         <v>2.611489364428689</v>
       </c>
       <c r="F2" t="n">
-        <v>2.601153640775839</v>
+        <v>2.601153640775837</v>
       </c>
       <c r="G2" t="n">
         <v>2.647981703778539</v>
@@ -5971,7 +5971,7 @@
         <v>2.627873859121117</v>
       </c>
       <c r="I2" t="n">
-        <v>2.611353948896538</v>
+        <v>2.611353948896539</v>
       </c>
       <c r="J2" t="n">
         <v>2.625473643986356</v>
@@ -5983,37 +5983,37 @@
         <v>2.596388198412539</v>
       </c>
       <c r="M2" t="n">
-        <v>2.614092382660252</v>
+        <v>2.614092382660251</v>
       </c>
       <c r="N2" t="n">
         <v>2.615856859862751</v>
       </c>
       <c r="O2" t="n">
-        <v>2.849451683731385</v>
+        <v>2.849451683731384</v>
       </c>
       <c r="P2" t="n">
-        <v>2.621699918692471</v>
+        <v>2.62169991869247</v>
       </c>
       <c r="Q2" t="n">
         <v>2.614165331036657</v>
       </c>
       <c r="R2" t="n">
-        <v>2.586778242491061</v>
+        <v>2.58677824249106</v>
       </c>
       <c r="S2" t="n">
-        <v>2.603701235933966</v>
+        <v>2.603701235933965</v>
       </c>
       <c r="T2" t="n">
-        <v>2.605780184235342</v>
+        <v>2.605780184235343</v>
       </c>
       <c r="U2" t="n">
         <v>3.004631089747467</v>
       </c>
       <c r="V2" t="n">
-        <v>2.620445472735094</v>
+        <v>2.620445472735093</v>
       </c>
       <c r="W2" t="n">
-        <v>2.999388065181918</v>
+        <v>2.999388065181916</v>
       </c>
       <c r="X2" t="n">
         <v>2.645891831777275</v>
@@ -6022,13 +6022,13 @@
         <v>2.655351378416348</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.765847543533496</v>
+        <v>2.765847543533495</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.627408436507476</v>
+        <v>2.627408436507475</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.640012895834657</v>
+        <v>2.640012895834656</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4271001902974372</v>
+        <v>0.5964602981798346</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4577331129789453</v>
+        <v>0.6244167986651624</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5557268338176538</v>
+        <v>0.6404992374227885</v>
       </c>
       <c r="E3" t="n">
-        <v>0.318303460419392</v>
+        <v>0.4959194801915192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1715936438745997</v>
+        <v>0.5083468996844905</v>
       </c>
       <c r="G3" t="n">
-        <v>1.254535119269164</v>
+        <v>0.8701347710423679</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7982594352041228</v>
+        <v>0.7268060153045565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4105793736927068</v>
+        <v>0.5900109440405128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7367516967003087</v>
+        <v>0.6996346860311687</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4871281403842138</v>
+        <v>0.6171305367338479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06531116658658109</v>
+        <v>0.4765131291031958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4837035325475478</v>
+        <v>0.6156971168988873</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5156743641346877</v>
+        <v>0.6266068158052512</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6165347026034703</v>
+        <v>0.8199075607143219</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6495698865376942</v>
+        <v>0.6714241643072522</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4763644645998331</v>
+        <v>0.6132711102070389</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1652659874269391</v>
+        <v>0.387614037349397</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2350985418630052</v>
+        <v>0.5334489119337581</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2805117379705905</v>
+        <v>0.5450002689389375</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9918329641675707</v>
+        <v>1.041832658269824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.621069109821422</v>
+        <v>0.6613529842281914</v>
       </c>
       <c r="W3" t="n">
-        <v>1.351214721748368</v>
+        <v>1.152841712450187</v>
       </c>
       <c r="X3" t="n">
-        <v>1.215855419976923</v>
+        <v>0.8668883780651844</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.432610579252052</v>
+        <v>0.9414986902986451</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7394476519151602</v>
+        <v>0.7984795937783672</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7836935879732941</v>
+        <v>0.7190597960048755</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.074108515824556</v>
+        <v>0.8234797226807727</v>
       </c>
     </row>
     <row r="4">
@@ -6126,85 +6126,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2855735580956001</v>
+        <v>-0.2855735580956008</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2526658675669146</v>
+        <v>-0.2526658675669189</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8027840859200817</v>
+        <v>0.802784085920083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4229971277215817</v>
+        <v>-0.4229971277215843</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.533581876977077</v>
+        <v>-2.53358187697708</v>
       </c>
       <c r="G4" t="n">
-        <v>5.967099154130492</v>
+        <v>5.967099154130494</v>
       </c>
       <c r="H4" t="n">
         <v>3.122543188285328</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4919870341964636</v>
+        <v>-0.4919870341964643</v>
       </c>
       <c r="J4" t="n">
         <v>2.107910753803697</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2258647736930784</v>
+        <v>0.2258647736930792</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.06516418669133</v>
+        <v>-3.065164186691328</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2006750521227125</v>
+        <v>0.2006750521227111</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4470513784209877</v>
+        <v>0.4470513784209861</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.633222285561202</v>
+        <v>-0.6332222855611982</v>
       </c>
       <c r="P4" t="n">
-        <v>1.487461105559453</v>
+        <v>1.487461105559451</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1220821589442113</v>
+        <v>0.1220821589442108</v>
       </c>
       <c r="R4" t="n">
-        <v>-5.795179305086736</v>
+        <v>-5.795179305086739</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.708941341131698</v>
+        <v>-1.708941341131695</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.634738695478031</v>
+        <v>-1.634738695478027</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15366407274253</v>
+        <v>1.153664072742528</v>
       </c>
       <c r="V4" t="n">
         <v>1.230671288044965</v>
       </c>
       <c r="W4" t="n">
-        <v>4.530854526839422</v>
+        <v>4.530854526839421</v>
       </c>
       <c r="X4" t="n">
-        <v>6.451732126647467</v>
+        <v>6.451732126647465</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.276034833985866</v>
+        <v>8.276034833985848</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.007804244318299</v>
+        <v>1.007804244318298</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.761136851797216</v>
+        <v>2.761136851797213</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.595425760545119</v>
+        <v>5.595425760545117</v>
       </c>
     </row>
     <row r="5">
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2044722070758011</v>
+        <v>0.204472207075801</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2825043269405216</v>
+        <v>0.282504326940522</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3427926979436191</v>
+        <v>0.3427926979436189</v>
       </c>
       <c r="E5" t="n">
         <v>0.2338184867509541</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09346898020549131</v>
+        <v>0.09346898020549213</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7020305155774839</v>
+        <v>0.7020305155774835</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4592036476113409</v>
+        <v>0.4592036476113416</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2726036620905506</v>
+        <v>0.2726036620905511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4317308177176369</v>
+        <v>0.4317308177176362</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3095679386394465</v>
+        <v>0.309567938639447</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1035586257884063</v>
+        <v>0.1035586257884069</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3080952532970584</v>
+        <v>0.3080952532970591</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4470513784209877</v>
+        <v>0.2647761378375356</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2129099833083728</v>
+        <v>0.2129099833083733</v>
       </c>
       <c r="P5" t="n">
-        <v>0.342951201310608</v>
+        <v>0.342951201310607</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2137675953992811</v>
+        <v>0.2137675953992807</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00499024714280577</v>
+        <v>-0.004990247142806006</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1861627487564057</v>
+        <v>0.186162748756406</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2096454261839074</v>
+        <v>0.2096454261839081</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3309352307565733</v>
+        <v>0.3309352307565735</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3518349109179125</v>
+        <v>0.3518349109179129</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5535749707257254</v>
+        <v>0.553574970725725</v>
       </c>
       <c r="X5" t="n">
         <v>0.5790722315509581</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8443181263057348</v>
+        <v>0.844318126305734</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2843561070945593</v>
+        <v>0.284356107094559</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4539464850852433</v>
+        <v>0.4539464850852435</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6723842485647916</v>
+        <v>0.6723842485647913</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3563364093817255</v>
+        <v>0.3563364093817252</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4336088402972794</v>
+        <v>0.433608840297279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4938972113003763</v>
+        <v>0.4938972113003765</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4079389568767517</v>
+        <v>0.4079389568767508</v>
       </c>
       <c r="F6" t="n">
         <v>0.1357038890167042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8374355682157942</v>
+        <v>0.8374355682157939</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6103081609680994</v>
+        <v>0.6103081609680984</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4237081754473075</v>
+        <v>0.4237081754473082</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5828353310743943</v>
+        <v>0.5828353310743946</v>
       </c>
       <c r="K6" t="n">
-        <v>0.460672451996204</v>
+        <v>0.4606724519962045</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2546631391451643</v>
+        <v>0.2546631391451649</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4591997666536552</v>
+        <v>0.459199766653656</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4470513784209877</v>
+        <v>0.4745706262520534</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4314153411512278</v>
+        <v>0.431415341151228</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5708121764542554</v>
+        <v>0.570812176454256</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.455464081796198</v>
+        <v>0.4554640817961983</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1461142662139512</v>
+        <v>0.1461142662139518</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3372672621131624</v>
+        <v>0.3372672621131633</v>
       </c>
       <c r="T6" t="n">
-        <v>0.360749939540664</v>
+        <v>0.3607499395406654</v>
       </c>
       <c r="U6" t="n">
-        <v>0.519307467437772</v>
+        <v>0.5193074674377726</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6104726598418898</v>
+        <v>0.6104726598418901</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7046646043999082</v>
+        <v>0.704664604399908</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8138294507962974</v>
+        <v>0.8138294507962978</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9206793816910837</v>
+        <v>0.9206793816910829</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4673897245192</v>
+        <v>0.4673897245192001</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6050509984420008</v>
+        <v>0.6050509984420013</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7444005614918102</v>
+        <v>0.7444005614918112</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.919037594972943</v>
+        <v>0.8445131728395114</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7639434923307629</v>
+        <v>0.7402860511221475</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8523018554938656</v>
+        <v>0.7917074158161389</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6436785705769053</v>
+        <v>0.6173810253126206</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8129137532584743</v>
+        <v>0.7638657051188409</v>
       </c>
       <c r="G3" t="n">
-        <v>1.007066868391658</v>
+        <v>0.9053497382015937</v>
       </c>
       <c r="H3" t="n">
-        <v>0.920818255993013</v>
+        <v>0.8364392242943198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8205561967678987</v>
+        <v>0.7694905312874852</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9246210070061189</v>
+        <v>0.8454435292966879</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9108054719143576</v>
+        <v>0.8323483175262285</v>
       </c>
       <c r="L3" t="n">
-        <v>1.027678516960402</v>
+        <v>0.9166567530763237</v>
       </c>
       <c r="M3" t="n">
-        <v>1.087683777099</v>
+        <v>0.9522701557138605</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9312044994928721</v>
+        <v>0.8476563246178634</v>
       </c>
       <c r="O3" t="n">
-        <v>1.176846472485359</v>
+        <v>1.112737077674751</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8800846679811848</v>
+        <v>0.8159469910832774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8545204612754762</v>
+        <v>0.7941341299423411</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8252882385401963</v>
+        <v>0.7722595104707048</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9508471853431525</v>
+        <v>0.8653528663252701</v>
       </c>
       <c r="T3" t="n">
-        <v>0.886319954360705</v>
+        <v>0.8148861503799646</v>
       </c>
       <c r="U3" t="n">
-        <v>1.410830773680003</v>
+        <v>1.30796592261997</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7890357080600784</v>
+        <v>0.7514049520259628</v>
       </c>
       <c r="W3" t="n">
-        <v>1.340199088347982</v>
+        <v>1.250910042532944</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8861111291758029</v>
+        <v>0.815592053026752</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8622618287639392</v>
+        <v>0.8006125690374734</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.027997285190209</v>
+        <v>0.9687242287132048</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9416638093524805</v>
+        <v>0.8556102866225201</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.079309635116534</v>
+        <v>0.9438211556579064</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5797931044775508</v>
+        <v>0.5847131013769615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5989694707355258</v>
+        <v>0.6058382501937041</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6076953588325148</v>
+        <v>0.6045457367175544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4970030143532489</v>
+        <v>0.4988099742461756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4986159930676781</v>
+        <v>0.5287497149817306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6378535779513194</v>
+        <v>0.6266077430907987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6330466951848065</v>
+        <v>0.6217545343780808</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5926454513232178</v>
+        <v>0.5940948912802756</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6132698394333544</v>
+        <v>0.608843758446703</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5910440457192809</v>
+        <v>0.5926365506410887</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4182260774375355</v>
+        <v>0.4683767263649386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5805810259671321</v>
+        <v>0.5854725658607824</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5879220651332568</v>
+        <v>0.5908744558180323</v>
       </c>
       <c r="O3" t="n">
-        <v>0.761820820250475</v>
+        <v>0.7793480164151895</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5804253278490608</v>
+        <v>0.5850776509588695</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6036119896608476</v>
+        <v>0.6017451808185879</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3219064928357973</v>
+        <v>0.408683138650432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5165864670245703</v>
+        <v>0.5390252905370383</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5426683046379246</v>
+        <v>0.559687250539315</v>
       </c>
       <c r="U3" t="n">
-        <v>1.016850550477679</v>
+        <v>1.00624489127987</v>
       </c>
       <c r="V3" t="n">
-        <v>0.661375323192461</v>
+        <v>0.6435129016015975</v>
       </c>
       <c r="W3" t="n">
-        <v>1.186936213939955</v>
+        <v>1.117764388611757</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9176113491493632</v>
+        <v>0.8227686367306757</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7848826792004776</v>
+        <v>0.7277257449495783</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7917512389247244</v>
+        <v>0.7784822852951273</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8556425782180381</v>
+        <v>0.7771611124426794</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6113997563238704</v>
+        <v>0.6069668636698217</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8610215861796742</v>
+        <v>0.8008616122696389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7391826580618438</v>
+        <v>0.7206692371902904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8672725534991891</v>
+        <v>0.799265466792014</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6354925682968564</v>
+        <v>0.6095993216322421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7731101816552444</v>
+        <v>0.7344869780160701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9860673713582356</v>
+        <v>0.8885864286184978</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8557785112308193</v>
+        <v>0.7897054223959571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7785435495881191</v>
+        <v>0.7379799902261365</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9056681866039387</v>
+        <v>0.8297272256745353</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8657714501888223</v>
+        <v>0.8015991643212832</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9837145912459326</v>
+        <v>0.8832965925417031</v>
       </c>
       <c r="M3" t="n">
-        <v>1.047469191571945</v>
+        <v>0.922442615855422</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8807116377260052</v>
+        <v>0.8099808673501099</v>
       </c>
       <c r="O3" t="n">
-        <v>1.123271883484728</v>
+        <v>1.069922737463208</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8958994425593492</v>
+        <v>0.8247920614445563</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8104579330234689</v>
+        <v>0.7611459899584783</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8191895155921367</v>
+        <v>0.7653271138308571</v>
       </c>
       <c r="S3" t="n">
-        <v>0.926564418171684</v>
+        <v>0.8461686864366169</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8279799843830318</v>
+        <v>0.7723150164285755</v>
       </c>
       <c r="U3" t="n">
-        <v>1.347678974451668</v>
+        <v>1.259873859414976</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7369574568837203</v>
+        <v>0.7123529557020304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.341564080352442</v>
+        <v>1.247917723749027</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8906953044341508</v>
+        <v>0.8163029339721067</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8416469797523185</v>
+        <v>0.7840154474026493</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9793365463253307</v>
+        <v>0.9306595803231528</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8763442023075317</v>
+        <v>0.8078872991587774</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05805543264278</v>
+        <v>0.9265500892252571</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8140692125159072</v>
+        <v>0.7655250972258559</v>
       </c>
       <c r="C3" t="n">
-        <v>0.749052195618946</v>
+        <v>0.7264403637295055</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8889294720840278</v>
+        <v>0.8133267682199599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6365357279312429</v>
+        <v>0.6093434666218409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.739612535707641</v>
+        <v>0.7104453624916487</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9619212541661866</v>
+        <v>0.8712646855131913</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8238391881482795</v>
+        <v>0.7664334070332955</v>
       </c>
       <c r="I3" t="n">
-        <v>0.770062439061027</v>
+        <v>0.7309596456400047</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8875706696859518</v>
+        <v>0.8161960320169334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8149630787413779</v>
+        <v>0.7661439833878493</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9332505916106235</v>
+        <v>0.8470604440549326</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9973792798214125</v>
+        <v>0.8866439441120575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8217334048080231</v>
+        <v>0.767731365587177</v>
       </c>
       <c r="O3" t="n">
-        <v>1.072017949328526</v>
+        <v>1.029435000426498</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8874466642508173</v>
+        <v>0.8181743869503048</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7285041361655062</v>
+        <v>0.7034083344105462</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7928487208830266</v>
+        <v>0.7460436625503908</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9000547344725752</v>
+        <v>0.8266009516541006</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8033473015762319</v>
+        <v>0.7540076771004727</v>
       </c>
       <c r="U3" t="n">
-        <v>1.283632896784622</v>
+        <v>1.212675456003699</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7646209248852265</v>
+        <v>0.7314411665888543</v>
       </c>
       <c r="W3" t="n">
-        <v>1.306462489110656</v>
+        <v>1.220387931462013</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9411291578644839</v>
+        <v>0.850172859373498</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9040852000606451</v>
+        <v>0.82631518836602</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9726311146053055</v>
+        <v>0.9261106312248872</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8633962609118244</v>
+        <v>0.7974741969918383</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02811630568665</v>
+        <v>0.9046176339455734</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7918008414569021</v>
+        <v>0.7501433053936475</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7596726072199461</v>
+        <v>0.7333532304652721</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8137968786631924</v>
+        <v>0.7624752572564697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6076597930984116</v>
+        <v>0.5892924482551261</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7536788566567401</v>
+        <v>0.7198618894178519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9128091643496121</v>
+        <v>0.8375878527001798</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8036831047623559</v>
+        <v>0.752166024536712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7705195974867736</v>
+        <v>0.7312304068573843</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8627179081859904</v>
+        <v>0.7991849942674052</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8420589044592336</v>
+        <v>0.7850051365231833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8851167056202983</v>
+        <v>0.8147934576114291</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9405705628747187</v>
+        <v>0.849815188573242</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7976680028105427</v>
+        <v>0.7504793964571488</v>
       </c>
       <c r="O3" t="n">
-        <v>1.033566276993093</v>
+        <v>0.9993182612592426</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8688627884704372</v>
+        <v>0.8060094523081209</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7507639893695106</v>
+        <v>0.7189985019374259</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7761247881310834</v>
+        <v>0.7341463691165748</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8725751660333662</v>
+        <v>0.8072269977959549</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7887830824388464</v>
+        <v>0.7434799417299487</v>
       </c>
       <c r="U3" t="n">
-        <v>1.294174040967793</v>
+        <v>1.220939679419619</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8280166068467206</v>
+        <v>0.7772294689267645</v>
       </c>
       <c r="W3" t="n">
-        <v>1.301920948420068</v>
+        <v>1.215874522917428</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9481226469413534</v>
+        <v>0.8564896909629455</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.008775195729786</v>
+        <v>0.8975542489500457</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9472139849804534</v>
+        <v>0.9081398180576991</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8742251236169024</v>
+        <v>0.804286372133536</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9879466106336092</v>
+        <v>0.8779679704493095</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6361935368024458</v>
+        <v>0.6276144717678857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6502285109151389</v>
+        <v>0.6446435795853767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6815152411469566</v>
+        <v>0.6581527212842198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5117766633118216</v>
+        <v>0.5116225237444209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6079827852895303</v>
+        <v>0.6073336977925582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7017850472266653</v>
+        <v>0.6757547994092397</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6441941848775462</v>
+        <v>0.6319828361134048</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6429635002382471</v>
+        <v>0.631417386967029</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6755548112951671</v>
+        <v>0.6557639005604456</v>
       </c>
       <c r="K3" t="n">
-        <v>0.681123539642529</v>
+        <v>0.6592292958094056</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6222618522285757</v>
+        <v>0.6175501080311178</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7181493151376277</v>
+        <v>0.6851154336548754</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6546248335717109</v>
+        <v>0.6400413490770344</v>
       </c>
       <c r="O3" t="n">
-        <v>0.866695021734724</v>
+        <v>0.8612523274805672</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6371724737225027</v>
+        <v>0.6282270850209859</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6337582886227658</v>
+        <v>0.6254752718965666</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5175425022625922</v>
+        <v>0.5457353307460745</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6523643993745871</v>
+        <v>0.639981748906535</v>
       </c>
       <c r="T3" t="n">
-        <v>0.629551962273717</v>
+        <v>0.6223691675551597</v>
       </c>
       <c r="U3" t="n">
-        <v>1.134619926698629</v>
+        <v>1.093274802394897</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6337929856935978</v>
+        <v>0.6259054003081439</v>
       </c>
       <c r="W3" t="n">
-        <v>1.231141498572048</v>
+        <v>1.152495786769066</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7311864010322152</v>
+        <v>0.692810593441508</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6621030514752193</v>
+        <v>0.645271268818845</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7834707719176441</v>
+        <v>0.7745706882600631</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7433344640593277</v>
+        <v>0.7018816079398073</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7114132478914482</v>
+        <v>0.6783558095336047</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5231263593167896</v>
+        <v>0.5422883789591765</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6167221002539748</v>
+        <v>0.6161089125709082</v>
       </c>
       <c r="D3" t="n">
-        <v>0.613870250180234</v>
+        <v>0.6068079974166246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3696919723125198</v>
+        <v>0.4074090650224449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4857605487316363</v>
+        <v>0.5173424780513253</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6585037369224913</v>
+        <v>0.6403455713640609</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5987735518057834</v>
+        <v>0.5960889686039849</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5754100409663363</v>
+        <v>0.5799382684718138</v>
       </c>
       <c r="J3" t="n">
-        <v>0.611772672780345</v>
+        <v>0.6058827270538962</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5762791653306009</v>
+        <v>0.5800588622718321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4689098540080167</v>
+        <v>0.4993438062414747</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5866423072136117</v>
+        <v>0.5872834716158111</v>
       </c>
       <c r="N3" t="n">
-        <v>0.640536961498537</v>
+        <v>0.6256904749631428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8177854073958447</v>
+        <v>0.8179837292253487</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5222833181149571</v>
+        <v>0.5415218560071312</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5980630112455281</v>
+        <v>0.5957791760041037</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3300333346288328</v>
+        <v>0.4110134985148777</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5608860919813065</v>
+        <v>0.568494157912208</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5513299089113861</v>
+        <v>0.5627176667548247</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9804819567620308</v>
+        <v>0.9759938967716988</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6163018258013735</v>
+        <v>0.6090538352764591</v>
       </c>
       <c r="W3" t="n">
-        <v>1.073461286579422</v>
+        <v>1.035117226671606</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8745303216830032</v>
+        <v>0.790950040224601</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6826251936659811</v>
+        <v>0.6547433477083152</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7375841027890591</v>
+        <v>0.7350800247412766</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8024916847189455</v>
+        <v>0.7384807348521435</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5919105823167611</v>
+        <v>0.5913680052845072</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4575063001979591</v>
+        <v>0.4933687312700128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5658831569895237</v>
+        <v>0.5782112154449747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5673431552004041</v>
+        <v>0.5723471990480659</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3487427928776702</v>
+        <v>0.389296817323512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4955048440799732</v>
+        <v>0.5228200575845802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6387138996358828</v>
+        <v>0.6236508209929651</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6051547198387246</v>
+        <v>0.5985365844074571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5890142432443018</v>
+        <v>0.5875146043278752</v>
       </c>
       <c r="J3" t="n">
-        <v>0.593273063067533</v>
+        <v>0.5905913461131849</v>
       </c>
       <c r="K3" t="n">
-        <v>0.578563354704971</v>
+        <v>0.5801061280142317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4308848064921135</v>
+        <v>0.4717970246207415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5924730243644782</v>
+        <v>0.5898359643953383</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6449261173098333</v>
+        <v>0.6266997842119135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7535761073023075</v>
+        <v>0.7672761792191142</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4967333139042611</v>
+        <v>0.5209281581390924</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5949975369133181</v>
+        <v>0.591801311772098</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3299701631138225</v>
+        <v>0.4097693439540889</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5257023495521841</v>
+        <v>0.5418464050900232</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5580525764711171</v>
+        <v>0.5659484798522381</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9700585774261649</v>
+        <v>0.96530102731227</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6206280021201623</v>
+        <v>0.6103871391230282</v>
       </c>
       <c r="W3" t="n">
-        <v>1.045724108798657</v>
+        <v>1.011477442552556</v>
       </c>
       <c r="X3" t="n">
-        <v>0.954910741562643</v>
+        <v>0.8470650084220511</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6502761305235029</v>
+        <v>0.6301507742923446</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6816744080770872</v>
+        <v>0.6909965741384988</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.828909941816836</v>
+        <v>0.7548733272323522</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5956079263665366</v>
+        <v>0.5920521362841238</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7613233176646573</v>
+        <v>0.7260902758066946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6958622877717484</v>
+        <v>0.6866159295699101</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7864611820029365</v>
+        <v>0.7397859689901837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5801745073858204</v>
+        <v>0.5675760040624969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6815184494295461</v>
+        <v>0.6677054977994359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9494499446798368</v>
+        <v>0.8617182171814998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.808667424255144</v>
+        <v>0.7537130751644232</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6976798678180125</v>
+        <v>0.6787542963560923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8420136194555626</v>
+        <v>0.7829072981714438</v>
       </c>
       <c r="K3" t="n">
-        <v>0.755730010667466</v>
+        <v>0.7212388366300461</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8971138537632433</v>
+        <v>0.8208656805226239</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9910233145276719</v>
+        <v>0.8857858367895697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7918514869927629</v>
+        <v>0.7445108554512704</v>
       </c>
       <c r="O3" t="n">
-        <v>1.018482227291572</v>
+        <v>0.9871170092750324</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7938226091071875</v>
+        <v>0.7485983010673402</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7192844399516672</v>
+        <v>0.6944724630050132</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6577963700075041</v>
+        <v>0.6512755423937154</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7935462816653412</v>
+        <v>0.7500912079922362</v>
       </c>
       <c r="T3" t="n">
-        <v>0.713365785545151</v>
+        <v>0.6895871965718622</v>
       </c>
       <c r="U3" t="n">
-        <v>1.270553595001589</v>
+        <v>1.200235880287039</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7113270815401825</v>
+        <v>0.6904270596179454</v>
       </c>
       <c r="W3" t="n">
-        <v>1.276408523320738</v>
+        <v>1.196419203607912</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8503839913285218</v>
+        <v>0.7845821982678454</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8212758594498193</v>
+        <v>0.7660901805291567</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.8983926848918418</v>
+        <v>0.8680466956892136</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8419562929306716</v>
+        <v>0.7801318059194571</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.992526198049735</v>
+        <v>0.8783793511194462</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5964602981798346</v>
+        <v>0.6012046865824445</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6244167986651624</v>
+        <v>0.6287699013910577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6404992374227885</v>
+        <v>0.6321221981158222</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4959194801915192</v>
+        <v>0.5023443831967627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5083468996844905</v>
+        <v>0.5402770485969737</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8701347710423679</v>
+        <v>0.8000901854968867</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7268060153045565</v>
+        <v>0.6902436687817778</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5900109440405128</v>
+        <v>0.5972988019100044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6996346860311687</v>
+        <v>0.6757001199580152</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6171305367338479</v>
+        <v>0.6157084573077938</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4765131291031958</v>
+        <v>0.5145547297252041</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6156971168988873</v>
+        <v>0.6145784266360539</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6266068158052512</v>
+        <v>0.6225330954717053</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8199075607143219</v>
+        <v>0.8287829489542172</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6714241643072522</v>
+        <v>0.6548857608844221</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6132711102070389</v>
+        <v>0.6131099953287054</v>
       </c>
       <c r="R3" t="n">
-        <v>0.387614037349397</v>
+        <v>0.4591895265644686</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5334489119337581</v>
+        <v>0.555198336973752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5450002689389375</v>
+        <v>0.566100882357999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.041832658269824</v>
+        <v>1.029292198698304</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6613529842281914</v>
+        <v>0.647887197540077</v>
       </c>
       <c r="W3" t="n">
-        <v>1.152841712450187</v>
+        <v>1.099471208604926</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8668883780651844</v>
+        <v>0.7903423808330985</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9414986902986451</v>
+        <v>0.8429829766268544</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7984795937783672</v>
+        <v>0.7877189161547611</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7190597960048755</v>
+        <v>0.6870533222661998</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8234797226807727</v>
+        <v>0.7569994898616325</v>
       </c>
     </row>
     <row r="4">
